--- a/patterns/results/exp1/4bins-results.xlsx
+++ b/patterns/results/exp1/4bins-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A3EEAB8-E2EE-854D-9930-875042309337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8248687B-F9E5-7E4C-8D40-3270BF32873D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5060" yWindow="1100" windowWidth="30760" windowHeight="16660" activeTab="4" xr2:uid="{9429E1C1-1F54-8A42-9286-E37255B8DAF7}"/>
   </bookViews>
@@ -454,7 +454,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="36">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -827,6 +827,17 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="medium">
         <color indexed="64"/>
       </top>
@@ -885,11 +896,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="185">
+  <cellXfs count="191">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -908,7 +932,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1008,36 +1031,34 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="12" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="4" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="32" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="4" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="33" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="33" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="34" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1073,7 +1094,7 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1089,6 +1110,15 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="5" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1733,98 +1763,98 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="47" t="s">
+      <c r="A1" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="47" t="s">
+      <c r="C1" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="47" t="s">
+      <c r="D1" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="47" t="s">
+      <c r="E1" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="47" t="s">
+      <c r="F1" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="47" t="s">
+      <c r="G1" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="47" t="s">
+      <c r="H1" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="I1" s="47" t="s">
+      <c r="I1" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="J1" s="47" t="s">
+      <c r="J1" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="47" t="s">
+      <c r="K1" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="L1" s="47" t="s">
+      <c r="L1" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="M1" s="47" t="s">
+      <c r="M1" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="N1" s="47" t="s">
+      <c r="N1" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="O1" s="47" t="s">
+      <c r="O1" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="P1" s="47" t="s">
+      <c r="P1" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="Q1" s="47" t="s">
+      <c r="Q1" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="R1" s="47" t="s">
+      <c r="R1" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="S1" s="48" t="s">
+      <c r="S1" s="47" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="38"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="39">
-        <v>0</v>
-      </c>
-      <c r="L2" s="49"/>
-      <c r="M2" s="49"/>
-      <c r="N2" s="19">
-        <v>0</v>
-      </c>
-      <c r="O2" s="19">
-        <v>0</v>
-      </c>
-      <c r="P2" s="61">
+      <c r="C2" s="37"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="38">
+        <v>0</v>
+      </c>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="18">
+        <v>0</v>
+      </c>
+      <c r="O2" s="18">
+        <v>0</v>
+      </c>
+      <c r="P2" s="60">
         <v>1</v>
       </c>
-      <c r="Q2" s="19">
-        <v>0</v>
-      </c>
-      <c r="R2" s="49"/>
-      <c r="S2" s="20">
+      <c r="Q2" s="18">
+        <v>0</v>
+      </c>
+      <c r="R2" s="48"/>
+      <c r="S2" s="19">
         <v>0</v>
       </c>
       <c r="T2" s="1">
@@ -1833,39 +1863,39 @@
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="50"/>
-      <c r="K3" s="59">
+      <c r="C3" s="34"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="58">
         <v>0.11111111111111099</v>
       </c>
-      <c r="L3" s="50"/>
-      <c r="M3" s="50"/>
-      <c r="N3" s="26">
-        <v>0</v>
-      </c>
-      <c r="O3" s="60">
+      <c r="L3" s="49"/>
+      <c r="M3" s="49"/>
+      <c r="N3" s="25">
+        <v>0</v>
+      </c>
+      <c r="O3" s="59">
         <v>0.33333333333333298</v>
       </c>
-      <c r="P3" s="26">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="26">
-        <v>0</v>
-      </c>
-      <c r="R3" s="50"/>
-      <c r="S3" s="62">
+      <c r="P3" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="25">
+        <v>0</v>
+      </c>
+      <c r="R3" s="49"/>
+      <c r="S3" s="61">
         <v>0.55555555555555503</v>
       </c>
       <c r="T3" s="1">
@@ -1874,39 +1904,39 @@
       </c>
     </row>
     <row r="4" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="35"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="28">
-        <v>0</v>
-      </c>
-      <c r="L4" s="50"/>
-      <c r="M4" s="50"/>
-      <c r="N4" s="60">
+      <c r="C4" s="34"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="49"/>
+      <c r="K4" s="27">
+        <v>0</v>
+      </c>
+      <c r="L4" s="49"/>
+      <c r="M4" s="49"/>
+      <c r="N4" s="59">
         <v>0.28571428571428498</v>
       </c>
-      <c r="O4" s="26">
-        <v>0</v>
-      </c>
-      <c r="P4" s="26">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="60">
+      <c r="O4" s="25">
+        <v>0</v>
+      </c>
+      <c r="P4" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="59">
         <v>0.71428571428571397</v>
       </c>
-      <c r="R4" s="50"/>
-      <c r="S4" s="17">
+      <c r="R4" s="49"/>
+      <c r="S4" s="16">
         <v>0</v>
       </c>
       <c r="T4" s="1">
@@ -1915,41 +1945,41 @@
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="136" t="s">
+      <c r="C5" s="133" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
-      <c r="K5" s="39">
-        <v>0</v>
-      </c>
-      <c r="L5" s="49"/>
-      <c r="M5" s="49"/>
-      <c r="N5" s="19">
-        <v>0</v>
-      </c>
-      <c r="O5" s="150">
-        <v>0</v>
-      </c>
-      <c r="P5" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="19">
-        <v>0</v>
-      </c>
-      <c r="R5" s="49"/>
-      <c r="S5" s="20">
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="48"/>
+      <c r="K5" s="38">
+        <v>0</v>
+      </c>
+      <c r="L5" s="48"/>
+      <c r="M5" s="48"/>
+      <c r="N5" s="18">
+        <v>0</v>
+      </c>
+      <c r="O5" s="147">
+        <v>0</v>
+      </c>
+      <c r="P5" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="18">
+        <v>0</v>
+      </c>
+      <c r="R5" s="48"/>
+      <c r="S5" s="19">
         <v>0</v>
       </c>
       <c r="T5" s="1">
@@ -1958,41 +1988,41 @@
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="173" t="s">
+      <c r="C6" s="170" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
-      <c r="J6" s="50"/>
-      <c r="K6" s="29">
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="49"/>
+      <c r="J6" s="49"/>
+      <c r="K6" s="28">
         <v>0.11111111111111099</v>
       </c>
-      <c r="L6" s="50"/>
-      <c r="M6" s="50"/>
-      <c r="N6" s="26">
-        <v>0</v>
-      </c>
-      <c r="O6" s="151">
+      <c r="L6" s="49"/>
+      <c r="M6" s="49"/>
+      <c r="N6" s="25">
+        <v>0</v>
+      </c>
+      <c r="O6" s="148">
         <v>0.33333333333333298</v>
       </c>
-      <c r="P6" s="26">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="26">
-        <v>0</v>
-      </c>
-      <c r="R6" s="50"/>
-      <c r="S6" s="17">
+      <c r="P6" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="25">
+        <v>0</v>
+      </c>
+      <c r="R6" s="49"/>
+      <c r="S6" s="16">
         <v>0.55555555555555503</v>
       </c>
       <c r="T6" s="1">
@@ -2001,41 +2031,41 @@
       </c>
     </row>
     <row r="7" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="174" t="s">
+      <c r="C7" s="171" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="52"/>
-      <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
-      <c r="J7" s="52"/>
-      <c r="K7" s="33">
-        <v>0</v>
-      </c>
-      <c r="L7" s="52"/>
-      <c r="M7" s="52"/>
-      <c r="N7" s="63">
-        <v>0</v>
-      </c>
-      <c r="O7" s="152">
-        <v>0</v>
-      </c>
-      <c r="P7" s="26">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="34">
-        <v>0</v>
-      </c>
-      <c r="R7" s="52"/>
-      <c r="S7" s="44">
+      <c r="D7" s="51"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="51"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="51"/>
+      <c r="J7" s="51"/>
+      <c r="K7" s="32">
+        <v>0</v>
+      </c>
+      <c r="L7" s="51"/>
+      <c r="M7" s="51"/>
+      <c r="N7" s="62">
+        <v>0</v>
+      </c>
+      <c r="O7" s="149">
+        <v>0</v>
+      </c>
+      <c r="P7" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="33">
+        <v>0</v>
+      </c>
+      <c r="R7" s="51"/>
+      <c r="S7" s="43">
         <v>0</v>
       </c>
       <c r="T7" s="1">
@@ -2044,41 +2074,41 @@
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="175" t="s">
+      <c r="C8" s="172" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="53"/>
-      <c r="G8" s="53"/>
-      <c r="H8" s="53"/>
-      <c r="I8" s="53"/>
-      <c r="J8" s="53"/>
-      <c r="K8" s="31">
-        <v>0</v>
-      </c>
-      <c r="L8" s="53"/>
-      <c r="M8" s="53"/>
-      <c r="N8" s="32">
-        <v>0</v>
-      </c>
-      <c r="O8" s="26">
-        <v>0</v>
-      </c>
-      <c r="P8" s="150">
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="52"/>
+      <c r="K8" s="30">
+        <v>0</v>
+      </c>
+      <c r="L8" s="52"/>
+      <c r="M8" s="52"/>
+      <c r="N8" s="31">
+        <v>0</v>
+      </c>
+      <c r="O8" s="25">
+        <v>0</v>
+      </c>
+      <c r="P8" s="147">
         <v>1</v>
       </c>
-      <c r="Q8" s="32">
-        <v>0</v>
-      </c>
-      <c r="R8" s="53"/>
-      <c r="S8" s="45">
+      <c r="Q8" s="31">
+        <v>0</v>
+      </c>
+      <c r="R8" s="52"/>
+      <c r="S8" s="44">
         <v>0</v>
       </c>
       <c r="T8" s="1">
@@ -2087,41 +2117,41 @@
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A9" s="24" t="s">
+      <c r="A9" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="137" t="s">
+      <c r="C9" s="134" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="50"/>
-      <c r="E9" s="50"/>
-      <c r="F9" s="50"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="50"/>
-      <c r="I9" s="50"/>
-      <c r="J9" s="50"/>
-      <c r="K9" s="28">
-        <v>0</v>
-      </c>
-      <c r="L9" s="50"/>
-      <c r="M9" s="50"/>
-      <c r="N9" s="26">
-        <v>0</v>
-      </c>
-      <c r="O9" s="26">
-        <v>0</v>
-      </c>
-      <c r="P9" s="151">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="26">
-        <v>0</v>
-      </c>
-      <c r="R9" s="50"/>
-      <c r="S9" s="17">
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="49"/>
+      <c r="H9" s="49"/>
+      <c r="I9" s="49"/>
+      <c r="J9" s="49"/>
+      <c r="K9" s="27">
+        <v>0</v>
+      </c>
+      <c r="L9" s="49"/>
+      <c r="M9" s="49"/>
+      <c r="N9" s="25">
+        <v>0</v>
+      </c>
+      <c r="O9" s="25">
+        <v>0</v>
+      </c>
+      <c r="P9" s="148">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="25">
+        <v>0</v>
+      </c>
+      <c r="R9" s="49"/>
+      <c r="S9" s="16">
         <v>0</v>
       </c>
       <c r="T9" s="1">
@@ -2130,41 +2160,41 @@
       </c>
     </row>
     <row r="10" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="176" t="s">
+      <c r="C10" s="173" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="52"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="52"/>
-      <c r="K10" s="33">
-        <v>0</v>
-      </c>
-      <c r="L10" s="52"/>
-      <c r="M10" s="52"/>
-      <c r="N10" s="34">
-        <v>0</v>
-      </c>
-      <c r="O10" s="34">
-        <v>0</v>
-      </c>
-      <c r="P10" s="152">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="26">
-        <v>0</v>
-      </c>
-      <c r="R10" s="52"/>
-      <c r="S10" s="44">
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="51"/>
+      <c r="K10" s="32">
+        <v>0</v>
+      </c>
+      <c r="L10" s="51"/>
+      <c r="M10" s="51"/>
+      <c r="N10" s="33">
+        <v>0</v>
+      </c>
+      <c r="O10" s="33">
+        <v>0</v>
+      </c>
+      <c r="P10" s="149">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="25">
+        <v>0</v>
+      </c>
+      <c r="R10" s="51"/>
+      <c r="S10" s="43">
         <v>0</v>
       </c>
       <c r="T10" s="1">
@@ -2173,41 +2203,41 @@
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A11" s="24" t="s">
+      <c r="A11" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="177" t="s">
+      <c r="C11" s="174" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="53"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="53"/>
-      <c r="I11" s="53"/>
-      <c r="J11" s="53"/>
-      <c r="K11" s="31">
-        <v>0</v>
-      </c>
-      <c r="L11" s="53"/>
-      <c r="M11" s="53"/>
-      <c r="N11" s="32">
-        <v>0</v>
-      </c>
-      <c r="O11" s="32">
-        <v>0</v>
-      </c>
-      <c r="P11" s="26">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="150">
-        <v>0</v>
-      </c>
-      <c r="R11" s="53"/>
-      <c r="S11" s="45">
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="52"/>
+      <c r="I11" s="52"/>
+      <c r="J11" s="52"/>
+      <c r="K11" s="30">
+        <v>0</v>
+      </c>
+      <c r="L11" s="52"/>
+      <c r="M11" s="52"/>
+      <c r="N11" s="31">
+        <v>0</v>
+      </c>
+      <c r="O11" s="31">
+        <v>0</v>
+      </c>
+      <c r="P11" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="147">
+        <v>0</v>
+      </c>
+      <c r="R11" s="52"/>
+      <c r="S11" s="44">
         <v>0</v>
       </c>
       <c r="T11" s="1">
@@ -2216,41 +2246,41 @@
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A12" s="24" t="s">
+      <c r="A12" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="138" t="s">
+      <c r="C12" s="135" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="50"/>
-      <c r="I12" s="50"/>
-      <c r="J12" s="50"/>
-      <c r="K12" s="28">
-        <v>0</v>
-      </c>
-      <c r="L12" s="50"/>
-      <c r="M12" s="50"/>
-      <c r="N12" s="26">
-        <v>0</v>
-      </c>
-      <c r="O12" s="26">
-        <v>0</v>
-      </c>
-      <c r="P12" s="26">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="151">
-        <v>0</v>
-      </c>
-      <c r="R12" s="50"/>
-      <c r="S12" s="17">
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="49"/>
+      <c r="H12" s="49"/>
+      <c r="I12" s="49"/>
+      <c r="J12" s="49"/>
+      <c r="K12" s="27">
+        <v>0</v>
+      </c>
+      <c r="L12" s="49"/>
+      <c r="M12" s="49"/>
+      <c r="N12" s="25">
+        <v>0</v>
+      </c>
+      <c r="O12" s="25">
+        <v>0</v>
+      </c>
+      <c r="P12" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="148">
+        <v>0</v>
+      </c>
+      <c r="R12" s="49"/>
+      <c r="S12" s="16">
         <v>0</v>
       </c>
       <c r="T12" s="1">
@@ -2259,41 +2289,41 @@
       </c>
     </row>
     <row r="13" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="178" t="s">
+      <c r="C13" s="175" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="52"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="52"/>
-      <c r="K13" s="33">
-        <v>0</v>
-      </c>
-      <c r="L13" s="52"/>
-      <c r="M13" s="52"/>
-      <c r="N13" s="56">
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="51"/>
+      <c r="K13" s="32">
+        <v>0</v>
+      </c>
+      <c r="L13" s="51"/>
+      <c r="M13" s="51"/>
+      <c r="N13" s="55">
         <v>0.18181818181818099</v>
       </c>
-      <c r="O13" s="34">
-        <v>0</v>
-      </c>
-      <c r="P13" s="34">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="90">
+      <c r="O13" s="33">
+        <v>0</v>
+      </c>
+      <c r="P13" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="89">
         <v>0.81818181818181801</v>
       </c>
-      <c r="R13" s="52"/>
-      <c r="S13" s="17">
+      <c r="R13" s="51"/>
+      <c r="S13" s="16">
         <v>0</v>
       </c>
       <c r="T13" s="1">
@@ -2302,41 +2332,41 @@
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="179" t="s">
+      <c r="C14" s="176" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="53"/>
-      <c r="E14" s="53"/>
-      <c r="F14" s="53"/>
-      <c r="G14" s="53"/>
-      <c r="H14" s="53"/>
-      <c r="I14" s="53"/>
-      <c r="J14" s="53"/>
-      <c r="K14" s="31">
-        <v>0</v>
-      </c>
-      <c r="L14" s="53"/>
-      <c r="M14" s="53"/>
-      <c r="N14" s="32">
-        <v>0</v>
-      </c>
-      <c r="O14" s="32">
-        <v>0</v>
-      </c>
-      <c r="P14" s="32">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="26">
-        <v>0</v>
-      </c>
-      <c r="R14" s="53"/>
-      <c r="S14" s="150">
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="52"/>
+      <c r="G14" s="52"/>
+      <c r="H14" s="52"/>
+      <c r="I14" s="52"/>
+      <c r="J14" s="52"/>
+      <c r="K14" s="30">
+        <v>0</v>
+      </c>
+      <c r="L14" s="52"/>
+      <c r="M14" s="52"/>
+      <c r="N14" s="31">
+        <v>0</v>
+      </c>
+      <c r="O14" s="31">
+        <v>0</v>
+      </c>
+      <c r="P14" s="31">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="25">
+        <v>0</v>
+      </c>
+      <c r="R14" s="52"/>
+      <c r="S14" s="147">
         <v>0</v>
       </c>
       <c r="T14" s="1">
@@ -2345,41 +2375,41 @@
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A15" s="24" t="s">
+      <c r="A15" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="95" t="s">
+      <c r="C15" s="94" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="50"/>
-      <c r="E15" s="50"/>
-      <c r="F15" s="50"/>
-      <c r="G15" s="50"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="50"/>
-      <c r="J15" s="50"/>
-      <c r="K15" s="28">
-        <v>0</v>
-      </c>
-      <c r="L15" s="50"/>
-      <c r="M15" s="50"/>
-      <c r="N15" s="26">
-        <v>0</v>
-      </c>
-      <c r="O15" s="26">
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="49"/>
+      <c r="G15" s="49"/>
+      <c r="H15" s="49"/>
+      <c r="I15" s="49"/>
+      <c r="J15" s="49"/>
+      <c r="K15" s="27">
+        <v>0</v>
+      </c>
+      <c r="L15" s="49"/>
+      <c r="M15" s="49"/>
+      <c r="N15" s="25">
+        <v>0</v>
+      </c>
+      <c r="O15" s="25">
         <v>0.28571428571428498</v>
       </c>
-      <c r="P15" s="26">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="26">
-        <v>0</v>
-      </c>
-      <c r="R15" s="50"/>
-      <c r="S15" s="91">
+      <c r="P15" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="25">
+        <v>0</v>
+      </c>
+      <c r="R15" s="49"/>
+      <c r="S15" s="90">
         <v>0.71428571428571397</v>
       </c>
       <c r="T15" s="1">
@@ -2388,41 +2418,41 @@
       </c>
     </row>
     <row r="16" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="24" t="s">
+      <c r="A16" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="24" t="s">
+      <c r="B16" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="171" t="s">
+      <c r="C16" s="168" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="51"/>
-      <c r="E16" s="51"/>
-      <c r="F16" s="51"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="51"/>
-      <c r="I16" s="51"/>
-      <c r="J16" s="51"/>
-      <c r="K16" s="43">
-        <v>0</v>
-      </c>
-      <c r="L16" s="51"/>
-      <c r="M16" s="51"/>
-      <c r="N16" s="18">
-        <v>0</v>
-      </c>
-      <c r="O16" s="18">
-        <v>0</v>
-      </c>
-      <c r="P16" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="18">
-        <v>0</v>
-      </c>
-      <c r="R16" s="51"/>
-      <c r="S16" s="152">
+      <c r="D16" s="50"/>
+      <c r="E16" s="50"/>
+      <c r="F16" s="50"/>
+      <c r="G16" s="50"/>
+      <c r="H16" s="50"/>
+      <c r="I16" s="50"/>
+      <c r="J16" s="50"/>
+      <c r="K16" s="42">
+        <v>0</v>
+      </c>
+      <c r="L16" s="50"/>
+      <c r="M16" s="50"/>
+      <c r="N16" s="17">
+        <v>0</v>
+      </c>
+      <c r="O16" s="17">
+        <v>0</v>
+      </c>
+      <c r="P16" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="17">
+        <v>0</v>
+      </c>
+      <c r="R16" s="50"/>
+      <c r="S16" s="149">
         <v>0</v>
       </c>
       <c r="T16" s="1">
@@ -2431,41 +2461,41 @@
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A17" s="36" t="s">
+      <c r="A17" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="37" t="s">
+      <c r="B17" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="C17" s="98" t="s">
+      <c r="C17" s="97" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="50"/>
-      <c r="E17" s="50"/>
-      <c r="F17" s="50"/>
-      <c r="G17" s="50"/>
-      <c r="H17" s="50"/>
-      <c r="I17" s="50"/>
-      <c r="J17" s="50"/>
-      <c r="K17" s="28">
-        <v>0</v>
-      </c>
-      <c r="L17" s="50"/>
-      <c r="M17" s="50"/>
-      <c r="N17" s="26">
-        <v>0</v>
-      </c>
-      <c r="O17" s="150">
-        <v>0</v>
-      </c>
-      <c r="P17" s="26">
+      <c r="D17" s="49"/>
+      <c r="E17" s="49"/>
+      <c r="F17" s="49"/>
+      <c r="G17" s="49"/>
+      <c r="H17" s="49"/>
+      <c r="I17" s="49"/>
+      <c r="J17" s="49"/>
+      <c r="K17" s="27">
+        <v>0</v>
+      </c>
+      <c r="L17" s="49"/>
+      <c r="M17" s="49"/>
+      <c r="N17" s="25">
+        <v>0</v>
+      </c>
+      <c r="O17" s="147">
+        <v>0</v>
+      </c>
+      <c r="P17" s="25">
         <v>1</v>
       </c>
-      <c r="Q17" s="26">
-        <v>0</v>
-      </c>
-      <c r="R17" s="50"/>
-      <c r="S17" s="17">
+      <c r="Q17" s="25">
+        <v>0</v>
+      </c>
+      <c r="R17" s="49"/>
+      <c r="S17" s="16">
         <v>0</v>
       </c>
       <c r="T17" s="1">
@@ -2474,41 +2504,41 @@
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A18" s="40" t="s">
+      <c r="A18" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="180" t="s">
+      <c r="C18" s="177" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="50"/>
-      <c r="E18" s="50"/>
-      <c r="F18" s="50"/>
-      <c r="G18" s="50"/>
-      <c r="H18" s="50"/>
-      <c r="I18" s="50"/>
-      <c r="J18" s="50"/>
-      <c r="K18" s="64">
+      <c r="D18" s="49"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="49"/>
+      <c r="G18" s="49"/>
+      <c r="H18" s="49"/>
+      <c r="I18" s="49"/>
+      <c r="J18" s="49"/>
+      <c r="K18" s="63">
         <v>0.5</v>
       </c>
-      <c r="L18" s="50"/>
-      <c r="M18" s="50"/>
-      <c r="N18" s="26">
-        <v>0</v>
-      </c>
-      <c r="O18" s="91">
+      <c r="L18" s="49"/>
+      <c r="M18" s="49"/>
+      <c r="N18" s="25">
+        <v>0</v>
+      </c>
+      <c r="O18" s="90">
         <v>0.5</v>
       </c>
-      <c r="P18" s="26">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="26">
-        <v>0</v>
-      </c>
-      <c r="R18" s="50"/>
-      <c r="S18" s="17">
+      <c r="P18" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="25">
+        <v>0</v>
+      </c>
+      <c r="R18" s="49"/>
+      <c r="S18" s="16">
         <v>0</v>
       </c>
       <c r="T18" s="1">
@@ -2517,41 +2547,41 @@
       </c>
     </row>
     <row r="19" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="40" t="s">
+      <c r="A19" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="24" t="s">
+      <c r="B19" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="97" t="s">
+      <c r="C19" s="96" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="52"/>
-      <c r="E19" s="52"/>
-      <c r="F19" s="52"/>
-      <c r="G19" s="52"/>
-      <c r="H19" s="52"/>
-      <c r="I19" s="52"/>
-      <c r="J19" s="52"/>
-      <c r="K19" s="33">
-        <v>0</v>
-      </c>
-      <c r="L19" s="52"/>
-      <c r="M19" s="52"/>
-      <c r="N19" s="63">
-        <v>0</v>
-      </c>
-      <c r="O19" s="152">
-        <v>0</v>
-      </c>
-      <c r="P19" s="26">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="34">
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="51"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="51"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="51"/>
+      <c r="K19" s="32">
+        <v>0</v>
+      </c>
+      <c r="L19" s="51"/>
+      <c r="M19" s="51"/>
+      <c r="N19" s="62">
+        <v>0</v>
+      </c>
+      <c r="O19" s="149">
+        <v>0</v>
+      </c>
+      <c r="P19" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="33">
         <v>1</v>
       </c>
-      <c r="R19" s="52"/>
-      <c r="S19" s="44">
+      <c r="R19" s="51"/>
+      <c r="S19" s="43">
         <v>0</v>
       </c>
       <c r="T19" s="1">
@@ -2560,41 +2590,41 @@
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A20" s="40" t="s">
+      <c r="A20" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="B20" s="24" t="s">
+      <c r="B20" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C20" s="140" t="s">
+      <c r="C20" s="137" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="53"/>
-      <c r="E20" s="53"/>
-      <c r="F20" s="53"/>
-      <c r="G20" s="53"/>
-      <c r="H20" s="53"/>
-      <c r="I20" s="53"/>
-      <c r="J20" s="53"/>
-      <c r="K20" s="31">
-        <v>0</v>
-      </c>
-      <c r="L20" s="53"/>
-      <c r="M20" s="53"/>
-      <c r="N20" s="32">
-        <v>0</v>
-      </c>
-      <c r="O20" s="26">
-        <v>0</v>
-      </c>
-      <c r="P20" s="150">
+      <c r="D20" s="52"/>
+      <c r="E20" s="52"/>
+      <c r="F20" s="52"/>
+      <c r="G20" s="52"/>
+      <c r="H20" s="52"/>
+      <c r="I20" s="52"/>
+      <c r="J20" s="52"/>
+      <c r="K20" s="30">
+        <v>0</v>
+      </c>
+      <c r="L20" s="52"/>
+      <c r="M20" s="52"/>
+      <c r="N20" s="31">
+        <v>0</v>
+      </c>
+      <c r="O20" s="25">
+        <v>0</v>
+      </c>
+      <c r="P20" s="147">
         <v>1</v>
       </c>
-      <c r="Q20" s="32">
-        <v>0</v>
-      </c>
-      <c r="R20" s="53"/>
-      <c r="S20" s="45">
+      <c r="Q20" s="31">
+        <v>0</v>
+      </c>
+      <c r="R20" s="52"/>
+      <c r="S20" s="44">
         <v>0</v>
       </c>
       <c r="T20" s="1">
@@ -2603,41 +2633,41 @@
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A21" s="40" t="s">
+      <c r="A21" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="181" t="s">
+      <c r="C21" s="178" t="s">
         <v>27</v>
       </c>
-      <c r="D21" s="50"/>
-      <c r="E21" s="50"/>
-      <c r="F21" s="50"/>
-      <c r="G21" s="50"/>
-      <c r="H21" s="50"/>
-      <c r="I21" s="50"/>
-      <c r="J21" s="50"/>
-      <c r="K21" s="28">
-        <v>0</v>
-      </c>
-      <c r="L21" s="50"/>
-      <c r="M21" s="50"/>
-      <c r="N21" s="26">
-        <v>0</v>
-      </c>
-      <c r="O21" s="26">
-        <v>0</v>
-      </c>
-      <c r="P21" s="151">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="26">
-        <v>0</v>
-      </c>
-      <c r="R21" s="50"/>
-      <c r="S21" s="17">
+      <c r="D21" s="49"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="49"/>
+      <c r="G21" s="49"/>
+      <c r="H21" s="49"/>
+      <c r="I21" s="49"/>
+      <c r="J21" s="49"/>
+      <c r="K21" s="27">
+        <v>0</v>
+      </c>
+      <c r="L21" s="49"/>
+      <c r="M21" s="49"/>
+      <c r="N21" s="25">
+        <v>0</v>
+      </c>
+      <c r="O21" s="25">
+        <v>0</v>
+      </c>
+      <c r="P21" s="148">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="25">
+        <v>0</v>
+      </c>
+      <c r="R21" s="49"/>
+      <c r="S21" s="16">
         <v>0</v>
       </c>
       <c r="T21" s="1">
@@ -2646,41 +2676,41 @@
       </c>
     </row>
     <row r="22" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="40" t="s">
+      <c r="A22" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="182" t="s">
+      <c r="C22" s="179" t="s">
         <v>27</v>
       </c>
-      <c r="D22" s="52"/>
-      <c r="E22" s="52"/>
-      <c r="F22" s="52"/>
-      <c r="G22" s="52"/>
-      <c r="H22" s="52"/>
-      <c r="I22" s="52"/>
-      <c r="J22" s="52"/>
-      <c r="K22" s="33">
-        <v>0</v>
-      </c>
-      <c r="L22" s="52"/>
-      <c r="M22" s="52"/>
-      <c r="N22" s="34">
-        <v>0</v>
-      </c>
-      <c r="O22" s="34">
-        <v>0</v>
-      </c>
-      <c r="P22" s="152">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="34">
-        <v>0</v>
-      </c>
-      <c r="R22" s="52"/>
-      <c r="S22" s="17">
+      <c r="D22" s="51"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="51"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="51"/>
+      <c r="J22" s="51"/>
+      <c r="K22" s="32">
+        <v>0</v>
+      </c>
+      <c r="L22" s="51"/>
+      <c r="M22" s="51"/>
+      <c r="N22" s="33">
+        <v>0</v>
+      </c>
+      <c r="O22" s="33">
+        <v>0</v>
+      </c>
+      <c r="P22" s="149">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="33">
+        <v>0</v>
+      </c>
+      <c r="R22" s="51"/>
+      <c r="S22" s="16">
         <v>0</v>
       </c>
       <c r="T22" s="1">
@@ -2689,41 +2719,41 @@
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A23" s="40" t="s">
+      <c r="A23" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="24" t="s">
+      <c r="B23" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="183" t="s">
+      <c r="C23" s="180" t="s">
         <v>30</v>
       </c>
-      <c r="D23" s="53"/>
-      <c r="E23" s="53"/>
-      <c r="F23" s="53"/>
-      <c r="G23" s="53"/>
-      <c r="H23" s="53"/>
-      <c r="I23" s="53"/>
-      <c r="J23" s="53"/>
-      <c r="K23" s="31">
-        <v>0</v>
-      </c>
-      <c r="L23" s="53"/>
-      <c r="M23" s="53"/>
-      <c r="N23" s="32">
-        <v>0</v>
-      </c>
-      <c r="O23" s="32">
-        <v>0</v>
-      </c>
-      <c r="P23" s="26">
+      <c r="D23" s="52"/>
+      <c r="E23" s="52"/>
+      <c r="F23" s="52"/>
+      <c r="G23" s="52"/>
+      <c r="H23" s="52"/>
+      <c r="I23" s="52"/>
+      <c r="J23" s="52"/>
+      <c r="K23" s="30">
+        <v>0</v>
+      </c>
+      <c r="L23" s="52"/>
+      <c r="M23" s="52"/>
+      <c r="N23" s="31">
+        <v>0</v>
+      </c>
+      <c r="O23" s="31">
+        <v>0</v>
+      </c>
+      <c r="P23" s="25">
         <v>1</v>
       </c>
-      <c r="Q23" s="32">
-        <v>0</v>
-      </c>
-      <c r="R23" s="53"/>
-      <c r="S23" s="150">
+      <c r="Q23" s="31">
+        <v>0</v>
+      </c>
+      <c r="R23" s="52"/>
+      <c r="S23" s="147">
         <v>0</v>
       </c>
       <c r="T23" s="1">
@@ -2732,41 +2762,41 @@
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A24" s="40" t="s">
+      <c r="A24" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="B24" s="24" t="s">
+      <c r="B24" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="184" t="s">
+      <c r="C24" s="181" t="s">
         <v>30</v>
       </c>
-      <c r="D24" s="50"/>
-      <c r="E24" s="50"/>
-      <c r="F24" s="50"/>
-      <c r="G24" s="50"/>
-      <c r="H24" s="50"/>
-      <c r="I24" s="50"/>
-      <c r="J24" s="50"/>
-      <c r="K24" s="28">
-        <v>0</v>
-      </c>
-      <c r="L24" s="50"/>
-      <c r="M24" s="50"/>
-      <c r="N24" s="26">
-        <v>0</v>
-      </c>
-      <c r="O24" s="29">
+      <c r="D24" s="49"/>
+      <c r="E24" s="49"/>
+      <c r="F24" s="49"/>
+      <c r="G24" s="49"/>
+      <c r="H24" s="49"/>
+      <c r="I24" s="49"/>
+      <c r="J24" s="49"/>
+      <c r="K24" s="27">
+        <v>0</v>
+      </c>
+      <c r="L24" s="49"/>
+      <c r="M24" s="49"/>
+      <c r="N24" s="25">
+        <v>0</v>
+      </c>
+      <c r="O24" s="28">
         <v>0.25</v>
       </c>
-      <c r="P24" s="26">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="26">
-        <v>0</v>
-      </c>
-      <c r="R24" s="50"/>
-      <c r="S24" s="91">
+      <c r="P24" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="25">
+        <v>0</v>
+      </c>
+      <c r="R24" s="49"/>
+      <c r="S24" s="90">
         <v>0.75</v>
       </c>
       <c r="T24" s="1">
@@ -2775,41 +2805,41 @@
       </c>
     </row>
     <row r="25" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="41" t="s">
+      <c r="A25" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="B25" s="42" t="s">
+      <c r="B25" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="141" t="s">
+      <c r="C25" s="138" t="s">
         <v>30</v>
       </c>
-      <c r="D25" s="51"/>
-      <c r="E25" s="51"/>
-      <c r="F25" s="51"/>
-      <c r="G25" s="51"/>
-      <c r="H25" s="51"/>
-      <c r="I25" s="51"/>
-      <c r="J25" s="51"/>
-      <c r="K25" s="43">
-        <v>0</v>
-      </c>
-      <c r="L25" s="51"/>
-      <c r="M25" s="51"/>
-      <c r="N25" s="18">
-        <v>0</v>
-      </c>
-      <c r="O25" s="18">
-        <v>0</v>
-      </c>
-      <c r="P25" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="57">
+      <c r="D25" s="50"/>
+      <c r="E25" s="50"/>
+      <c r="F25" s="50"/>
+      <c r="G25" s="50"/>
+      <c r="H25" s="50"/>
+      <c r="I25" s="50"/>
+      <c r="J25" s="50"/>
+      <c r="K25" s="42">
+        <v>0</v>
+      </c>
+      <c r="L25" s="50"/>
+      <c r="M25" s="50"/>
+      <c r="N25" s="17">
+        <v>0</v>
+      </c>
+      <c r="O25" s="17">
+        <v>0</v>
+      </c>
+      <c r="P25" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="56">
         <v>1</v>
       </c>
-      <c r="R25" s="51"/>
-      <c r="S25" s="152">
+      <c r="R25" s="50"/>
+      <c r="S25" s="149">
         <v>0</v>
       </c>
       <c r="T25" s="1">
@@ -2818,53 +2848,53 @@
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A26" s="24"/>
-      <c r="B26" s="24"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="25"/>
-      <c r="I26" s="25"/>
-      <c r="J26" s="25"/>
-      <c r="K26" s="25"/>
-      <c r="L26" s="25"/>
-      <c r="M26" s="25"/>
+      <c r="A26" s="23"/>
+      <c r="B26" s="23"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="24"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="24"/>
+      <c r="J26" s="24"/>
+      <c r="K26" s="24"/>
+      <c r="L26" s="24"/>
+      <c r="M26" s="24"/>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A27" s="24" t="s">
+      <c r="A27" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="B27" s="24"/>
-      <c r="C27" s="24"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="25"/>
-      <c r="I27" s="25"/>
-      <c r="J27" s="25"/>
-      <c r="K27" s="25"/>
-      <c r="L27" s="25"/>
-      <c r="M27" s="25"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="24"/>
+      <c r="H27" s="24"/>
+      <c r="I27" s="24"/>
+      <c r="J27" s="24"/>
+      <c r="K27" s="24"/>
+      <c r="L27" s="24"/>
+      <c r="M27" s="24"/>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A28" s="24" t="s">
+      <c r="A28" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="24"/>
-      <c r="C28" s="24"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="25"/>
-      <c r="F28" s="25"/>
-      <c r="G28" s="25"/>
-      <c r="H28" s="30"/>
-      <c r="I28" s="25"/>
-      <c r="J28" s="25"/>
-      <c r="K28" s="25"/>
-      <c r="L28" s="25"/>
-      <c r="M28" s="25"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="24"/>
+      <c r="J28" s="24"/>
+      <c r="K28" s="24"/>
+      <c r="L28" s="24"/>
+      <c r="M28" s="24"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A17:S25">
@@ -2956,34 +2986,34 @@
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A2" s="68" t="s">
+      <c r="A2" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="69" t="s">
+      <c r="B2" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="65"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="49"/>
-      <c r="M2" s="77"/>
-      <c r="N2" s="61">
+      <c r="C2" s="64"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="76"/>
+      <c r="N2" s="60">
         <v>5.5555555555555497E-2</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="61">
+      <c r="O2" s="76"/>
+      <c r="P2" s="60">
         <v>8.7301587301587297E-2</v>
       </c>
-      <c r="Q2" s="61">
+      <c r="Q2" s="60">
         <v>0.79365079365079305</v>
       </c>
-      <c r="R2" s="61">
+      <c r="R2" s="60">
         <v>6.3492063492063405E-2</v>
       </c>
       <c r="S2" s="4">
@@ -2995,37 +3025,37 @@
       </c>
     </row>
     <row r="3" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="71" t="s">
+      <c r="A3" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="72" t="s">
+      <c r="B3" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="66"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="50"/>
-      <c r="K3" s="50"/>
-      <c r="L3" s="50"/>
-      <c r="M3" s="79"/>
-      <c r="N3" s="23">
-        <v>0</v>
-      </c>
-      <c r="O3" s="79"/>
-      <c r="P3" s="23">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="23">
-        <v>0</v>
-      </c>
-      <c r="R3" s="23">
-        <v>0</v>
-      </c>
-      <c r="S3" s="62">
+      <c r="C3" s="65"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="49"/>
+      <c r="M3" s="78"/>
+      <c r="N3" s="22">
+        <v>0</v>
+      </c>
+      <c r="O3" s="78"/>
+      <c r="P3" s="22">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="22">
+        <v>0</v>
+      </c>
+      <c r="R3" s="22">
+        <v>0</v>
+      </c>
+      <c r="S3" s="61">
         <v>1</v>
       </c>
       <c r="T3" s="1">
@@ -3034,29 +3064,29 @@
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A4" s="68" t="s">
+      <c r="A4" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="69" t="s">
+      <c r="B4" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="94" t="s">
+      <c r="C4" s="93" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="49"/>
-      <c r="K4" s="49"/>
-      <c r="L4" s="49"/>
-      <c r="M4" s="77"/>
-      <c r="N4" s="92">
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
+      <c r="K4" s="48"/>
+      <c r="L4" s="48"/>
+      <c r="M4" s="76"/>
+      <c r="N4" s="91">
         <v>0.5</v>
       </c>
-      <c r="O4" s="77"/>
+      <c r="O4" s="76"/>
       <c r="P4" s="3">
         <v>0</v>
       </c>
@@ -3075,39 +3105,39 @@
       </c>
     </row>
     <row r="5" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="74" t="s">
+      <c r="A5" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="165" t="s">
+      <c r="C5" s="162" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="52"/>
-      <c r="L5" s="52"/>
-      <c r="M5" s="85"/>
-      <c r="N5" s="152">
-        <v>0</v>
-      </c>
-      <c r="O5" s="85"/>
-      <c r="P5" s="23">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="86">
-        <v>0</v>
-      </c>
-      <c r="R5" s="86">
-        <v>0</v>
-      </c>
-      <c r="S5" s="87">
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="51"/>
+      <c r="J5" s="51"/>
+      <c r="K5" s="51"/>
+      <c r="L5" s="51"/>
+      <c r="M5" s="84"/>
+      <c r="N5" s="149">
+        <v>0</v>
+      </c>
+      <c r="O5" s="84"/>
+      <c r="P5" s="22">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="85">
+        <v>0</v>
+      </c>
+      <c r="R5" s="85">
+        <v>0</v>
+      </c>
+      <c r="S5" s="86">
         <v>1</v>
       </c>
       <c r="T5" s="1">
@@ -3116,39 +3146,39 @@
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A6" s="74" t="s">
+      <c r="A6" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="167" t="s">
+      <c r="C6" s="164" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="53"/>
-      <c r="K6" s="53"/>
-      <c r="L6" s="53"/>
-      <c r="M6" s="83"/>
-      <c r="N6" s="23">
-        <v>0</v>
-      </c>
-      <c r="O6" s="83"/>
-      <c r="P6" s="92">
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="52"/>
+      <c r="K6" s="52"/>
+      <c r="L6" s="52"/>
+      <c r="M6" s="82"/>
+      <c r="N6" s="22">
+        <v>0</v>
+      </c>
+      <c r="O6" s="82"/>
+      <c r="P6" s="91">
         <v>0.64705882352941102</v>
       </c>
-      <c r="Q6" s="54">
+      <c r="Q6" s="53">
         <v>0.35294117647058798</v>
       </c>
-      <c r="R6" s="84">
-        <v>0</v>
-      </c>
-      <c r="S6" s="88">
+      <c r="R6" s="83">
+        <v>0</v>
+      </c>
+      <c r="S6" s="87">
         <v>0</v>
       </c>
       <c r="T6" s="1">
@@ -3157,39 +3187,39 @@
       </c>
     </row>
     <row r="7" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="74" t="s">
+      <c r="A7" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="168" t="s">
+      <c r="C7" s="165" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="52"/>
-      <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
-      <c r="J7" s="52"/>
-      <c r="K7" s="52"/>
-      <c r="L7" s="52"/>
-      <c r="M7" s="85"/>
-      <c r="N7" s="86">
-        <v>0</v>
-      </c>
-      <c r="O7" s="85"/>
-      <c r="P7" s="152">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="23">
-        <v>0</v>
-      </c>
-      <c r="R7" s="86">
-        <v>0</v>
-      </c>
-      <c r="S7" s="87">
+      <c r="D7" s="51"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="51"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="51"/>
+      <c r="J7" s="51"/>
+      <c r="K7" s="51"/>
+      <c r="L7" s="51"/>
+      <c r="M7" s="84"/>
+      <c r="N7" s="85">
+        <v>0</v>
+      </c>
+      <c r="O7" s="84"/>
+      <c r="P7" s="149">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="22">
+        <v>0</v>
+      </c>
+      <c r="R7" s="85">
+        <v>0</v>
+      </c>
+      <c r="S7" s="86">
         <v>1</v>
       </c>
       <c r="T7" s="1">
@@ -3198,39 +3228,39 @@
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A8" s="74" t="s">
+      <c r="A8" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="166" t="s">
+      <c r="C8" s="163" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="53"/>
-      <c r="G8" s="53"/>
-      <c r="H8" s="53"/>
-      <c r="I8" s="53"/>
-      <c r="J8" s="53"/>
-      <c r="K8" s="53"/>
-      <c r="L8" s="53"/>
-      <c r="M8" s="83"/>
-      <c r="N8" s="84">
-        <v>0</v>
-      </c>
-      <c r="O8" s="83"/>
-      <c r="P8" s="23">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="92">
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="52"/>
+      <c r="K8" s="52"/>
+      <c r="L8" s="52"/>
+      <c r="M8" s="82"/>
+      <c r="N8" s="83">
+        <v>0</v>
+      </c>
+      <c r="O8" s="82"/>
+      <c r="P8" s="22">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="91">
         <v>1</v>
       </c>
-      <c r="R8" s="84">
-        <v>0</v>
-      </c>
-      <c r="S8" s="88">
+      <c r="R8" s="83">
+        <v>0</v>
+      </c>
+      <c r="S8" s="87">
         <v>0</v>
       </c>
       <c r="T8" s="1">
@@ -3239,39 +3269,39 @@
       </c>
     </row>
     <row r="9" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="74" t="s">
+      <c r="A9" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="169" t="s">
+      <c r="C9" s="166" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="52"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="52"/>
-      <c r="G9" s="52"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="52"/>
-      <c r="K9" s="52"/>
-      <c r="L9" s="52"/>
-      <c r="M9" s="85"/>
-      <c r="N9" s="86">
-        <v>0</v>
-      </c>
-      <c r="O9" s="85"/>
-      <c r="P9" s="86">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="152">
-        <v>0</v>
-      </c>
-      <c r="R9" s="23">
-        <v>0</v>
-      </c>
-      <c r="S9" s="87">
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="51"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="51"/>
+      <c r="J9" s="51"/>
+      <c r="K9" s="51"/>
+      <c r="L9" s="51"/>
+      <c r="M9" s="84"/>
+      <c r="N9" s="85">
+        <v>0</v>
+      </c>
+      <c r="O9" s="84"/>
+      <c r="P9" s="85">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="149">
+        <v>0</v>
+      </c>
+      <c r="R9" s="22">
+        <v>0</v>
+      </c>
+      <c r="S9" s="86">
         <v>1</v>
       </c>
       <c r="T9" s="1">
@@ -3280,39 +3310,39 @@
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A10" s="74" t="s">
+      <c r="A10" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="170" t="s">
+      <c r="C10" s="167" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="53"/>
-      <c r="K10" s="53"/>
-      <c r="L10" s="53"/>
-      <c r="M10" s="83"/>
-      <c r="N10" s="84">
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="52"/>
+      <c r="K10" s="52"/>
+      <c r="L10" s="52"/>
+      <c r="M10" s="82"/>
+      <c r="N10" s="83">
         <v>8.3333333333333301E-2</v>
       </c>
-      <c r="O10" s="83"/>
-      <c r="P10" s="84">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="23">
+      <c r="O10" s="82"/>
+      <c r="P10" s="83">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="22">
         <v>0.33333333333333298</v>
       </c>
-      <c r="R10" s="92">
+      <c r="R10" s="91">
         <v>0.58333333333333304</v>
       </c>
-      <c r="S10" s="88">
+      <c r="S10" s="87">
         <v>0</v>
       </c>
       <c r="T10" s="1">
@@ -3321,39 +3351,39 @@
       </c>
     </row>
     <row r="11" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="74" t="s">
+      <c r="A11" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="171" t="s">
+      <c r="C11" s="168" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="85"/>
-      <c r="E11" s="85"/>
-      <c r="F11" s="85"/>
-      <c r="G11" s="85"/>
-      <c r="H11" s="85"/>
-      <c r="I11" s="85"/>
-      <c r="J11" s="85"/>
-      <c r="K11" s="85"/>
-      <c r="L11" s="85"/>
-      <c r="M11" s="85"/>
-      <c r="N11" s="86">
-        <v>0</v>
-      </c>
-      <c r="O11" s="85"/>
-      <c r="P11" s="86">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="86">
-        <v>0</v>
-      </c>
-      <c r="R11" s="152">
-        <v>0</v>
-      </c>
-      <c r="S11" s="80">
+      <c r="D11" s="84"/>
+      <c r="E11" s="84"/>
+      <c r="F11" s="84"/>
+      <c r="G11" s="84"/>
+      <c r="H11" s="84"/>
+      <c r="I11" s="84"/>
+      <c r="J11" s="84"/>
+      <c r="K11" s="84"/>
+      <c r="L11" s="84"/>
+      <c r="M11" s="84"/>
+      <c r="N11" s="85">
+        <v>0</v>
+      </c>
+      <c r="O11" s="84"/>
+      <c r="P11" s="85">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="85">
+        <v>0</v>
+      </c>
+      <c r="R11" s="149">
+        <v>0</v>
+      </c>
+      <c r="S11" s="79">
         <v>1</v>
       </c>
       <c r="T11" s="1">
@@ -3362,39 +3392,39 @@
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A12" s="74" t="s">
+      <c r="A12" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="172" t="s">
+      <c r="C12" s="169" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="53"/>
-      <c r="E12" s="53"/>
-      <c r="F12" s="53"/>
-      <c r="G12" s="53"/>
-      <c r="H12" s="53"/>
-      <c r="I12" s="53"/>
-      <c r="J12" s="53"/>
-      <c r="K12" s="53"/>
-      <c r="L12" s="53"/>
-      <c r="M12" s="83"/>
-      <c r="N12" s="84">
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="52"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="52"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="52"/>
+      <c r="K12" s="52"/>
+      <c r="L12" s="52"/>
+      <c r="M12" s="82"/>
+      <c r="N12" s="83">
         <v>8.1967213114753995E-2</v>
       </c>
-      <c r="O12" s="83"/>
-      <c r="P12" s="84">
+      <c r="O12" s="82"/>
+      <c r="P12" s="83">
         <v>0.18032786885245899</v>
       </c>
-      <c r="Q12" s="84">
+      <c r="Q12" s="83">
         <v>0.73770491803278604</v>
       </c>
-      <c r="R12" s="23">
-        <v>0</v>
-      </c>
-      <c r="S12" s="150">
+      <c r="R12" s="22">
+        <v>0</v>
+      </c>
+      <c r="S12" s="147">
         <v>0</v>
       </c>
       <c r="T12" s="1">
@@ -3406,26 +3436,26 @@
       <c r="A13" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="75" t="s">
+      <c r="B13" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="96" t="s">
+      <c r="C13" s="95" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="78"/>
-      <c r="E13" s="78"/>
-      <c r="F13" s="78"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="78"/>
-      <c r="I13" s="78"/>
-      <c r="J13" s="78"/>
-      <c r="K13" s="78"/>
-      <c r="L13" s="78"/>
-      <c r="M13" s="78"/>
+      <c r="D13" s="77"/>
+      <c r="E13" s="77"/>
+      <c r="F13" s="77"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="77"/>
+      <c r="J13" s="77"/>
+      <c r="K13" s="77"/>
+      <c r="L13" s="77"/>
+      <c r="M13" s="77"/>
       <c r="N13" s="6">
         <v>0</v>
       </c>
-      <c r="O13" s="78"/>
+      <c r="O13" s="77"/>
       <c r="P13" s="6">
         <v>0</v>
       </c>
@@ -3435,7 +3465,7 @@
       <c r="R13" s="6">
         <v>0</v>
       </c>
-      <c r="S13" s="90">
+      <c r="S13" s="89">
         <v>1</v>
       </c>
       <c r="T13" s="1">
@@ -3447,36 +3477,36 @@
       <c r="A14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="76" t="s">
+      <c r="B14" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="98" t="s">
+      <c r="C14" s="97" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="77"/>
-      <c r="E14" s="77"/>
-      <c r="F14" s="77"/>
-      <c r="G14" s="77"/>
-      <c r="H14" s="77"/>
-      <c r="I14" s="77"/>
-      <c r="J14" s="77"/>
-      <c r="K14" s="77"/>
-      <c r="L14" s="77"/>
-      <c r="M14" s="77"/>
-      <c r="N14" s="58">
+      <c r="D14" s="76"/>
+      <c r="E14" s="76"/>
+      <c r="F14" s="76"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="76"/>
+      <c r="I14" s="76"/>
+      <c r="J14" s="76"/>
+      <c r="K14" s="76"/>
+      <c r="L14" s="76"/>
+      <c r="M14" s="76"/>
+      <c r="N14" s="57">
         <v>3.0769230769230702E-2</v>
       </c>
-      <c r="O14" s="77"/>
-      <c r="P14" s="39">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="93">
+      <c r="O14" s="76"/>
+      <c r="P14" s="38">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="92">
         <v>0.84615384615384603</v>
       </c>
-      <c r="R14" s="81">
+      <c r="R14" s="80">
         <v>0.123076923076923</v>
       </c>
-      <c r="S14" s="89">
+      <c r="S14" s="88">
         <v>0</v>
       </c>
       <c r="T14" s="1">
@@ -3488,36 +3518,36 @@
       <c r="A15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="75" t="s">
+      <c r="B15" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="97" t="s">
+      <c r="C15" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="78"/>
-      <c r="E15" s="78"/>
-      <c r="F15" s="78"/>
-      <c r="G15" s="78"/>
-      <c r="H15" s="78"/>
-      <c r="I15" s="78"/>
-      <c r="J15" s="78"/>
-      <c r="K15" s="78"/>
-      <c r="L15" s="78"/>
-      <c r="M15" s="78"/>
-      <c r="N15" s="73">
-        <v>0</v>
-      </c>
-      <c r="O15" s="78"/>
-      <c r="P15" s="73">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="153">
-        <v>0</v>
-      </c>
-      <c r="R15" s="73">
-        <v>0</v>
-      </c>
-      <c r="S15" s="82">
+      <c r="D15" s="77"/>
+      <c r="E15" s="77"/>
+      <c r="F15" s="77"/>
+      <c r="G15" s="77"/>
+      <c r="H15" s="77"/>
+      <c r="I15" s="77"/>
+      <c r="J15" s="77"/>
+      <c r="K15" s="77"/>
+      <c r="L15" s="77"/>
+      <c r="M15" s="77"/>
+      <c r="N15" s="72">
+        <v>0</v>
+      </c>
+      <c r="O15" s="77"/>
+      <c r="P15" s="72">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="150">
+        <v>0</v>
+      </c>
+      <c r="R15" s="72">
+        <v>0</v>
+      </c>
+      <c r="S15" s="81">
         <v>1</v>
       </c>
       <c r="T15" s="1">
@@ -3588,7 +3618,7 @@
       <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="9" t="s">
@@ -3641,37 +3671,37 @@
       </c>
     </row>
     <row r="2" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="99" t="s">
+      <c r="A2" s="98" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="100" t="s">
+      <c r="B2" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="103"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="77"/>
-      <c r="M2" s="109">
+      <c r="C2" s="102"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="76"/>
+      <c r="L2" s="76"/>
+      <c r="M2" s="107">
         <v>1.0869565217391301E-2</v>
       </c>
-      <c r="N2" s="14"/>
-      <c r="O2" s="14"/>
-      <c r="P2" s="109">
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="107">
         <v>0.26086956521739102</v>
       </c>
-      <c r="Q2" s="109">
+      <c r="Q2" s="107">
         <v>0.70652173913043403</v>
       </c>
-      <c r="R2" s="109">
+      <c r="R2" s="107">
         <v>1.0869565217391301E-2</v>
       </c>
-      <c r="S2" s="110">
+      <c r="S2" s="108">
         <v>1.0869565217391301E-2</v>
       </c>
       <c r="T2" s="1">
@@ -3680,39 +3710,39 @@
       </c>
     </row>
     <row r="3" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="101" t="s">
+      <c r="A3" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="105" t="s">
+      <c r="C3" s="103" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="111"/>
-      <c r="E3" s="112"/>
-      <c r="F3" s="112"/>
-      <c r="G3" s="112"/>
-      <c r="H3" s="112"/>
-      <c r="I3" s="113"/>
-      <c r="J3" s="113"/>
-      <c r="K3" s="113"/>
-      <c r="L3" s="113"/>
-      <c r="M3" s="114">
-        <v>0</v>
-      </c>
-      <c r="N3" s="115"/>
-      <c r="O3" s="115"/>
-      <c r="P3" s="125">
+      <c r="D3" s="113"/>
+      <c r="E3" s="114"/>
+      <c r="F3" s="114"/>
+      <c r="G3" s="114"/>
+      <c r="H3" s="114"/>
+      <c r="I3" s="115"/>
+      <c r="J3" s="115"/>
+      <c r="K3" s="115"/>
+      <c r="L3" s="115"/>
+      <c r="M3" s="116">
+        <v>0</v>
+      </c>
+      <c r="N3" s="117"/>
+      <c r="O3" s="117"/>
+      <c r="P3" s="127">
         <v>0.79310344827586199</v>
       </c>
-      <c r="Q3" s="58">
+      <c r="Q3" s="57">
         <v>0.20689655172413701</v>
       </c>
-      <c r="R3" s="114">
-        <v>0</v>
-      </c>
-      <c r="S3" s="116">
+      <c r="R3" s="116">
+        <v>0</v>
+      </c>
+      <c r="S3" s="118">
         <v>0</v>
       </c>
       <c r="T3" s="1">
@@ -3721,33 +3751,33 @@
       </c>
     </row>
     <row r="4" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="102" t="s">
+      <c r="A4" s="101" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="43" t="s">
+      <c r="B4" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="106" t="s">
+      <c r="C4" s="104" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="78"/>
-      <c r="J4" s="78"/>
-      <c r="K4" s="78"/>
-      <c r="L4" s="78"/>
-      <c r="M4" s="57">
+      <c r="D4" s="119"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="77"/>
+      <c r="M4" s="56">
         <v>2.8571428571428501E-2</v>
       </c>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14"/>
       <c r="P4" s="6">
         <v>0</v>
       </c>
-      <c r="Q4" s="125">
+      <c r="Q4" s="127">
         <v>0.97142857142857097</v>
       </c>
       <c r="R4" s="6">
@@ -3762,39 +3792,39 @@
       </c>
     </row>
     <row r="5" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="101" t="s">
+      <c r="A5" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="107" t="s">
+      <c r="C5" s="105" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="111"/>
-      <c r="E5" s="112"/>
-      <c r="F5" s="112"/>
-      <c r="G5" s="112"/>
-      <c r="H5" s="112"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="113"/>
-      <c r="K5" s="113"/>
-      <c r="L5" s="113"/>
-      <c r="M5" s="114">
-        <v>0</v>
-      </c>
-      <c r="N5" s="115"/>
-      <c r="O5" s="115"/>
-      <c r="P5" s="126">
+      <c r="D5" s="113"/>
+      <c r="E5" s="114"/>
+      <c r="F5" s="114"/>
+      <c r="G5" s="114"/>
+      <c r="H5" s="114"/>
+      <c r="I5" s="115"/>
+      <c r="J5" s="115"/>
+      <c r="K5" s="115"/>
+      <c r="L5" s="115"/>
+      <c r="M5" s="116">
+        <v>0</v>
+      </c>
+      <c r="N5" s="117"/>
+      <c r="O5" s="117"/>
+      <c r="P5" s="128">
         <v>0.11111111111111099</v>
       </c>
-      <c r="Q5" s="81">
+      <c r="Q5" s="80">
         <v>0.88888888888888795</v>
       </c>
-      <c r="R5" s="114">
-        <v>0</v>
-      </c>
-      <c r="S5" s="116">
+      <c r="R5" s="116">
+        <v>0</v>
+      </c>
+      <c r="S5" s="118">
         <v>0</v>
       </c>
       <c r="T5" s="1">
@@ -3803,39 +3833,39 @@
       </c>
     </row>
     <row r="6" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="108" t="s">
+      <c r="C6" s="106" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="118"/>
-      <c r="E6" s="119"/>
-      <c r="F6" s="119"/>
-      <c r="G6" s="119"/>
-      <c r="H6" s="119"/>
-      <c r="I6" s="120"/>
-      <c r="J6" s="120"/>
-      <c r="K6" s="120"/>
-      <c r="L6" s="120"/>
-      <c r="M6" s="121">
+      <c r="D6" s="120"/>
+      <c r="E6" s="121"/>
+      <c r="F6" s="121"/>
+      <c r="G6" s="121"/>
+      <c r="H6" s="121"/>
+      <c r="I6" s="122"/>
+      <c r="J6" s="122"/>
+      <c r="K6" s="122"/>
+      <c r="L6" s="122"/>
+      <c r="M6" s="123">
         <v>0.05</v>
       </c>
-      <c r="N6" s="122"/>
-      <c r="O6" s="122"/>
+      <c r="N6" s="124"/>
+      <c r="O6" s="124"/>
       <c r="P6" s="6">
         <v>0</v>
       </c>
-      <c r="Q6" s="125">
+      <c r="Q6" s="127">
         <v>0.95</v>
       </c>
-      <c r="R6" s="123">
-        <v>0</v>
-      </c>
-      <c r="S6" s="124">
+      <c r="R6" s="125">
+        <v>0</v>
+      </c>
+      <c r="S6" s="126">
         <v>0</v>
       </c>
       <c r="T6" s="1">
@@ -3844,12 +3874,12 @@
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="27" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="27" t="s">
         <v>32</v>
       </c>
     </row>
@@ -3889,7 +3919,7 @@
       <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="9" t="s">
@@ -3942,41 +3972,41 @@
       </c>
     </row>
     <row r="2" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="127" t="s">
+      <c r="A2" s="129" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="128" t="s">
+      <c r="B2" s="130" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="129"/>
-      <c r="D2" s="130">
+      <c r="C2" s="64"/>
+      <c r="D2" s="142">
         <v>0.40625</v>
       </c>
-      <c r="E2" s="104"/>
-      <c r="F2" s="104"/>
-      <c r="G2" s="104"/>
-      <c r="H2" s="104"/>
-      <c r="I2" s="130">
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="142">
         <v>6.25E-2</v>
       </c>
-      <c r="J2" s="104"/>
-      <c r="K2" s="130">
+      <c r="J2" s="48"/>
+      <c r="K2" s="142">
         <v>3.125E-2</v>
       </c>
-      <c r="L2" s="130">
+      <c r="L2" s="142">
         <v>0.1875</v>
       </c>
-      <c r="M2" s="130">
+      <c r="M2" s="142">
         <v>3.125E-2</v>
       </c>
-      <c r="N2" s="104"/>
-      <c r="O2" s="131">
+      <c r="N2" s="48"/>
+      <c r="O2" s="141">
         <v>6.25E-2</v>
       </c>
-      <c r="P2" s="104"/>
-      <c r="Q2" s="104"/>
-      <c r="R2" s="104"/>
-      <c r="S2" s="132">
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="182">
         <v>0.21875</v>
       </c>
       <c r="T2" s="1">
@@ -3985,43 +4015,43 @@
       </c>
     </row>
     <row r="3" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="136" t="s">
+      <c r="C3" s="133" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="134">
+      <c r="D3" s="131">
         <v>1</v>
       </c>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="70">
-        <v>0</v>
-      </c>
-      <c r="J3" s="77"/>
-      <c r="K3" s="70">
-        <v>0</v>
-      </c>
-      <c r="L3" s="70">
-        <v>0</v>
-      </c>
-      <c r="M3" s="70">
-        <v>0</v>
-      </c>
-      <c r="N3" s="49"/>
-      <c r="O3" s="3">
-        <v>0</v>
-      </c>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="4">
+      <c r="E3" s="115"/>
+      <c r="F3" s="115"/>
+      <c r="G3" s="115"/>
+      <c r="H3" s="115"/>
+      <c r="I3" s="69">
+        <v>0</v>
+      </c>
+      <c r="J3" s="115"/>
+      <c r="K3" s="187">
+        <v>0</v>
+      </c>
+      <c r="L3" s="187">
+        <v>0</v>
+      </c>
+      <c r="M3" s="187">
+        <v>0</v>
+      </c>
+      <c r="N3" s="114"/>
+      <c r="O3" s="116">
+        <v>0</v>
+      </c>
+      <c r="P3" s="115"/>
+      <c r="Q3" s="115"/>
+      <c r="R3" s="115"/>
+      <c r="S3" s="118">
         <v>0</v>
       </c>
       <c r="T3" s="1">
@@ -4030,43 +4060,43 @@
       </c>
     </row>
     <row r="4" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="137" t="s">
+      <c r="C4" s="134" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="25">
-        <v>0</v>
-      </c>
-      <c r="E4" s="79"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="79"/>
-      <c r="H4" s="79"/>
-      <c r="I4" s="134">
+      <c r="D4" s="152">
+        <v>0</v>
+      </c>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="131">
         <v>0.22222222222222199</v>
       </c>
-      <c r="J4" s="79"/>
-      <c r="K4" s="25">
-        <v>0</v>
-      </c>
-      <c r="L4" s="64">
+      <c r="J4" s="110"/>
+      <c r="K4" s="151">
+        <v>0</v>
+      </c>
+      <c r="L4" s="112">
         <v>0.66666666666666596</v>
       </c>
-      <c r="M4" s="64">
+      <c r="M4" s="112">
         <v>0.11111111111111099</v>
       </c>
-      <c r="N4" s="50"/>
-      <c r="O4" s="23">
-        <v>0</v>
-      </c>
-      <c r="P4" s="79"/>
-      <c r="Q4" s="79"/>
-      <c r="R4" s="79"/>
-      <c r="S4" s="12">
+      <c r="N4" s="109"/>
+      <c r="O4" s="111">
+        <v>0</v>
+      </c>
+      <c r="P4" s="110"/>
+      <c r="Q4" s="110"/>
+      <c r="R4" s="110"/>
+      <c r="S4" s="188">
         <v>0</v>
       </c>
       <c r="T4" s="1">
@@ -4075,43 +4105,43 @@
       </c>
     </row>
     <row r="5" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="40" t="s">
+      <c r="A5" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="138" t="s">
+      <c r="C5" s="135" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="25">
-        <v>0</v>
-      </c>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79"/>
-      <c r="H5" s="79"/>
-      <c r="I5" s="25">
-        <v>0</v>
-      </c>
-      <c r="J5" s="79"/>
-      <c r="K5" s="134">
+      <c r="D5" s="183">
+        <v>0</v>
+      </c>
+      <c r="E5" s="110"/>
+      <c r="F5" s="110"/>
+      <c r="G5" s="110"/>
+      <c r="H5" s="110"/>
+      <c r="I5" s="152">
+        <v>0</v>
+      </c>
+      <c r="J5" s="110"/>
+      <c r="K5" s="131">
         <v>0.1</v>
       </c>
-      <c r="L5" s="25">
-        <v>0</v>
-      </c>
-      <c r="M5" s="25">
-        <v>0</v>
-      </c>
-      <c r="N5" s="50"/>
-      <c r="O5" s="64">
+      <c r="L5" s="151">
+        <v>0</v>
+      </c>
+      <c r="M5" s="183">
+        <v>0</v>
+      </c>
+      <c r="N5" s="109"/>
+      <c r="O5" s="112">
         <v>0.2</v>
       </c>
-      <c r="P5" s="79"/>
-      <c r="Q5" s="79"/>
-      <c r="R5" s="79"/>
-      <c r="S5" s="80">
+      <c r="P5" s="110"/>
+      <c r="Q5" s="110"/>
+      <c r="R5" s="110"/>
+      <c r="S5" s="189">
         <v>0.7</v>
       </c>
       <c r="T5" s="1">
@@ -4120,43 +4150,43 @@
       </c>
     </row>
     <row r="6" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="40" t="s">
+      <c r="A6" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="95" t="s">
+      <c r="C6" s="94" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="25">
-        <v>0</v>
-      </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79"/>
-      <c r="H6" s="79"/>
-      <c r="I6" s="64">
+      <c r="D6" s="183">
+        <v>0</v>
+      </c>
+      <c r="E6" s="110"/>
+      <c r="F6" s="110"/>
+      <c r="G6" s="110"/>
+      <c r="H6" s="110"/>
+      <c r="I6" s="112">
         <v>0.125</v>
       </c>
-      <c r="J6" s="79"/>
-      <c r="K6" s="25">
-        <v>0</v>
-      </c>
-      <c r="L6" s="134">
+      <c r="J6" s="110"/>
+      <c r="K6" s="152">
+        <v>0</v>
+      </c>
+      <c r="L6" s="131">
         <v>0.75</v>
       </c>
-      <c r="M6" s="133">
+      <c r="M6" s="184">
         <v>0.125</v>
       </c>
-      <c r="N6" s="50"/>
-      <c r="O6" s="23">
-        <v>0</v>
-      </c>
-      <c r="P6" s="79"/>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="12">
+      <c r="N6" s="109"/>
+      <c r="O6" s="83">
+        <v>0</v>
+      </c>
+      <c r="P6" s="110"/>
+      <c r="Q6" s="110"/>
+      <c r="R6" s="110"/>
+      <c r="S6" s="188">
         <v>0</v>
       </c>
       <c r="T6" s="1">
@@ -4165,43 +4195,43 @@
       </c>
     </row>
     <row r="7" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="40" t="s">
+      <c r="A7" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="139" t="s">
+      <c r="C7" s="136" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="25">
-        <v>0</v>
-      </c>
-      <c r="E7" s="79"/>
-      <c r="F7" s="79"/>
-      <c r="G7" s="79"/>
-      <c r="H7" s="79"/>
-      <c r="I7" s="25">
-        <v>0</v>
-      </c>
-      <c r="J7" s="79"/>
-      <c r="K7" s="25">
-        <v>0</v>
-      </c>
-      <c r="L7" s="25">
-        <v>0</v>
-      </c>
-      <c r="M7" s="25">
-        <v>0</v>
-      </c>
-      <c r="N7" s="50"/>
-      <c r="O7" s="125">
+      <c r="D7" s="183">
+        <v>0</v>
+      </c>
+      <c r="E7" s="110"/>
+      <c r="F7" s="110"/>
+      <c r="G7" s="110"/>
+      <c r="H7" s="110"/>
+      <c r="I7" s="183">
+        <v>0</v>
+      </c>
+      <c r="J7" s="110"/>
+      <c r="K7" s="183">
+        <v>0</v>
+      </c>
+      <c r="L7" s="152">
+        <v>0</v>
+      </c>
+      <c r="M7" s="183">
+        <v>0</v>
+      </c>
+      <c r="N7" s="109"/>
+      <c r="O7" s="127">
         <v>0.22222222222222199</v>
       </c>
-      <c r="P7" s="79"/>
-      <c r="Q7" s="79"/>
-      <c r="R7" s="79"/>
-      <c r="S7" s="80">
+      <c r="P7" s="110"/>
+      <c r="Q7" s="110"/>
+      <c r="R7" s="110"/>
+      <c r="S7" s="190">
         <v>0.77777777777777701</v>
       </c>
       <c r="T7" s="1">
@@ -4210,43 +4240,43 @@
       </c>
     </row>
     <row r="8" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="41" t="s">
+      <c r="A8" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="97" t="s">
+      <c r="C8" s="185" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="73">
-        <v>0</v>
-      </c>
-      <c r="E8" s="78"/>
-      <c r="F8" s="78"/>
-      <c r="G8" s="78"/>
-      <c r="H8" s="78"/>
-      <c r="I8" s="73">
-        <v>0</v>
-      </c>
-      <c r="J8" s="78"/>
-      <c r="K8" s="73">
-        <v>0</v>
-      </c>
-      <c r="L8" s="73">
-        <v>0</v>
-      </c>
-      <c r="M8" s="73">
-        <v>0</v>
-      </c>
-      <c r="N8" s="51"/>
+      <c r="D8" s="72">
+        <v>0</v>
+      </c>
+      <c r="E8" s="77"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="72">
+        <v>0</v>
+      </c>
+      <c r="J8" s="77"/>
+      <c r="K8" s="72">
+        <v>0</v>
+      </c>
+      <c r="L8" s="72">
+        <v>0</v>
+      </c>
+      <c r="M8" s="72">
+        <v>0</v>
+      </c>
+      <c r="N8" s="50"/>
       <c r="O8" s="6">
         <v>0</v>
       </c>
-      <c r="P8" s="78"/>
-      <c r="Q8" s="78"/>
-      <c r="R8" s="78"/>
-      <c r="S8" s="125">
+      <c r="P8" s="77"/>
+      <c r="Q8" s="77"/>
+      <c r="R8" s="77"/>
+      <c r="S8" s="127">
         <v>1</v>
       </c>
       <c r="T8" s="1">
@@ -4255,42 +4285,42 @@
       </c>
     </row>
     <row r="9" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="37" t="s">
+      <c r="B9" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="140" t="s">
+      <c r="C9" s="137" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="70">
-        <v>0</v>
-      </c>
-      <c r="E9" s="77"/>
-      <c r="F9" s="77"/>
-      <c r="G9" s="77"/>
-      <c r="H9" s="77"/>
-      <c r="I9" s="70">
-        <v>0</v>
-      </c>
-      <c r="J9" s="77"/>
-      <c r="K9" s="70">
-        <v>0</v>
-      </c>
-      <c r="L9" s="70">
-        <v>0</v>
-      </c>
-      <c r="M9" s="70">
-        <v>0</v>
-      </c>
-      <c r="N9" s="49"/>
-      <c r="O9" s="135">
+      <c r="D9" s="187">
+        <v>0</v>
+      </c>
+      <c r="E9" s="115"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="115"/>
+      <c r="H9" s="115"/>
+      <c r="I9" s="187">
+        <v>0</v>
+      </c>
+      <c r="J9" s="115"/>
+      <c r="K9" s="187">
+        <v>0</v>
+      </c>
+      <c r="L9" s="187">
+        <v>0</v>
+      </c>
+      <c r="M9" s="187">
+        <v>0</v>
+      </c>
+      <c r="N9" s="114"/>
+      <c r="O9" s="132">
         <v>1</v>
       </c>
-      <c r="P9" s="77"/>
-      <c r="Q9" s="77"/>
-      <c r="R9" s="77"/>
+      <c r="P9" s="115"/>
+      <c r="Q9" s="115"/>
+      <c r="R9" s="115"/>
       <c r="S9" s="4">
         <v>0</v>
       </c>
@@ -4300,43 +4330,43 @@
       </c>
     </row>
     <row r="10" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="41" t="s">
+      <c r="A10" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="141" t="s">
+      <c r="C10" s="186" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="73">
-        <v>0</v>
-      </c>
-      <c r="E10" s="78"/>
-      <c r="F10" s="78"/>
-      <c r="G10" s="78"/>
-      <c r="H10" s="78"/>
-      <c r="I10" s="73">
-        <v>0</v>
-      </c>
-      <c r="J10" s="78"/>
-      <c r="K10" s="73">
-        <v>0</v>
-      </c>
-      <c r="L10" s="73">
-        <v>0</v>
-      </c>
-      <c r="M10" s="73">
-        <v>0</v>
-      </c>
-      <c r="N10" s="51"/>
+      <c r="D10" s="72">
+        <v>0</v>
+      </c>
+      <c r="E10" s="77"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="77"/>
+      <c r="I10" s="72">
+        <v>0</v>
+      </c>
+      <c r="J10" s="77"/>
+      <c r="K10" s="72">
+        <v>0</v>
+      </c>
+      <c r="L10" s="72">
+        <v>0</v>
+      </c>
+      <c r="M10" s="72">
+        <v>0</v>
+      </c>
+      <c r="N10" s="50"/>
       <c r="O10" s="6">
         <v>0</v>
       </c>
-      <c r="P10" s="78"/>
-      <c r="Q10" s="78"/>
-      <c r="R10" s="78"/>
-      <c r="S10" s="135">
+      <c r="P10" s="77"/>
+      <c r="Q10" s="77"/>
+      <c r="R10" s="77"/>
+      <c r="S10" s="132">
         <v>1</v>
       </c>
       <c r="T10" s="1">
@@ -4392,7 +4422,7 @@
       <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="9" t="s">
@@ -4445,322 +4475,322 @@
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="142"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="145">
+      <c r="C2" s="139"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="142">
         <v>0.33333333333333298</v>
       </c>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="145">
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="142">
         <v>0.38888888888888801</v>
       </c>
-      <c r="K2" s="49"/>
-      <c r="L2" s="49"/>
-      <c r="M2" s="70">
-        <v>0</v>
-      </c>
-      <c r="N2" s="144">
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="69">
+        <v>0</v>
+      </c>
+      <c r="N2" s="141">
         <v>0.27777777777777701</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
       <c r="Q2" s="3">
         <v>0</v>
       </c>
-      <c r="R2" s="77"/>
-      <c r="S2" s="147"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="144"/>
       <c r="T2" s="1">
         <f>SUM(D2:S2)</f>
         <v>0.999999999999998</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="67"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="25">
-        <v>0</v>
-      </c>
-      <c r="G3" s="79"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="146">
+      <c r="C3" s="66"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="24">
+        <v>0</v>
+      </c>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="143">
         <v>0.04</v>
       </c>
-      <c r="K3" s="50"/>
-      <c r="L3" s="50"/>
-      <c r="M3" s="25">
-        <v>0</v>
-      </c>
-      <c r="N3" s="143">
+      <c r="K3" s="49"/>
+      <c r="L3" s="49"/>
+      <c r="M3" s="24">
+        <v>0</v>
+      </c>
+      <c r="N3" s="140">
         <v>0.24</v>
       </c>
-      <c r="O3" s="79"/>
-      <c r="P3" s="79"/>
-      <c r="Q3" s="143">
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="140">
         <v>0.72</v>
       </c>
-      <c r="R3" s="79"/>
-      <c r="S3" s="148"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="145"/>
       <c r="T3" s="1">
         <f t="shared" ref="T3:T25" si="0">SUM(D3:S3)</f>
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="67"/>
-      <c r="D4" s="79"/>
-      <c r="E4" s="79"/>
-      <c r="F4" s="146">
+      <c r="C4" s="66"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="143">
         <v>5.2631578947368397E-2</v>
       </c>
-      <c r="G4" s="79"/>
-      <c r="H4" s="79"/>
-      <c r="I4" s="79"/>
-      <c r="J4" s="146">
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="143">
         <v>5.2631578947368397E-2</v>
       </c>
-      <c r="K4" s="50"/>
-      <c r="L4" s="50"/>
-      <c r="M4" s="146">
+      <c r="K4" s="49"/>
+      <c r="L4" s="49"/>
+      <c r="M4" s="143">
         <v>5.2631578947368397E-2</v>
       </c>
-      <c r="N4" s="143">
+      <c r="N4" s="140">
         <v>0.105263157894736</v>
       </c>
-      <c r="O4" s="79"/>
-      <c r="P4" s="79"/>
-      <c r="Q4" s="143">
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="140">
         <v>0.73684210526315697</v>
       </c>
-      <c r="R4" s="79"/>
-      <c r="S4" s="148"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="145"/>
       <c r="T4" s="1">
         <f t="shared" si="0"/>
         <v>0.99999999999999822</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="136" t="s">
+      <c r="C5" s="133" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="93">
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="92">
         <v>0.83333333333333304</v>
       </c>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="58">
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="57">
         <v>0.16666666666666599</v>
       </c>
-      <c r="K5" s="49"/>
-      <c r="L5" s="49"/>
-      <c r="M5" s="70">
+      <c r="K5" s="48"/>
+      <c r="L5" s="48"/>
+      <c r="M5" s="69">
         <v>0</v>
       </c>
       <c r="N5" s="3">
         <v>0</v>
       </c>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="76"/>
       <c r="Q5" s="3">
         <v>0</v>
       </c>
-      <c r="R5" s="77"/>
-      <c r="S5" s="147"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="144"/>
       <c r="T5" s="1">
         <f t="shared" si="0"/>
         <v>0.999999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A6" s="40" t="s">
+      <c r="A6" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="173" t="s">
+      <c r="C6" s="170" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="79"/>
-      <c r="E6" s="79"/>
-      <c r="F6" s="158">
-        <v>0</v>
-      </c>
-      <c r="G6" s="79"/>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
-      <c r="J6" s="25">
-        <v>0</v>
-      </c>
-      <c r="K6" s="50"/>
-      <c r="L6" s="50"/>
-      <c r="M6" s="25">
-        <v>0</v>
-      </c>
-      <c r="N6" s="23">
-        <v>0</v>
-      </c>
-      <c r="O6" s="79"/>
-      <c r="P6" s="79"/>
-      <c r="Q6" s="23">
-        <v>0</v>
-      </c>
-      <c r="R6" s="79"/>
-      <c r="S6" s="148"/>
+      <c r="D6" s="78"/>
+      <c r="E6" s="78"/>
+      <c r="F6" s="155">
+        <v>0</v>
+      </c>
+      <c r="G6" s="78"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
+      <c r="J6" s="24">
+        <v>0</v>
+      </c>
+      <c r="K6" s="49"/>
+      <c r="L6" s="49"/>
+      <c r="M6" s="24">
+        <v>0</v>
+      </c>
+      <c r="N6" s="22">
+        <v>0</v>
+      </c>
+      <c r="O6" s="78"/>
+      <c r="P6" s="78"/>
+      <c r="Q6" s="22">
+        <v>0</v>
+      </c>
+      <c r="R6" s="78"/>
+      <c r="S6" s="145"/>
       <c r="T6" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="40" t="s">
+      <c r="A7" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="174" t="s">
+      <c r="C7" s="171" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="85"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="159">
-        <v>0</v>
-      </c>
-      <c r="G7" s="85"/>
-      <c r="H7" s="85"/>
-      <c r="I7" s="85"/>
-      <c r="J7" s="25">
-        <v>0</v>
-      </c>
-      <c r="K7" s="52"/>
-      <c r="L7" s="52"/>
-      <c r="M7" s="155">
-        <v>0</v>
-      </c>
-      <c r="N7" s="86">
-        <v>0</v>
-      </c>
-      <c r="O7" s="85"/>
-      <c r="P7" s="85"/>
-      <c r="Q7" s="86">
-        <v>0</v>
-      </c>
-      <c r="R7" s="85"/>
-      <c r="S7" s="156"/>
+      <c r="D7" s="84"/>
+      <c r="E7" s="84"/>
+      <c r="F7" s="156">
+        <v>0</v>
+      </c>
+      <c r="G7" s="84"/>
+      <c r="H7" s="84"/>
+      <c r="I7" s="84"/>
+      <c r="J7" s="24">
+        <v>0</v>
+      </c>
+      <c r="K7" s="51"/>
+      <c r="L7" s="51"/>
+      <c r="M7" s="152">
+        <v>0</v>
+      </c>
+      <c r="N7" s="85">
+        <v>0</v>
+      </c>
+      <c r="O7" s="84"/>
+      <c r="P7" s="84"/>
+      <c r="Q7" s="85">
+        <v>0</v>
+      </c>
+      <c r="R7" s="84"/>
+      <c r="S7" s="153"/>
       <c r="T7" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A8" s="40" t="s">
+      <c r="A8" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="175" t="s">
+      <c r="C8" s="172" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="83"/>
-      <c r="E8" s="83"/>
-      <c r="F8" s="29">
+      <c r="D8" s="82"/>
+      <c r="E8" s="82"/>
+      <c r="F8" s="28">
         <v>0.33333333333333298</v>
       </c>
-      <c r="G8" s="83"/>
-      <c r="H8" s="83"/>
-      <c r="I8" s="83"/>
-      <c r="J8" s="93">
+      <c r="G8" s="82"/>
+      <c r="H8" s="82"/>
+      <c r="I8" s="82"/>
+      <c r="J8" s="92">
         <v>0.66666666666666596</v>
       </c>
-      <c r="K8" s="53"/>
-      <c r="L8" s="53"/>
-      <c r="M8" s="154">
-        <v>0</v>
-      </c>
-      <c r="N8" s="84">
-        <v>0</v>
-      </c>
-      <c r="O8" s="83"/>
-      <c r="P8" s="83"/>
-      <c r="Q8" s="84">
-        <v>0</v>
-      </c>
-      <c r="R8" s="83"/>
-      <c r="S8" s="157"/>
+      <c r="K8" s="52"/>
+      <c r="L8" s="52"/>
+      <c r="M8" s="151">
+        <v>0</v>
+      </c>
+      <c r="N8" s="83">
+        <v>0</v>
+      </c>
+      <c r="O8" s="82"/>
+      <c r="P8" s="82"/>
+      <c r="Q8" s="83">
+        <v>0</v>
+      </c>
+      <c r="R8" s="82"/>
+      <c r="S8" s="154"/>
       <c r="T8" s="1">
         <f t="shared" si="0"/>
         <v>0.99999999999999889</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="137" t="s">
+      <c r="C9" s="134" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="79"/>
-      <c r="E9" s="79"/>
-      <c r="F9" s="25">
-        <v>0</v>
-      </c>
-      <c r="G9" s="79"/>
-      <c r="H9" s="79"/>
-      <c r="I9" s="79"/>
-      <c r="J9" s="160">
-        <v>0</v>
-      </c>
-      <c r="K9" s="50"/>
-      <c r="L9" s="50"/>
-      <c r="M9" s="25">
-        <v>0</v>
-      </c>
-      <c r="N9" s="23">
-        <v>0</v>
-      </c>
-      <c r="O9" s="79"/>
-      <c r="P9" s="79"/>
-      <c r="Q9" s="23">
-        <v>0</v>
-      </c>
-      <c r="R9" s="79"/>
-      <c r="S9" s="148"/>
+      <c r="D9" s="78"/>
+      <c r="E9" s="78"/>
+      <c r="F9" s="24">
+        <v>0</v>
+      </c>
+      <c r="G9" s="78"/>
+      <c r="H9" s="78"/>
+      <c r="I9" s="78"/>
+      <c r="J9" s="157">
+        <v>0</v>
+      </c>
+      <c r="K9" s="49"/>
+      <c r="L9" s="49"/>
+      <c r="M9" s="24">
+        <v>0</v>
+      </c>
+      <c r="N9" s="22">
+        <v>0</v>
+      </c>
+      <c r="O9" s="78"/>
+      <c r="P9" s="78"/>
+      <c r="Q9" s="22">
+        <v>0</v>
+      </c>
+      <c r="R9" s="78"/>
+      <c r="S9" s="145"/>
       <c r="T9" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4770,120 +4800,120 @@
       <c r="A10" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="176" t="s">
+      <c r="C10" s="173" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="85"/>
-      <c r="E10" s="85"/>
-      <c r="F10" s="86">
-        <v>0</v>
-      </c>
-      <c r="G10" s="85"/>
-      <c r="H10" s="85"/>
-      <c r="I10" s="85"/>
-      <c r="J10" s="161">
-        <v>0</v>
-      </c>
-      <c r="K10" s="52"/>
-      <c r="L10" s="52"/>
-      <c r="M10" s="86">
-        <v>0</v>
-      </c>
-      <c r="N10" s="23">
-        <v>0</v>
-      </c>
-      <c r="O10" s="85"/>
-      <c r="P10" s="85"/>
-      <c r="Q10" s="86">
-        <v>0</v>
-      </c>
-      <c r="R10" s="85"/>
-      <c r="S10" s="156"/>
+      <c r="D10" s="84"/>
+      <c r="E10" s="84"/>
+      <c r="F10" s="85">
+        <v>0</v>
+      </c>
+      <c r="G10" s="84"/>
+      <c r="H10" s="84"/>
+      <c r="I10" s="84"/>
+      <c r="J10" s="158">
+        <v>0</v>
+      </c>
+      <c r="K10" s="51"/>
+      <c r="L10" s="51"/>
+      <c r="M10" s="85">
+        <v>0</v>
+      </c>
+      <c r="N10" s="22">
+        <v>0</v>
+      </c>
+      <c r="O10" s="84"/>
+      <c r="P10" s="84"/>
+      <c r="Q10" s="85">
+        <v>0</v>
+      </c>
+      <c r="R10" s="84"/>
+      <c r="S10" s="153"/>
       <c r="T10" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A11" s="40" t="s">
+      <c r="A11" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="177" t="s">
+      <c r="C11" s="174" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="83"/>
-      <c r="E11" s="83"/>
-      <c r="F11" s="54">
+      <c r="D11" s="82"/>
+      <c r="E11" s="82"/>
+      <c r="F11" s="53">
         <v>0.33333333333333298</v>
       </c>
-      <c r="G11" s="83"/>
-      <c r="H11" s="83"/>
-      <c r="I11" s="83"/>
-      <c r="J11" s="29">
+      <c r="G11" s="82"/>
+      <c r="H11" s="82"/>
+      <c r="I11" s="82"/>
+      <c r="J11" s="28">
         <v>0.38888888888888801</v>
       </c>
-      <c r="K11" s="53"/>
-      <c r="L11" s="53"/>
-      <c r="M11" s="154">
-        <v>0</v>
-      </c>
-      <c r="N11" s="150">
+      <c r="K11" s="52"/>
+      <c r="L11" s="52"/>
+      <c r="M11" s="151">
+        <v>0</v>
+      </c>
+      <c r="N11" s="147">
         <v>0.27777777777777701</v>
       </c>
-      <c r="O11" s="83"/>
-      <c r="P11" s="83"/>
-      <c r="Q11" s="84">
-        <v>0</v>
-      </c>
-      <c r="R11" s="83"/>
-      <c r="S11" s="157"/>
+      <c r="O11" s="82"/>
+      <c r="P11" s="82"/>
+      <c r="Q11" s="83">
+        <v>0</v>
+      </c>
+      <c r="R11" s="82"/>
+      <c r="S11" s="154"/>
       <c r="T11" s="1">
         <f t="shared" si="0"/>
         <v>0.999999999999998</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A12" s="40" t="s">
+      <c r="A12" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="138" t="s">
+      <c r="C12" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="79"/>
-      <c r="E12" s="79"/>
-      <c r="F12" s="25">
-        <v>0</v>
-      </c>
-      <c r="G12" s="79"/>
-      <c r="H12" s="79"/>
-      <c r="I12" s="79"/>
-      <c r="J12" s="25">
-        <v>0</v>
-      </c>
-      <c r="K12" s="50"/>
-      <c r="L12" s="50"/>
-      <c r="M12" s="25">
-        <v>0</v>
-      </c>
-      <c r="N12" s="162">
-        <v>0</v>
-      </c>
-      <c r="O12" s="79"/>
-      <c r="P12" s="79"/>
-      <c r="Q12" s="23">
-        <v>0</v>
-      </c>
-      <c r="R12" s="79"/>
-      <c r="S12" s="148"/>
+      <c r="D12" s="78"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="24">
+        <v>0</v>
+      </c>
+      <c r="G12" s="78"/>
+      <c r="H12" s="78"/>
+      <c r="I12" s="78"/>
+      <c r="J12" s="24">
+        <v>0</v>
+      </c>
+      <c r="K12" s="49"/>
+      <c r="L12" s="49"/>
+      <c r="M12" s="24">
+        <v>0</v>
+      </c>
+      <c r="N12" s="159">
+        <v>0</v>
+      </c>
+      <c r="O12" s="78"/>
+      <c r="P12" s="78"/>
+      <c r="Q12" s="22">
+        <v>0</v>
+      </c>
+      <c r="R12" s="78"/>
+      <c r="S12" s="145"/>
       <c r="T12" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4893,120 +4923,120 @@
       <c r="A13" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="178" t="s">
+      <c r="C13" s="175" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="85"/>
-      <c r="E13" s="85"/>
-      <c r="F13" s="86">
-        <v>0</v>
-      </c>
-      <c r="G13" s="85"/>
-      <c r="H13" s="85"/>
-      <c r="I13" s="85"/>
-      <c r="J13" s="86">
-        <v>0</v>
-      </c>
-      <c r="K13" s="52"/>
-      <c r="L13" s="52"/>
-      <c r="M13" s="86">
-        <v>0</v>
-      </c>
-      <c r="N13" s="161">
-        <v>0</v>
-      </c>
-      <c r="O13" s="85"/>
-      <c r="P13" s="85"/>
-      <c r="Q13" s="23">
-        <v>0</v>
-      </c>
-      <c r="R13" s="85"/>
-      <c r="S13" s="156"/>
+      <c r="D13" s="84"/>
+      <c r="E13" s="84"/>
+      <c r="F13" s="85">
+        <v>0</v>
+      </c>
+      <c r="G13" s="84"/>
+      <c r="H13" s="84"/>
+      <c r="I13" s="84"/>
+      <c r="J13" s="85">
+        <v>0</v>
+      </c>
+      <c r="K13" s="51"/>
+      <c r="L13" s="51"/>
+      <c r="M13" s="85">
+        <v>0</v>
+      </c>
+      <c r="N13" s="158">
+        <v>0</v>
+      </c>
+      <c r="O13" s="84"/>
+      <c r="P13" s="84"/>
+      <c r="Q13" s="22">
+        <v>0</v>
+      </c>
+      <c r="R13" s="84"/>
+      <c r="S13" s="153"/>
       <c r="T13" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A14" s="40" t="s">
+      <c r="A14" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="179" t="s">
+      <c r="C14" s="176" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="83"/>
-      <c r="E14" s="83"/>
-      <c r="F14" s="54">
+      <c r="D14" s="82"/>
+      <c r="E14" s="82"/>
+      <c r="F14" s="53">
         <v>0.15384615384615299</v>
       </c>
-      <c r="G14" s="83"/>
-      <c r="H14" s="83"/>
-      <c r="I14" s="83"/>
-      <c r="J14" s="55">
+      <c r="G14" s="82"/>
+      <c r="H14" s="82"/>
+      <c r="I14" s="82"/>
+      <c r="J14" s="54">
         <v>0.46153846153846101</v>
       </c>
-      <c r="K14" s="53"/>
-      <c r="L14" s="53"/>
-      <c r="M14" s="154">
-        <v>0</v>
-      </c>
-      <c r="N14" s="64">
+      <c r="K14" s="52"/>
+      <c r="L14" s="52"/>
+      <c r="M14" s="151">
+        <v>0</v>
+      </c>
+      <c r="N14" s="63">
         <v>0.38461538461538403</v>
       </c>
-      <c r="O14" s="83"/>
-      <c r="P14" s="83"/>
-      <c r="Q14" s="150">
-        <v>0</v>
-      </c>
-      <c r="R14" s="83"/>
-      <c r="S14" s="157"/>
+      <c r="O14" s="82"/>
+      <c r="P14" s="82"/>
+      <c r="Q14" s="147">
+        <v>0</v>
+      </c>
+      <c r="R14" s="82"/>
+      <c r="S14" s="154"/>
       <c r="T14" s="1">
         <f t="shared" si="0"/>
         <v>0.999999999999998</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A15" s="40" t="s">
+      <c r="A15" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="95" t="s">
+      <c r="C15" s="94" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="79"/>
-      <c r="E15" s="79"/>
-      <c r="F15" s="25">
-        <v>0</v>
-      </c>
-      <c r="G15" s="79"/>
-      <c r="H15" s="79"/>
-      <c r="I15" s="79"/>
-      <c r="J15" s="25">
-        <v>0</v>
-      </c>
-      <c r="K15" s="50"/>
-      <c r="L15" s="50"/>
-      <c r="M15" s="25">
-        <v>0</v>
-      </c>
-      <c r="N15" s="29">
+      <c r="D15" s="78"/>
+      <c r="E15" s="78"/>
+      <c r="F15" s="24">
+        <v>0</v>
+      </c>
+      <c r="G15" s="78"/>
+      <c r="H15" s="78"/>
+      <c r="I15" s="78"/>
+      <c r="J15" s="24">
+        <v>0</v>
+      </c>
+      <c r="K15" s="49"/>
+      <c r="L15" s="49"/>
+      <c r="M15" s="24">
+        <v>0</v>
+      </c>
+      <c r="N15" s="28">
         <v>0.14285714285714199</v>
       </c>
-      <c r="O15" s="79"/>
-      <c r="P15" s="79"/>
-      <c r="Q15" s="91">
+      <c r="O15" s="78"/>
+      <c r="P15" s="78"/>
+      <c r="Q15" s="90">
         <v>0.85714285714285698</v>
       </c>
-      <c r="R15" s="79"/>
-      <c r="S15" s="148"/>
+      <c r="R15" s="78"/>
+      <c r="S15" s="145"/>
       <c r="T15" s="1">
         <f t="shared" si="0"/>
         <v>0.999999999999999</v>
@@ -5016,38 +5046,38 @@
       <c r="A16" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="75" t="s">
+      <c r="B16" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="171" t="s">
+      <c r="C16" s="168" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="78"/>
-      <c r="E16" s="78"/>
+      <c r="D16" s="77"/>
+      <c r="E16" s="77"/>
       <c r="F16" s="6">
         <v>0</v>
       </c>
-      <c r="G16" s="78"/>
-      <c r="H16" s="78"/>
-      <c r="I16" s="78"/>
+      <c r="G16" s="77"/>
+      <c r="H16" s="77"/>
+      <c r="I16" s="77"/>
       <c r="J16" s="6">
         <v>0</v>
       </c>
-      <c r="K16" s="51"/>
-      <c r="L16" s="51"/>
+      <c r="K16" s="50"/>
+      <c r="L16" s="50"/>
       <c r="M16" s="6">
         <v>7.1428571428571397E-2</v>
       </c>
-      <c r="N16" s="16">
+      <c r="N16" s="15">
         <v>7.1428571428571397E-2</v>
       </c>
-      <c r="O16" s="78"/>
-      <c r="P16" s="78"/>
-      <c r="Q16" s="90">
+      <c r="O16" s="77"/>
+      <c r="P16" s="77"/>
+      <c r="Q16" s="89">
         <v>0.85714285714285698</v>
       </c>
-      <c r="R16" s="78"/>
-      <c r="S16" s="149"/>
+      <c r="R16" s="77"/>
+      <c r="S16" s="146"/>
       <c r="T16" s="1">
         <f t="shared" si="0"/>
         <v>0.99999999999999978</v>
@@ -5057,38 +5087,38 @@
       <c r="A17" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="76" t="s">
+      <c r="B17" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="98" t="s">
+      <c r="C17" s="97" t="s">
         <v>17</v>
       </c>
-      <c r="D17" s="77"/>
-      <c r="E17" s="77"/>
-      <c r="F17" s="150">
+      <c r="D17" s="76"/>
+      <c r="E17" s="76"/>
+      <c r="F17" s="147">
         <v>0.33333333333333298</v>
       </c>
-      <c r="G17" s="77"/>
-      <c r="H17" s="77"/>
-      <c r="I17" s="77"/>
-      <c r="J17" s="58">
+      <c r="G17" s="76"/>
+      <c r="H17" s="76"/>
+      <c r="I17" s="76"/>
+      <c r="J17" s="57">
         <v>0.38888888888888801</v>
       </c>
-      <c r="K17" s="49"/>
-      <c r="L17" s="49"/>
+      <c r="K17" s="48"/>
+      <c r="L17" s="48"/>
       <c r="M17" s="3">
         <v>0</v>
       </c>
-      <c r="N17" s="58">
+      <c r="N17" s="57">
         <v>0.27777777777777701</v>
       </c>
-      <c r="O17" s="77"/>
-      <c r="P17" s="77"/>
+      <c r="O17" s="76"/>
+      <c r="P17" s="76"/>
       <c r="Q17" s="3">
         <v>0</v>
       </c>
-      <c r="R17" s="77"/>
-      <c r="S17" s="147"/>
+      <c r="R17" s="76"/>
+      <c r="S17" s="144"/>
       <c r="T17" s="1">
         <f t="shared" si="0"/>
         <v>0.999999999999998</v>
@@ -5098,38 +5128,38 @@
       <c r="A18" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="180" t="s">
+      <c r="C18" s="177" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="79"/>
-      <c r="E18" s="79"/>
-      <c r="F18" s="151">
-        <v>0</v>
-      </c>
-      <c r="G18" s="79"/>
-      <c r="H18" s="79"/>
-      <c r="I18" s="79"/>
-      <c r="J18" s="23">
-        <v>0</v>
-      </c>
-      <c r="K18" s="50"/>
-      <c r="L18" s="50"/>
-      <c r="M18" s="23">
-        <v>0</v>
-      </c>
-      <c r="N18" s="23">
-        <v>0</v>
-      </c>
-      <c r="O18" s="79"/>
-      <c r="P18" s="79"/>
-      <c r="Q18" s="23">
-        <v>0</v>
-      </c>
-      <c r="R18" s="79"/>
-      <c r="S18" s="148"/>
+      <c r="D18" s="78"/>
+      <c r="E18" s="78"/>
+      <c r="F18" s="148">
+        <v>0</v>
+      </c>
+      <c r="G18" s="78"/>
+      <c r="H18" s="78"/>
+      <c r="I18" s="78"/>
+      <c r="J18" s="22">
+        <v>0</v>
+      </c>
+      <c r="K18" s="49"/>
+      <c r="L18" s="49"/>
+      <c r="M18" s="22">
+        <v>0</v>
+      </c>
+      <c r="N18" s="22">
+        <v>0</v>
+      </c>
+      <c r="O18" s="78"/>
+      <c r="P18" s="78"/>
+      <c r="Q18" s="22">
+        <v>0</v>
+      </c>
+      <c r="R18" s="78"/>
+      <c r="S18" s="145"/>
       <c r="T18" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5139,38 +5169,38 @@
       <c r="A19" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="22" t="s">
+      <c r="B19" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="97" t="s">
+      <c r="C19" s="96" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="85"/>
-      <c r="E19" s="85"/>
-      <c r="F19" s="163">
-        <v>0</v>
-      </c>
-      <c r="G19" s="85"/>
-      <c r="H19" s="85"/>
-      <c r="I19" s="85"/>
-      <c r="J19" s="23">
-        <v>0</v>
-      </c>
-      <c r="K19" s="52"/>
-      <c r="L19" s="52"/>
-      <c r="M19" s="86">
-        <v>0</v>
-      </c>
-      <c r="N19" s="86">
-        <v>0</v>
-      </c>
-      <c r="O19" s="85"/>
-      <c r="P19" s="85"/>
-      <c r="Q19" s="86">
-        <v>0</v>
-      </c>
-      <c r="R19" s="85"/>
-      <c r="S19" s="156"/>
+      <c r="D19" s="84"/>
+      <c r="E19" s="84"/>
+      <c r="F19" s="160">
+        <v>0</v>
+      </c>
+      <c r="G19" s="84"/>
+      <c r="H19" s="84"/>
+      <c r="I19" s="84"/>
+      <c r="J19" s="22">
+        <v>0</v>
+      </c>
+      <c r="K19" s="51"/>
+      <c r="L19" s="51"/>
+      <c r="M19" s="85">
+        <v>0</v>
+      </c>
+      <c r="N19" s="85">
+        <v>0</v>
+      </c>
+      <c r="O19" s="84"/>
+      <c r="P19" s="84"/>
+      <c r="Q19" s="85">
+        <v>0</v>
+      </c>
+      <c r="R19" s="84"/>
+      <c r="S19" s="153"/>
       <c r="T19" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5180,38 +5210,38 @@
       <c r="A20" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="140" t="s">
+      <c r="C20" s="137" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="83"/>
-      <c r="E20" s="83"/>
-      <c r="F20" s="29">
+      <c r="D20" s="82"/>
+      <c r="E20" s="82"/>
+      <c r="F20" s="28">
         <v>0.33333333333333298</v>
       </c>
-      <c r="G20" s="83"/>
-      <c r="H20" s="83"/>
-      <c r="I20" s="83"/>
-      <c r="J20" s="164">
+      <c r="G20" s="82"/>
+      <c r="H20" s="82"/>
+      <c r="I20" s="82"/>
+      <c r="J20" s="161">
         <v>0.38888888888888801</v>
       </c>
-      <c r="K20" s="53"/>
-      <c r="L20" s="53"/>
-      <c r="M20" s="84">
-        <v>0</v>
-      </c>
-      <c r="N20" s="54">
+      <c r="K20" s="52"/>
+      <c r="L20" s="52"/>
+      <c r="M20" s="83">
+        <v>0</v>
+      </c>
+      <c r="N20" s="53">
         <v>0.27777777777777701</v>
       </c>
-      <c r="O20" s="83"/>
-      <c r="P20" s="83"/>
-      <c r="Q20" s="84">
-        <v>0</v>
-      </c>
-      <c r="R20" s="83"/>
-      <c r="S20" s="157"/>
+      <c r="O20" s="82"/>
+      <c r="P20" s="82"/>
+      <c r="Q20" s="83">
+        <v>0</v>
+      </c>
+      <c r="R20" s="82"/>
+      <c r="S20" s="154"/>
       <c r="T20" s="1">
         <f t="shared" si="0"/>
         <v>0.999999999999998</v>
@@ -5221,38 +5251,38 @@
       <c r="A21" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C21" s="181" t="s">
+      <c r="C21" s="178" t="s">
         <v>21</v>
       </c>
-      <c r="D21" s="79"/>
-      <c r="E21" s="79"/>
-      <c r="F21" s="23">
-        <v>0</v>
-      </c>
-      <c r="G21" s="79"/>
-      <c r="H21" s="79"/>
-      <c r="I21" s="79"/>
-      <c r="J21" s="162">
-        <v>0</v>
-      </c>
-      <c r="K21" s="50"/>
-      <c r="L21" s="50"/>
-      <c r="M21" s="23">
-        <v>0</v>
-      </c>
-      <c r="N21" s="23">
-        <v>0</v>
-      </c>
-      <c r="O21" s="79"/>
-      <c r="P21" s="79"/>
-      <c r="Q21" s="23">
-        <v>0</v>
-      </c>
-      <c r="R21" s="79"/>
-      <c r="S21" s="148"/>
+      <c r="D21" s="78"/>
+      <c r="E21" s="78"/>
+      <c r="F21" s="22">
+        <v>0</v>
+      </c>
+      <c r="G21" s="78"/>
+      <c r="H21" s="78"/>
+      <c r="I21" s="78"/>
+      <c r="J21" s="159">
+        <v>0</v>
+      </c>
+      <c r="K21" s="49"/>
+      <c r="L21" s="49"/>
+      <c r="M21" s="22">
+        <v>0</v>
+      </c>
+      <c r="N21" s="22">
+        <v>0</v>
+      </c>
+      <c r="O21" s="78"/>
+      <c r="P21" s="78"/>
+      <c r="Q21" s="22">
+        <v>0</v>
+      </c>
+      <c r="R21" s="78"/>
+      <c r="S21" s="145"/>
       <c r="T21" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5262,38 +5292,38 @@
       <c r="A22" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C22" s="182" t="s">
+      <c r="C22" s="179" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="85"/>
-      <c r="E22" s="85"/>
-      <c r="F22" s="86">
-        <v>0</v>
-      </c>
-      <c r="G22" s="85"/>
-      <c r="H22" s="85"/>
-      <c r="I22" s="85"/>
-      <c r="J22" s="161">
-        <v>0</v>
-      </c>
-      <c r="K22" s="52"/>
-      <c r="L22" s="52"/>
-      <c r="M22" s="86">
-        <v>0</v>
-      </c>
-      <c r="N22" s="86">
-        <v>0</v>
-      </c>
-      <c r="O22" s="85"/>
-      <c r="P22" s="85"/>
-      <c r="Q22" s="23">
-        <v>0</v>
-      </c>
-      <c r="R22" s="85"/>
-      <c r="S22" s="156"/>
+      <c r="D22" s="84"/>
+      <c r="E22" s="84"/>
+      <c r="F22" s="85">
+        <v>0</v>
+      </c>
+      <c r="G22" s="84"/>
+      <c r="H22" s="84"/>
+      <c r="I22" s="84"/>
+      <c r="J22" s="158">
+        <v>0</v>
+      </c>
+      <c r="K22" s="51"/>
+      <c r="L22" s="51"/>
+      <c r="M22" s="85">
+        <v>0</v>
+      </c>
+      <c r="N22" s="85">
+        <v>0</v>
+      </c>
+      <c r="O22" s="84"/>
+      <c r="P22" s="84"/>
+      <c r="Q22" s="22">
+        <v>0</v>
+      </c>
+      <c r="R22" s="84"/>
+      <c r="S22" s="153"/>
       <c r="T22" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5303,38 +5333,38 @@
       <c r="A23" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="183" t="s">
+      <c r="C23" s="180" t="s">
         <v>28</v>
       </c>
-      <c r="D23" s="79"/>
-      <c r="E23" s="79"/>
-      <c r="F23" s="23">
-        <v>0</v>
-      </c>
-      <c r="G23" s="79"/>
-      <c r="H23" s="79"/>
-      <c r="I23" s="79"/>
-      <c r="J23" s="29">
+      <c r="D23" s="78"/>
+      <c r="E23" s="78"/>
+      <c r="F23" s="22">
+        <v>0</v>
+      </c>
+      <c r="G23" s="78"/>
+      <c r="H23" s="78"/>
+      <c r="I23" s="78"/>
+      <c r="J23" s="28">
         <v>0.28571428571428498</v>
       </c>
-      <c r="K23" s="50"/>
-      <c r="L23" s="50"/>
-      <c r="M23" s="23">
-        <v>0</v>
-      </c>
-      <c r="N23" s="64">
+      <c r="K23" s="49"/>
+      <c r="L23" s="49"/>
+      <c r="M23" s="22">
+        <v>0</v>
+      </c>
+      <c r="N23" s="63">
         <v>0.71428571428571397</v>
       </c>
-      <c r="O23" s="79"/>
-      <c r="P23" s="79"/>
-      <c r="Q23" s="150">
-        <v>0</v>
-      </c>
-      <c r="R23" s="79"/>
-      <c r="S23" s="148"/>
+      <c r="O23" s="78"/>
+      <c r="P23" s="78"/>
+      <c r="Q23" s="147">
+        <v>0</v>
+      </c>
+      <c r="R23" s="78"/>
+      <c r="S23" s="145"/>
       <c r="T23" s="1">
         <f t="shared" si="0"/>
         <v>0.99999999999999889</v>
@@ -5344,38 +5374,38 @@
       <c r="A24" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B24" s="22" t="s">
+      <c r="B24" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C24" s="184" t="s">
+      <c r="C24" s="181" t="s">
         <v>28</v>
       </c>
-      <c r="D24" s="79"/>
-      <c r="E24" s="79"/>
-      <c r="F24" s="23">
-        <v>0</v>
-      </c>
-      <c r="G24" s="79"/>
-      <c r="H24" s="79"/>
-      <c r="I24" s="79"/>
-      <c r="J24" s="23">
-        <v>0</v>
-      </c>
-      <c r="K24" s="50"/>
-      <c r="L24" s="50"/>
-      <c r="M24" s="23">
-        <v>0</v>
-      </c>
-      <c r="N24" s="29">
+      <c r="D24" s="78"/>
+      <c r="E24" s="78"/>
+      <c r="F24" s="22">
+        <v>0</v>
+      </c>
+      <c r="G24" s="78"/>
+      <c r="H24" s="78"/>
+      <c r="I24" s="78"/>
+      <c r="J24" s="22">
+        <v>0</v>
+      </c>
+      <c r="K24" s="49"/>
+      <c r="L24" s="49"/>
+      <c r="M24" s="22">
+        <v>0</v>
+      </c>
+      <c r="N24" s="28">
         <v>0.2</v>
       </c>
-      <c r="O24" s="79"/>
-      <c r="P24" s="79"/>
-      <c r="Q24" s="91">
+      <c r="O24" s="78"/>
+      <c r="P24" s="78"/>
+      <c r="Q24" s="90">
         <v>0.8</v>
       </c>
-      <c r="R24" s="79"/>
-      <c r="S24" s="148"/>
+      <c r="R24" s="78"/>
+      <c r="S24" s="145"/>
       <c r="T24" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -5385,38 +5415,38 @@
       <c r="A25" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B25" s="75" t="s">
+      <c r="B25" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="141" t="s">
+      <c r="C25" s="138" t="s">
         <v>28</v>
       </c>
-      <c r="D25" s="78"/>
-      <c r="E25" s="78"/>
+      <c r="D25" s="77"/>
+      <c r="E25" s="77"/>
       <c r="F25" s="6">
         <v>0</v>
       </c>
-      <c r="G25" s="78"/>
-      <c r="H25" s="78"/>
-      <c r="I25" s="78"/>
+      <c r="G25" s="77"/>
+      <c r="H25" s="77"/>
+      <c r="I25" s="77"/>
       <c r="J25" s="6">
         <v>0</v>
       </c>
-      <c r="K25" s="51"/>
-      <c r="L25" s="51"/>
+      <c r="K25" s="50"/>
+      <c r="L25" s="50"/>
       <c r="M25" s="6">
         <v>0</v>
       </c>
-      <c r="N25" s="57">
+      <c r="N25" s="56">
         <v>0.25</v>
       </c>
-      <c r="O25" s="78"/>
-      <c r="P25" s="78"/>
-      <c r="Q25" s="90">
+      <c r="O25" s="77"/>
+      <c r="P25" s="77"/>
+      <c r="Q25" s="89">
         <v>0.75</v>
       </c>
-      <c r="R25" s="78"/>
-      <c r="S25" s="149"/>
+      <c r="R25" s="77"/>
+      <c r="S25" s="146"/>
       <c r="T25" s="1">
         <f t="shared" si="0"/>
         <v>1</v>

--- a/patterns/results/exp1/4bins-results.xlsx
+++ b/patterns/results/exp1/4bins-results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8248687B-F9E5-7E4C-8D40-3270BF32873D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7B7D647-72DD-6C4C-A9C5-B693C9B45D88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5060" yWindow="1100" windowWidth="30760" windowHeight="16660" activeTab="4" xr2:uid="{9429E1C1-1F54-8A42-9286-E37255B8DAF7}"/>
+    <workbookView xWindow="5060" yWindow="1100" windowWidth="30760" windowHeight="16660" activeTab="1" xr2:uid="{9429E1C1-1F54-8A42-9286-E37255B8DAF7}"/>
   </bookViews>
   <sheets>
     <sheet name="GO" sheetId="1" r:id="rId1"/>
@@ -368,7 +368,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -396,12 +396,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -990,7 +984,6 @@
     <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="6" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1021,20 +1014,20 @@
     <xf numFmtId="2" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="12" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="10" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="11" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="4" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1061,12 +1054,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1090,35 +1083,36 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="9" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="5" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1951,7 +1945,7 @@
       <c r="B5" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="133" t="s">
+      <c r="C5" s="132" t="s">
         <v>26</v>
       </c>
       <c r="D5" s="48"/>
@@ -1969,7 +1963,7 @@
       <c r="N5" s="18">
         <v>0</v>
       </c>
-      <c r="O5" s="147">
+      <c r="O5" s="146">
         <v>0</v>
       </c>
       <c r="P5" s="18">
@@ -1994,7 +1988,7 @@
       <c r="B6" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="170" t="s">
+      <c r="C6" s="169" t="s">
         <v>26</v>
       </c>
       <c r="D6" s="49"/>
@@ -2012,7 +2006,7 @@
       <c r="N6" s="25">
         <v>0</v>
       </c>
-      <c r="O6" s="148">
+      <c r="O6" s="147">
         <v>0.33333333333333298</v>
       </c>
       <c r="P6" s="25">
@@ -2037,7 +2031,7 @@
       <c r="B7" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="171" t="s">
+      <c r="C7" s="170" t="s">
         <v>26</v>
       </c>
       <c r="D7" s="51"/>
@@ -2052,10 +2046,10 @@
       </c>
       <c r="L7" s="51"/>
       <c r="M7" s="51"/>
-      <c r="N7" s="62">
-        <v>0</v>
-      </c>
-      <c r="O7" s="149">
+      <c r="N7" s="190">
+        <v>0</v>
+      </c>
+      <c r="O7" s="148">
         <v>0</v>
       </c>
       <c r="P7" s="25">
@@ -2080,7 +2074,7 @@
       <c r="B8" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="172" t="s">
+      <c r="C8" s="171" t="s">
         <v>27</v>
       </c>
       <c r="D8" s="52"/>
@@ -2101,7 +2095,7 @@
       <c r="O8" s="25">
         <v>0</v>
       </c>
-      <c r="P8" s="147">
+      <c r="P8" s="146">
         <v>1</v>
       </c>
       <c r="Q8" s="31">
@@ -2123,7 +2117,7 @@
       <c r="B9" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="134" t="s">
+      <c r="C9" s="133" t="s">
         <v>27</v>
       </c>
       <c r="D9" s="49"/>
@@ -2144,7 +2138,7 @@
       <c r="O9" s="25">
         <v>0</v>
       </c>
-      <c r="P9" s="148">
+      <c r="P9" s="147">
         <v>0</v>
       </c>
       <c r="Q9" s="25">
@@ -2166,7 +2160,7 @@
       <c r="B10" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="173" t="s">
+      <c r="C10" s="172" t="s">
         <v>27</v>
       </c>
       <c r="D10" s="51"/>
@@ -2187,7 +2181,7 @@
       <c r="O10" s="33">
         <v>0</v>
       </c>
-      <c r="P10" s="149">
+      <c r="P10" s="148">
         <v>0</v>
       </c>
       <c r="Q10" s="25">
@@ -2209,7 +2203,7 @@
       <c r="B11" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="174" t="s">
+      <c r="C11" s="173" t="s">
         <v>28</v>
       </c>
       <c r="D11" s="52"/>
@@ -2233,7 +2227,7 @@
       <c r="P11" s="25">
         <v>0</v>
       </c>
-      <c r="Q11" s="147">
+      <c r="Q11" s="146">
         <v>0</v>
       </c>
       <c r="R11" s="52"/>
@@ -2252,7 +2246,7 @@
       <c r="B12" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="135" t="s">
+      <c r="C12" s="134" t="s">
         <v>28</v>
       </c>
       <c r="D12" s="49"/>
@@ -2276,7 +2270,7 @@
       <c r="P12" s="25">
         <v>0</v>
       </c>
-      <c r="Q12" s="148">
+      <c r="Q12" s="147">
         <v>0</v>
       </c>
       <c r="R12" s="49"/>
@@ -2295,7 +2289,7 @@
       <c r="B13" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="175" t="s">
+      <c r="C13" s="174" t="s">
         <v>28</v>
       </c>
       <c r="D13" s="51"/>
@@ -2319,7 +2313,7 @@
       <c r="P13" s="33">
         <v>0</v>
       </c>
-      <c r="Q13" s="89">
+      <c r="Q13" s="88">
         <v>0.81818181818181801</v>
       </c>
       <c r="R13" s="51"/>
@@ -2338,7 +2332,7 @@
       <c r="B14" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="176" t="s">
+      <c r="C14" s="175" t="s">
         <v>30</v>
       </c>
       <c r="D14" s="52"/>
@@ -2366,7 +2360,7 @@
         <v>0</v>
       </c>
       <c r="R14" s="52"/>
-      <c r="S14" s="147">
+      <c r="S14" s="146">
         <v>0</v>
       </c>
       <c r="T14" s="1">
@@ -2381,7 +2375,7 @@
       <c r="B15" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="94" t="s">
+      <c r="C15" s="93" t="s">
         <v>30</v>
       </c>
       <c r="D15" s="49"/>
@@ -2409,7 +2403,7 @@
         <v>0</v>
       </c>
       <c r="R15" s="49"/>
-      <c r="S15" s="90">
+      <c r="S15" s="89">
         <v>0.71428571428571397</v>
       </c>
       <c r="T15" s="1">
@@ -2424,7 +2418,7 @@
       <c r="B16" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="168" t="s">
+      <c r="C16" s="167" t="s">
         <v>30</v>
       </c>
       <c r="D16" s="50"/>
@@ -2452,7 +2446,7 @@
         <v>0</v>
       </c>
       <c r="R16" s="50"/>
-      <c r="S16" s="149">
+      <c r="S16" s="148">
         <v>0</v>
       </c>
       <c r="T16" s="1">
@@ -2467,7 +2461,7 @@
       <c r="B17" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="C17" s="97" t="s">
+      <c r="C17" s="96" t="s">
         <v>26</v>
       </c>
       <c r="D17" s="49"/>
@@ -2485,7 +2479,7 @@
       <c r="N17" s="25">
         <v>0</v>
       </c>
-      <c r="O17" s="147">
+      <c r="O17" s="146">
         <v>0</v>
       </c>
       <c r="P17" s="25">
@@ -2510,7 +2504,7 @@
       <c r="B18" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="177" t="s">
+      <c r="C18" s="176" t="s">
         <v>26</v>
       </c>
       <c r="D18" s="49"/>
@@ -2520,7 +2514,7 @@
       <c r="H18" s="49"/>
       <c r="I18" s="49"/>
       <c r="J18" s="49"/>
-      <c r="K18" s="63">
+      <c r="K18" s="62">
         <v>0.5</v>
       </c>
       <c r="L18" s="49"/>
@@ -2528,7 +2522,7 @@
       <c r="N18" s="25">
         <v>0</v>
       </c>
-      <c r="O18" s="90">
+      <c r="O18" s="89">
         <v>0.5</v>
       </c>
       <c r="P18" s="25">
@@ -2553,7 +2547,7 @@
       <c r="B19" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="96" t="s">
+      <c r="C19" s="95" t="s">
         <v>26</v>
       </c>
       <c r="D19" s="51"/>
@@ -2568,10 +2562,10 @@
       </c>
       <c r="L19" s="51"/>
       <c r="M19" s="51"/>
-      <c r="N19" s="62">
-        <v>0</v>
-      </c>
-      <c r="O19" s="149">
+      <c r="N19" s="190">
+        <v>0</v>
+      </c>
+      <c r="O19" s="148">
         <v>0</v>
       </c>
       <c r="P19" s="25">
@@ -2596,7 +2590,7 @@
       <c r="B20" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C20" s="137" t="s">
+      <c r="C20" s="136" t="s">
         <v>27</v>
       </c>
       <c r="D20" s="52"/>
@@ -2617,7 +2611,7 @@
       <c r="O20" s="25">
         <v>0</v>
       </c>
-      <c r="P20" s="147">
+      <c r="P20" s="146">
         <v>1</v>
       </c>
       <c r="Q20" s="31">
@@ -2639,7 +2633,7 @@
       <c r="B21" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="178" t="s">
+      <c r="C21" s="177" t="s">
         <v>27</v>
       </c>
       <c r="D21" s="49"/>
@@ -2660,7 +2654,7 @@
       <c r="O21" s="25">
         <v>0</v>
       </c>
-      <c r="P21" s="148">
+      <c r="P21" s="147">
         <v>0</v>
       </c>
       <c r="Q21" s="25">
@@ -2682,7 +2676,7 @@
       <c r="B22" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="179" t="s">
+      <c r="C22" s="178" t="s">
         <v>27</v>
       </c>
       <c r="D22" s="51"/>
@@ -2703,7 +2697,7 @@
       <c r="O22" s="33">
         <v>0</v>
       </c>
-      <c r="P22" s="149">
+      <c r="P22" s="148">
         <v>0</v>
       </c>
       <c r="Q22" s="33">
@@ -2725,7 +2719,7 @@
       <c r="B23" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="180" t="s">
+      <c r="C23" s="179" t="s">
         <v>30</v>
       </c>
       <c r="D23" s="52"/>
@@ -2753,7 +2747,7 @@
         <v>0</v>
       </c>
       <c r="R23" s="52"/>
-      <c r="S23" s="147">
+      <c r="S23" s="146">
         <v>0</v>
       </c>
       <c r="T23" s="1">
@@ -2768,7 +2762,7 @@
       <c r="B24" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="181" t="s">
+      <c r="C24" s="180" t="s">
         <v>30</v>
       </c>
       <c r="D24" s="49"/>
@@ -2796,7 +2790,7 @@
         <v>0</v>
       </c>
       <c r="R24" s="49"/>
-      <c r="S24" s="90">
+      <c r="S24" s="89">
         <v>0.75</v>
       </c>
       <c r="T24" s="1">
@@ -2811,7 +2805,7 @@
       <c r="B25" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="138" t="s">
+      <c r="C25" s="137" t="s">
         <v>30</v>
       </c>
       <c r="D25" s="50"/>
@@ -2839,7 +2833,7 @@
         <v>1</v>
       </c>
       <c r="R25" s="50"/>
-      <c r="S25" s="149">
+      <c r="S25" s="148">
         <v>0</v>
       </c>
       <c r="T25" s="1">
@@ -2986,13 +2980,13 @@
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="64"/>
+      <c r="C2" s="63"/>
       <c r="D2" s="48"/>
       <c r="E2" s="48"/>
       <c r="F2" s="48"/>
@@ -3002,11 +2996,11 @@
       <c r="J2" s="48"/>
       <c r="K2" s="48"/>
       <c r="L2" s="48"/>
-      <c r="M2" s="76"/>
+      <c r="M2" s="75"/>
       <c r="N2" s="60">
         <v>5.5555555555555497E-2</v>
       </c>
-      <c r="O2" s="76"/>
+      <c r="O2" s="75"/>
       <c r="P2" s="60">
         <v>8.7301587301587297E-2</v>
       </c>
@@ -3025,13 +3019,13 @@
       </c>
     </row>
     <row r="3" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="70" t="s">
+      <c r="A3" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="71" t="s">
+      <c r="B3" s="70" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="65"/>
+      <c r="C3" s="64"/>
       <c r="D3" s="49"/>
       <c r="E3" s="49"/>
       <c r="F3" s="49"/>
@@ -3041,11 +3035,11 @@
       <c r="J3" s="49"/>
       <c r="K3" s="49"/>
       <c r="L3" s="49"/>
-      <c r="M3" s="78"/>
+      <c r="M3" s="77"/>
       <c r="N3" s="22">
         <v>0</v>
       </c>
-      <c r="O3" s="78"/>
+      <c r="O3" s="77"/>
       <c r="P3" s="22">
         <v>0</v>
       </c>
@@ -3064,13 +3058,13 @@
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A4" s="67" t="s">
+      <c r="A4" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="68" t="s">
+      <c r="B4" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="93" t="s">
+      <c r="C4" s="92" t="s">
         <v>25</v>
       </c>
       <c r="D4" s="48"/>
@@ -3082,11 +3076,11 @@
       <c r="J4" s="48"/>
       <c r="K4" s="48"/>
       <c r="L4" s="48"/>
-      <c r="M4" s="76"/>
-      <c r="N4" s="91">
+      <c r="M4" s="75"/>
+      <c r="N4" s="90">
         <v>0.5</v>
       </c>
-      <c r="O4" s="76"/>
+      <c r="O4" s="75"/>
       <c r="P4" s="3">
         <v>0</v>
       </c>
@@ -3105,13 +3099,13 @@
       </c>
     </row>
     <row r="5" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="72" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="162" t="s">
+      <c r="C5" s="161" t="s">
         <v>25</v>
       </c>
       <c r="D5" s="51"/>
@@ -3123,21 +3117,21 @@
       <c r="J5" s="51"/>
       <c r="K5" s="51"/>
       <c r="L5" s="51"/>
-      <c r="M5" s="84"/>
-      <c r="N5" s="149">
-        <v>0</v>
-      </c>
-      <c r="O5" s="84"/>
+      <c r="M5" s="83"/>
+      <c r="N5" s="148">
+        <v>0</v>
+      </c>
+      <c r="O5" s="83"/>
       <c r="P5" s="22">
         <v>0</v>
       </c>
-      <c r="Q5" s="85">
-        <v>0</v>
-      </c>
-      <c r="R5" s="85">
-        <v>0</v>
-      </c>
-      <c r="S5" s="86">
+      <c r="Q5" s="84">
+        <v>0</v>
+      </c>
+      <c r="R5" s="84">
+        <v>0</v>
+      </c>
+      <c r="S5" s="85">
         <v>1</v>
       </c>
       <c r="T5" s="1">
@@ -3146,13 +3140,13 @@
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A6" s="73" t="s">
+      <c r="A6" s="72" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="164" t="s">
+      <c r="C6" s="163" t="s">
         <v>27</v>
       </c>
       <c r="D6" s="52"/>
@@ -3164,21 +3158,21 @@
       <c r="J6" s="52"/>
       <c r="K6" s="52"/>
       <c r="L6" s="52"/>
-      <c r="M6" s="82"/>
+      <c r="M6" s="81"/>
       <c r="N6" s="22">
         <v>0</v>
       </c>
-      <c r="O6" s="82"/>
-      <c r="P6" s="91">
+      <c r="O6" s="81"/>
+      <c r="P6" s="90">
         <v>0.64705882352941102</v>
       </c>
       <c r="Q6" s="53">
         <v>0.35294117647058798</v>
       </c>
-      <c r="R6" s="83">
-        <v>0</v>
-      </c>
-      <c r="S6" s="87">
+      <c r="R6" s="82">
+        <v>0</v>
+      </c>
+      <c r="S6" s="86">
         <v>0</v>
       </c>
       <c r="T6" s="1">
@@ -3187,13 +3181,13 @@
       </c>
     </row>
     <row r="7" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="73" t="s">
+      <c r="A7" s="72" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="165" t="s">
+      <c r="C7" s="164" t="s">
         <v>27</v>
       </c>
       <c r="D7" s="51"/>
@@ -3205,21 +3199,21 @@
       <c r="J7" s="51"/>
       <c r="K7" s="51"/>
       <c r="L7" s="51"/>
-      <c r="M7" s="84"/>
-      <c r="N7" s="85">
-        <v>0</v>
-      </c>
-      <c r="O7" s="84"/>
-      <c r="P7" s="149">
+      <c r="M7" s="83"/>
+      <c r="N7" s="84">
+        <v>0</v>
+      </c>
+      <c r="O7" s="83"/>
+      <c r="P7" s="148">
         <v>0</v>
       </c>
       <c r="Q7" s="22">
         <v>0</v>
       </c>
-      <c r="R7" s="85">
-        <v>0</v>
-      </c>
-      <c r="S7" s="86">
+      <c r="R7" s="84">
+        <v>0</v>
+      </c>
+      <c r="S7" s="85">
         <v>1</v>
       </c>
       <c r="T7" s="1">
@@ -3228,13 +3222,13 @@
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A8" s="73" t="s">
+      <c r="A8" s="72" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="163" t="s">
+      <c r="C8" s="162" t="s">
         <v>28</v>
       </c>
       <c r="D8" s="52"/>
@@ -3246,21 +3240,21 @@
       <c r="J8" s="52"/>
       <c r="K8" s="52"/>
       <c r="L8" s="52"/>
-      <c r="M8" s="82"/>
-      <c r="N8" s="83">
-        <v>0</v>
-      </c>
-      <c r="O8" s="82"/>
+      <c r="M8" s="81"/>
+      <c r="N8" s="82">
+        <v>0</v>
+      </c>
+      <c r="O8" s="81"/>
       <c r="P8" s="22">
         <v>0</v>
       </c>
-      <c r="Q8" s="91">
+      <c r="Q8" s="90">
         <v>1</v>
       </c>
-      <c r="R8" s="83">
-        <v>0</v>
-      </c>
-      <c r="S8" s="87">
+      <c r="R8" s="82">
+        <v>0</v>
+      </c>
+      <c r="S8" s="86">
         <v>0</v>
       </c>
       <c r="T8" s="1">
@@ -3269,13 +3263,13 @@
       </c>
     </row>
     <row r="9" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="73" t="s">
+      <c r="A9" s="72" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="166" t="s">
+      <c r="C9" s="165" t="s">
         <v>28</v>
       </c>
       <c r="D9" s="51"/>
@@ -3287,21 +3281,21 @@
       <c r="J9" s="51"/>
       <c r="K9" s="51"/>
       <c r="L9" s="51"/>
-      <c r="M9" s="84"/>
-      <c r="N9" s="85">
-        <v>0</v>
-      </c>
-      <c r="O9" s="84"/>
-      <c r="P9" s="85">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="149">
+      <c r="M9" s="83"/>
+      <c r="N9" s="84">
+        <v>0</v>
+      </c>
+      <c r="O9" s="83"/>
+      <c r="P9" s="84">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="148">
         <v>0</v>
       </c>
       <c r="R9" s="22">
         <v>0</v>
       </c>
-      <c r="S9" s="86">
+      <c r="S9" s="85">
         <v>1</v>
       </c>
       <c r="T9" s="1">
@@ -3310,13 +3304,13 @@
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A10" s="73" t="s">
+      <c r="A10" s="72" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="167" t="s">
+      <c r="C10" s="166" t="s">
         <v>29</v>
       </c>
       <c r="D10" s="52"/>
@@ -3328,21 +3322,21 @@
       <c r="J10" s="52"/>
       <c r="K10" s="52"/>
       <c r="L10" s="52"/>
-      <c r="M10" s="82"/>
-      <c r="N10" s="83">
+      <c r="M10" s="81"/>
+      <c r="N10" s="82">
         <v>8.3333333333333301E-2</v>
       </c>
-      <c r="O10" s="82"/>
-      <c r="P10" s="83">
+      <c r="O10" s="81"/>
+      <c r="P10" s="82">
         <v>0</v>
       </c>
       <c r="Q10" s="22">
         <v>0.33333333333333298</v>
       </c>
-      <c r="R10" s="91">
+      <c r="R10" s="90">
         <v>0.58333333333333304</v>
       </c>
-      <c r="S10" s="87">
+      <c r="S10" s="86">
         <v>0</v>
       </c>
       <c r="T10" s="1">
@@ -3351,39 +3345,39 @@
       </c>
     </row>
     <row r="11" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="73" t="s">
+      <c r="A11" s="72" t="s">
         <v>7</v>
       </c>
       <c r="B11" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="168" t="s">
+      <c r="C11" s="167" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="84"/>
-      <c r="E11" s="84"/>
-      <c r="F11" s="84"/>
-      <c r="G11" s="84"/>
-      <c r="H11" s="84"/>
-      <c r="I11" s="84"/>
-      <c r="J11" s="84"/>
-      <c r="K11" s="84"/>
-      <c r="L11" s="84"/>
-      <c r="M11" s="84"/>
-      <c r="N11" s="85">
-        <v>0</v>
-      </c>
-      <c r="O11" s="84"/>
-      <c r="P11" s="85">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="85">
-        <v>0</v>
-      </c>
-      <c r="R11" s="149">
-        <v>0</v>
-      </c>
-      <c r="S11" s="79">
+      <c r="D11" s="83"/>
+      <c r="E11" s="83"/>
+      <c r="F11" s="83"/>
+      <c r="G11" s="83"/>
+      <c r="H11" s="83"/>
+      <c r="I11" s="83"/>
+      <c r="J11" s="83"/>
+      <c r="K11" s="83"/>
+      <c r="L11" s="83"/>
+      <c r="M11" s="83"/>
+      <c r="N11" s="84">
+        <v>0</v>
+      </c>
+      <c r="O11" s="83"/>
+      <c r="P11" s="84">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="84">
+        <v>0</v>
+      </c>
+      <c r="R11" s="148">
+        <v>0</v>
+      </c>
+      <c r="S11" s="78">
         <v>1</v>
       </c>
       <c r="T11" s="1">
@@ -3392,13 +3386,13 @@
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A12" s="73" t="s">
+      <c r="A12" s="72" t="s">
         <v>7</v>
       </c>
       <c r="B12" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="169" t="s">
+      <c r="C12" s="168" t="s">
         <v>30</v>
       </c>
       <c r="D12" s="52"/>
@@ -3410,21 +3404,21 @@
       <c r="J12" s="52"/>
       <c r="K12" s="52"/>
       <c r="L12" s="52"/>
-      <c r="M12" s="82"/>
-      <c r="N12" s="83">
+      <c r="M12" s="81"/>
+      <c r="N12" s="82">
         <v>8.1967213114753995E-2</v>
       </c>
-      <c r="O12" s="82"/>
-      <c r="P12" s="83">
+      <c r="O12" s="81"/>
+      <c r="P12" s="82">
         <v>0.18032786885245899</v>
       </c>
-      <c r="Q12" s="83">
+      <c r="Q12" s="82">
         <v>0.73770491803278604</v>
       </c>
       <c r="R12" s="22">
         <v>0</v>
       </c>
-      <c r="S12" s="147">
+      <c r="S12" s="146">
         <v>0</v>
       </c>
       <c r="T12" s="1">
@@ -3436,26 +3430,26 @@
       <c r="A13" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="74" t="s">
+      <c r="B13" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="95" t="s">
+      <c r="C13" s="94" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="77"/>
-      <c r="E13" s="77"/>
-      <c r="F13" s="77"/>
-      <c r="G13" s="77"/>
-      <c r="H13" s="77"/>
-      <c r="I13" s="77"/>
-      <c r="J13" s="77"/>
-      <c r="K13" s="77"/>
-      <c r="L13" s="77"/>
-      <c r="M13" s="77"/>
+      <c r="D13" s="76"/>
+      <c r="E13" s="76"/>
+      <c r="F13" s="76"/>
+      <c r="G13" s="76"/>
+      <c r="H13" s="76"/>
+      <c r="I13" s="76"/>
+      <c r="J13" s="76"/>
+      <c r="K13" s="76"/>
+      <c r="L13" s="76"/>
+      <c r="M13" s="76"/>
       <c r="N13" s="6">
         <v>0</v>
       </c>
-      <c r="O13" s="77"/>
+      <c r="O13" s="76"/>
       <c r="P13" s="6">
         <v>0</v>
       </c>
@@ -3465,7 +3459,7 @@
       <c r="R13" s="6">
         <v>0</v>
       </c>
-      <c r="S13" s="89">
+      <c r="S13" s="88">
         <v>1</v>
       </c>
       <c r="T13" s="1">
@@ -3477,36 +3471,36 @@
       <c r="A14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="75" t="s">
+      <c r="B14" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="97" t="s">
+      <c r="C14" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="76"/>
-      <c r="E14" s="76"/>
-      <c r="F14" s="76"/>
-      <c r="G14" s="76"/>
-      <c r="H14" s="76"/>
-      <c r="I14" s="76"/>
-      <c r="J14" s="76"/>
-      <c r="K14" s="76"/>
-      <c r="L14" s="76"/>
-      <c r="M14" s="76"/>
+      <c r="D14" s="75"/>
+      <c r="E14" s="75"/>
+      <c r="F14" s="75"/>
+      <c r="G14" s="75"/>
+      <c r="H14" s="75"/>
+      <c r="I14" s="75"/>
+      <c r="J14" s="75"/>
+      <c r="K14" s="75"/>
+      <c r="L14" s="75"/>
+      <c r="M14" s="75"/>
       <c r="N14" s="57">
         <v>3.0769230769230702E-2</v>
       </c>
-      <c r="O14" s="76"/>
+      <c r="O14" s="75"/>
       <c r="P14" s="38">
         <v>0</v>
       </c>
-      <c r="Q14" s="92">
+      <c r="Q14" s="91">
         <v>0.84615384615384603</v>
       </c>
-      <c r="R14" s="80">
+      <c r="R14" s="79">
         <v>0.123076923076923</v>
       </c>
-      <c r="S14" s="88">
+      <c r="S14" s="87">
         <v>0</v>
       </c>
       <c r="T14" s="1">
@@ -3518,36 +3512,36 @@
       <c r="A15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="74" t="s">
+      <c r="B15" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="96" t="s">
+      <c r="C15" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="77"/>
-      <c r="E15" s="77"/>
-      <c r="F15" s="77"/>
-      <c r="G15" s="77"/>
-      <c r="H15" s="77"/>
-      <c r="I15" s="77"/>
-      <c r="J15" s="77"/>
-      <c r="K15" s="77"/>
-      <c r="L15" s="77"/>
-      <c r="M15" s="77"/>
-      <c r="N15" s="72">
-        <v>0</v>
-      </c>
-      <c r="O15" s="77"/>
-      <c r="P15" s="72">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="150">
-        <v>0</v>
-      </c>
-      <c r="R15" s="72">
-        <v>0</v>
-      </c>
-      <c r="S15" s="81">
+      <c r="D15" s="76"/>
+      <c r="E15" s="76"/>
+      <c r="F15" s="76"/>
+      <c r="G15" s="76"/>
+      <c r="H15" s="76"/>
+      <c r="I15" s="76"/>
+      <c r="J15" s="76"/>
+      <c r="K15" s="76"/>
+      <c r="L15" s="76"/>
+      <c r="M15" s="76"/>
+      <c r="N15" s="71">
+        <v>0</v>
+      </c>
+      <c r="O15" s="76"/>
+      <c r="P15" s="71">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="149">
+        <v>0</v>
+      </c>
+      <c r="R15" s="71">
+        <v>0</v>
+      </c>
+      <c r="S15" s="80">
         <v>1</v>
       </c>
       <c r="T15" s="1">
@@ -3671,37 +3665,37 @@
       </c>
     </row>
     <row r="2" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="98" t="s">
+      <c r="A2" s="97" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="99" t="s">
+      <c r="B2" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="102"/>
+      <c r="C2" s="101"/>
       <c r="D2" s="48"/>
       <c r="E2" s="48"/>
       <c r="F2" s="48"/>
       <c r="G2" s="48"/>
       <c r="H2" s="48"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
-      <c r="L2" s="76"/>
-      <c r="M2" s="107">
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
+      <c r="K2" s="75"/>
+      <c r="L2" s="75"/>
+      <c r="M2" s="106">
         <v>1.0869565217391301E-2</v>
       </c>
       <c r="N2" s="13"/>
       <c r="O2" s="13"/>
-      <c r="P2" s="107">
+      <c r="P2" s="106">
         <v>0.26086956521739102</v>
       </c>
-      <c r="Q2" s="107">
+      <c r="Q2" s="106">
         <v>0.70652173913043403</v>
       </c>
-      <c r="R2" s="107">
+      <c r="R2" s="106">
         <v>1.0869565217391301E-2</v>
       </c>
-      <c r="S2" s="108">
+      <c r="S2" s="107">
         <v>1.0869565217391301E-2</v>
       </c>
       <c r="T2" s="1">
@@ -3710,39 +3704,39 @@
       </c>
     </row>
     <row r="3" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="100" t="s">
+      <c r="A3" s="99" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="103" t="s">
+      <c r="C3" s="102" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="113"/>
-      <c r="E3" s="114"/>
-      <c r="F3" s="114"/>
-      <c r="G3" s="114"/>
-      <c r="H3" s="114"/>
-      <c r="I3" s="115"/>
-      <c r="J3" s="115"/>
-      <c r="K3" s="115"/>
-      <c r="L3" s="115"/>
-      <c r="M3" s="116">
-        <v>0</v>
-      </c>
-      <c r="N3" s="117"/>
-      <c r="O3" s="117"/>
-      <c r="P3" s="127">
+      <c r="D3" s="112"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="113"/>
+      <c r="G3" s="113"/>
+      <c r="H3" s="113"/>
+      <c r="I3" s="114"/>
+      <c r="J3" s="114"/>
+      <c r="K3" s="114"/>
+      <c r="L3" s="114"/>
+      <c r="M3" s="115">
+        <v>0</v>
+      </c>
+      <c r="N3" s="116"/>
+      <c r="O3" s="116"/>
+      <c r="P3" s="126">
         <v>0.79310344827586199</v>
       </c>
       <c r="Q3" s="57">
         <v>0.20689655172413701</v>
       </c>
-      <c r="R3" s="116">
-        <v>0</v>
-      </c>
-      <c r="S3" s="118">
+      <c r="R3" s="115">
+        <v>0</v>
+      </c>
+      <c r="S3" s="117">
         <v>0</v>
       </c>
       <c r="T3" s="1">
@@ -3751,24 +3745,24 @@
       </c>
     </row>
     <row r="4" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="101" t="s">
+      <c r="A4" s="100" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="104" t="s">
+      <c r="C4" s="103" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="119"/>
+      <c r="D4" s="118"/>
       <c r="E4" s="50"/>
       <c r="F4" s="50"/>
       <c r="G4" s="50"/>
       <c r="H4" s="50"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
-      <c r="K4" s="77"/>
-      <c r="L4" s="77"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
+      <c r="K4" s="76"/>
+      <c r="L4" s="76"/>
       <c r="M4" s="56">
         <v>2.8571428571428501E-2</v>
       </c>
@@ -3777,7 +3771,7 @@
       <c r="P4" s="6">
         <v>0</v>
       </c>
-      <c r="Q4" s="127">
+      <c r="Q4" s="126">
         <v>0.97142857142857097</v>
       </c>
       <c r="R4" s="6">
@@ -3792,39 +3786,39 @@
       </c>
     </row>
     <row r="5" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="100" t="s">
+      <c r="A5" s="99" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="105" t="s">
+      <c r="C5" s="104" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="113"/>
-      <c r="E5" s="114"/>
-      <c r="F5" s="114"/>
-      <c r="G5" s="114"/>
-      <c r="H5" s="114"/>
-      <c r="I5" s="115"/>
-      <c r="J5" s="115"/>
-      <c r="K5" s="115"/>
-      <c r="L5" s="115"/>
-      <c r="M5" s="116">
-        <v>0</v>
-      </c>
-      <c r="N5" s="117"/>
-      <c r="O5" s="117"/>
-      <c r="P5" s="128">
+      <c r="D5" s="112"/>
+      <c r="E5" s="113"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="113"/>
+      <c r="I5" s="114"/>
+      <c r="J5" s="114"/>
+      <c r="K5" s="114"/>
+      <c r="L5" s="114"/>
+      <c r="M5" s="115">
+        <v>0</v>
+      </c>
+      <c r="N5" s="116"/>
+      <c r="O5" s="116"/>
+      <c r="P5" s="127">
         <v>0.11111111111111099</v>
       </c>
-      <c r="Q5" s="80">
+      <c r="Q5" s="79">
         <v>0.88888888888888795</v>
       </c>
-      <c r="R5" s="116">
-        <v>0</v>
-      </c>
-      <c r="S5" s="118">
+      <c r="R5" s="115">
+        <v>0</v>
+      </c>
+      <c r="S5" s="117">
         <v>0</v>
       </c>
       <c r="T5" s="1">
@@ -3839,33 +3833,33 @@
       <c r="B6" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="106" t="s">
+      <c r="C6" s="105" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="120"/>
-      <c r="E6" s="121"/>
-      <c r="F6" s="121"/>
-      <c r="G6" s="121"/>
-      <c r="H6" s="121"/>
-      <c r="I6" s="122"/>
-      <c r="J6" s="122"/>
-      <c r="K6" s="122"/>
-      <c r="L6" s="122"/>
-      <c r="M6" s="123">
+      <c r="D6" s="119"/>
+      <c r="E6" s="120"/>
+      <c r="F6" s="120"/>
+      <c r="G6" s="120"/>
+      <c r="H6" s="120"/>
+      <c r="I6" s="121"/>
+      <c r="J6" s="121"/>
+      <c r="K6" s="121"/>
+      <c r="L6" s="121"/>
+      <c r="M6" s="122">
         <v>0.05</v>
       </c>
-      <c r="N6" s="124"/>
-      <c r="O6" s="124"/>
+      <c r="N6" s="123"/>
+      <c r="O6" s="123"/>
       <c r="P6" s="6">
         <v>0</v>
       </c>
-      <c r="Q6" s="127">
+      <c r="Q6" s="126">
         <v>0.95</v>
       </c>
-      <c r="R6" s="125">
-        <v>0</v>
-      </c>
-      <c r="S6" s="126">
+      <c r="R6" s="124">
+        <v>0</v>
+      </c>
+      <c r="S6" s="125">
         <v>0</v>
       </c>
       <c r="T6" s="1">
@@ -3972,41 +3966,41 @@
       </c>
     </row>
     <row r="2" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="129" t="s">
+      <c r="A2" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="130" t="s">
+      <c r="B2" s="129" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="64"/>
-      <c r="D2" s="142">
+      <c r="C2" s="63"/>
+      <c r="D2" s="141">
         <v>0.40625</v>
       </c>
       <c r="E2" s="48"/>
       <c r="F2" s="48"/>
       <c r="G2" s="48"/>
       <c r="H2" s="48"/>
-      <c r="I2" s="142">
+      <c r="I2" s="141">
         <v>6.25E-2</v>
       </c>
       <c r="J2" s="48"/>
-      <c r="K2" s="142">
+      <c r="K2" s="141">
         <v>3.125E-2</v>
       </c>
-      <c r="L2" s="142">
+      <c r="L2" s="141">
         <v>0.1875</v>
       </c>
-      <c r="M2" s="142">
+      <c r="M2" s="141">
         <v>3.125E-2</v>
       </c>
       <c r="N2" s="48"/>
-      <c r="O2" s="141">
+      <c r="O2" s="140">
         <v>6.25E-2</v>
       </c>
       <c r="P2" s="48"/>
       <c r="Q2" s="48"/>
       <c r="R2" s="48"/>
-      <c r="S2" s="182">
+      <c r="S2" s="181">
         <v>0.21875</v>
       </c>
       <c r="T2" s="1">
@@ -4021,37 +4015,37 @@
       <c r="B3" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="133" t="s">
+      <c r="C3" s="132" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="131">
+      <c r="D3" s="130">
         <v>1</v>
       </c>
-      <c r="E3" s="115"/>
-      <c r="F3" s="115"/>
-      <c r="G3" s="115"/>
-      <c r="H3" s="115"/>
-      <c r="I3" s="69">
-        <v>0</v>
-      </c>
-      <c r="J3" s="115"/>
-      <c r="K3" s="187">
-        <v>0</v>
-      </c>
-      <c r="L3" s="187">
-        <v>0</v>
-      </c>
-      <c r="M3" s="187">
-        <v>0</v>
-      </c>
-      <c r="N3" s="114"/>
-      <c r="O3" s="116">
-        <v>0</v>
-      </c>
-      <c r="P3" s="115"/>
-      <c r="Q3" s="115"/>
-      <c r="R3" s="115"/>
-      <c r="S3" s="118">
+      <c r="E3" s="114"/>
+      <c r="F3" s="114"/>
+      <c r="G3" s="114"/>
+      <c r="H3" s="114"/>
+      <c r="I3" s="68">
+        <v>0</v>
+      </c>
+      <c r="J3" s="114"/>
+      <c r="K3" s="186">
+        <v>0</v>
+      </c>
+      <c r="L3" s="186">
+        <v>0</v>
+      </c>
+      <c r="M3" s="186">
+        <v>0</v>
+      </c>
+      <c r="N3" s="113"/>
+      <c r="O3" s="115">
+        <v>0</v>
+      </c>
+      <c r="P3" s="114"/>
+      <c r="Q3" s="114"/>
+      <c r="R3" s="114"/>
+      <c r="S3" s="117">
         <v>0</v>
       </c>
       <c r="T3" s="1">
@@ -4066,37 +4060,37 @@
       <c r="B4" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="134" t="s">
+      <c r="C4" s="133" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="152">
-        <v>0</v>
-      </c>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="131">
+      <c r="D4" s="151">
+        <v>0</v>
+      </c>
+      <c r="E4" s="109"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="130">
         <v>0.22222222222222199</v>
       </c>
-      <c r="J4" s="110"/>
-      <c r="K4" s="151">
-        <v>0</v>
-      </c>
-      <c r="L4" s="112">
+      <c r="J4" s="109"/>
+      <c r="K4" s="150">
+        <v>0</v>
+      </c>
+      <c r="L4" s="111">
         <v>0.66666666666666596</v>
       </c>
-      <c r="M4" s="112">
+      <c r="M4" s="111">
         <v>0.11111111111111099</v>
       </c>
-      <c r="N4" s="109"/>
-      <c r="O4" s="111">
-        <v>0</v>
-      </c>
-      <c r="P4" s="110"/>
-      <c r="Q4" s="110"/>
-      <c r="R4" s="110"/>
-      <c r="S4" s="188">
+      <c r="N4" s="108"/>
+      <c r="O4" s="110">
+        <v>0</v>
+      </c>
+      <c r="P4" s="109"/>
+      <c r="Q4" s="109"/>
+      <c r="R4" s="109"/>
+      <c r="S4" s="187">
         <v>0</v>
       </c>
       <c r="T4" s="1">
@@ -4111,37 +4105,37 @@
       <c r="B5" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="135" t="s">
+      <c r="C5" s="134" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="183">
-        <v>0</v>
-      </c>
-      <c r="E5" s="110"/>
-      <c r="F5" s="110"/>
-      <c r="G5" s="110"/>
-      <c r="H5" s="110"/>
-      <c r="I5" s="152">
-        <v>0</v>
-      </c>
-      <c r="J5" s="110"/>
-      <c r="K5" s="131">
+      <c r="D5" s="182">
+        <v>0</v>
+      </c>
+      <c r="E5" s="109"/>
+      <c r="F5" s="109"/>
+      <c r="G5" s="109"/>
+      <c r="H5" s="109"/>
+      <c r="I5" s="151">
+        <v>0</v>
+      </c>
+      <c r="J5" s="109"/>
+      <c r="K5" s="130">
         <v>0.1</v>
       </c>
-      <c r="L5" s="151">
-        <v>0</v>
-      </c>
-      <c r="M5" s="183">
-        <v>0</v>
-      </c>
-      <c r="N5" s="109"/>
-      <c r="O5" s="112">
+      <c r="L5" s="150">
+        <v>0</v>
+      </c>
+      <c r="M5" s="182">
+        <v>0</v>
+      </c>
+      <c r="N5" s="108"/>
+      <c r="O5" s="111">
         <v>0.2</v>
       </c>
-      <c r="P5" s="110"/>
-      <c r="Q5" s="110"/>
-      <c r="R5" s="110"/>
-      <c r="S5" s="189">
+      <c r="P5" s="109"/>
+      <c r="Q5" s="109"/>
+      <c r="R5" s="109"/>
+      <c r="S5" s="188">
         <v>0.7</v>
       </c>
       <c r="T5" s="1">
@@ -4156,37 +4150,37 @@
       <c r="B6" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="94" t="s">
+      <c r="C6" s="93" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="183">
-        <v>0</v>
-      </c>
-      <c r="E6" s="110"/>
-      <c r="F6" s="110"/>
-      <c r="G6" s="110"/>
-      <c r="H6" s="110"/>
-      <c r="I6" s="112">
+      <c r="D6" s="182">
+        <v>0</v>
+      </c>
+      <c r="E6" s="109"/>
+      <c r="F6" s="109"/>
+      <c r="G6" s="109"/>
+      <c r="H6" s="109"/>
+      <c r="I6" s="111">
         <v>0.125</v>
       </c>
-      <c r="J6" s="110"/>
-      <c r="K6" s="152">
-        <v>0</v>
-      </c>
-      <c r="L6" s="131">
+      <c r="J6" s="109"/>
+      <c r="K6" s="151">
+        <v>0</v>
+      </c>
+      <c r="L6" s="130">
         <v>0.75</v>
       </c>
-      <c r="M6" s="184">
+      <c r="M6" s="183">
         <v>0.125</v>
       </c>
-      <c r="N6" s="109"/>
-      <c r="O6" s="83">
-        <v>0</v>
-      </c>
-      <c r="P6" s="110"/>
-      <c r="Q6" s="110"/>
-      <c r="R6" s="110"/>
-      <c r="S6" s="188">
+      <c r="N6" s="108"/>
+      <c r="O6" s="82">
+        <v>0</v>
+      </c>
+      <c r="P6" s="109"/>
+      <c r="Q6" s="109"/>
+      <c r="R6" s="109"/>
+      <c r="S6" s="187">
         <v>0</v>
       </c>
       <c r="T6" s="1">
@@ -4201,37 +4195,37 @@
       <c r="B7" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="136" t="s">
+      <c r="C7" s="135" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="183">
-        <v>0</v>
-      </c>
-      <c r="E7" s="110"/>
-      <c r="F7" s="110"/>
-      <c r="G7" s="110"/>
-      <c r="H7" s="110"/>
-      <c r="I7" s="183">
-        <v>0</v>
-      </c>
-      <c r="J7" s="110"/>
-      <c r="K7" s="183">
-        <v>0</v>
-      </c>
-      <c r="L7" s="152">
-        <v>0</v>
-      </c>
-      <c r="M7" s="183">
-        <v>0</v>
-      </c>
-      <c r="N7" s="109"/>
-      <c r="O7" s="127">
+      <c r="D7" s="182">
+        <v>0</v>
+      </c>
+      <c r="E7" s="109"/>
+      <c r="F7" s="109"/>
+      <c r="G7" s="109"/>
+      <c r="H7" s="109"/>
+      <c r="I7" s="182">
+        <v>0</v>
+      </c>
+      <c r="J7" s="109"/>
+      <c r="K7" s="182">
+        <v>0</v>
+      </c>
+      <c r="L7" s="151">
+        <v>0</v>
+      </c>
+      <c r="M7" s="182">
+        <v>0</v>
+      </c>
+      <c r="N7" s="108"/>
+      <c r="O7" s="126">
         <v>0.22222222222222199</v>
       </c>
-      <c r="P7" s="110"/>
-      <c r="Q7" s="110"/>
-      <c r="R7" s="110"/>
-      <c r="S7" s="190">
+      <c r="P7" s="109"/>
+      <c r="Q7" s="109"/>
+      <c r="R7" s="109"/>
+      <c r="S7" s="189">
         <v>0.77777777777777701</v>
       </c>
       <c r="T7" s="1">
@@ -4246,37 +4240,37 @@
       <c r="B8" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="185" t="s">
+      <c r="C8" s="184" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="72">
-        <v>0</v>
-      </c>
-      <c r="E8" s="77"/>
-      <c r="F8" s="77"/>
-      <c r="G8" s="77"/>
-      <c r="H8" s="77"/>
-      <c r="I8" s="72">
-        <v>0</v>
-      </c>
-      <c r="J8" s="77"/>
-      <c r="K8" s="72">
-        <v>0</v>
-      </c>
-      <c r="L8" s="72">
-        <v>0</v>
-      </c>
-      <c r="M8" s="72">
+      <c r="D8" s="71">
+        <v>0</v>
+      </c>
+      <c r="E8" s="76"/>
+      <c r="F8" s="76"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="71">
+        <v>0</v>
+      </c>
+      <c r="J8" s="76"/>
+      <c r="K8" s="71">
+        <v>0</v>
+      </c>
+      <c r="L8" s="71">
+        <v>0</v>
+      </c>
+      <c r="M8" s="71">
         <v>0</v>
       </c>
       <c r="N8" s="50"/>
       <c r="O8" s="6">
         <v>0</v>
       </c>
-      <c r="P8" s="77"/>
-      <c r="Q8" s="77"/>
-      <c r="R8" s="77"/>
-      <c r="S8" s="127">
+      <c r="P8" s="76"/>
+      <c r="Q8" s="76"/>
+      <c r="R8" s="76"/>
+      <c r="S8" s="126">
         <v>1</v>
       </c>
       <c r="T8" s="1">
@@ -4291,36 +4285,36 @@
       <c r="B9" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="137" t="s">
+      <c r="C9" s="136" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="187">
-        <v>0</v>
-      </c>
-      <c r="E9" s="115"/>
-      <c r="F9" s="115"/>
-      <c r="G9" s="115"/>
-      <c r="H9" s="115"/>
-      <c r="I9" s="187">
-        <v>0</v>
-      </c>
-      <c r="J9" s="115"/>
-      <c r="K9" s="187">
-        <v>0</v>
-      </c>
-      <c r="L9" s="187">
-        <v>0</v>
-      </c>
-      <c r="M9" s="187">
-        <v>0</v>
-      </c>
-      <c r="N9" s="114"/>
-      <c r="O9" s="132">
+      <c r="D9" s="186">
+        <v>0</v>
+      </c>
+      <c r="E9" s="114"/>
+      <c r="F9" s="114"/>
+      <c r="G9" s="114"/>
+      <c r="H9" s="114"/>
+      <c r="I9" s="186">
+        <v>0</v>
+      </c>
+      <c r="J9" s="114"/>
+      <c r="K9" s="186">
+        <v>0</v>
+      </c>
+      <c r="L9" s="186">
+        <v>0</v>
+      </c>
+      <c r="M9" s="186">
+        <v>0</v>
+      </c>
+      <c r="N9" s="113"/>
+      <c r="O9" s="131">
         <v>1</v>
       </c>
-      <c r="P9" s="115"/>
-      <c r="Q9" s="115"/>
-      <c r="R9" s="115"/>
+      <c r="P9" s="114"/>
+      <c r="Q9" s="114"/>
+      <c r="R9" s="114"/>
       <c r="S9" s="4">
         <v>0</v>
       </c>
@@ -4336,37 +4330,37 @@
       <c r="B10" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="186" t="s">
+      <c r="C10" s="185" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="72">
-        <v>0</v>
-      </c>
-      <c r="E10" s="77"/>
-      <c r="F10" s="77"/>
-      <c r="G10" s="77"/>
-      <c r="H10" s="77"/>
-      <c r="I10" s="72">
-        <v>0</v>
-      </c>
-      <c r="J10" s="77"/>
-      <c r="K10" s="72">
-        <v>0</v>
-      </c>
-      <c r="L10" s="72">
-        <v>0</v>
-      </c>
-      <c r="M10" s="72">
+      <c r="D10" s="71">
+        <v>0</v>
+      </c>
+      <c r="E10" s="76"/>
+      <c r="F10" s="76"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="71">
+        <v>0</v>
+      </c>
+      <c r="J10" s="76"/>
+      <c r="K10" s="71">
+        <v>0</v>
+      </c>
+      <c r="L10" s="71">
+        <v>0</v>
+      </c>
+      <c r="M10" s="71">
         <v>0</v>
       </c>
       <c r="N10" s="50"/>
       <c r="O10" s="6">
         <v>0</v>
       </c>
-      <c r="P10" s="77"/>
-      <c r="Q10" s="77"/>
-      <c r="R10" s="77"/>
-      <c r="S10" s="132">
+      <c r="P10" s="76"/>
+      <c r="Q10" s="76"/>
+      <c r="R10" s="76"/>
+      <c r="S10" s="131">
         <v>1</v>
       </c>
       <c r="T10" s="1">
@@ -4481,33 +4475,33 @@
       <c r="B2" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="139"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="142">
+      <c r="C2" s="138"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="141">
         <v>0.33333333333333298</v>
       </c>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="142">
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="141">
         <v>0.38888888888888801</v>
       </c>
       <c r="K2" s="48"/>
       <c r="L2" s="48"/>
-      <c r="M2" s="69">
-        <v>0</v>
-      </c>
-      <c r="N2" s="141">
+      <c r="M2" s="68">
+        <v>0</v>
+      </c>
+      <c r="N2" s="140">
         <v>0.27777777777777701</v>
       </c>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="75"/>
       <c r="Q2" s="3">
         <v>0</v>
       </c>
-      <c r="R2" s="76"/>
-      <c r="S2" s="144"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="143"/>
       <c r="T2" s="1">
         <f>SUM(D2:S2)</f>
         <v>0.999999999999998</v>
@@ -4520,16 +4514,16 @@
       <c r="B3" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="66"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="78"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
       <c r="F3" s="24">
         <v>0</v>
       </c>
-      <c r="G3" s="78"/>
-      <c r="H3" s="78"/>
-      <c r="I3" s="78"/>
-      <c r="J3" s="143">
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="142">
         <v>0.04</v>
       </c>
       <c r="K3" s="49"/>
@@ -4537,16 +4531,16 @@
       <c r="M3" s="24">
         <v>0</v>
       </c>
-      <c r="N3" s="140">
+      <c r="N3" s="139">
         <v>0.24</v>
       </c>
-      <c r="O3" s="78"/>
-      <c r="P3" s="78"/>
-      <c r="Q3" s="140">
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="139">
         <v>0.72</v>
       </c>
-      <c r="R3" s="78"/>
-      <c r="S3" s="145"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="144"/>
       <c r="T3" s="1">
         <f t="shared" ref="T3:T25" si="0">SUM(D3:S3)</f>
         <v>1</v>
@@ -4559,33 +4553,33 @@
       <c r="B4" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="66"/>
-      <c r="D4" s="78"/>
-      <c r="E4" s="78"/>
-      <c r="F4" s="143">
+      <c r="C4" s="65"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="142">
         <v>5.2631578947368397E-2</v>
       </c>
-      <c r="G4" s="78"/>
-      <c r="H4" s="78"/>
-      <c r="I4" s="78"/>
-      <c r="J4" s="143">
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="142">
         <v>5.2631578947368397E-2</v>
       </c>
       <c r="K4" s="49"/>
       <c r="L4" s="49"/>
-      <c r="M4" s="143">
+      <c r="M4" s="142">
         <v>5.2631578947368397E-2</v>
       </c>
-      <c r="N4" s="140">
+      <c r="N4" s="139">
         <v>0.105263157894736</v>
       </c>
-      <c r="O4" s="78"/>
-      <c r="P4" s="78"/>
-      <c r="Q4" s="140">
+      <c r="O4" s="77"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="139">
         <v>0.73684210526315697</v>
       </c>
-      <c r="R4" s="78"/>
-      <c r="S4" s="145"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="144"/>
       <c r="T4" s="1">
         <f t="shared" si="0"/>
         <v>0.99999999999999822</v>
@@ -4598,35 +4592,35 @@
       <c r="B5" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="133" t="s">
+      <c r="C5" s="132" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="92">
+      <c r="D5" s="75"/>
+      <c r="E5" s="75"/>
+      <c r="F5" s="91">
         <v>0.83333333333333304</v>
       </c>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
       <c r="J5" s="57">
         <v>0.16666666666666599</v>
       </c>
       <c r="K5" s="48"/>
       <c r="L5" s="48"/>
-      <c r="M5" s="69">
+      <c r="M5" s="68">
         <v>0</v>
       </c>
       <c r="N5" s="3">
         <v>0</v>
       </c>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
+      <c r="O5" s="75"/>
+      <c r="P5" s="75"/>
       <c r="Q5" s="3">
         <v>0</v>
       </c>
-      <c r="R5" s="76"/>
-      <c r="S5" s="144"/>
+      <c r="R5" s="75"/>
+      <c r="S5" s="143"/>
       <c r="T5" s="1">
         <f t="shared" si="0"/>
         <v>0.999999999999999</v>
@@ -4639,17 +4633,17 @@
       <c r="B6" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="170" t="s">
+      <c r="C6" s="169" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="78"/>
-      <c r="E6" s="78"/>
-      <c r="F6" s="155">
-        <v>0</v>
-      </c>
-      <c r="G6" s="78"/>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
+      <c r="D6" s="77"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="154">
+        <v>0</v>
+      </c>
+      <c r="G6" s="77"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
       <c r="J6" s="24">
         <v>0</v>
       </c>
@@ -4661,13 +4655,13 @@
       <c r="N6" s="22">
         <v>0</v>
       </c>
-      <c r="O6" s="78"/>
-      <c r="P6" s="78"/>
+      <c r="O6" s="77"/>
+      <c r="P6" s="77"/>
       <c r="Q6" s="22">
         <v>0</v>
       </c>
-      <c r="R6" s="78"/>
-      <c r="S6" s="145"/>
+      <c r="R6" s="77"/>
+      <c r="S6" s="144"/>
       <c r="T6" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4680,35 +4674,35 @@
       <c r="B7" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="171" t="s">
+      <c r="C7" s="170" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="84"/>
-      <c r="E7" s="84"/>
-      <c r="F7" s="156">
-        <v>0</v>
-      </c>
-      <c r="G7" s="84"/>
-      <c r="H7" s="84"/>
-      <c r="I7" s="84"/>
+      <c r="D7" s="83"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="155">
+        <v>0</v>
+      </c>
+      <c r="G7" s="83"/>
+      <c r="H7" s="83"/>
+      <c r="I7" s="83"/>
       <c r="J7" s="24">
         <v>0</v>
       </c>
       <c r="K7" s="51"/>
       <c r="L7" s="51"/>
-      <c r="M7" s="152">
-        <v>0</v>
-      </c>
-      <c r="N7" s="85">
-        <v>0</v>
-      </c>
-      <c r="O7" s="84"/>
-      <c r="P7" s="84"/>
-      <c r="Q7" s="85">
-        <v>0</v>
-      </c>
-      <c r="R7" s="84"/>
-      <c r="S7" s="153"/>
+      <c r="M7" s="151">
+        <v>0</v>
+      </c>
+      <c r="N7" s="84">
+        <v>0</v>
+      </c>
+      <c r="O7" s="83"/>
+      <c r="P7" s="83"/>
+      <c r="Q7" s="84">
+        <v>0</v>
+      </c>
+      <c r="R7" s="83"/>
+      <c r="S7" s="152"/>
       <c r="T7" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4721,35 +4715,35 @@
       <c r="B8" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="172" t="s">
+      <c r="C8" s="171" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="82"/>
-      <c r="E8" s="82"/>
+      <c r="D8" s="81"/>
+      <c r="E8" s="81"/>
       <c r="F8" s="28">
         <v>0.33333333333333298</v>
       </c>
-      <c r="G8" s="82"/>
-      <c r="H8" s="82"/>
-      <c r="I8" s="82"/>
-      <c r="J8" s="92">
+      <c r="G8" s="81"/>
+      <c r="H8" s="81"/>
+      <c r="I8" s="81"/>
+      <c r="J8" s="91">
         <v>0.66666666666666596</v>
       </c>
       <c r="K8" s="52"/>
       <c r="L8" s="52"/>
-      <c r="M8" s="151">
-        <v>0</v>
-      </c>
-      <c r="N8" s="83">
-        <v>0</v>
-      </c>
-      <c r="O8" s="82"/>
-      <c r="P8" s="82"/>
-      <c r="Q8" s="83">
-        <v>0</v>
-      </c>
-      <c r="R8" s="82"/>
-      <c r="S8" s="154"/>
+      <c r="M8" s="150">
+        <v>0</v>
+      </c>
+      <c r="N8" s="82">
+        <v>0</v>
+      </c>
+      <c r="O8" s="81"/>
+      <c r="P8" s="81"/>
+      <c r="Q8" s="82">
+        <v>0</v>
+      </c>
+      <c r="R8" s="81"/>
+      <c r="S8" s="153"/>
       <c r="T8" s="1">
         <f t="shared" si="0"/>
         <v>0.99999999999999889</v>
@@ -4762,18 +4756,18 @@
       <c r="B9" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="134" t="s">
+      <c r="C9" s="133" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="78"/>
-      <c r="E9" s="78"/>
+      <c r="D9" s="77"/>
+      <c r="E9" s="77"/>
       <c r="F9" s="24">
         <v>0</v>
       </c>
-      <c r="G9" s="78"/>
-      <c r="H9" s="78"/>
-      <c r="I9" s="78"/>
-      <c r="J9" s="157">
+      <c r="G9" s="77"/>
+      <c r="H9" s="77"/>
+      <c r="I9" s="77"/>
+      <c r="J9" s="156">
         <v>0</v>
       </c>
       <c r="K9" s="49"/>
@@ -4784,13 +4778,13 @@
       <c r="N9" s="22">
         <v>0</v>
       </c>
-      <c r="O9" s="78"/>
-      <c r="P9" s="78"/>
+      <c r="O9" s="77"/>
+      <c r="P9" s="77"/>
       <c r="Q9" s="22">
         <v>0</v>
       </c>
-      <c r="R9" s="78"/>
-      <c r="S9" s="145"/>
+      <c r="R9" s="77"/>
+      <c r="S9" s="144"/>
       <c r="T9" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4803,35 +4797,35 @@
       <c r="B10" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="173" t="s">
+      <c r="C10" s="172" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="84"/>
-      <c r="E10" s="84"/>
-      <c r="F10" s="85">
-        <v>0</v>
-      </c>
-      <c r="G10" s="84"/>
-      <c r="H10" s="84"/>
-      <c r="I10" s="84"/>
-      <c r="J10" s="158">
+      <c r="D10" s="83"/>
+      <c r="E10" s="83"/>
+      <c r="F10" s="84">
+        <v>0</v>
+      </c>
+      <c r="G10" s="83"/>
+      <c r="H10" s="83"/>
+      <c r="I10" s="83"/>
+      <c r="J10" s="157">
         <v>0</v>
       </c>
       <c r="K10" s="51"/>
       <c r="L10" s="51"/>
-      <c r="M10" s="85">
+      <c r="M10" s="84">
         <v>0</v>
       </c>
       <c r="N10" s="22">
         <v>0</v>
       </c>
-      <c r="O10" s="84"/>
-      <c r="P10" s="84"/>
-      <c r="Q10" s="85">
-        <v>0</v>
-      </c>
-      <c r="R10" s="84"/>
-      <c r="S10" s="153"/>
+      <c r="O10" s="83"/>
+      <c r="P10" s="83"/>
+      <c r="Q10" s="84">
+        <v>0</v>
+      </c>
+      <c r="R10" s="83"/>
+      <c r="S10" s="152"/>
       <c r="T10" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4844,35 +4838,35 @@
       <c r="B11" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="174" t="s">
+      <c r="C11" s="173" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="82"/>
-      <c r="E11" s="82"/>
+      <c r="D11" s="81"/>
+      <c r="E11" s="81"/>
       <c r="F11" s="53">
         <v>0.33333333333333298</v>
       </c>
-      <c r="G11" s="82"/>
-      <c r="H11" s="82"/>
-      <c r="I11" s="82"/>
+      <c r="G11" s="81"/>
+      <c r="H11" s="81"/>
+      <c r="I11" s="81"/>
       <c r="J11" s="28">
         <v>0.38888888888888801</v>
       </c>
       <c r="K11" s="52"/>
       <c r="L11" s="52"/>
-      <c r="M11" s="151">
-        <v>0</v>
-      </c>
-      <c r="N11" s="147">
+      <c r="M11" s="150">
+        <v>0</v>
+      </c>
+      <c r="N11" s="146">
         <v>0.27777777777777701</v>
       </c>
-      <c r="O11" s="82"/>
-      <c r="P11" s="82"/>
-      <c r="Q11" s="83">
-        <v>0</v>
-      </c>
-      <c r="R11" s="82"/>
-      <c r="S11" s="154"/>
+      <c r="O11" s="81"/>
+      <c r="P11" s="81"/>
+      <c r="Q11" s="82">
+        <v>0</v>
+      </c>
+      <c r="R11" s="81"/>
+      <c r="S11" s="153"/>
       <c r="T11" s="1">
         <f t="shared" si="0"/>
         <v>0.999999999999998</v>
@@ -4885,17 +4879,17 @@
       <c r="B12" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="135" t="s">
+      <c r="C12" s="134" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
+      <c r="D12" s="77"/>
+      <c r="E12" s="77"/>
       <c r="F12" s="24">
         <v>0</v>
       </c>
-      <c r="G12" s="78"/>
-      <c r="H12" s="78"/>
-      <c r="I12" s="78"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="77"/>
       <c r="J12" s="24">
         <v>0</v>
       </c>
@@ -4904,16 +4898,16 @@
       <c r="M12" s="24">
         <v>0</v>
       </c>
-      <c r="N12" s="159">
-        <v>0</v>
-      </c>
-      <c r="O12" s="78"/>
-      <c r="P12" s="78"/>
+      <c r="N12" s="158">
+        <v>0</v>
+      </c>
+      <c r="O12" s="77"/>
+      <c r="P12" s="77"/>
       <c r="Q12" s="22">
         <v>0</v>
       </c>
-      <c r="R12" s="78"/>
-      <c r="S12" s="145"/>
+      <c r="R12" s="77"/>
+      <c r="S12" s="144"/>
       <c r="T12" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4926,35 +4920,35 @@
       <c r="B13" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="175" t="s">
+      <c r="C13" s="174" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="84"/>
-      <c r="E13" s="84"/>
-      <c r="F13" s="85">
-        <v>0</v>
-      </c>
-      <c r="G13" s="84"/>
-      <c r="H13" s="84"/>
-      <c r="I13" s="84"/>
-      <c r="J13" s="85">
+      <c r="D13" s="83"/>
+      <c r="E13" s="83"/>
+      <c r="F13" s="84">
+        <v>0</v>
+      </c>
+      <c r="G13" s="83"/>
+      <c r="H13" s="83"/>
+      <c r="I13" s="83"/>
+      <c r="J13" s="84">
         <v>0</v>
       </c>
       <c r="K13" s="51"/>
       <c r="L13" s="51"/>
-      <c r="M13" s="85">
-        <v>0</v>
-      </c>
-      <c r="N13" s="158">
-        <v>0</v>
-      </c>
-      <c r="O13" s="84"/>
-      <c r="P13" s="84"/>
+      <c r="M13" s="84">
+        <v>0</v>
+      </c>
+      <c r="N13" s="157">
+        <v>0</v>
+      </c>
+      <c r="O13" s="83"/>
+      <c r="P13" s="83"/>
       <c r="Q13" s="22">
         <v>0</v>
       </c>
-      <c r="R13" s="84"/>
-      <c r="S13" s="153"/>
+      <c r="R13" s="83"/>
+      <c r="S13" s="152"/>
       <c r="T13" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4967,35 +4961,35 @@
       <c r="B14" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="176" t="s">
+      <c r="C14" s="175" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="82"/>
-      <c r="E14" s="82"/>
+      <c r="D14" s="81"/>
+      <c r="E14" s="81"/>
       <c r="F14" s="53">
         <v>0.15384615384615299</v>
       </c>
-      <c r="G14" s="82"/>
-      <c r="H14" s="82"/>
-      <c r="I14" s="82"/>
+      <c r="G14" s="81"/>
+      <c r="H14" s="81"/>
+      <c r="I14" s="81"/>
       <c r="J14" s="54">
         <v>0.46153846153846101</v>
       </c>
       <c r="K14" s="52"/>
       <c r="L14" s="52"/>
-      <c r="M14" s="151">
-        <v>0</v>
-      </c>
-      <c r="N14" s="63">
+      <c r="M14" s="150">
+        <v>0</v>
+      </c>
+      <c r="N14" s="62">
         <v>0.38461538461538403</v>
       </c>
-      <c r="O14" s="82"/>
-      <c r="P14" s="82"/>
-      <c r="Q14" s="147">
-        <v>0</v>
-      </c>
-      <c r="R14" s="82"/>
-      <c r="S14" s="154"/>
+      <c r="O14" s="81"/>
+      <c r="P14" s="81"/>
+      <c r="Q14" s="146">
+        <v>0</v>
+      </c>
+      <c r="R14" s="81"/>
+      <c r="S14" s="153"/>
       <c r="T14" s="1">
         <f t="shared" si="0"/>
         <v>0.999999999999998</v>
@@ -5008,17 +5002,17 @@
       <c r="B15" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="94" t="s">
+      <c r="C15" s="93" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="78"/>
-      <c r="E15" s="78"/>
+      <c r="D15" s="77"/>
+      <c r="E15" s="77"/>
       <c r="F15" s="24">
         <v>0</v>
       </c>
-      <c r="G15" s="78"/>
-      <c r="H15" s="78"/>
-      <c r="I15" s="78"/>
+      <c r="G15" s="77"/>
+      <c r="H15" s="77"/>
+      <c r="I15" s="77"/>
       <c r="J15" s="24">
         <v>0</v>
       </c>
@@ -5030,13 +5024,13 @@
       <c r="N15" s="28">
         <v>0.14285714285714199</v>
       </c>
-      <c r="O15" s="78"/>
-      <c r="P15" s="78"/>
-      <c r="Q15" s="90">
+      <c r="O15" s="77"/>
+      <c r="P15" s="77"/>
+      <c r="Q15" s="89">
         <v>0.85714285714285698</v>
       </c>
-      <c r="R15" s="78"/>
-      <c r="S15" s="145"/>
+      <c r="R15" s="77"/>
+      <c r="S15" s="144"/>
       <c r="T15" s="1">
         <f t="shared" si="0"/>
         <v>0.999999999999999</v>
@@ -5046,20 +5040,20 @@
       <c r="A16" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="74" t="s">
+      <c r="B16" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="168" t="s">
+      <c r="C16" s="167" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="77"/>
-      <c r="E16" s="77"/>
+      <c r="D16" s="76"/>
+      <c r="E16" s="76"/>
       <c r="F16" s="6">
         <v>0</v>
       </c>
-      <c r="G16" s="77"/>
-      <c r="H16" s="77"/>
-      <c r="I16" s="77"/>
+      <c r="G16" s="76"/>
+      <c r="H16" s="76"/>
+      <c r="I16" s="76"/>
       <c r="J16" s="6">
         <v>0</v>
       </c>
@@ -5071,13 +5065,13 @@
       <c r="N16" s="15">
         <v>7.1428571428571397E-2</v>
       </c>
-      <c r="O16" s="77"/>
-      <c r="P16" s="77"/>
-      <c r="Q16" s="89">
+      <c r="O16" s="76"/>
+      <c r="P16" s="76"/>
+      <c r="Q16" s="88">
         <v>0.85714285714285698</v>
       </c>
-      <c r="R16" s="77"/>
-      <c r="S16" s="146"/>
+      <c r="R16" s="76"/>
+      <c r="S16" s="145"/>
       <c r="T16" s="1">
         <f t="shared" si="0"/>
         <v>0.99999999999999978</v>
@@ -5087,20 +5081,20 @@
       <c r="A17" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="75" t="s">
+      <c r="B17" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="97" t="s">
+      <c r="C17" s="96" t="s">
         <v>17</v>
       </c>
-      <c r="D17" s="76"/>
-      <c r="E17" s="76"/>
-      <c r="F17" s="147">
+      <c r="D17" s="75"/>
+      <c r="E17" s="75"/>
+      <c r="F17" s="146">
         <v>0.33333333333333298</v>
       </c>
-      <c r="G17" s="76"/>
-      <c r="H17" s="76"/>
-      <c r="I17" s="76"/>
+      <c r="G17" s="75"/>
+      <c r="H17" s="75"/>
+      <c r="I17" s="75"/>
       <c r="J17" s="57">
         <v>0.38888888888888801</v>
       </c>
@@ -5112,13 +5106,13 @@
       <c r="N17" s="57">
         <v>0.27777777777777701</v>
       </c>
-      <c r="O17" s="76"/>
-      <c r="P17" s="76"/>
+      <c r="O17" s="75"/>
+      <c r="P17" s="75"/>
       <c r="Q17" s="3">
         <v>0</v>
       </c>
-      <c r="R17" s="76"/>
-      <c r="S17" s="144"/>
+      <c r="R17" s="75"/>
+      <c r="S17" s="143"/>
       <c r="T17" s="1">
         <f t="shared" si="0"/>
         <v>0.999999999999998</v>
@@ -5131,17 +5125,17 @@
       <c r="B18" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="177" t="s">
+      <c r="C18" s="176" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="78"/>
-      <c r="E18" s="78"/>
-      <c r="F18" s="148">
-        <v>0</v>
-      </c>
-      <c r="G18" s="78"/>
-      <c r="H18" s="78"/>
-      <c r="I18" s="78"/>
+      <c r="D18" s="77"/>
+      <c r="E18" s="77"/>
+      <c r="F18" s="147">
+        <v>0</v>
+      </c>
+      <c r="G18" s="77"/>
+      <c r="H18" s="77"/>
+      <c r="I18" s="77"/>
       <c r="J18" s="22">
         <v>0</v>
       </c>
@@ -5153,13 +5147,13 @@
       <c r="N18" s="22">
         <v>0</v>
       </c>
-      <c r="O18" s="78"/>
-      <c r="P18" s="78"/>
+      <c r="O18" s="77"/>
+      <c r="P18" s="77"/>
       <c r="Q18" s="22">
         <v>0</v>
       </c>
-      <c r="R18" s="78"/>
-      <c r="S18" s="145"/>
+      <c r="R18" s="77"/>
+      <c r="S18" s="144"/>
       <c r="T18" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5172,35 +5166,35 @@
       <c r="B19" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="96" t="s">
+      <c r="C19" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="84"/>
-      <c r="E19" s="84"/>
-      <c r="F19" s="160">
-        <v>0</v>
-      </c>
-      <c r="G19" s="84"/>
-      <c r="H19" s="84"/>
-      <c r="I19" s="84"/>
+      <c r="D19" s="83"/>
+      <c r="E19" s="83"/>
+      <c r="F19" s="159">
+        <v>0</v>
+      </c>
+      <c r="G19" s="83"/>
+      <c r="H19" s="83"/>
+      <c r="I19" s="83"/>
       <c r="J19" s="22">
         <v>0</v>
       </c>
       <c r="K19" s="51"/>
       <c r="L19" s="51"/>
-      <c r="M19" s="85">
-        <v>0</v>
-      </c>
-      <c r="N19" s="85">
-        <v>0</v>
-      </c>
-      <c r="O19" s="84"/>
-      <c r="P19" s="84"/>
-      <c r="Q19" s="85">
-        <v>0</v>
-      </c>
-      <c r="R19" s="84"/>
-      <c r="S19" s="153"/>
+      <c r="M19" s="84">
+        <v>0</v>
+      </c>
+      <c r="N19" s="84">
+        <v>0</v>
+      </c>
+      <c r="O19" s="83"/>
+      <c r="P19" s="83"/>
+      <c r="Q19" s="84">
+        <v>0</v>
+      </c>
+      <c r="R19" s="83"/>
+      <c r="S19" s="152"/>
       <c r="T19" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5213,35 +5207,35 @@
       <c r="B20" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="137" t="s">
+      <c r="C20" s="136" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="82"/>
-      <c r="E20" s="82"/>
+      <c r="D20" s="81"/>
+      <c r="E20" s="81"/>
       <c r="F20" s="28">
         <v>0.33333333333333298</v>
       </c>
-      <c r="G20" s="82"/>
-      <c r="H20" s="82"/>
-      <c r="I20" s="82"/>
-      <c r="J20" s="161">
+      <c r="G20" s="81"/>
+      <c r="H20" s="81"/>
+      <c r="I20" s="81"/>
+      <c r="J20" s="160">
         <v>0.38888888888888801</v>
       </c>
       <c r="K20" s="52"/>
       <c r="L20" s="52"/>
-      <c r="M20" s="83">
+      <c r="M20" s="82">
         <v>0</v>
       </c>
       <c r="N20" s="53">
         <v>0.27777777777777701</v>
       </c>
-      <c r="O20" s="82"/>
-      <c r="P20" s="82"/>
-      <c r="Q20" s="83">
-        <v>0</v>
-      </c>
-      <c r="R20" s="82"/>
-      <c r="S20" s="154"/>
+      <c r="O20" s="81"/>
+      <c r="P20" s="81"/>
+      <c r="Q20" s="82">
+        <v>0</v>
+      </c>
+      <c r="R20" s="81"/>
+      <c r="S20" s="153"/>
       <c r="T20" s="1">
         <f t="shared" si="0"/>
         <v>0.999999999999998</v>
@@ -5254,18 +5248,18 @@
       <c r="B21" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C21" s="178" t="s">
+      <c r="C21" s="177" t="s">
         <v>21</v>
       </c>
-      <c r="D21" s="78"/>
-      <c r="E21" s="78"/>
+      <c r="D21" s="77"/>
+      <c r="E21" s="77"/>
       <c r="F21" s="22">
         <v>0</v>
       </c>
-      <c r="G21" s="78"/>
-      <c r="H21" s="78"/>
-      <c r="I21" s="78"/>
-      <c r="J21" s="159">
+      <c r="G21" s="77"/>
+      <c r="H21" s="77"/>
+      <c r="I21" s="77"/>
+      <c r="J21" s="158">
         <v>0</v>
       </c>
       <c r="K21" s="49"/>
@@ -5276,13 +5270,13 @@
       <c r="N21" s="22">
         <v>0</v>
       </c>
-      <c r="O21" s="78"/>
-      <c r="P21" s="78"/>
+      <c r="O21" s="77"/>
+      <c r="P21" s="77"/>
       <c r="Q21" s="22">
         <v>0</v>
       </c>
-      <c r="R21" s="78"/>
-      <c r="S21" s="145"/>
+      <c r="R21" s="77"/>
+      <c r="S21" s="144"/>
       <c r="T21" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5295,35 +5289,35 @@
       <c r="B22" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C22" s="179" t="s">
+      <c r="C22" s="178" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="84"/>
-      <c r="E22" s="84"/>
-      <c r="F22" s="85">
-        <v>0</v>
-      </c>
-      <c r="G22" s="84"/>
-      <c r="H22" s="84"/>
-      <c r="I22" s="84"/>
-      <c r="J22" s="158">
+      <c r="D22" s="83"/>
+      <c r="E22" s="83"/>
+      <c r="F22" s="84">
+        <v>0</v>
+      </c>
+      <c r="G22" s="83"/>
+      <c r="H22" s="83"/>
+      <c r="I22" s="83"/>
+      <c r="J22" s="157">
         <v>0</v>
       </c>
       <c r="K22" s="51"/>
       <c r="L22" s="51"/>
-      <c r="M22" s="85">
-        <v>0</v>
-      </c>
-      <c r="N22" s="85">
-        <v>0</v>
-      </c>
-      <c r="O22" s="84"/>
-      <c r="P22" s="84"/>
+      <c r="M22" s="84">
+        <v>0</v>
+      </c>
+      <c r="N22" s="84">
+        <v>0</v>
+      </c>
+      <c r="O22" s="83"/>
+      <c r="P22" s="83"/>
       <c r="Q22" s="22">
         <v>0</v>
       </c>
-      <c r="R22" s="84"/>
-      <c r="S22" s="153"/>
+      <c r="R22" s="83"/>
+      <c r="S22" s="152"/>
       <c r="T22" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5336,17 +5330,17 @@
       <c r="B23" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="180" t="s">
+      <c r="C23" s="179" t="s">
         <v>28</v>
       </c>
-      <c r="D23" s="78"/>
-      <c r="E23" s="78"/>
+      <c r="D23" s="77"/>
+      <c r="E23" s="77"/>
       <c r="F23" s="22">
         <v>0</v>
       </c>
-      <c r="G23" s="78"/>
-      <c r="H23" s="78"/>
-      <c r="I23" s="78"/>
+      <c r="G23" s="77"/>
+      <c r="H23" s="77"/>
+      <c r="I23" s="77"/>
       <c r="J23" s="28">
         <v>0.28571428571428498</v>
       </c>
@@ -5355,16 +5349,16 @@
       <c r="M23" s="22">
         <v>0</v>
       </c>
-      <c r="N23" s="63">
+      <c r="N23" s="62">
         <v>0.71428571428571397</v>
       </c>
-      <c r="O23" s="78"/>
-      <c r="P23" s="78"/>
-      <c r="Q23" s="147">
-        <v>0</v>
-      </c>
-      <c r="R23" s="78"/>
-      <c r="S23" s="145"/>
+      <c r="O23" s="77"/>
+      <c r="P23" s="77"/>
+      <c r="Q23" s="146">
+        <v>0</v>
+      </c>
+      <c r="R23" s="77"/>
+      <c r="S23" s="144"/>
       <c r="T23" s="1">
         <f t="shared" si="0"/>
         <v>0.99999999999999889</v>
@@ -5377,17 +5371,17 @@
       <c r="B24" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C24" s="181" t="s">
+      <c r="C24" s="180" t="s">
         <v>28</v>
       </c>
-      <c r="D24" s="78"/>
-      <c r="E24" s="78"/>
+      <c r="D24" s="77"/>
+      <c r="E24" s="77"/>
       <c r="F24" s="22">
         <v>0</v>
       </c>
-      <c r="G24" s="78"/>
-      <c r="H24" s="78"/>
-      <c r="I24" s="78"/>
+      <c r="G24" s="77"/>
+      <c r="H24" s="77"/>
+      <c r="I24" s="77"/>
       <c r="J24" s="22">
         <v>0</v>
       </c>
@@ -5399,13 +5393,13 @@
       <c r="N24" s="28">
         <v>0.2</v>
       </c>
-      <c r="O24" s="78"/>
-      <c r="P24" s="78"/>
-      <c r="Q24" s="90">
+      <c r="O24" s="77"/>
+      <c r="P24" s="77"/>
+      <c r="Q24" s="89">
         <v>0.8</v>
       </c>
-      <c r="R24" s="78"/>
-      <c r="S24" s="145"/>
+      <c r="R24" s="77"/>
+      <c r="S24" s="144"/>
       <c r="T24" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -5415,20 +5409,20 @@
       <c r="A25" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B25" s="74" t="s">
+      <c r="B25" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="138" t="s">
+      <c r="C25" s="137" t="s">
         <v>28</v>
       </c>
-      <c r="D25" s="77"/>
-      <c r="E25" s="77"/>
+      <c r="D25" s="76"/>
+      <c r="E25" s="76"/>
       <c r="F25" s="6">
         <v>0</v>
       </c>
-      <c r="G25" s="77"/>
-      <c r="H25" s="77"/>
-      <c r="I25" s="77"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="76"/>
+      <c r="I25" s="76"/>
       <c r="J25" s="6">
         <v>0</v>
       </c>
@@ -5440,13 +5434,13 @@
       <c r="N25" s="56">
         <v>0.25</v>
       </c>
-      <c r="O25" s="77"/>
-      <c r="P25" s="77"/>
-      <c r="Q25" s="89">
+      <c r="O25" s="76"/>
+      <c r="P25" s="76"/>
+      <c r="Q25" s="88">
         <v>0.75</v>
       </c>
-      <c r="R25" s="77"/>
-      <c r="S25" s="146"/>
+      <c r="R25" s="76"/>
+      <c r="S25" s="145"/>
       <c r="T25" s="1">
         <f t="shared" si="0"/>
         <v>1</v>

--- a/patterns/results/exp1/4bins-results.xlsx
+++ b/patterns/results/exp1/4bins-results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7B7D647-72DD-6C4C-A9C5-B693C9B45D88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA83682F-0839-6340-8F2E-7999E4523EA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5060" yWindow="1100" windowWidth="30760" windowHeight="16660" activeTab="1" xr2:uid="{9429E1C1-1F54-8A42-9286-E37255B8DAF7}"/>
+    <workbookView xWindow="6400" yWindow="1480" windowWidth="30840" windowHeight="19340" xr2:uid="{9429E1C1-1F54-8A42-9286-E37255B8DAF7}"/>
   </bookViews>
   <sheets>
     <sheet name="GO" sheetId="1" r:id="rId1"/>
@@ -124,7 +124,7 @@
     </textPr>
   </connection>
   <connection id="4" xr16:uid="{7B95F622-C983-F145-A4DD-4DFC5DCB8877}" name="results-go" type="6" refreshedVersion="8" background="1" saveData="1">
-    <textPr codePage="10000" sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/results-go.csv" decimal="," thousands="." comma="1">
+    <textPr codePage="10000" sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/4bins-results-go.csv" decimal="," thousands="." comma="1">
       <textFields count="19">
         <textField/>
         <textField/>
@@ -368,7 +368,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -396,6 +396,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -907,7 +913,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="191">
+  <cellXfs count="195">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1014,26 +1020,27 @@
     <xf numFmtId="2" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="10" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="11" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="12" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="4" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="4" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="32" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -1054,12 +1061,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1083,36 +1090,39 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="9" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="5" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1140,8 +1150,8 @@
       <xdr:rowOff>48846</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>317176</xdr:colOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>181103</xdr:colOff>
       <xdr:row>59</xdr:row>
       <xdr:rowOff>115167</xdr:rowOff>
     </xdr:to>
@@ -1745,15 +1755,16 @@
   <dimension ref="A1:T28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="16" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="10" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -1823,18 +1834,36 @@
         <v>4</v>
       </c>
       <c r="C2" s="37"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
+      <c r="D2" s="48">
+        <v>0</v>
+      </c>
+      <c r="E2" s="48">
+        <v>0</v>
+      </c>
+      <c r="F2" s="48">
+        <v>0</v>
+      </c>
+      <c r="G2" s="48">
+        <v>0</v>
+      </c>
+      <c r="H2" s="48">
+        <v>0</v>
+      </c>
+      <c r="I2" s="48">
+        <v>0</v>
+      </c>
+      <c r="J2" s="48">
+        <v>0</v>
+      </c>
       <c r="K2" s="38">
         <v>0</v>
       </c>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
+      <c r="L2" s="48">
+        <v>0</v>
+      </c>
+      <c r="M2" s="48">
+        <v>0</v>
+      </c>
       <c r="N2" s="18">
         <v>0</v>
       </c>
@@ -1847,7 +1876,9 @@
       <c r="Q2" s="18">
         <v>0</v>
       </c>
-      <c r="R2" s="48"/>
+      <c r="R2" s="48">
+        <v>0</v>
+      </c>
       <c r="S2" s="19">
         <v>0</v>
       </c>
@@ -1864,18 +1895,36 @@
         <v>5</v>
       </c>
       <c r="C3" s="34"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="49"/>
-      <c r="J3" s="49"/>
+      <c r="D3" s="49">
+        <v>0</v>
+      </c>
+      <c r="E3" s="49">
+        <v>0</v>
+      </c>
+      <c r="F3" s="49">
+        <v>0</v>
+      </c>
+      <c r="G3" s="49">
+        <v>0</v>
+      </c>
+      <c r="H3" s="49">
+        <v>0</v>
+      </c>
+      <c r="I3" s="49">
+        <v>0</v>
+      </c>
+      <c r="J3" s="49">
+        <v>0</v>
+      </c>
       <c r="K3" s="58">
         <v>0.11111111111111099</v>
       </c>
-      <c r="L3" s="49"/>
-      <c r="M3" s="49"/>
+      <c r="L3" s="49">
+        <v>0</v>
+      </c>
+      <c r="M3" s="49">
+        <v>0</v>
+      </c>
       <c r="N3" s="25">
         <v>0</v>
       </c>
@@ -1888,7 +1937,9 @@
       <c r="Q3" s="25">
         <v>0</v>
       </c>
-      <c r="R3" s="49"/>
+      <c r="R3" s="49">
+        <v>0</v>
+      </c>
       <c r="S3" s="61">
         <v>0.55555555555555503</v>
       </c>
@@ -1905,18 +1956,36 @@
         <v>6</v>
       </c>
       <c r="C4" s="34"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="49"/>
+      <c r="D4" s="49">
+        <v>0</v>
+      </c>
+      <c r="E4" s="49">
+        <v>0</v>
+      </c>
+      <c r="F4" s="49">
+        <v>0</v>
+      </c>
+      <c r="G4" s="49">
+        <v>0</v>
+      </c>
+      <c r="H4" s="49">
+        <v>0</v>
+      </c>
+      <c r="I4" s="49">
+        <v>0</v>
+      </c>
+      <c r="J4" s="49">
+        <v>0</v>
+      </c>
       <c r="K4" s="27">
         <v>0</v>
       </c>
-      <c r="L4" s="49"/>
-      <c r="M4" s="49"/>
+      <c r="L4" s="49">
+        <v>0</v>
+      </c>
+      <c r="M4" s="49">
+        <v>0</v>
+      </c>
       <c r="N4" s="59">
         <v>0.28571428571428498</v>
       </c>
@@ -1929,7 +1998,9 @@
       <c r="Q4" s="59">
         <v>0.71428571428571397</v>
       </c>
-      <c r="R4" s="49"/>
+      <c r="R4" s="49">
+        <v>0</v>
+      </c>
       <c r="S4" s="16">
         <v>0</v>
       </c>
@@ -1939,31 +2010,49 @@
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="39" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="132" t="s">
+      <c r="C5" s="133" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
+      <c r="D5" s="48">
+        <v>0</v>
+      </c>
+      <c r="E5" s="48">
+        <v>0</v>
+      </c>
+      <c r="F5" s="48">
+        <v>0</v>
+      </c>
+      <c r="G5" s="48">
+        <v>0</v>
+      </c>
+      <c r="H5" s="48">
+        <v>0</v>
+      </c>
+      <c r="I5" s="48">
+        <v>0</v>
+      </c>
+      <c r="J5" s="48">
+        <v>0</v>
+      </c>
       <c r="K5" s="38">
         <v>0</v>
       </c>
-      <c r="L5" s="48"/>
-      <c r="M5" s="48"/>
+      <c r="L5" s="48">
+        <v>0</v>
+      </c>
+      <c r="M5" s="48">
+        <v>0</v>
+      </c>
       <c r="N5" s="18">
         <v>0</v>
       </c>
-      <c r="O5" s="146">
+      <c r="O5" s="191">
         <v>0</v>
       </c>
       <c r="P5" s="18">
@@ -1972,7 +2061,9 @@
       <c r="Q5" s="18">
         <v>0</v>
       </c>
-      <c r="R5" s="48"/>
+      <c r="R5" s="48">
+        <v>0</v>
+      </c>
       <c r="S5" s="19">
         <v>0</v>
       </c>
@@ -1982,31 +2073,49 @@
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="39" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="169" t="s">
+      <c r="C6" s="170" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="49"/>
-      <c r="K6" s="28">
+      <c r="D6" s="49">
+        <v>0</v>
+      </c>
+      <c r="E6" s="49">
+        <v>0</v>
+      </c>
+      <c r="F6" s="49">
+        <v>0</v>
+      </c>
+      <c r="G6" s="49">
+        <v>0</v>
+      </c>
+      <c r="H6" s="49">
+        <v>0</v>
+      </c>
+      <c r="I6" s="49">
+        <v>0</v>
+      </c>
+      <c r="J6" s="49">
+        <v>0</v>
+      </c>
+      <c r="K6" s="194">
         <v>0.11111111111111099</v>
       </c>
-      <c r="L6" s="49"/>
-      <c r="M6" s="49"/>
+      <c r="L6" s="49">
+        <v>0</v>
+      </c>
+      <c r="M6" s="49">
+        <v>0</v>
+      </c>
       <c r="N6" s="25">
         <v>0</v>
       </c>
-      <c r="O6" s="147">
+      <c r="O6" s="148">
         <v>0.33333333333333298</v>
       </c>
       <c r="P6" s="25">
@@ -2015,7 +2124,9 @@
       <c r="Q6" s="25">
         <v>0</v>
       </c>
-      <c r="R6" s="49"/>
+      <c r="R6" s="49">
+        <v>0</v>
+      </c>
       <c r="S6" s="16">
         <v>0.55555555555555503</v>
       </c>
@@ -2025,31 +2136,49 @@
       </c>
     </row>
     <row r="7" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="39" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="170" t="s">
+      <c r="C7" s="171" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="51"/>
-      <c r="E7" s="51"/>
-      <c r="F7" s="51"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="51"/>
-      <c r="I7" s="51"/>
-      <c r="J7" s="51"/>
+      <c r="D7" s="51">
+        <v>0</v>
+      </c>
+      <c r="E7" s="51">
+        <v>0</v>
+      </c>
+      <c r="F7" s="51">
+        <v>0</v>
+      </c>
+      <c r="G7" s="51">
+        <v>0</v>
+      </c>
+      <c r="H7" s="51">
+        <v>0</v>
+      </c>
+      <c r="I7" s="51">
+        <v>0</v>
+      </c>
+      <c r="J7" s="51">
+        <v>0</v>
+      </c>
       <c r="K7" s="32">
         <v>0</v>
       </c>
-      <c r="L7" s="51"/>
-      <c r="M7" s="51"/>
-      <c r="N7" s="190">
-        <v>0</v>
-      </c>
-      <c r="O7" s="148">
+      <c r="L7" s="51">
+        <v>0</v>
+      </c>
+      <c r="M7" s="51">
+        <v>0</v>
+      </c>
+      <c r="N7" s="32">
+        <v>0</v>
+      </c>
+      <c r="O7" s="192">
         <v>0</v>
       </c>
       <c r="P7" s="25">
@@ -2058,7 +2187,9 @@
       <c r="Q7" s="33">
         <v>0</v>
       </c>
-      <c r="R7" s="51"/>
+      <c r="R7" s="51">
+        <v>0</v>
+      </c>
       <c r="S7" s="43">
         <v>0</v>
       </c>
@@ -2068,40 +2199,60 @@
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="39" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="171" t="s">
+      <c r="C8" s="172" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="52"/>
+      <c r="D8" s="52">
+        <v>0</v>
+      </c>
+      <c r="E8" s="52">
+        <v>0</v>
+      </c>
+      <c r="F8" s="52">
+        <v>0</v>
+      </c>
+      <c r="G8" s="52">
+        <v>0</v>
+      </c>
+      <c r="H8" s="52">
+        <v>0</v>
+      </c>
+      <c r="I8" s="52">
+        <v>0</v>
+      </c>
+      <c r="J8" s="52">
+        <v>0</v>
+      </c>
       <c r="K8" s="30">
         <v>0</v>
       </c>
-      <c r="L8" s="52"/>
-      <c r="M8" s="52"/>
+      <c r="L8" s="52">
+        <v>0</v>
+      </c>
+      <c r="M8" s="52">
+        <v>0</v>
+      </c>
       <c r="N8" s="31">
         <v>0</v>
       </c>
       <c r="O8" s="25">
         <v>0</v>
       </c>
-      <c r="P8" s="146">
+      <c r="P8" s="147">
         <v>1</v>
       </c>
       <c r="Q8" s="31">
         <v>0</v>
       </c>
-      <c r="R8" s="52"/>
+      <c r="R8" s="52">
+        <v>0</v>
+      </c>
       <c r="S8" s="44">
         <v>0</v>
       </c>
@@ -2111,40 +2262,60 @@
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="39" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="133" t="s">
+      <c r="C9" s="134" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="49"/>
-      <c r="E9" s="49"/>
-      <c r="F9" s="49"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="49"/>
-      <c r="J9" s="49"/>
+      <c r="D9" s="49">
+        <v>0</v>
+      </c>
+      <c r="E9" s="49">
+        <v>0</v>
+      </c>
+      <c r="F9" s="49">
+        <v>0</v>
+      </c>
+      <c r="G9" s="49">
+        <v>0</v>
+      </c>
+      <c r="H9" s="49">
+        <v>0</v>
+      </c>
+      <c r="I9" s="49">
+        <v>0</v>
+      </c>
+      <c r="J9" s="49">
+        <v>0</v>
+      </c>
       <c r="K9" s="27">
         <v>0</v>
       </c>
-      <c r="L9" s="49"/>
-      <c r="M9" s="49"/>
+      <c r="L9" s="49">
+        <v>0</v>
+      </c>
+      <c r="M9" s="49">
+        <v>0</v>
+      </c>
       <c r="N9" s="25">
         <v>0</v>
       </c>
       <c r="O9" s="25">
         <v>0</v>
       </c>
-      <c r="P9" s="147">
+      <c r="P9" s="193">
         <v>0</v>
       </c>
       <c r="Q9" s="25">
         <v>0</v>
       </c>
-      <c r="R9" s="49"/>
+      <c r="R9" s="49">
+        <v>0</v>
+      </c>
       <c r="S9" s="16">
         <v>0</v>
       </c>
@@ -2154,40 +2325,60 @@
       </c>
     </row>
     <row r="10" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="39" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="172" t="s">
+      <c r="C10" s="173" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="51"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="51"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="51"/>
-      <c r="J10" s="51"/>
+      <c r="D10" s="51">
+        <v>0</v>
+      </c>
+      <c r="E10" s="51">
+        <v>0</v>
+      </c>
+      <c r="F10" s="51">
+        <v>0</v>
+      </c>
+      <c r="G10" s="51">
+        <v>0</v>
+      </c>
+      <c r="H10" s="51">
+        <v>0</v>
+      </c>
+      <c r="I10" s="51">
+        <v>0</v>
+      </c>
+      <c r="J10" s="51">
+        <v>0</v>
+      </c>
       <c r="K10" s="32">
         <v>0</v>
       </c>
-      <c r="L10" s="51"/>
-      <c r="M10" s="51"/>
+      <c r="L10" s="51">
+        <v>0</v>
+      </c>
+      <c r="M10" s="51">
+        <v>0</v>
+      </c>
       <c r="N10" s="33">
         <v>0</v>
       </c>
       <c r="O10" s="33">
         <v>0</v>
       </c>
-      <c r="P10" s="148">
+      <c r="P10" s="192">
         <v>0</v>
       </c>
       <c r="Q10" s="25">
         <v>0</v>
       </c>
-      <c r="R10" s="51"/>
+      <c r="R10" s="51">
+        <v>0</v>
+      </c>
       <c r="S10" s="43">
         <v>0</v>
       </c>
@@ -2197,27 +2388,45 @@
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="39" t="s">
         <v>7</v>
       </c>
       <c r="B11" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="173" t="s">
+      <c r="C11" s="174" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="52"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="52"/>
-      <c r="G11" s="52"/>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="52"/>
+      <c r="D11" s="52">
+        <v>0</v>
+      </c>
+      <c r="E11" s="52">
+        <v>0</v>
+      </c>
+      <c r="F11" s="52">
+        <v>0</v>
+      </c>
+      <c r="G11" s="52">
+        <v>0</v>
+      </c>
+      <c r="H11" s="52">
+        <v>0</v>
+      </c>
+      <c r="I11" s="52">
+        <v>0</v>
+      </c>
+      <c r="J11" s="52">
+        <v>0</v>
+      </c>
       <c r="K11" s="30">
         <v>0</v>
       </c>
-      <c r="L11" s="52"/>
-      <c r="M11" s="52"/>
+      <c r="L11" s="52">
+        <v>0</v>
+      </c>
+      <c r="M11" s="52">
+        <v>0</v>
+      </c>
       <c r="N11" s="31">
         <v>0</v>
       </c>
@@ -2227,10 +2436,12 @@
       <c r="P11" s="25">
         <v>0</v>
       </c>
-      <c r="Q11" s="146">
-        <v>0</v>
-      </c>
-      <c r="R11" s="52"/>
+      <c r="Q11" s="191">
+        <v>0</v>
+      </c>
+      <c r="R11" s="52">
+        <v>0</v>
+      </c>
       <c r="S11" s="44">
         <v>0</v>
       </c>
@@ -2240,27 +2451,45 @@
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="39" t="s">
         <v>7</v>
       </c>
       <c r="B12" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="134" t="s">
+      <c r="C12" s="135" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
-      <c r="H12" s="49"/>
-      <c r="I12" s="49"/>
-      <c r="J12" s="49"/>
+      <c r="D12" s="49">
+        <v>0</v>
+      </c>
+      <c r="E12" s="49">
+        <v>0</v>
+      </c>
+      <c r="F12" s="49">
+        <v>0</v>
+      </c>
+      <c r="G12" s="49">
+        <v>0</v>
+      </c>
+      <c r="H12" s="49">
+        <v>0</v>
+      </c>
+      <c r="I12" s="49">
+        <v>0</v>
+      </c>
+      <c r="J12" s="49">
+        <v>0</v>
+      </c>
       <c r="K12" s="27">
         <v>0</v>
       </c>
-      <c r="L12" s="49"/>
-      <c r="M12" s="49"/>
+      <c r="L12" s="49">
+        <v>0</v>
+      </c>
+      <c r="M12" s="49">
+        <v>0</v>
+      </c>
       <c r="N12" s="25">
         <v>0</v>
       </c>
@@ -2270,10 +2499,12 @@
       <c r="P12" s="25">
         <v>0</v>
       </c>
-      <c r="Q12" s="147">
-        <v>0</v>
-      </c>
-      <c r="R12" s="49"/>
+      <c r="Q12" s="193">
+        <v>0</v>
+      </c>
+      <c r="R12" s="49">
+        <v>0</v>
+      </c>
       <c r="S12" s="16">
         <v>0</v>
       </c>
@@ -2283,27 +2514,45 @@
       </c>
     </row>
     <row r="13" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="39" t="s">
         <v>7</v>
       </c>
       <c r="B13" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="174" t="s">
+      <c r="C13" s="175" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="51"/>
-      <c r="E13" s="51"/>
-      <c r="F13" s="51"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="51"/>
-      <c r="J13" s="51"/>
+      <c r="D13" s="51">
+        <v>0</v>
+      </c>
+      <c r="E13" s="51">
+        <v>0</v>
+      </c>
+      <c r="F13" s="51">
+        <v>0</v>
+      </c>
+      <c r="G13" s="51">
+        <v>0</v>
+      </c>
+      <c r="H13" s="51">
+        <v>0</v>
+      </c>
+      <c r="I13" s="51">
+        <v>0</v>
+      </c>
+      <c r="J13" s="51">
+        <v>0</v>
+      </c>
       <c r="K13" s="32">
         <v>0</v>
       </c>
-      <c r="L13" s="51"/>
-      <c r="M13" s="51"/>
+      <c r="L13" s="51">
+        <v>0</v>
+      </c>
+      <c r="M13" s="51">
+        <v>0</v>
+      </c>
       <c r="N13" s="55">
         <v>0.18181818181818099</v>
       </c>
@@ -2316,7 +2565,9 @@
       <c r="Q13" s="88">
         <v>0.81818181818181801</v>
       </c>
-      <c r="R13" s="51"/>
+      <c r="R13" s="51">
+        <v>0</v>
+      </c>
       <c r="S13" s="16">
         <v>0</v>
       </c>
@@ -2326,27 +2577,45 @@
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A14" s="23" t="s">
+      <c r="A14" s="39" t="s">
         <v>7</v>
       </c>
       <c r="B14" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="175" t="s">
+      <c r="C14" s="176" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="52"/>
-      <c r="E14" s="52"/>
-      <c r="F14" s="52"/>
-      <c r="G14" s="52"/>
-      <c r="H14" s="52"/>
-      <c r="I14" s="52"/>
-      <c r="J14" s="52"/>
+      <c r="D14" s="52">
+        <v>0</v>
+      </c>
+      <c r="E14" s="52">
+        <v>0</v>
+      </c>
+      <c r="F14" s="52">
+        <v>0</v>
+      </c>
+      <c r="G14" s="52">
+        <v>0</v>
+      </c>
+      <c r="H14" s="52">
+        <v>0</v>
+      </c>
+      <c r="I14" s="52">
+        <v>0</v>
+      </c>
+      <c r="J14" s="52">
+        <v>0</v>
+      </c>
       <c r="K14" s="30">
         <v>0</v>
       </c>
-      <c r="L14" s="52"/>
-      <c r="M14" s="52"/>
+      <c r="L14" s="52">
+        <v>0</v>
+      </c>
+      <c r="M14" s="52">
+        <v>0</v>
+      </c>
       <c r="N14" s="31">
         <v>0</v>
       </c>
@@ -2359,8 +2628,10 @@
       <c r="Q14" s="25">
         <v>0</v>
       </c>
-      <c r="R14" s="52"/>
-      <c r="S14" s="146">
+      <c r="R14" s="52">
+        <v>0</v>
+      </c>
+      <c r="S14" s="191">
         <v>0</v>
       </c>
       <c r="T14" s="1">
@@ -2369,7 +2640,7 @@
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="39" t="s">
         <v>7</v>
       </c>
       <c r="B15" s="23" t="s">
@@ -2378,22 +2649,40 @@
       <c r="C15" s="93" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="49"/>
-      <c r="E15" s="49"/>
-      <c r="F15" s="49"/>
-      <c r="G15" s="49"/>
-      <c r="H15" s="49"/>
-      <c r="I15" s="49"/>
-      <c r="J15" s="49"/>
+      <c r="D15" s="49">
+        <v>0</v>
+      </c>
+      <c r="E15" s="49">
+        <v>0</v>
+      </c>
+      <c r="F15" s="49">
+        <v>0</v>
+      </c>
+      <c r="G15" s="49">
+        <v>0</v>
+      </c>
+      <c r="H15" s="49">
+        <v>0</v>
+      </c>
+      <c r="I15" s="49">
+        <v>0</v>
+      </c>
+      <c r="J15" s="49">
+        <v>0</v>
+      </c>
       <c r="K15" s="27">
         <v>0</v>
       </c>
-      <c r="L15" s="49"/>
-      <c r="M15" s="49"/>
+      <c r="L15" s="49">
+        <v>0</v>
+      </c>
+      <c r="M15" s="49">
+        <v>0</v>
+      </c>
       <c r="N15" s="25">
         <v>0</v>
       </c>
-      <c r="O15" s="25">
+      <c r="O15" s="28">
         <v>0.28571428571428498</v>
       </c>
       <c r="P15" s="25">
@@ -2402,7 +2691,9 @@
       <c r="Q15" s="25">
         <v>0</v>
       </c>
-      <c r="R15" s="49"/>
+      <c r="R15" s="49">
+        <v>0</v>
+      </c>
       <c r="S15" s="89">
         <v>0.71428571428571397</v>
       </c>
@@ -2412,27 +2703,45 @@
       </c>
     </row>
     <row r="16" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="39" t="s">
         <v>7</v>
       </c>
       <c r="B16" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="167" t="s">
+      <c r="C16" s="168" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="50"/>
-      <c r="E16" s="50"/>
-      <c r="F16" s="50"/>
-      <c r="G16" s="50"/>
-      <c r="H16" s="50"/>
-      <c r="I16" s="50"/>
-      <c r="J16" s="50"/>
+      <c r="D16" s="50">
+        <v>0</v>
+      </c>
+      <c r="E16" s="50">
+        <v>0</v>
+      </c>
+      <c r="F16" s="50">
+        <v>0</v>
+      </c>
+      <c r="G16" s="50">
+        <v>0</v>
+      </c>
+      <c r="H16" s="50">
+        <v>0</v>
+      </c>
+      <c r="I16" s="50">
+        <v>0</v>
+      </c>
+      <c r="J16" s="50">
+        <v>0</v>
+      </c>
       <c r="K16" s="42">
         <v>0</v>
       </c>
-      <c r="L16" s="50"/>
-      <c r="M16" s="50"/>
+      <c r="L16" s="50">
+        <v>0</v>
+      </c>
+      <c r="M16" s="50">
+        <v>0</v>
+      </c>
       <c r="N16" s="17">
         <v>0</v>
       </c>
@@ -2445,8 +2754,10 @@
       <c r="Q16" s="17">
         <v>0</v>
       </c>
-      <c r="R16" s="50"/>
-      <c r="S16" s="148">
+      <c r="R16" s="50">
+        <v>0</v>
+      </c>
+      <c r="S16" s="192">
         <v>0</v>
       </c>
       <c r="T16" s="1">
@@ -2464,31 +2775,51 @@
       <c r="C17" s="96" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="49"/>
-      <c r="E17" s="49"/>
-      <c r="F17" s="49"/>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49"/>
-      <c r="I17" s="49"/>
-      <c r="J17" s="49"/>
+      <c r="D17" s="49">
+        <v>0</v>
+      </c>
+      <c r="E17" s="49">
+        <v>0</v>
+      </c>
+      <c r="F17" s="49">
+        <v>0</v>
+      </c>
+      <c r="G17" s="49">
+        <v>0</v>
+      </c>
+      <c r="H17" s="49">
+        <v>0</v>
+      </c>
+      <c r="I17" s="49">
+        <v>0</v>
+      </c>
+      <c r="J17" s="49">
+        <v>0</v>
+      </c>
       <c r="K17" s="27">
         <v>0</v>
       </c>
-      <c r="L17" s="49"/>
-      <c r="M17" s="49"/>
+      <c r="L17" s="49">
+        <v>0</v>
+      </c>
+      <c r="M17" s="49">
+        <v>0</v>
+      </c>
       <c r="N17" s="25">
         <v>0</v>
       </c>
-      <c r="O17" s="146">
-        <v>0</v>
-      </c>
-      <c r="P17" s="25">
+      <c r="O17" s="191">
+        <v>0</v>
+      </c>
+      <c r="P17" s="194">
         <v>1</v>
       </c>
       <c r="Q17" s="25">
         <v>0</v>
       </c>
-      <c r="R17" s="49"/>
+      <c r="R17" s="49">
+        <v>0</v>
+      </c>
       <c r="S17" s="16">
         <v>0</v>
       </c>
@@ -2504,21 +2835,39 @@
       <c r="B18" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="176" t="s">
+      <c r="C18" s="177" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="49"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="49"/>
-      <c r="G18" s="49"/>
-      <c r="H18" s="49"/>
-      <c r="I18" s="49"/>
-      <c r="J18" s="49"/>
+      <c r="D18" s="49">
+        <v>0</v>
+      </c>
+      <c r="E18" s="49">
+        <v>0</v>
+      </c>
+      <c r="F18" s="49">
+        <v>0</v>
+      </c>
+      <c r="G18" s="49">
+        <v>0</v>
+      </c>
+      <c r="H18" s="49">
+        <v>0</v>
+      </c>
+      <c r="I18" s="49">
+        <v>0</v>
+      </c>
+      <c r="J18" s="49">
+        <v>0</v>
+      </c>
       <c r="K18" s="62">
         <v>0.5</v>
       </c>
-      <c r="L18" s="49"/>
-      <c r="M18" s="49"/>
+      <c r="L18" s="49">
+        <v>0</v>
+      </c>
+      <c r="M18" s="49">
+        <v>0</v>
+      </c>
       <c r="N18" s="25">
         <v>0</v>
       </c>
@@ -2531,7 +2880,9 @@
       <c r="Q18" s="25">
         <v>0</v>
       </c>
-      <c r="R18" s="49"/>
+      <c r="R18" s="49">
+        <v>0</v>
+      </c>
       <c r="S18" s="16">
         <v>0</v>
       </c>
@@ -2550,31 +2901,51 @@
       <c r="C19" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="51"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="51"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="51"/>
-      <c r="J19" s="51"/>
+      <c r="D19" s="51">
+        <v>0</v>
+      </c>
+      <c r="E19" s="51">
+        <v>0</v>
+      </c>
+      <c r="F19" s="51">
+        <v>0</v>
+      </c>
+      <c r="G19" s="51">
+        <v>0</v>
+      </c>
+      <c r="H19" s="51">
+        <v>0</v>
+      </c>
+      <c r="I19" s="51">
+        <v>0</v>
+      </c>
+      <c r="J19" s="51">
+        <v>0</v>
+      </c>
       <c r="K19" s="32">
         <v>0</v>
       </c>
-      <c r="L19" s="51"/>
-      <c r="M19" s="51"/>
-      <c r="N19" s="190">
-        <v>0</v>
-      </c>
-      <c r="O19" s="148">
+      <c r="L19" s="51">
+        <v>0</v>
+      </c>
+      <c r="M19" s="51">
+        <v>0</v>
+      </c>
+      <c r="N19" s="32">
+        <v>0</v>
+      </c>
+      <c r="O19" s="192">
         <v>0</v>
       </c>
       <c r="P19" s="25">
         <v>0</v>
       </c>
-      <c r="Q19" s="33">
+      <c r="Q19" s="112">
         <v>1</v>
       </c>
-      <c r="R19" s="51"/>
+      <c r="R19" s="51">
+        <v>0</v>
+      </c>
       <c r="S19" s="43">
         <v>0</v>
       </c>
@@ -2590,34 +2961,54 @@
       <c r="B20" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C20" s="136" t="s">
+      <c r="C20" s="137" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="52"/>
-      <c r="E20" s="52"/>
-      <c r="F20" s="52"/>
-      <c r="G20" s="52"/>
-      <c r="H20" s="52"/>
-      <c r="I20" s="52"/>
-      <c r="J20" s="52"/>
+      <c r="D20" s="52">
+        <v>0</v>
+      </c>
+      <c r="E20" s="52">
+        <v>0</v>
+      </c>
+      <c r="F20" s="52">
+        <v>0</v>
+      </c>
+      <c r="G20" s="52">
+        <v>0</v>
+      </c>
+      <c r="H20" s="52">
+        <v>0</v>
+      </c>
+      <c r="I20" s="52">
+        <v>0</v>
+      </c>
+      <c r="J20" s="52">
+        <v>0</v>
+      </c>
       <c r="K20" s="30">
         <v>0</v>
       </c>
-      <c r="L20" s="52"/>
-      <c r="M20" s="52"/>
+      <c r="L20" s="52">
+        <v>0</v>
+      </c>
+      <c r="M20" s="52">
+        <v>0</v>
+      </c>
       <c r="N20" s="31">
         <v>0</v>
       </c>
       <c r="O20" s="25">
         <v>0</v>
       </c>
-      <c r="P20" s="146">
+      <c r="P20" s="147">
         <v>1</v>
       </c>
       <c r="Q20" s="31">
         <v>0</v>
       </c>
-      <c r="R20" s="52"/>
+      <c r="R20" s="52">
+        <v>0</v>
+      </c>
       <c r="S20" s="44">
         <v>0</v>
       </c>
@@ -2633,34 +3024,54 @@
       <c r="B21" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="177" t="s">
+      <c r="C21" s="178" t="s">
         <v>27</v>
       </c>
-      <c r="D21" s="49"/>
-      <c r="E21" s="49"/>
-      <c r="F21" s="49"/>
-      <c r="G21" s="49"/>
-      <c r="H21" s="49"/>
-      <c r="I21" s="49"/>
-      <c r="J21" s="49"/>
+      <c r="D21" s="49">
+        <v>0</v>
+      </c>
+      <c r="E21" s="49">
+        <v>0</v>
+      </c>
+      <c r="F21" s="49">
+        <v>0</v>
+      </c>
+      <c r="G21" s="49">
+        <v>0</v>
+      </c>
+      <c r="H21" s="49">
+        <v>0</v>
+      </c>
+      <c r="I21" s="49">
+        <v>0</v>
+      </c>
+      <c r="J21" s="49">
+        <v>0</v>
+      </c>
       <c r="K21" s="27">
         <v>0</v>
       </c>
-      <c r="L21" s="49"/>
-      <c r="M21" s="49"/>
+      <c r="L21" s="49">
+        <v>0</v>
+      </c>
+      <c r="M21" s="49">
+        <v>0</v>
+      </c>
       <c r="N21" s="25">
         <v>0</v>
       </c>
       <c r="O21" s="25">
         <v>0</v>
       </c>
-      <c r="P21" s="147">
+      <c r="P21" s="193">
         <v>0</v>
       </c>
       <c r="Q21" s="25">
         <v>0</v>
       </c>
-      <c r="R21" s="49"/>
+      <c r="R21" s="49">
+        <v>0</v>
+      </c>
       <c r="S21" s="16">
         <v>0</v>
       </c>
@@ -2676,34 +3087,54 @@
       <c r="B22" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="178" t="s">
+      <c r="C22" s="179" t="s">
         <v>27</v>
       </c>
-      <c r="D22" s="51"/>
-      <c r="E22" s="51"/>
-      <c r="F22" s="51"/>
-      <c r="G22" s="51"/>
-      <c r="H22" s="51"/>
-      <c r="I22" s="51"/>
-      <c r="J22" s="51"/>
+      <c r="D22" s="51">
+        <v>0</v>
+      </c>
+      <c r="E22" s="51">
+        <v>0</v>
+      </c>
+      <c r="F22" s="51">
+        <v>0</v>
+      </c>
+      <c r="G22" s="51">
+        <v>0</v>
+      </c>
+      <c r="H22" s="51">
+        <v>0</v>
+      </c>
+      <c r="I22" s="51">
+        <v>0</v>
+      </c>
+      <c r="J22" s="51">
+        <v>0</v>
+      </c>
       <c r="K22" s="32">
         <v>0</v>
       </c>
-      <c r="L22" s="51"/>
-      <c r="M22" s="51"/>
+      <c r="L22" s="51">
+        <v>0</v>
+      </c>
+      <c r="M22" s="51">
+        <v>0</v>
+      </c>
       <c r="N22" s="33">
         <v>0</v>
       </c>
       <c r="O22" s="33">
         <v>0</v>
       </c>
-      <c r="P22" s="148">
+      <c r="P22" s="192">
         <v>0</v>
       </c>
       <c r="Q22" s="33">
         <v>0</v>
       </c>
-      <c r="R22" s="51"/>
+      <c r="R22" s="51">
+        <v>0</v>
+      </c>
       <c r="S22" s="16">
         <v>0</v>
       </c>
@@ -2719,21 +3150,39 @@
       <c r="B23" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="179" t="s">
+      <c r="C23" s="180" t="s">
         <v>30</v>
       </c>
-      <c r="D23" s="52"/>
-      <c r="E23" s="52"/>
-      <c r="F23" s="52"/>
-      <c r="G23" s="52"/>
-      <c r="H23" s="52"/>
-      <c r="I23" s="52"/>
-      <c r="J23" s="52"/>
+      <c r="D23" s="52">
+        <v>0</v>
+      </c>
+      <c r="E23" s="52">
+        <v>0</v>
+      </c>
+      <c r="F23" s="52">
+        <v>0</v>
+      </c>
+      <c r="G23" s="52">
+        <v>0</v>
+      </c>
+      <c r="H23" s="52">
+        <v>0</v>
+      </c>
+      <c r="I23" s="52">
+        <v>0</v>
+      </c>
+      <c r="J23" s="52">
+        <v>0</v>
+      </c>
       <c r="K23" s="30">
         <v>0</v>
       </c>
-      <c r="L23" s="52"/>
-      <c r="M23" s="52"/>
+      <c r="L23" s="52">
+        <v>0</v>
+      </c>
+      <c r="M23" s="52">
+        <v>0</v>
+      </c>
       <c r="N23" s="31">
         <v>0</v>
       </c>
@@ -2746,8 +3195,10 @@
       <c r="Q23" s="31">
         <v>0</v>
       </c>
-      <c r="R23" s="52"/>
-      <c r="S23" s="146">
+      <c r="R23" s="52">
+        <v>0</v>
+      </c>
+      <c r="S23" s="191">
         <v>0</v>
       </c>
       <c r="T23" s="1">
@@ -2762,21 +3213,39 @@
       <c r="B24" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="180" t="s">
+      <c r="C24" s="181" t="s">
         <v>30</v>
       </c>
-      <c r="D24" s="49"/>
-      <c r="E24" s="49"/>
-      <c r="F24" s="49"/>
-      <c r="G24" s="49"/>
-      <c r="H24" s="49"/>
-      <c r="I24" s="49"/>
-      <c r="J24" s="49"/>
+      <c r="D24" s="49">
+        <v>0</v>
+      </c>
+      <c r="E24" s="49">
+        <v>0</v>
+      </c>
+      <c r="F24" s="49">
+        <v>0</v>
+      </c>
+      <c r="G24" s="49">
+        <v>0</v>
+      </c>
+      <c r="H24" s="49">
+        <v>0</v>
+      </c>
+      <c r="I24" s="49">
+        <v>0</v>
+      </c>
+      <c r="J24" s="49">
+        <v>0</v>
+      </c>
       <c r="K24" s="27">
         <v>0</v>
       </c>
-      <c r="L24" s="49"/>
-      <c r="M24" s="49"/>
+      <c r="L24" s="49">
+        <v>0</v>
+      </c>
+      <c r="M24" s="49">
+        <v>0</v>
+      </c>
       <c r="N24" s="25">
         <v>0</v>
       </c>
@@ -2789,7 +3258,9 @@
       <c r="Q24" s="25">
         <v>0</v>
       </c>
-      <c r="R24" s="49"/>
+      <c r="R24" s="49">
+        <v>0</v>
+      </c>
       <c r="S24" s="89">
         <v>0.75</v>
       </c>
@@ -2805,21 +3276,39 @@
       <c r="B25" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="137" t="s">
+      <c r="C25" s="138" t="s">
         <v>30</v>
       </c>
-      <c r="D25" s="50"/>
-      <c r="E25" s="50"/>
-      <c r="F25" s="50"/>
-      <c r="G25" s="50"/>
-      <c r="H25" s="50"/>
-      <c r="I25" s="50"/>
-      <c r="J25" s="50"/>
+      <c r="D25" s="50">
+        <v>0</v>
+      </c>
+      <c r="E25" s="50">
+        <v>0</v>
+      </c>
+      <c r="F25" s="50">
+        <v>0</v>
+      </c>
+      <c r="G25" s="50">
+        <v>0</v>
+      </c>
+      <c r="H25" s="50">
+        <v>0</v>
+      </c>
+      <c r="I25" s="50">
+        <v>0</v>
+      </c>
+      <c r="J25" s="50">
+        <v>0</v>
+      </c>
       <c r="K25" s="42">
         <v>0</v>
       </c>
-      <c r="L25" s="50"/>
-      <c r="M25" s="50"/>
+      <c r="L25" s="50">
+        <v>0</v>
+      </c>
+      <c r="M25" s="50">
+        <v>0</v>
+      </c>
       <c r="N25" s="17">
         <v>0</v>
       </c>
@@ -2832,8 +3321,10 @@
       <c r="Q25" s="56">
         <v>1</v>
       </c>
-      <c r="R25" s="50"/>
-      <c r="S25" s="148">
+      <c r="R25" s="50">
+        <v>0</v>
+      </c>
+      <c r="S25" s="192">
         <v>0</v>
       </c>
       <c r="T25" s="1">
@@ -3105,7 +3596,7 @@
       <c r="B5" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="161" t="s">
+      <c r="C5" s="162" t="s">
         <v>25</v>
       </c>
       <c r="D5" s="51"/>
@@ -3118,7 +3609,7 @@
       <c r="K5" s="51"/>
       <c r="L5" s="51"/>
       <c r="M5" s="83"/>
-      <c r="N5" s="148">
+      <c r="N5" s="149">
         <v>0</v>
       </c>
       <c r="O5" s="83"/>
@@ -3146,7 +3637,7 @@
       <c r="B6" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="163" t="s">
+      <c r="C6" s="164" t="s">
         <v>27</v>
       </c>
       <c r="D6" s="52"/>
@@ -3187,7 +3678,7 @@
       <c r="B7" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="164" t="s">
+      <c r="C7" s="165" t="s">
         <v>27</v>
       </c>
       <c r="D7" s="51"/>
@@ -3204,7 +3695,7 @@
         <v>0</v>
       </c>
       <c r="O7" s="83"/>
-      <c r="P7" s="148">
+      <c r="P7" s="149">
         <v>0</v>
       </c>
       <c r="Q7" s="22">
@@ -3228,7 +3719,7 @@
       <c r="B8" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="162" t="s">
+      <c r="C8" s="163" t="s">
         <v>28</v>
       </c>
       <c r="D8" s="52"/>
@@ -3269,7 +3760,7 @@
       <c r="B9" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="165" t="s">
+      <c r="C9" s="166" t="s">
         <v>28</v>
       </c>
       <c r="D9" s="51"/>
@@ -3289,7 +3780,7 @@
       <c r="P9" s="84">
         <v>0</v>
       </c>
-      <c r="Q9" s="148">
+      <c r="Q9" s="149">
         <v>0</v>
       </c>
       <c r="R9" s="22">
@@ -3310,7 +3801,7 @@
       <c r="B10" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="166" t="s">
+      <c r="C10" s="167" t="s">
         <v>29</v>
       </c>
       <c r="D10" s="52"/>
@@ -3351,7 +3842,7 @@
       <c r="B11" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="167" t="s">
+      <c r="C11" s="168" t="s">
         <v>29</v>
       </c>
       <c r="D11" s="83"/>
@@ -3374,7 +3865,7 @@
       <c r="Q11" s="84">
         <v>0</v>
       </c>
-      <c r="R11" s="148">
+      <c r="R11" s="149">
         <v>0</v>
       </c>
       <c r="S11" s="78">
@@ -3392,7 +3883,7 @@
       <c r="B12" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="168" t="s">
+      <c r="C12" s="169" t="s">
         <v>30</v>
       </c>
       <c r="D12" s="52"/>
@@ -3418,7 +3909,7 @@
       <c r="R12" s="22">
         <v>0</v>
       </c>
-      <c r="S12" s="146">
+      <c r="S12" s="147">
         <v>0</v>
       </c>
       <c r="T12" s="1">
@@ -3535,7 +4026,7 @@
       <c r="P15" s="71">
         <v>0</v>
       </c>
-      <c r="Q15" s="149">
+      <c r="Q15" s="150">
         <v>0</v>
       </c>
       <c r="R15" s="71">
@@ -3713,30 +4204,30 @@
       <c r="C3" s="102" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="112"/>
-      <c r="E3" s="113"/>
-      <c r="F3" s="113"/>
-      <c r="G3" s="113"/>
-      <c r="H3" s="113"/>
-      <c r="I3" s="114"/>
-      <c r="J3" s="114"/>
-      <c r="K3" s="114"/>
-      <c r="L3" s="114"/>
-      <c r="M3" s="115">
-        <v>0</v>
-      </c>
-      <c r="N3" s="116"/>
-      <c r="O3" s="116"/>
-      <c r="P3" s="126">
+      <c r="D3" s="113"/>
+      <c r="E3" s="114"/>
+      <c r="F3" s="114"/>
+      <c r="G3" s="114"/>
+      <c r="H3" s="114"/>
+      <c r="I3" s="115"/>
+      <c r="J3" s="115"/>
+      <c r="K3" s="115"/>
+      <c r="L3" s="115"/>
+      <c r="M3" s="116">
+        <v>0</v>
+      </c>
+      <c r="N3" s="117"/>
+      <c r="O3" s="117"/>
+      <c r="P3" s="127">
         <v>0.79310344827586199</v>
       </c>
       <c r="Q3" s="57">
         <v>0.20689655172413701</v>
       </c>
-      <c r="R3" s="115">
-        <v>0</v>
-      </c>
-      <c r="S3" s="117">
+      <c r="R3" s="116">
+        <v>0</v>
+      </c>
+      <c r="S3" s="118">
         <v>0</v>
       </c>
       <c r="T3" s="1">
@@ -3754,7 +4245,7 @@
       <c r="C4" s="103" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="118"/>
+      <c r="D4" s="119"/>
       <c r="E4" s="50"/>
       <c r="F4" s="50"/>
       <c r="G4" s="50"/>
@@ -3771,7 +4262,7 @@
       <c r="P4" s="6">
         <v>0</v>
       </c>
-      <c r="Q4" s="126">
+      <c r="Q4" s="127">
         <v>0.97142857142857097</v>
       </c>
       <c r="R4" s="6">
@@ -3795,30 +4286,30 @@
       <c r="C5" s="104" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="112"/>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="114"/>
-      <c r="J5" s="114"/>
-      <c r="K5" s="114"/>
-      <c r="L5" s="114"/>
-      <c r="M5" s="115">
-        <v>0</v>
-      </c>
-      <c r="N5" s="116"/>
-      <c r="O5" s="116"/>
-      <c r="P5" s="127">
+      <c r="D5" s="113"/>
+      <c r="E5" s="114"/>
+      <c r="F5" s="114"/>
+      <c r="G5" s="114"/>
+      <c r="H5" s="114"/>
+      <c r="I5" s="115"/>
+      <c r="J5" s="115"/>
+      <c r="K5" s="115"/>
+      <c r="L5" s="115"/>
+      <c r="M5" s="116">
+        <v>0</v>
+      </c>
+      <c r="N5" s="117"/>
+      <c r="O5" s="117"/>
+      <c r="P5" s="128">
         <v>0.11111111111111099</v>
       </c>
       <c r="Q5" s="79">
         <v>0.88888888888888795</v>
       </c>
-      <c r="R5" s="115">
-        <v>0</v>
-      </c>
-      <c r="S5" s="117">
+      <c r="R5" s="116">
+        <v>0</v>
+      </c>
+      <c r="S5" s="118">
         <v>0</v>
       </c>
       <c r="T5" s="1">
@@ -3836,30 +4327,30 @@
       <c r="C6" s="105" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="119"/>
-      <c r="E6" s="120"/>
-      <c r="F6" s="120"/>
-      <c r="G6" s="120"/>
-      <c r="H6" s="120"/>
-      <c r="I6" s="121"/>
-      <c r="J6" s="121"/>
-      <c r="K6" s="121"/>
-      <c r="L6" s="121"/>
-      <c r="M6" s="122">
+      <c r="D6" s="120"/>
+      <c r="E6" s="121"/>
+      <c r="F6" s="121"/>
+      <c r="G6" s="121"/>
+      <c r="H6" s="121"/>
+      <c r="I6" s="122"/>
+      <c r="J6" s="122"/>
+      <c r="K6" s="122"/>
+      <c r="L6" s="122"/>
+      <c r="M6" s="123">
         <v>0.05</v>
       </c>
-      <c r="N6" s="123"/>
-      <c r="O6" s="123"/>
+      <c r="N6" s="124"/>
+      <c r="O6" s="124"/>
       <c r="P6" s="6">
         <v>0</v>
       </c>
-      <c r="Q6" s="126">
+      <c r="Q6" s="127">
         <v>0.95</v>
       </c>
-      <c r="R6" s="124">
-        <v>0</v>
-      </c>
-      <c r="S6" s="125">
+      <c r="R6" s="125">
+        <v>0</v>
+      </c>
+      <c r="S6" s="126">
         <v>0</v>
       </c>
       <c r="T6" s="1">
@@ -3966,41 +4457,41 @@
       </c>
     </row>
     <row r="2" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="128" t="s">
+      <c r="A2" s="129" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="129" t="s">
+      <c r="B2" s="130" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="63"/>
-      <c r="D2" s="141">
+      <c r="D2" s="142">
         <v>0.40625</v>
       </c>
       <c r="E2" s="48"/>
       <c r="F2" s="48"/>
       <c r="G2" s="48"/>
       <c r="H2" s="48"/>
-      <c r="I2" s="141">
+      <c r="I2" s="142">
         <v>6.25E-2</v>
       </c>
       <c r="J2" s="48"/>
-      <c r="K2" s="141">
+      <c r="K2" s="142">
         <v>3.125E-2</v>
       </c>
-      <c r="L2" s="141">
+      <c r="L2" s="142">
         <v>0.1875</v>
       </c>
-      <c r="M2" s="141">
+      <c r="M2" s="142">
         <v>3.125E-2</v>
       </c>
       <c r="N2" s="48"/>
-      <c r="O2" s="140">
+      <c r="O2" s="141">
         <v>6.25E-2</v>
       </c>
       <c r="P2" s="48"/>
       <c r="Q2" s="48"/>
       <c r="R2" s="48"/>
-      <c r="S2" s="181">
+      <c r="S2" s="182">
         <v>0.21875</v>
       </c>
       <c r="T2" s="1">
@@ -4015,37 +4506,37 @@
       <c r="B3" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="132" t="s">
+      <c r="C3" s="133" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="130">
+      <c r="D3" s="131">
         <v>1</v>
       </c>
-      <c r="E3" s="114"/>
-      <c r="F3" s="114"/>
-      <c r="G3" s="114"/>
-      <c r="H3" s="114"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="115"/>
+      <c r="G3" s="115"/>
+      <c r="H3" s="115"/>
       <c r="I3" s="68">
         <v>0</v>
       </c>
-      <c r="J3" s="114"/>
-      <c r="K3" s="186">
-        <v>0</v>
-      </c>
-      <c r="L3" s="186">
-        <v>0</v>
-      </c>
-      <c r="M3" s="186">
-        <v>0</v>
-      </c>
-      <c r="N3" s="113"/>
-      <c r="O3" s="115">
-        <v>0</v>
-      </c>
-      <c r="P3" s="114"/>
-      <c r="Q3" s="114"/>
-      <c r="R3" s="114"/>
-      <c r="S3" s="117">
+      <c r="J3" s="115"/>
+      <c r="K3" s="187">
+        <v>0</v>
+      </c>
+      <c r="L3" s="187">
+        <v>0</v>
+      </c>
+      <c r="M3" s="187">
+        <v>0</v>
+      </c>
+      <c r="N3" s="114"/>
+      <c r="O3" s="116">
+        <v>0</v>
+      </c>
+      <c r="P3" s="115"/>
+      <c r="Q3" s="115"/>
+      <c r="R3" s="115"/>
+      <c r="S3" s="118">
         <v>0</v>
       </c>
       <c r="T3" s="1">
@@ -4060,21 +4551,21 @@
       <c r="B4" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="133" t="s">
+      <c r="C4" s="134" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="151">
+      <c r="D4" s="152">
         <v>0</v>
       </c>
       <c r="E4" s="109"/>
       <c r="F4" s="109"/>
       <c r="G4" s="109"/>
       <c r="H4" s="109"/>
-      <c r="I4" s="130">
+      <c r="I4" s="131">
         <v>0.22222222222222199</v>
       </c>
       <c r="J4" s="109"/>
-      <c r="K4" s="150">
+      <c r="K4" s="151">
         <v>0</v>
       </c>
       <c r="L4" s="111">
@@ -4090,7 +4581,7 @@
       <c r="P4" s="109"/>
       <c r="Q4" s="109"/>
       <c r="R4" s="109"/>
-      <c r="S4" s="187">
+      <c r="S4" s="188">
         <v>0</v>
       </c>
       <c r="T4" s="1">
@@ -4105,27 +4596,27 @@
       <c r="B5" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="134" t="s">
+      <c r="C5" s="135" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="182">
+      <c r="D5" s="183">
         <v>0</v>
       </c>
       <c r="E5" s="109"/>
       <c r="F5" s="109"/>
       <c r="G5" s="109"/>
       <c r="H5" s="109"/>
-      <c r="I5" s="151">
+      <c r="I5" s="152">
         <v>0</v>
       </c>
       <c r="J5" s="109"/>
-      <c r="K5" s="130">
+      <c r="K5" s="131">
         <v>0.1</v>
       </c>
-      <c r="L5" s="150">
-        <v>0</v>
-      </c>
-      <c r="M5" s="182">
+      <c r="L5" s="151">
+        <v>0</v>
+      </c>
+      <c r="M5" s="183">
         <v>0</v>
       </c>
       <c r="N5" s="108"/>
@@ -4135,7 +4626,7 @@
       <c r="P5" s="109"/>
       <c r="Q5" s="109"/>
       <c r="R5" s="109"/>
-      <c r="S5" s="188">
+      <c r="S5" s="189">
         <v>0.7</v>
       </c>
       <c r="T5" s="1">
@@ -4153,7 +4644,7 @@
       <c r="C6" s="93" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="182">
+      <c r="D6" s="183">
         <v>0</v>
       </c>
       <c r="E6" s="109"/>
@@ -4164,13 +4655,13 @@
         <v>0.125</v>
       </c>
       <c r="J6" s="109"/>
-      <c r="K6" s="151">
-        <v>0</v>
-      </c>
-      <c r="L6" s="130">
+      <c r="K6" s="152">
+        <v>0</v>
+      </c>
+      <c r="L6" s="131">
         <v>0.75</v>
       </c>
-      <c r="M6" s="183">
+      <c r="M6" s="184">
         <v>0.125</v>
       </c>
       <c r="N6" s="108"/>
@@ -4180,7 +4671,7 @@
       <c r="P6" s="109"/>
       <c r="Q6" s="109"/>
       <c r="R6" s="109"/>
-      <c r="S6" s="187">
+      <c r="S6" s="188">
         <v>0</v>
       </c>
       <c r="T6" s="1">
@@ -4195,37 +4686,37 @@
       <c r="B7" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="135" t="s">
+      <c r="C7" s="136" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="182">
+      <c r="D7" s="183">
         <v>0</v>
       </c>
       <c r="E7" s="109"/>
       <c r="F7" s="109"/>
       <c r="G7" s="109"/>
       <c r="H7" s="109"/>
-      <c r="I7" s="182">
+      <c r="I7" s="183">
         <v>0</v>
       </c>
       <c r="J7" s="109"/>
-      <c r="K7" s="182">
-        <v>0</v>
-      </c>
-      <c r="L7" s="151">
-        <v>0</v>
-      </c>
-      <c r="M7" s="182">
+      <c r="K7" s="183">
+        <v>0</v>
+      </c>
+      <c r="L7" s="152">
+        <v>0</v>
+      </c>
+      <c r="M7" s="183">
         <v>0</v>
       </c>
       <c r="N7" s="108"/>
-      <c r="O7" s="126">
+      <c r="O7" s="127">
         <v>0.22222222222222199</v>
       </c>
       <c r="P7" s="109"/>
       <c r="Q7" s="109"/>
       <c r="R7" s="109"/>
-      <c r="S7" s="189">
+      <c r="S7" s="190">
         <v>0.77777777777777701</v>
       </c>
       <c r="T7" s="1">
@@ -4240,7 +4731,7 @@
       <c r="B8" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="184" t="s">
+      <c r="C8" s="185" t="s">
         <v>30</v>
       </c>
       <c r="D8" s="71">
@@ -4270,7 +4761,7 @@
       <c r="P8" s="76"/>
       <c r="Q8" s="76"/>
       <c r="R8" s="76"/>
-      <c r="S8" s="126">
+      <c r="S8" s="127">
         <v>1</v>
       </c>
       <c r="T8" s="1">
@@ -4285,36 +4776,36 @@
       <c r="B9" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="136" t="s">
+      <c r="C9" s="137" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="186">
-        <v>0</v>
-      </c>
-      <c r="E9" s="114"/>
-      <c r="F9" s="114"/>
-      <c r="G9" s="114"/>
-      <c r="H9" s="114"/>
-      <c r="I9" s="186">
-        <v>0</v>
-      </c>
-      <c r="J9" s="114"/>
-      <c r="K9" s="186">
-        <v>0</v>
-      </c>
-      <c r="L9" s="186">
-        <v>0</v>
-      </c>
-      <c r="M9" s="186">
-        <v>0</v>
-      </c>
-      <c r="N9" s="113"/>
-      <c r="O9" s="131">
+      <c r="D9" s="187">
+        <v>0</v>
+      </c>
+      <c r="E9" s="115"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="115"/>
+      <c r="H9" s="115"/>
+      <c r="I9" s="187">
+        <v>0</v>
+      </c>
+      <c r="J9" s="115"/>
+      <c r="K9" s="187">
+        <v>0</v>
+      </c>
+      <c r="L9" s="187">
+        <v>0</v>
+      </c>
+      <c r="M9" s="187">
+        <v>0</v>
+      </c>
+      <c r="N9" s="114"/>
+      <c r="O9" s="132">
         <v>1</v>
       </c>
-      <c r="P9" s="114"/>
-      <c r="Q9" s="114"/>
-      <c r="R9" s="114"/>
+      <c r="P9" s="115"/>
+      <c r="Q9" s="115"/>
+      <c r="R9" s="115"/>
       <c r="S9" s="4">
         <v>0</v>
       </c>
@@ -4330,7 +4821,7 @@
       <c r="B10" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="185" t="s">
+      <c r="C10" s="186" t="s">
         <v>30</v>
       </c>
       <c r="D10" s="71">
@@ -4360,7 +4851,7 @@
       <c r="P10" s="76"/>
       <c r="Q10" s="76"/>
       <c r="R10" s="76"/>
-      <c r="S10" s="131">
+      <c r="S10" s="132">
         <v>1</v>
       </c>
       <c r="T10" s="1">
@@ -4475,16 +4966,16 @@
       <c r="B2" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="138"/>
+      <c r="C2" s="139"/>
       <c r="D2" s="75"/>
       <c r="E2" s="75"/>
-      <c r="F2" s="141">
+      <c r="F2" s="142">
         <v>0.33333333333333298</v>
       </c>
       <c r="G2" s="75"/>
       <c r="H2" s="75"/>
       <c r="I2" s="75"/>
-      <c r="J2" s="141">
+      <c r="J2" s="142">
         <v>0.38888888888888801</v>
       </c>
       <c r="K2" s="48"/>
@@ -4492,7 +4983,7 @@
       <c r="M2" s="68">
         <v>0</v>
       </c>
-      <c r="N2" s="140">
+      <c r="N2" s="141">
         <v>0.27777777777777701</v>
       </c>
       <c r="O2" s="75"/>
@@ -4501,7 +4992,7 @@
         <v>0</v>
       </c>
       <c r="R2" s="75"/>
-      <c r="S2" s="143"/>
+      <c r="S2" s="144"/>
       <c r="T2" s="1">
         <f>SUM(D2:S2)</f>
         <v>0.999999999999998</v>
@@ -4523,7 +5014,7 @@
       <c r="G3" s="77"/>
       <c r="H3" s="77"/>
       <c r="I3" s="77"/>
-      <c r="J3" s="142">
+      <c r="J3" s="143">
         <v>0.04</v>
       </c>
       <c r="K3" s="49"/>
@@ -4531,16 +5022,16 @@
       <c r="M3" s="24">
         <v>0</v>
       </c>
-      <c r="N3" s="139">
+      <c r="N3" s="140">
         <v>0.24</v>
       </c>
       <c r="O3" s="77"/>
       <c r="P3" s="77"/>
-      <c r="Q3" s="139">
+      <c r="Q3" s="140">
         <v>0.72</v>
       </c>
       <c r="R3" s="77"/>
-      <c r="S3" s="144"/>
+      <c r="S3" s="145"/>
       <c r="T3" s="1">
         <f t="shared" ref="T3:T25" si="0">SUM(D3:S3)</f>
         <v>1</v>
@@ -4556,30 +5047,30 @@
       <c r="C4" s="65"/>
       <c r="D4" s="77"/>
       <c r="E4" s="77"/>
-      <c r="F4" s="142">
+      <c r="F4" s="143">
         <v>5.2631578947368397E-2</v>
       </c>
       <c r="G4" s="77"/>
       <c r="H4" s="77"/>
       <c r="I4" s="77"/>
-      <c r="J4" s="142">
+      <c r="J4" s="143">
         <v>5.2631578947368397E-2</v>
       </c>
       <c r="K4" s="49"/>
       <c r="L4" s="49"/>
-      <c r="M4" s="142">
+      <c r="M4" s="143">
         <v>5.2631578947368397E-2</v>
       </c>
-      <c r="N4" s="139">
+      <c r="N4" s="140">
         <v>0.105263157894736</v>
       </c>
       <c r="O4" s="77"/>
       <c r="P4" s="77"/>
-      <c r="Q4" s="139">
+      <c r="Q4" s="140">
         <v>0.73684210526315697</v>
       </c>
       <c r="R4" s="77"/>
-      <c r="S4" s="144"/>
+      <c r="S4" s="145"/>
       <c r="T4" s="1">
         <f t="shared" si="0"/>
         <v>0.99999999999999822</v>
@@ -4592,7 +5083,7 @@
       <c r="B5" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="132" t="s">
+      <c r="C5" s="133" t="s">
         <v>17</v>
       </c>
       <c r="D5" s="75"/>
@@ -4620,7 +5111,7 @@
         <v>0</v>
       </c>
       <c r="R5" s="75"/>
-      <c r="S5" s="143"/>
+      <c r="S5" s="144"/>
       <c r="T5" s="1">
         <f t="shared" si="0"/>
         <v>0.999999999999999</v>
@@ -4633,12 +5124,12 @@
       <c r="B6" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="169" t="s">
+      <c r="C6" s="170" t="s">
         <v>17</v>
       </c>
       <c r="D6" s="77"/>
       <c r="E6" s="77"/>
-      <c r="F6" s="154">
+      <c r="F6" s="155">
         <v>0</v>
       </c>
       <c r="G6" s="77"/>
@@ -4661,7 +5152,7 @@
         <v>0</v>
       </c>
       <c r="R6" s="77"/>
-      <c r="S6" s="144"/>
+      <c r="S6" s="145"/>
       <c r="T6" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4674,12 +5165,12 @@
       <c r="B7" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="170" t="s">
+      <c r="C7" s="171" t="s">
         <v>17</v>
       </c>
       <c r="D7" s="83"/>
       <c r="E7" s="83"/>
-      <c r="F7" s="155">
+      <c r="F7" s="156">
         <v>0</v>
       </c>
       <c r="G7" s="83"/>
@@ -4690,7 +5181,7 @@
       </c>
       <c r="K7" s="51"/>
       <c r="L7" s="51"/>
-      <c r="M7" s="151">
+      <c r="M7" s="152">
         <v>0</v>
       </c>
       <c r="N7" s="84">
@@ -4702,7 +5193,7 @@
         <v>0</v>
       </c>
       <c r="R7" s="83"/>
-      <c r="S7" s="152"/>
+      <c r="S7" s="153"/>
       <c r="T7" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4715,7 +5206,7 @@
       <c r="B8" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="171" t="s">
+      <c r="C8" s="172" t="s">
         <v>21</v>
       </c>
       <c r="D8" s="81"/>
@@ -4731,7 +5222,7 @@
       </c>
       <c r="K8" s="52"/>
       <c r="L8" s="52"/>
-      <c r="M8" s="150">
+      <c r="M8" s="151">
         <v>0</v>
       </c>
       <c r="N8" s="82">
@@ -4743,7 +5234,7 @@
         <v>0</v>
       </c>
       <c r="R8" s="81"/>
-      <c r="S8" s="153"/>
+      <c r="S8" s="154"/>
       <c r="T8" s="1">
         <f t="shared" si="0"/>
         <v>0.99999999999999889</v>
@@ -4756,7 +5247,7 @@
       <c r="B9" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="133" t="s">
+      <c r="C9" s="134" t="s">
         <v>21</v>
       </c>
       <c r="D9" s="77"/>
@@ -4767,7 +5258,7 @@
       <c r="G9" s="77"/>
       <c r="H9" s="77"/>
       <c r="I9" s="77"/>
-      <c r="J9" s="156">
+      <c r="J9" s="157">
         <v>0</v>
       </c>
       <c r="K9" s="49"/>
@@ -4784,7 +5275,7 @@
         <v>0</v>
       </c>
       <c r="R9" s="77"/>
-      <c r="S9" s="144"/>
+      <c r="S9" s="145"/>
       <c r="T9" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4797,7 +5288,7 @@
       <c r="B10" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="172" t="s">
+      <c r="C10" s="173" t="s">
         <v>21</v>
       </c>
       <c r="D10" s="83"/>
@@ -4808,7 +5299,7 @@
       <c r="G10" s="83"/>
       <c r="H10" s="83"/>
       <c r="I10" s="83"/>
-      <c r="J10" s="157">
+      <c r="J10" s="158">
         <v>0</v>
       </c>
       <c r="K10" s="51"/>
@@ -4825,7 +5316,7 @@
         <v>0</v>
       </c>
       <c r="R10" s="83"/>
-      <c r="S10" s="152"/>
+      <c r="S10" s="153"/>
       <c r="T10" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4838,7 +5329,7 @@
       <c r="B11" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="173" t="s">
+      <c r="C11" s="174" t="s">
         <v>25</v>
       </c>
       <c r="D11" s="81"/>
@@ -4854,10 +5345,10 @@
       </c>
       <c r="K11" s="52"/>
       <c r="L11" s="52"/>
-      <c r="M11" s="150">
-        <v>0</v>
-      </c>
-      <c r="N11" s="146">
+      <c r="M11" s="151">
+        <v>0</v>
+      </c>
+      <c r="N11" s="147">
         <v>0.27777777777777701</v>
       </c>
       <c r="O11" s="81"/>
@@ -4866,7 +5357,7 @@
         <v>0</v>
       </c>
       <c r="R11" s="81"/>
-      <c r="S11" s="153"/>
+      <c r="S11" s="154"/>
       <c r="T11" s="1">
         <f t="shared" si="0"/>
         <v>0.999999999999998</v>
@@ -4879,7 +5370,7 @@
       <c r="B12" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="134" t="s">
+      <c r="C12" s="135" t="s">
         <v>25</v>
       </c>
       <c r="D12" s="77"/>
@@ -4898,7 +5389,7 @@
       <c r="M12" s="24">
         <v>0</v>
       </c>
-      <c r="N12" s="158">
+      <c r="N12" s="159">
         <v>0</v>
       </c>
       <c r="O12" s="77"/>
@@ -4907,7 +5398,7 @@
         <v>0</v>
       </c>
       <c r="R12" s="77"/>
-      <c r="S12" s="144"/>
+      <c r="S12" s="145"/>
       <c r="T12" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4920,7 +5411,7 @@
       <c r="B13" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="174" t="s">
+      <c r="C13" s="175" t="s">
         <v>25</v>
       </c>
       <c r="D13" s="83"/>
@@ -4939,7 +5430,7 @@
       <c r="M13" s="84">
         <v>0</v>
       </c>
-      <c r="N13" s="157">
+      <c r="N13" s="158">
         <v>0</v>
       </c>
       <c r="O13" s="83"/>
@@ -4948,7 +5439,7 @@
         <v>0</v>
       </c>
       <c r="R13" s="83"/>
-      <c r="S13" s="152"/>
+      <c r="S13" s="153"/>
       <c r="T13" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4961,7 +5452,7 @@
       <c r="B14" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="175" t="s">
+      <c r="C14" s="176" t="s">
         <v>28</v>
       </c>
       <c r="D14" s="81"/>
@@ -4977,7 +5468,7 @@
       </c>
       <c r="K14" s="52"/>
       <c r="L14" s="52"/>
-      <c r="M14" s="150">
+      <c r="M14" s="151">
         <v>0</v>
       </c>
       <c r="N14" s="62">
@@ -4985,11 +5476,11 @@
       </c>
       <c r="O14" s="81"/>
       <c r="P14" s="81"/>
-      <c r="Q14" s="146">
+      <c r="Q14" s="147">
         <v>0</v>
       </c>
       <c r="R14" s="81"/>
-      <c r="S14" s="153"/>
+      <c r="S14" s="154"/>
       <c r="T14" s="1">
         <f t="shared" si="0"/>
         <v>0.999999999999998</v>
@@ -5030,7 +5521,7 @@
         <v>0.85714285714285698</v>
       </c>
       <c r="R15" s="77"/>
-      <c r="S15" s="144"/>
+      <c r="S15" s="145"/>
       <c r="T15" s="1">
         <f t="shared" si="0"/>
         <v>0.999999999999999</v>
@@ -5043,7 +5534,7 @@
       <c r="B16" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="167" t="s">
+      <c r="C16" s="168" t="s">
         <v>28</v>
       </c>
       <c r="D16" s="76"/>
@@ -5071,7 +5562,7 @@
         <v>0.85714285714285698</v>
       </c>
       <c r="R16" s="76"/>
-      <c r="S16" s="145"/>
+      <c r="S16" s="146"/>
       <c r="T16" s="1">
         <f t="shared" si="0"/>
         <v>0.99999999999999978</v>
@@ -5089,7 +5580,7 @@
       </c>
       <c r="D17" s="75"/>
       <c r="E17" s="75"/>
-      <c r="F17" s="146">
+      <c r="F17" s="147">
         <v>0.33333333333333298</v>
       </c>
       <c r="G17" s="75"/>
@@ -5112,7 +5603,7 @@
         <v>0</v>
       </c>
       <c r="R17" s="75"/>
-      <c r="S17" s="143"/>
+      <c r="S17" s="144"/>
       <c r="T17" s="1">
         <f t="shared" si="0"/>
         <v>0.999999999999998</v>
@@ -5125,12 +5616,12 @@
       <c r="B18" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="176" t="s">
+      <c r="C18" s="177" t="s">
         <v>17</v>
       </c>
       <c r="D18" s="77"/>
       <c r="E18" s="77"/>
-      <c r="F18" s="147">
+      <c r="F18" s="148">
         <v>0</v>
       </c>
       <c r="G18" s="77"/>
@@ -5153,7 +5644,7 @@
         <v>0</v>
       </c>
       <c r="R18" s="77"/>
-      <c r="S18" s="144"/>
+      <c r="S18" s="145"/>
       <c r="T18" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5171,7 +5662,7 @@
       </c>
       <c r="D19" s="83"/>
       <c r="E19" s="83"/>
-      <c r="F19" s="159">
+      <c r="F19" s="160">
         <v>0</v>
       </c>
       <c r="G19" s="83"/>
@@ -5194,7 +5685,7 @@
         <v>0</v>
       </c>
       <c r="R19" s="83"/>
-      <c r="S19" s="152"/>
+      <c r="S19" s="153"/>
       <c r="T19" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5207,7 +5698,7 @@
       <c r="B20" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="136" t="s">
+      <c r="C20" s="137" t="s">
         <v>21</v>
       </c>
       <c r="D20" s="81"/>
@@ -5218,7 +5709,7 @@
       <c r="G20" s="81"/>
       <c r="H20" s="81"/>
       <c r="I20" s="81"/>
-      <c r="J20" s="160">
+      <c r="J20" s="161">
         <v>0.38888888888888801</v>
       </c>
       <c r="K20" s="52"/>
@@ -5235,7 +5726,7 @@
         <v>0</v>
       </c>
       <c r="R20" s="81"/>
-      <c r="S20" s="153"/>
+      <c r="S20" s="154"/>
       <c r="T20" s="1">
         <f t="shared" si="0"/>
         <v>0.999999999999998</v>
@@ -5248,7 +5739,7 @@
       <c r="B21" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C21" s="177" t="s">
+      <c r="C21" s="178" t="s">
         <v>21</v>
       </c>
       <c r="D21" s="77"/>
@@ -5259,7 +5750,7 @@
       <c r="G21" s="77"/>
       <c r="H21" s="77"/>
       <c r="I21" s="77"/>
-      <c r="J21" s="158">
+      <c r="J21" s="159">
         <v>0</v>
       </c>
       <c r="K21" s="49"/>
@@ -5276,7 +5767,7 @@
         <v>0</v>
       </c>
       <c r="R21" s="77"/>
-      <c r="S21" s="144"/>
+      <c r="S21" s="145"/>
       <c r="T21" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5289,7 +5780,7 @@
       <c r="B22" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C22" s="178" t="s">
+      <c r="C22" s="179" t="s">
         <v>21</v>
       </c>
       <c r="D22" s="83"/>
@@ -5300,7 +5791,7 @@
       <c r="G22" s="83"/>
       <c r="H22" s="83"/>
       <c r="I22" s="83"/>
-      <c r="J22" s="157">
+      <c r="J22" s="158">
         <v>0</v>
       </c>
       <c r="K22" s="51"/>
@@ -5317,7 +5808,7 @@
         <v>0</v>
       </c>
       <c r="R22" s="83"/>
-      <c r="S22" s="152"/>
+      <c r="S22" s="153"/>
       <c r="T22" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5330,7 +5821,7 @@
       <c r="B23" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="179" t="s">
+      <c r="C23" s="180" t="s">
         <v>28</v>
       </c>
       <c r="D23" s="77"/>
@@ -5354,11 +5845,11 @@
       </c>
       <c r="O23" s="77"/>
       <c r="P23" s="77"/>
-      <c r="Q23" s="146">
+      <c r="Q23" s="147">
         <v>0</v>
       </c>
       <c r="R23" s="77"/>
-      <c r="S23" s="144"/>
+      <c r="S23" s="145"/>
       <c r="T23" s="1">
         <f t="shared" si="0"/>
         <v>0.99999999999999889</v>
@@ -5371,7 +5862,7 @@
       <c r="B24" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C24" s="180" t="s">
+      <c r="C24" s="181" t="s">
         <v>28</v>
       </c>
       <c r="D24" s="77"/>
@@ -5399,7 +5890,7 @@
         <v>0.8</v>
       </c>
       <c r="R24" s="77"/>
-      <c r="S24" s="144"/>
+      <c r="S24" s="145"/>
       <c r="T24" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -5412,7 +5903,7 @@
       <c r="B25" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="137" t="s">
+      <c r="C25" s="138" t="s">
         <v>28</v>
       </c>
       <c r="D25" s="76"/>
@@ -5440,7 +5931,7 @@
         <v>0.75</v>
       </c>
       <c r="R25" s="76"/>
-      <c r="S25" s="145"/>
+      <c r="S25" s="146"/>
       <c r="T25" s="1">
         <f t="shared" si="0"/>
         <v>1</v>

--- a/patterns/results/exp1/4bins-results.xlsx
+++ b/patterns/results/exp1/4bins-results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E143A659-665A-DD45-BAF3-FB505A1275A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59FFEA09-34E1-3F49-9EE6-410F73ED2096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2060" yWindow="1020" windowWidth="33880" windowHeight="19340" activeTab="4" xr2:uid="{9429E1C1-1F54-8A42-9286-E37255B8DAF7}"/>
+    <workbookView xWindow="2060" yWindow="1020" windowWidth="31680" windowHeight="19340" activeTab="4" xr2:uid="{9429E1C1-1F54-8A42-9286-E37255B8DAF7}"/>
   </bookViews>
   <sheets>
     <sheet name="GO" sheetId="1" r:id="rId1"/>
@@ -21,14 +21,14 @@
   </sheets>
   <definedNames>
     <definedName name="metrics_acl" localSheetId="2">ACL!$A$8:$L$10</definedName>
-    <definedName name="metrics_cqrs_1" localSheetId="1">CQRS!$A$17:$L$19</definedName>
-    <definedName name="metrics_ga" localSheetId="3">GA!$A$12:$L$14</definedName>
-    <definedName name="metrics_go" localSheetId="0">GO!$A$27:$L$29</definedName>
+    <definedName name="metrics_cqrs_2" localSheetId="1">CQRS!$A$22:$L$24</definedName>
+    <definedName name="metrics_ga_1" localSheetId="3">GA!$A$19:$L$21</definedName>
+    <definedName name="metrics_go_1" localSheetId="0">GO!$A$34:$L$36</definedName>
     <definedName name="metrics_paf" localSheetId="4">PAF!$A$27:$L$29</definedName>
     <definedName name="results_acl_1" localSheetId="2">ACL!$A$1:$S$6</definedName>
     <definedName name="results_cqrs_1" localSheetId="1">CQRS!$A$1:$S$15</definedName>
-    <definedName name="results_ga_1" localSheetId="3">GA!$A$1:$S$10</definedName>
-    <definedName name="results_go_1" localSheetId="0">GO!$A$1:$S$25</definedName>
+    <definedName name="results_ga_1" localSheetId="3">GA!$A$1:$S$13</definedName>
+    <definedName name="results_go_1" localSheetId="0">GO!$A$1:$S$28</definedName>
     <definedName name="results_paf_1" localSheetId="4">PAF!$A$1:$S$25</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -71,7 +71,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="2" xr16:uid="{1A2C4BBC-B258-B443-99E1-E260B10683EC}" name="metrics-cqrs" type="6" refreshedVersion="8" background="1" saveData="1">
+  <connection id="2" xr16:uid="{8F71BCCB-9DA0-144F-9D06-AF730388E029}" name="metrics-cqrs1" type="6" refreshedVersion="8" background="1" saveData="1">
     <textPr codePage="10000" sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/metrics-cqrs.csv" thousands="." comma="1">
       <textFields count="12">
         <textField/>
@@ -89,7 +89,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="3" xr16:uid="{1A55998B-10E0-5D45-9211-5397053EE175}" name="metrics-ga" type="6" refreshedVersion="8" background="1" saveData="1">
+  <connection id="3" xr16:uid="{0A4337A6-686E-6040-92B7-22F1899AA00C}" name="metrics-ga1" type="6" refreshedVersion="8" background="1" saveData="1">
     <textPr codePage="10000" sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/metrics-ga.csv" thousands="." comma="1">
       <textFields count="12">
         <textField/>
@@ -107,7 +107,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="4" xr16:uid="{2114976D-1869-8740-9F18-CEC2C35CD2E0}" name="metrics-go" type="6" refreshedVersion="8" background="1" saveData="1">
+  <connection id="4" xr16:uid="{134B4E51-F17D-E24F-8C43-5587947006CC}" name="metrics-go1" type="6" refreshedVersion="8" background="1" saveData="1">
     <textPr codePage="10000" sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/metrics-go.csv" thousands="." comma="1">
       <textFields count="12">
         <textField/>
@@ -272,7 +272,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="51">
   <si>
     <t>method</t>
   </si>
@@ -420,6 +420,12 @@
   <si>
     <t>complexity_std</t>
   </si>
+  <si>
+    <t>cart: 4 boxes</t>
+  </si>
+  <si>
+    <t>cart: 5 boxes</t>
+  </si>
 </sst>
 </file>
 
@@ -468,7 +474,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -553,8 +559,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="38">
+  <borders count="41">
     <border>
       <left/>
       <right/>
@@ -1009,11 +1027,46 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="167">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1116,7 +1169,6 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -1129,6 +1181,7 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1137,8 +1190,6 @@
     <xf numFmtId="2" fontId="1" fillId="13" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="14" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="14" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="14" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1159,7 +1210,6 @@
     <xf numFmtId="2" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1170,6 +1220,42 @@
     <xf numFmtId="2" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="13" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="36" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1191,16 +1277,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>449384</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>85130</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>422168</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>193989</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>26889</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>151452</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>362530</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>60738</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1229,7 +1315,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2780741" y="6235559"/>
+          <a:off x="4667597" y="7759560"/>
           <a:ext cx="7251933" cy="6452607"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1246,16 +1332,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>199571</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>96158</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>317500</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>87086</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>244324</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>185057</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>271538</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>175986</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1284,7 +1370,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2422071" y="4232729"/>
+          <a:off x="2222500" y="5021943"/>
           <a:ext cx="7338181" cy="6275614"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1307,8 +1393,8 @@
       <xdr:rowOff>70477</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>692405</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>53172</xdr:colOff>
       <xdr:row>42</xdr:row>
       <xdr:rowOff>157422</xdr:rowOff>
     </xdr:to>
@@ -1357,15 +1443,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>385885</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>87923</xdr:rowOff>
+      <xdr:colOff>385884</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>124209</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>128953</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>176822</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>373881</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>13537</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1394,7 +1480,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2309028" y="3262923"/>
+          <a:off x="2073170" y="4696209"/>
           <a:ext cx="7344925" cy="6275613"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1417,8 +1503,8 @@
       <xdr:rowOff>96593</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>933084</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>225512</xdr:colOff>
       <xdr:row>61</xdr:row>
       <xdr:rowOff>188668</xdr:rowOff>
     </xdr:to>
@@ -1463,7 +1549,7 @@
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="metrics-go" connectionId="4" xr16:uid="{88B83275-2535-0042-861D-3DC7927985B6}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="metrics_go_1" connectionId="4" xr16:uid="{63DCC8F5-17EE-1340-9B93-10B151E3B558}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable10.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1475,7 +1561,7 @@
 </file>
 
 <file path=xl/queryTables/queryTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="metrics_cqrs_1" connectionId="2" xr16:uid="{71614961-092E-4F4B-A5C3-D642E6580EA2}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="metrics_cqrs_2" connectionId="2" xr16:uid="{77D8AEF2-F397-354F-B98D-BFCA42AA18FB}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1491,7 +1577,7 @@
 </file>
 
 <file path=xl/queryTables/queryTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="metrics-ga" connectionId="3" xr16:uid="{E584EA8A-CDED-294E-AEF1-EC567A4582B7}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="metrics_ga_1" connectionId="3" xr16:uid="{D3FD6001-8A85-AD43-91C6-1F875D4FBFD9}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable8.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1819,15 +1905,1206 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24E96F0A-AEE0-C546-9A77-15D1887CC59C}">
-  <dimension ref="A1:V29"/>
+  <dimension ref="A1:V36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5" customWidth="1"/>
+    <col min="3" max="3" width="11.5" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="15.5" customWidth="1"/>
+    <col min="9" max="9" width="11.6640625" customWidth="1"/>
+    <col min="10" max="10" width="10.33203125" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="14.83203125" customWidth="1"/>
+    <col min="13" max="13" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="M1" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="N1" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="O1" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="P1" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="R1" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="S1" s="21" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="17"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="88">
+        <v>0</v>
+      </c>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
+      <c r="N2" s="88">
+        <v>0</v>
+      </c>
+      <c r="O2" s="88">
+        <v>0</v>
+      </c>
+      <c r="P2" s="102">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="88">
+        <v>0</v>
+      </c>
+      <c r="R2" s="22"/>
+      <c r="S2" s="89">
+        <v>0</v>
+      </c>
+      <c r="T2" s="1">
+        <f>SUM(D2:S2)</f>
+        <v>1</v>
+      </c>
+      <c r="V2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A3" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="15"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="109">
+        <v>0.11111111111111099</v>
+      </c>
+      <c r="L3" s="23"/>
+      <c r="M3" s="23"/>
+      <c r="N3" s="90">
+        <v>0</v>
+      </c>
+      <c r="O3" s="101">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="P3" s="90">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="90">
+        <v>0</v>
+      </c>
+      <c r="R3" s="23"/>
+      <c r="S3" s="103">
+        <v>0.55555555555555503</v>
+      </c>
+      <c r="T3" s="1">
+        <f t="shared" ref="T3:T28" si="0">SUM(D3:S3)</f>
+        <v>0.999999999999999</v>
+      </c>
+      <c r="V3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="15"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="90">
+        <v>0</v>
+      </c>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="109">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="O4" s="90">
+        <v>0</v>
+      </c>
+      <c r="P4" s="90">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="101">
+        <v>0.71428571428571397</v>
+      </c>
+      <c r="R4" s="23"/>
+      <c r="S4" s="91">
+        <v>0</v>
+      </c>
+      <c r="T4" s="1">
+        <f t="shared" si="0"/>
+        <v>0.99999999999999889</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="60" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="22"/>
+      <c r="K5" s="88"/>
+      <c r="L5" s="22"/>
+      <c r="M5" s="22"/>
+      <c r="N5" s="88"/>
+      <c r="O5" s="92">
+        <v>0</v>
+      </c>
+      <c r="P5" s="88"/>
+      <c r="Q5" s="88"/>
+      <c r="R5" s="22"/>
+      <c r="S5" s="89"/>
+      <c r="T5" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="75" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="90">
+        <v>0.11111111111111099</v>
+      </c>
+      <c r="L6" s="23"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="90"/>
+      <c r="O6" s="104">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="P6" s="90"/>
+      <c r="Q6" s="90"/>
+      <c r="R6" s="23"/>
+      <c r="S6" s="91">
+        <v>0.55555555555555503</v>
+      </c>
+      <c r="T6" s="1">
+        <f t="shared" si="0"/>
+        <v>0.999999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="76" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="93"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="93"/>
+      <c r="O7" s="94">
+        <v>0</v>
+      </c>
+      <c r="P7" s="90"/>
+      <c r="Q7" s="93"/>
+      <c r="R7" s="25"/>
+      <c r="S7" s="95"/>
+      <c r="T7" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="77" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="96"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="26"/>
+      <c r="N8" s="96"/>
+      <c r="O8" s="90"/>
+      <c r="P8" s="105">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="96"/>
+      <c r="R8" s="26"/>
+      <c r="S8" s="97"/>
+      <c r="T8" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="61" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="90"/>
+      <c r="L9" s="23"/>
+      <c r="M9" s="23"/>
+      <c r="N9" s="90"/>
+      <c r="O9" s="90"/>
+      <c r="P9" s="98">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="90"/>
+      <c r="R9" s="23"/>
+      <c r="S9" s="91"/>
+      <c r="T9" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="78" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="93"/>
+      <c r="L10" s="25"/>
+      <c r="M10" s="25"/>
+      <c r="N10" s="93"/>
+      <c r="O10" s="93"/>
+      <c r="P10" s="94">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="90"/>
+      <c r="R10" s="25"/>
+      <c r="S10" s="95"/>
+      <c r="T10" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A11" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="79" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="26"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="96"/>
+      <c r="L11" s="26"/>
+      <c r="M11" s="26"/>
+      <c r="N11" s="96"/>
+      <c r="O11" s="96"/>
+      <c r="P11" s="90"/>
+      <c r="Q11" s="92">
+        <v>0</v>
+      </c>
+      <c r="R11" s="26"/>
+      <c r="S11" s="97"/>
+      <c r="T11" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A12" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="62" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="90"/>
+      <c r="L12" s="23"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="90"/>
+      <c r="O12" s="90"/>
+      <c r="P12" s="90"/>
+      <c r="Q12" s="98">
+        <v>0</v>
+      </c>
+      <c r="R12" s="23"/>
+      <c r="S12" s="91"/>
+      <c r="T12" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="80" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="93"/>
+      <c r="L13" s="25"/>
+      <c r="M13" s="25"/>
+      <c r="N13" s="93">
+        <v>0.18181818181818099</v>
+      </c>
+      <c r="O13" s="93"/>
+      <c r="P13" s="93"/>
+      <c r="Q13" s="107">
+        <v>0.81818181818181801</v>
+      </c>
+      <c r="R13" s="25"/>
+      <c r="S13" s="91"/>
+      <c r="T13" s="1">
+        <f t="shared" si="0"/>
+        <v>0.999999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A14" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="81" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="96"/>
+      <c r="L14" s="26"/>
+      <c r="M14" s="26"/>
+      <c r="N14" s="96"/>
+      <c r="O14" s="96"/>
+      <c r="P14" s="96"/>
+      <c r="Q14" s="90"/>
+      <c r="R14" s="26"/>
+      <c r="S14" s="92">
+        <v>0</v>
+      </c>
+      <c r="T14" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A15" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="90"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="90"/>
+      <c r="O15" s="90">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="P15" s="90"/>
+      <c r="Q15" s="90"/>
+      <c r="R15" s="23"/>
+      <c r="S15" s="108">
+        <v>0.71428571428571397</v>
+      </c>
+      <c r="T15" s="1">
+        <f t="shared" si="0"/>
+        <v>0.99999999999999889</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="139" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="140"/>
+      <c r="E16" s="140"/>
+      <c r="F16" s="140"/>
+      <c r="G16" s="140"/>
+      <c r="H16" s="140"/>
+      <c r="I16" s="140"/>
+      <c r="J16" s="140"/>
+      <c r="K16" s="136"/>
+      <c r="L16" s="140"/>
+      <c r="M16" s="140"/>
+      <c r="N16" s="136"/>
+      <c r="O16" s="136"/>
+      <c r="P16" s="136"/>
+      <c r="Q16" s="136"/>
+      <c r="R16" s="140"/>
+      <c r="S16" s="98">
+        <v>0</v>
+      </c>
+      <c r="T16" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="143" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="88"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="22"/>
+      <c r="N17" s="88"/>
+      <c r="O17" s="92">
+        <v>0</v>
+      </c>
+      <c r="P17" s="88"/>
+      <c r="Q17" s="88"/>
+      <c r="R17" s="22"/>
+      <c r="S17" s="89"/>
+      <c r="T17" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A18" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="141" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="144" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="140"/>
+      <c r="E18" s="140"/>
+      <c r="F18" s="140"/>
+      <c r="G18" s="140"/>
+      <c r="H18" s="140"/>
+      <c r="I18" s="140"/>
+      <c r="J18" s="140"/>
+      <c r="K18" s="136"/>
+      <c r="L18" s="140"/>
+      <c r="M18" s="140"/>
+      <c r="N18" s="136"/>
+      <c r="O18" s="108">
+        <v>1</v>
+      </c>
+      <c r="P18" s="136"/>
+      <c r="Q18" s="136"/>
+      <c r="R18" s="140"/>
+      <c r="S18" s="91"/>
+      <c r="T18" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="155" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="150" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="151" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="25"/>
+      <c r="K19" s="93"/>
+      <c r="L19" s="25"/>
+      <c r="M19" s="25"/>
+      <c r="N19" s="93"/>
+      <c r="O19" s="94">
+        <v>0</v>
+      </c>
+      <c r="P19" s="136"/>
+      <c r="Q19" s="93"/>
+      <c r="R19" s="25"/>
+      <c r="S19" s="95"/>
+      <c r="T19" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A20" s="156" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="149" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="152" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="26"/>
+      <c r="K20" s="96"/>
+      <c r="L20" s="26"/>
+      <c r="M20" s="26"/>
+      <c r="N20" s="96"/>
+      <c r="O20" s="136"/>
+      <c r="P20" s="111">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="96"/>
+      <c r="R20" s="26"/>
+      <c r="S20" s="97"/>
+      <c r="T20" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A21" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="141" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" s="140"/>
+      <c r="E21" s="140"/>
+      <c r="F21" s="140"/>
+      <c r="G21" s="140"/>
+      <c r="H21" s="140"/>
+      <c r="I21" s="140"/>
+      <c r="J21" s="140"/>
+      <c r="K21" s="136"/>
+      <c r="L21" s="140"/>
+      <c r="M21" s="140"/>
+      <c r="N21" s="136"/>
+      <c r="O21" s="136"/>
+      <c r="P21" s="98">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="136"/>
+      <c r="R21" s="140"/>
+      <c r="S21" s="91"/>
+      <c r="T21" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="155" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="150" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="25"/>
+      <c r="J22" s="25"/>
+      <c r="K22" s="93"/>
+      <c r="L22" s="25"/>
+      <c r="M22" s="25"/>
+      <c r="N22" s="93"/>
+      <c r="O22" s="93"/>
+      <c r="P22" s="94">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="136"/>
+      <c r="R22" s="25"/>
+      <c r="S22" s="95"/>
+      <c r="T22" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A23" s="156" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="149" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="138" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="26"/>
+      <c r="K23" s="96"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="26"/>
+      <c r="N23" s="96"/>
+      <c r="O23" s="96"/>
+      <c r="P23" s="136"/>
+      <c r="Q23" s="92">
+        <v>0</v>
+      </c>
+      <c r="R23" s="26"/>
+      <c r="S23" s="97"/>
+      <c r="T23" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A24" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" s="141" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="146" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="140"/>
+      <c r="E24" s="140"/>
+      <c r="F24" s="140"/>
+      <c r="G24" s="140"/>
+      <c r="H24" s="140"/>
+      <c r="I24" s="140"/>
+      <c r="J24" s="140"/>
+      <c r="K24" s="136"/>
+      <c r="L24" s="140"/>
+      <c r="M24" s="140"/>
+      <c r="N24" s="136"/>
+      <c r="O24" s="136"/>
+      <c r="P24" s="136"/>
+      <c r="Q24" s="98">
+        <v>0</v>
+      </c>
+      <c r="R24" s="140"/>
+      <c r="S24" s="91"/>
+      <c r="T24" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="155" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="150" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="154" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="25"/>
+      <c r="J25" s="25"/>
+      <c r="K25" s="93"/>
+      <c r="L25" s="25"/>
+      <c r="M25" s="25"/>
+      <c r="N25" s="93"/>
+      <c r="O25" s="93"/>
+      <c r="P25" s="93"/>
+      <c r="Q25" s="107">
+        <v>1</v>
+      </c>
+      <c r="R25" s="25"/>
+      <c r="S25" s="91"/>
+      <c r="T25" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="141" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" s="147" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" s="140"/>
+      <c r="E26" s="140"/>
+      <c r="F26" s="140"/>
+      <c r="G26" s="140"/>
+      <c r="H26" s="140"/>
+      <c r="I26" s="140"/>
+      <c r="J26" s="140"/>
+      <c r="K26" s="136"/>
+      <c r="L26" s="140"/>
+      <c r="M26" s="140"/>
+      <c r="N26" s="136"/>
+      <c r="O26" s="136"/>
+      <c r="P26" s="136"/>
+      <c r="Q26" s="136"/>
+      <c r="R26" s="140"/>
+      <c r="S26" s="92">
+        <v>0</v>
+      </c>
+      <c r="T26" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A27" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="141" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="147" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" s="140"/>
+      <c r="E27" s="140"/>
+      <c r="F27" s="140"/>
+      <c r="G27" s="140"/>
+      <c r="H27" s="140"/>
+      <c r="I27" s="140"/>
+      <c r="J27" s="140"/>
+      <c r="K27" s="136"/>
+      <c r="L27" s="140"/>
+      <c r="M27" s="140"/>
+      <c r="N27" s="136"/>
+      <c r="O27" s="136">
+        <v>0.16666666666666599</v>
+      </c>
+      <c r="P27" s="136"/>
+      <c r="Q27" s="136"/>
+      <c r="R27" s="140"/>
+      <c r="S27" s="108">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="T27" s="1">
+        <f t="shared" si="0"/>
+        <v>0.999999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="148" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="24"/>
+      <c r="I28" s="24"/>
+      <c r="J28" s="24"/>
+      <c r="K28" s="99"/>
+      <c r="L28" s="24"/>
+      <c r="M28" s="24"/>
+      <c r="N28" s="99"/>
+      <c r="O28" s="99"/>
+      <c r="P28" s="99"/>
+      <c r="Q28" s="99"/>
+      <c r="R28" s="24"/>
+      <c r="S28" s="94">
+        <v>0</v>
+      </c>
+      <c r="T28" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="D29" s="14"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A30" s="137"/>
+      <c r="B30" s="137"/>
+      <c r="C30" s="137"/>
+      <c r="D30" s="136"/>
+      <c r="E30" s="136"/>
+      <c r="F30" s="136"/>
+      <c r="G30" s="136"/>
+      <c r="H30" s="136"/>
+      <c r="I30" s="136"/>
+      <c r="J30" s="136"/>
+      <c r="K30" s="136"/>
+      <c r="L30" s="136"/>
+      <c r="M30" s="1"/>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A31" s="137"/>
+      <c r="B31" s="136"/>
+      <c r="C31" s="136"/>
+      <c r="D31" s="136"/>
+      <c r="E31" s="136"/>
+      <c r="F31" s="136"/>
+      <c r="G31" s="136"/>
+      <c r="H31" s="136"/>
+      <c r="I31" s="136"/>
+      <c r="J31" s="136"/>
+      <c r="K31" s="136"/>
+      <c r="L31" s="136"/>
+      <c r="M31" s="1"/>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A32" s="137"/>
+      <c r="B32" s="136"/>
+      <c r="C32" s="136"/>
+      <c r="D32" s="136"/>
+      <c r="E32" s="136"/>
+      <c r="F32" s="136"/>
+      <c r="G32" s="136"/>
+      <c r="H32" s="136"/>
+      <c r="I32" s="136"/>
+      <c r="J32" s="136"/>
+      <c r="K32" s="136"/>
+      <c r="L32" s="136"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A34" s="116"/>
+      <c r="B34" s="116" t="s">
+        <v>38</v>
+      </c>
+      <c r="C34" s="116" t="s">
+        <v>39</v>
+      </c>
+      <c r="D34" s="116" t="s">
+        <v>40</v>
+      </c>
+      <c r="E34" s="116" t="s">
+        <v>41</v>
+      </c>
+      <c r="F34" s="116" t="s">
+        <v>42</v>
+      </c>
+      <c r="G34" s="116" t="s">
+        <v>43</v>
+      </c>
+      <c r="H34" s="116" t="s">
+        <v>44</v>
+      </c>
+      <c r="I34" s="116" t="s">
+        <v>45</v>
+      </c>
+      <c r="J34" s="116" t="s">
+        <v>46</v>
+      </c>
+      <c r="K34" s="116" t="s">
+        <v>47</v>
+      </c>
+      <c r="L34" s="116" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" s="1">
+        <v>0.47763347763347702</v>
+      </c>
+      <c r="C35" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="D35" s="14">
+        <v>0.53174603174603097</v>
+      </c>
+      <c r="E35" s="14">
+        <v>0.31096681096681</v>
+      </c>
+      <c r="F35" s="1">
+        <v>2</v>
+      </c>
+      <c r="G35" s="14">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="H35" s="1">
+        <v>0.39198942303110901</v>
+      </c>
+      <c r="I35" s="1">
+        <v>0.46097722286464399</v>
+      </c>
+      <c r="J35" s="1">
+        <v>0.404684088380379</v>
+      </c>
+      <c r="K35" s="1">
+        <v>0.314997533323503</v>
+      </c>
+      <c r="L35" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>8</v>
+      </c>
+      <c r="B36" s="1">
+        <v>0.63888888888888895</v>
+      </c>
+      <c r="C36" s="1">
+        <v>0.48888888888888798</v>
+      </c>
+      <c r="D36" s="14">
+        <v>0.52651515151515105</v>
+      </c>
+      <c r="E36" s="14">
+        <v>0.47222222222222199</v>
+      </c>
+      <c r="F36" s="1">
+        <v>2</v>
+      </c>
+      <c r="G36" s="14">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="H36" s="1">
+        <v>0.455589429634909</v>
+      </c>
+      <c r="I36" s="1">
+        <v>0.41573970964154899</v>
+      </c>
+      <c r="J36" s="1">
+        <v>0.40324456027362099</v>
+      </c>
+      <c r="K36" s="1">
+        <v>0.39928078125199801</v>
+      </c>
+      <c r="L36" s="1">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A17:S28">
+    <sortCondition ref="C17:C28"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAF50480-301C-0843-A08D-1FF82088E86E}">
+  <dimension ref="A1:V24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9" customWidth="1"/>
-    <col min="6" max="6" width="9.1640625" customWidth="1"/>
+    <col min="3" max="3" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.5" bestFit="1" customWidth="1"/>
@@ -1842,1067 +3119,6 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="J1" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="K1" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="M1" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="N1" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="O1" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="P1" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="R1" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="S1" s="21" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="89">
-        <v>0</v>
-      </c>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="89">
-        <v>0</v>
-      </c>
-      <c r="O2" s="89">
-        <v>0</v>
-      </c>
-      <c r="P2" s="102">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="89">
-        <v>0</v>
-      </c>
-      <c r="R2" s="22"/>
-      <c r="S2" s="90">
-        <v>0</v>
-      </c>
-      <c r="T2" s="1">
-        <f>SUM(D2:S2)</f>
-        <v>1</v>
-      </c>
-      <c r="V2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A3" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="23"/>
-      <c r="K3" s="111">
-        <v>0.11111111111111099</v>
-      </c>
-      <c r="L3" s="23"/>
-      <c r="M3" s="23"/>
-      <c r="N3" s="91">
-        <v>0</v>
-      </c>
-      <c r="O3" s="101">
-        <v>0.33333333333333298</v>
-      </c>
-      <c r="P3" s="91">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="91">
-        <v>0</v>
-      </c>
-      <c r="R3" s="23"/>
-      <c r="S3" s="103">
-        <v>0.55555555555555503</v>
-      </c>
-      <c r="T3" s="1">
-        <f t="shared" ref="T3:T25" si="0">SUM(D3:S3)</f>
-        <v>0.999999999999999</v>
-      </c>
-      <c r="V3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="91">
-        <v>0</v>
-      </c>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
-      <c r="N4" s="111">
-        <v>0.28571428571428498</v>
-      </c>
-      <c r="O4" s="91">
-        <v>0</v>
-      </c>
-      <c r="P4" s="91">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="111">
-        <v>0.71428571428571397</v>
-      </c>
-      <c r="R4" s="23"/>
-      <c r="S4" s="92">
-        <v>0</v>
-      </c>
-      <c r="T4" s="1">
-        <f t="shared" si="0"/>
-        <v>0.99999999999999889</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A5" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="60" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="89"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="89"/>
-      <c r="O5" s="93">
-        <v>0</v>
-      </c>
-      <c r="P5" s="89"/>
-      <c r="Q5" s="89"/>
-      <c r="R5" s="22"/>
-      <c r="S5" s="90"/>
-      <c r="T5" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A6" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="75" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
-      <c r="K6" s="91">
-        <v>0.11111111111111099</v>
-      </c>
-      <c r="L6" s="23"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="91"/>
-      <c r="O6" s="104">
-        <v>0.33333333333333298</v>
-      </c>
-      <c r="P6" s="91"/>
-      <c r="Q6" s="91"/>
-      <c r="R6" s="23"/>
-      <c r="S6" s="92">
-        <v>0.55555555555555503</v>
-      </c>
-      <c r="T6" s="1">
-        <f t="shared" si="0"/>
-        <v>0.999999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="76" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
-      <c r="I7" s="25"/>
-      <c r="J7" s="25"/>
-      <c r="K7" s="94"/>
-      <c r="L7" s="25"/>
-      <c r="M7" s="25"/>
-      <c r="N7" s="94"/>
-      <c r="O7" s="95">
-        <v>0</v>
-      </c>
-      <c r="P7" s="91"/>
-      <c r="Q7" s="94"/>
-      <c r="R7" s="25"/>
-      <c r="S7" s="96"/>
-      <c r="T7" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="77" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="26"/>
-      <c r="K8" s="97"/>
-      <c r="L8" s="26"/>
-      <c r="M8" s="26"/>
-      <c r="N8" s="97"/>
-      <c r="O8" s="91"/>
-      <c r="P8" s="105">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="97"/>
-      <c r="R8" s="26"/>
-      <c r="S8" s="98"/>
-      <c r="T8" s="1">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="61" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="23"/>
-      <c r="K9" s="91"/>
-      <c r="L9" s="23"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="91"/>
-      <c r="O9" s="91"/>
-      <c r="P9" s="99">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="91"/>
-      <c r="R9" s="23"/>
-      <c r="S9" s="92"/>
-      <c r="T9" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="78" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="25"/>
-      <c r="J10" s="25"/>
-      <c r="K10" s="94"/>
-      <c r="L10" s="25"/>
-      <c r="M10" s="25"/>
-      <c r="N10" s="94"/>
-      <c r="O10" s="94"/>
-      <c r="P10" s="95">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="91"/>
-      <c r="R10" s="25"/>
-      <c r="S10" s="96"/>
-      <c r="T10" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A11" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" s="79" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="26"/>
-      <c r="K11" s="97"/>
-      <c r="L11" s="26"/>
-      <c r="M11" s="26"/>
-      <c r="N11" s="97"/>
-      <c r="O11" s="97"/>
-      <c r="P11" s="91"/>
-      <c r="Q11" s="93">
-        <v>0</v>
-      </c>
-      <c r="R11" s="26"/>
-      <c r="S11" s="98"/>
-      <c r="T11" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A12" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="62" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="23"/>
-      <c r="I12" s="23"/>
-      <c r="J12" s="23"/>
-      <c r="K12" s="91"/>
-      <c r="L12" s="23"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="91"/>
-      <c r="O12" s="91"/>
-      <c r="P12" s="91"/>
-      <c r="Q12" s="99">
-        <v>0</v>
-      </c>
-      <c r="R12" s="23"/>
-      <c r="S12" s="92"/>
-      <c r="T12" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="80" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="25"/>
-      <c r="I13" s="25"/>
-      <c r="J13" s="25"/>
-      <c r="K13" s="94"/>
-      <c r="L13" s="25"/>
-      <c r="M13" s="25"/>
-      <c r="N13" s="94">
-        <v>0.18181818181818099</v>
-      </c>
-      <c r="O13" s="94"/>
-      <c r="P13" s="94"/>
-      <c r="Q13" s="107">
-        <v>0.81818181818181801</v>
-      </c>
-      <c r="R13" s="25"/>
-      <c r="S13" s="92"/>
-      <c r="T13" s="1">
-        <f t="shared" si="0"/>
-        <v>0.999999999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A14" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" t="s">
-        <v>4</v>
-      </c>
-      <c r="C14" s="81" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="26"/>
-      <c r="K14" s="97"/>
-      <c r="L14" s="26"/>
-      <c r="M14" s="26"/>
-      <c r="N14" s="97"/>
-      <c r="O14" s="97"/>
-      <c r="P14" s="97"/>
-      <c r="Q14" s="91"/>
-      <c r="R14" s="26"/>
-      <c r="S14" s="93">
-        <v>0</v>
-      </c>
-      <c r="T14" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A15" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
-      <c r="I15" s="23"/>
-      <c r="J15" s="23"/>
-      <c r="K15" s="91"/>
-      <c r="L15" s="23"/>
-      <c r="M15" s="23"/>
-      <c r="N15" s="91"/>
-      <c r="O15" s="91">
-        <v>0.28571428571428498</v>
-      </c>
-      <c r="P15" s="91"/>
-      <c r="Q15" s="91"/>
-      <c r="R15" s="23"/>
-      <c r="S15" s="108">
-        <v>0.71428571428571397</v>
-      </c>
-      <c r="T15" s="1">
-        <f t="shared" si="0"/>
-        <v>0.99999999999999889</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="73" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="24"/>
-      <c r="K16" s="100"/>
-      <c r="L16" s="24"/>
-      <c r="M16" s="24"/>
-      <c r="N16" s="100"/>
-      <c r="O16" s="100"/>
-      <c r="P16" s="100"/>
-      <c r="Q16" s="100"/>
-      <c r="R16" s="24"/>
-      <c r="S16" s="95">
-        <v>0</v>
-      </c>
-      <c r="T16" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="C17" s="41" t="s">
-        <v>26</v>
-      </c>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="23"/>
-      <c r="H17" s="23"/>
-      <c r="I17" s="23"/>
-      <c r="J17" s="23"/>
-      <c r="K17" s="91"/>
-      <c r="L17" s="23"/>
-      <c r="M17" s="23"/>
-      <c r="N17" s="91"/>
-      <c r="O17" s="93">
-        <v>0</v>
-      </c>
-      <c r="P17" s="91">
-        <v>1</v>
-      </c>
-      <c r="Q17" s="91"/>
-      <c r="R17" s="23"/>
-      <c r="S17" s="92"/>
-      <c r="T17" s="1">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A18" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" t="s">
-        <v>5</v>
-      </c>
-      <c r="C18" s="82" t="s">
-        <v>26</v>
-      </c>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="23"/>
-      <c r="H18" s="23"/>
-      <c r="I18" s="23"/>
-      <c r="J18" s="23"/>
-      <c r="K18" s="91">
-        <v>0.5</v>
-      </c>
-      <c r="L18" s="23"/>
-      <c r="M18" s="23"/>
-      <c r="N18" s="91"/>
-      <c r="O18" s="108">
-        <v>0.5</v>
-      </c>
-      <c r="P18" s="91"/>
-      <c r="Q18" s="91"/>
-      <c r="R18" s="23"/>
-      <c r="S18" s="92"/>
-      <c r="T18" s="1">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="25"/>
-      <c r="J19" s="25"/>
-      <c r="K19" s="94"/>
-      <c r="L19" s="25"/>
-      <c r="M19" s="25"/>
-      <c r="N19" s="94"/>
-      <c r="O19" s="95">
-        <v>0</v>
-      </c>
-      <c r="P19" s="91"/>
-      <c r="Q19" s="94">
-        <v>1</v>
-      </c>
-      <c r="R19" s="25"/>
-      <c r="S19" s="96"/>
-      <c r="T19" s="1">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A20" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" t="s">
-        <v>4</v>
-      </c>
-      <c r="C20" s="64" t="s">
-        <v>27</v>
-      </c>
-      <c r="D20" s="26"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="26"/>
-      <c r="J20" s="26"/>
-      <c r="K20" s="26"/>
-      <c r="L20" s="26"/>
-      <c r="M20" s="26"/>
-      <c r="N20" s="26"/>
-      <c r="O20" s="91"/>
-      <c r="P20" s="105">
-        <v>1</v>
-      </c>
-      <c r="Q20" s="97"/>
-      <c r="R20" s="26"/>
-      <c r="S20" s="98"/>
-      <c r="T20" s="1">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A21" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" t="s">
-        <v>5</v>
-      </c>
-      <c r="C21" s="83" t="s">
-        <v>27</v>
-      </c>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="23"/>
-      <c r="I21" s="23"/>
-      <c r="J21" s="23"/>
-      <c r="K21" s="23"/>
-      <c r="L21" s="23"/>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="91"/>
-      <c r="P21" s="99">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="91"/>
-      <c r="R21" s="23"/>
-      <c r="S21" s="92"/>
-      <c r="T21" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="84" t="s">
-        <v>27</v>
-      </c>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="25"/>
-      <c r="I22" s="25"/>
-      <c r="J22" s="25"/>
-      <c r="K22" s="25"/>
-      <c r="L22" s="25"/>
-      <c r="M22" s="25"/>
-      <c r="N22" s="25"/>
-      <c r="O22" s="94"/>
-      <c r="P22" s="95">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="94"/>
-      <c r="R22" s="25"/>
-      <c r="S22" s="92"/>
-      <c r="T22" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A23" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="85" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="26"/>
-      <c r="K23" s="26"/>
-      <c r="L23" s="26"/>
-      <c r="M23" s="26"/>
-      <c r="N23" s="26"/>
-      <c r="O23" s="97"/>
-      <c r="P23" s="91">
-        <v>1</v>
-      </c>
-      <c r="Q23" s="97"/>
-      <c r="R23" s="26"/>
-      <c r="S23" s="93">
-        <v>0</v>
-      </c>
-      <c r="T23" s="1">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A24" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24" t="s">
-        <v>5</v>
-      </c>
-      <c r="C24" s="86" t="s">
-        <v>30</v>
-      </c>
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23"/>
-      <c r="J24" s="23"/>
-      <c r="K24" s="23"/>
-      <c r="L24" s="23"/>
-      <c r="M24" s="23"/>
-      <c r="N24" s="23"/>
-      <c r="O24" s="91">
-        <v>0.25</v>
-      </c>
-      <c r="P24" s="91"/>
-      <c r="Q24" s="91"/>
-      <c r="R24" s="23"/>
-      <c r="S24" s="108">
-        <v>0.75</v>
-      </c>
-      <c r="T24" s="1">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B25" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" s="65" t="s">
-        <v>30</v>
-      </c>
-      <c r="D25" s="24"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="24"/>
-      <c r="H25" s="24"/>
-      <c r="I25" s="24"/>
-      <c r="J25" s="24"/>
-      <c r="K25" s="24"/>
-      <c r="L25" s="24"/>
-      <c r="M25" s="24"/>
-      <c r="N25" s="24"/>
-      <c r="O25" s="100"/>
-      <c r="P25" s="100"/>
-      <c r="Q25" s="100">
-        <v>1</v>
-      </c>
-      <c r="R25" s="24"/>
-      <c r="S25" s="95">
-        <v>0</v>
-      </c>
-      <c r="T25" s="1">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="D26" s="14"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A27" s="109"/>
-      <c r="B27" s="109" t="s">
-        <v>38</v>
-      </c>
-      <c r="C27" s="109" t="s">
-        <v>39</v>
-      </c>
-      <c r="D27" s="110" t="s">
-        <v>40</v>
-      </c>
-      <c r="E27" s="110" t="s">
-        <v>41</v>
-      </c>
-      <c r="F27" s="110" t="s">
-        <v>42</v>
-      </c>
-      <c r="G27" s="110" t="s">
-        <v>43</v>
-      </c>
-      <c r="H27" s="110" t="s">
-        <v>44</v>
-      </c>
-      <c r="I27" s="110" t="s">
-        <v>45</v>
-      </c>
-      <c r="J27" s="110" t="s">
-        <v>46</v>
-      </c>
-      <c r="K27" s="110" t="s">
-        <v>47</v>
-      </c>
-      <c r="L27" s="110" t="s">
-        <v>48</v>
-      </c>
-      <c r="M27" s="1"/>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>7</v>
-      </c>
-      <c r="B28" s="12">
-        <v>0.47763347763347702</v>
-      </c>
-      <c r="C28" s="12">
-        <v>0.65</v>
-      </c>
-      <c r="D28" s="14">
-        <v>0.53174603174603097</v>
-      </c>
-      <c r="E28" s="14">
-        <v>0.31096681096681</v>
-      </c>
-      <c r="F28" s="12">
-        <v>2</v>
-      </c>
-      <c r="G28" s="14">
-        <v>0.66666666666666596</v>
-      </c>
-      <c r="H28" s="12">
-        <v>0.39198942303110901</v>
-      </c>
-      <c r="I28" s="12">
-        <v>0.46097722286464399</v>
-      </c>
-      <c r="J28" s="12">
-        <v>0.404684088380379</v>
-      </c>
-      <c r="K28" s="12">
-        <v>0.314997533323503</v>
-      </c>
-      <c r="L28" s="12">
-        <v>0</v>
-      </c>
-      <c r="M28" s="1"/>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>8</v>
-      </c>
-      <c r="B29" s="12">
-        <v>0.24444444444444399</v>
-      </c>
-      <c r="C29" s="12">
-        <v>0.19722222222222199</v>
-      </c>
-      <c r="D29" s="14">
-        <v>0.17037037037037001</v>
-      </c>
-      <c r="E29" s="14">
-        <v>7.7777777777777696E-2</v>
-      </c>
-      <c r="F29" s="12">
-        <v>1.33</v>
-      </c>
-      <c r="G29" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="H29" s="12">
-        <v>0.35572912430182402</v>
-      </c>
-      <c r="I29" s="12">
-        <v>0.22369304916986901</v>
-      </c>
-      <c r="J29" s="12">
-        <v>0.180382157953865</v>
-      </c>
-      <c r="K29" s="12">
-        <v>0.33167390544507902</v>
-      </c>
-      <c r="L29" s="12">
-        <v>0.47140452079103101</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A17:S25">
-    <sortCondition ref="C17:C25"/>
-  </sortState>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAF50480-301C-0843-A08D-1FF82088E86E}">
-  <dimension ref="A1:V19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="4.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6" customWidth="1"/>
-    <col min="5" max="5" width="8.1640625" customWidth="1"/>
-    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.83203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.1640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2979,20 +3195,22 @@
       <c r="K2" s="22"/>
       <c r="L2" s="22"/>
       <c r="M2" s="22"/>
-      <c r="N2" s="115">
+      <c r="N2" s="113">
         <v>5.5555555555555497E-2</v>
       </c>
-      <c r="O2" s="22"/>
-      <c r="P2" s="115">
+      <c r="O2" s="22">
+        <v>0</v>
+      </c>
+      <c r="P2" s="113">
         <v>8.7301587301587297E-2</v>
       </c>
       <c r="Q2" s="102">
         <v>0.79365079365079305</v>
       </c>
-      <c r="R2" s="115">
+      <c r="R2" s="113">
         <v>6.3492063492063405E-2</v>
       </c>
-      <c r="S2" s="90">
+      <c r="S2" s="89">
         <v>0</v>
       </c>
       <c r="T2" s="1">
@@ -3021,20 +3239,22 @@
       <c r="K3" s="23"/>
       <c r="L3" s="23"/>
       <c r="M3" s="23"/>
-      <c r="N3" s="91">
-        <v>0</v>
-      </c>
-      <c r="O3" s="23"/>
-      <c r="P3" s="91">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="91">
-        <v>0</v>
-      </c>
-      <c r="R3" s="91">
-        <v>0</v>
-      </c>
-      <c r="S3" s="116">
+      <c r="N3" s="90">
+        <v>0</v>
+      </c>
+      <c r="O3" s="23">
+        <v>0</v>
+      </c>
+      <c r="P3" s="90">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="90">
+        <v>0</v>
+      </c>
+      <c r="R3" s="90">
+        <v>0</v>
+      </c>
+      <c r="S3" s="114">
         <v>1</v>
       </c>
       <c r="T3" s="1">
@@ -3065,16 +3285,16 @@
       <c r="K4" s="22"/>
       <c r="L4" s="22"/>
       <c r="M4" s="22"/>
-      <c r="N4" s="113">
+      <c r="N4" s="111">
         <v>0.5</v>
       </c>
       <c r="O4" s="22"/>
-      <c r="P4" s="89"/>
-      <c r="Q4" s="89">
+      <c r="P4" s="88"/>
+      <c r="Q4" s="88">
         <v>0.5</v>
       </c>
-      <c r="R4" s="89"/>
-      <c r="S4" s="90"/>
+      <c r="R4" s="88"/>
+      <c r="S4" s="89"/>
       <c r="T4" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -3100,14 +3320,14 @@
       <c r="K5" s="25"/>
       <c r="L5" s="25"/>
       <c r="M5" s="25"/>
-      <c r="N5" s="95">
+      <c r="N5" s="94">
         <v>0</v>
       </c>
       <c r="O5" s="25"/>
-      <c r="P5" s="91"/>
-      <c r="Q5" s="94"/>
-      <c r="R5" s="94"/>
-      <c r="S5" s="96">
+      <c r="P5" s="90"/>
+      <c r="Q5" s="93"/>
+      <c r="R5" s="93"/>
+      <c r="S5" s="95">
         <v>1</v>
       </c>
       <c r="T5" s="1">
@@ -3135,16 +3355,16 @@
       <c r="K6" s="26"/>
       <c r="L6" s="26"/>
       <c r="M6" s="26"/>
-      <c r="N6" s="91"/>
+      <c r="N6" s="90"/>
       <c r="O6" s="26"/>
-      <c r="P6" s="113">
+      <c r="P6" s="111">
         <v>0.64705882352941102</v>
       </c>
-      <c r="Q6" s="97">
+      <c r="Q6" s="96">
         <v>0.35294117647058798</v>
       </c>
-      <c r="R6" s="97"/>
-      <c r="S6" s="98"/>
+      <c r="R6" s="96"/>
+      <c r="S6" s="97"/>
       <c r="T6" s="1">
         <f t="shared" si="0"/>
         <v>0.999999999999999</v>
@@ -3170,14 +3390,14 @@
       <c r="K7" s="25"/>
       <c r="L7" s="25"/>
       <c r="M7" s="25"/>
-      <c r="N7" s="94"/>
+      <c r="N7" s="93"/>
       <c r="O7" s="25"/>
-      <c r="P7" s="95">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="91"/>
-      <c r="R7" s="94"/>
-      <c r="S7" s="96">
+      <c r="P7" s="94">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="90"/>
+      <c r="R7" s="93"/>
+      <c r="S7" s="95">
         <v>1</v>
       </c>
       <c r="T7" s="1">
@@ -3205,14 +3425,14 @@
       <c r="K8" s="26"/>
       <c r="L8" s="26"/>
       <c r="M8" s="26"/>
-      <c r="N8" s="97"/>
+      <c r="N8" s="96"/>
       <c r="O8" s="26"/>
-      <c r="P8" s="91"/>
-      <c r="Q8" s="113">
+      <c r="P8" s="90"/>
+      <c r="Q8" s="111">
         <v>1</v>
       </c>
-      <c r="R8" s="97"/>
-      <c r="S8" s="98"/>
+      <c r="R8" s="96"/>
+      <c r="S8" s="97"/>
       <c r="T8" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -3238,14 +3458,14 @@
       <c r="K9" s="25"/>
       <c r="L9" s="25"/>
       <c r="M9" s="25"/>
-      <c r="N9" s="94"/>
+      <c r="N9" s="93"/>
       <c r="O9" s="25"/>
-      <c r="P9" s="94"/>
-      <c r="Q9" s="95">
-        <v>0</v>
-      </c>
-      <c r="R9" s="91"/>
-      <c r="S9" s="96">
+      <c r="P9" s="93"/>
+      <c r="Q9" s="94">
+        <v>0</v>
+      </c>
+      <c r="R9" s="90"/>
+      <c r="S9" s="95">
         <v>1</v>
       </c>
       <c r="T9" s="1">
@@ -3273,18 +3493,18 @@
       <c r="K10" s="26"/>
       <c r="L10" s="26"/>
       <c r="M10" s="26"/>
-      <c r="N10" s="97">
+      <c r="N10" s="96">
         <v>8.3333333333333301E-2</v>
       </c>
       <c r="O10" s="26"/>
-      <c r="P10" s="97"/>
-      <c r="Q10" s="91">
+      <c r="P10" s="96"/>
+      <c r="Q10" s="90">
         <v>0.33333333333333298</v>
       </c>
-      <c r="R10" s="113">
+      <c r="R10" s="111">
         <v>0.58333333333333304</v>
       </c>
-      <c r="S10" s="98"/>
+      <c r="S10" s="97"/>
       <c r="T10" s="1">
         <f t="shared" si="0"/>
         <v>0.99999999999999933</v>
@@ -3310,14 +3530,14 @@
       <c r="K11" s="25"/>
       <c r="L11" s="25"/>
       <c r="M11" s="25"/>
-      <c r="N11" s="94"/>
+      <c r="N11" s="93"/>
       <c r="O11" s="25"/>
-      <c r="P11" s="94"/>
-      <c r="Q11" s="94"/>
-      <c r="R11" s="95">
-        <v>0</v>
-      </c>
-      <c r="S11" s="92">
+      <c r="P11" s="93"/>
+      <c r="Q11" s="93"/>
+      <c r="R11" s="94">
+        <v>0</v>
+      </c>
+      <c r="S11" s="91">
         <v>1</v>
       </c>
       <c r="T11" s="1">
@@ -3345,20 +3565,18 @@
       <c r="K12" s="26"/>
       <c r="L12" s="26"/>
       <c r="M12" s="26"/>
-      <c r="N12" s="97">
+      <c r="N12" s="96">
         <v>8.1967213114753995E-2</v>
       </c>
       <c r="O12" s="26"/>
-      <c r="P12" s="97">
+      <c r="P12" s="96">
         <v>0.18032786885245899</v>
       </c>
-      <c r="Q12" s="97">
+      <c r="Q12" s="96">
         <v>0.73770491803278604</v>
       </c>
-      <c r="R12" s="91"/>
-      <c r="S12" s="93">
-        <v>0</v>
-      </c>
+      <c r="R12" s="90"/>
+      <c r="S12" s="92"/>
       <c r="T12" s="1">
         <f t="shared" si="0"/>
         <v>0.999999999999999</v>
@@ -3384,12 +3602,12 @@
       <c r="K13" s="24"/>
       <c r="L13" s="24"/>
       <c r="M13" s="24"/>
-      <c r="N13" s="100"/>
+      <c r="N13" s="99"/>
       <c r="O13" s="24"/>
-      <c r="P13" s="100"/>
-      <c r="Q13" s="100"/>
-      <c r="R13" s="100"/>
-      <c r="S13" s="114">
+      <c r="P13" s="99"/>
+      <c r="Q13" s="99"/>
+      <c r="R13" s="99"/>
+      <c r="S13" s="112">
         <v>1</v>
       </c>
       <c r="T13" s="1">
@@ -3417,21 +3635,17 @@
       <c r="K14" s="22"/>
       <c r="L14" s="22"/>
       <c r="M14" s="22"/>
-      <c r="N14" s="89">
-        <v>3.0769230769230702E-2</v>
-      </c>
+      <c r="N14" s="88"/>
       <c r="O14" s="22"/>
-      <c r="P14" s="89"/>
-      <c r="Q14" s="113">
-        <v>0.84615384615384603</v>
-      </c>
-      <c r="R14" s="89">
-        <v>0.123076923076923</v>
-      </c>
-      <c r="S14" s="90"/>
+      <c r="P14" s="88"/>
+      <c r="Q14" s="111">
+        <v>1</v>
+      </c>
+      <c r="R14" s="88"/>
+      <c r="S14" s="89"/>
       <c r="T14" s="1">
         <f t="shared" si="0"/>
-        <v>0.99999999999999967</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -3454,14 +3668,14 @@
       <c r="K15" s="24"/>
       <c r="L15" s="24"/>
       <c r="M15" s="24"/>
-      <c r="N15" s="100"/>
+      <c r="N15" s="99"/>
       <c r="O15" s="24"/>
-      <c r="P15" s="100"/>
-      <c r="Q15" s="95">
-        <v>0</v>
-      </c>
-      <c r="R15" s="100"/>
-      <c r="S15" s="112">
+      <c r="P15" s="99"/>
+      <c r="Q15" s="94">
+        <v>0</v>
+      </c>
+      <c r="R15" s="99"/>
+      <c r="S15" s="110">
         <v>1</v>
       </c>
       <c r="T15" s="1">
@@ -3469,116 +3683,182 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A17" s="117"/>
-      <c r="B17" s="117" t="s">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A16" s="135"/>
+      <c r="B16" s="135"/>
+      <c r="C16" s="135"/>
+      <c r="D16" s="136"/>
+      <c r="E16" s="136"/>
+      <c r="F16" s="136"/>
+      <c r="G16" s="136"/>
+      <c r="H16" s="136"/>
+      <c r="I16" s="136"/>
+      <c r="J16" s="136"/>
+      <c r="K16" s="136"/>
+      <c r="L16" s="136"/>
+      <c r="M16" s="136"/>
+      <c r="N16" s="136"/>
+      <c r="O16" s="136"/>
+      <c r="P16" s="136"/>
+      <c r="Q16" s="136"/>
+      <c r="R16" s="136"/>
+      <c r="S16" s="136"/>
+      <c r="T16" s="1"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A18" s="157"/>
+      <c r="B18" s="157"/>
+      <c r="C18" s="157"/>
+      <c r="D18" s="157"/>
+      <c r="E18" s="157"/>
+      <c r="F18" s="157"/>
+      <c r="G18" s="157"/>
+      <c r="H18" s="157"/>
+      <c r="I18" s="157"/>
+      <c r="J18" s="157"/>
+      <c r="K18" s="157"/>
+      <c r="L18" s="157"/>
+      <c r="M18" s="158"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A19" s="136"/>
+      <c r="B19" s="136"/>
+      <c r="C19" s="136"/>
+      <c r="D19" s="136"/>
+      <c r="E19" s="136"/>
+      <c r="F19" s="136"/>
+      <c r="G19" s="136"/>
+      <c r="H19" s="136"/>
+      <c r="I19" s="136"/>
+      <c r="J19" s="136"/>
+      <c r="K19" s="136"/>
+      <c r="L19" s="136"/>
+      <c r="M19" s="137"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A20" s="136"/>
+      <c r="B20" s="136"/>
+      <c r="C20" s="136"/>
+      <c r="D20" s="136"/>
+      <c r="E20" s="136"/>
+      <c r="F20" s="136"/>
+      <c r="G20" s="136"/>
+      <c r="H20" s="136"/>
+      <c r="I20" s="136"/>
+      <c r="J20" s="136"/>
+      <c r="K20" s="136"/>
+      <c r="L20" s="136"/>
+      <c r="M20" s="137"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A22" s="116"/>
+      <c r="B22" s="116" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="117" t="s">
+      <c r="C22" s="116" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="117" t="s">
+      <c r="D22" s="116" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="117" t="s">
+      <c r="E22" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="F17" s="117" t="s">
+      <c r="F22" s="116" t="s">
         <v>42</v>
       </c>
-      <c r="G17" s="117" t="s">
+      <c r="G22" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="H17" s="117" t="s">
+      <c r="H22" s="116" t="s">
         <v>44</v>
       </c>
-      <c r="I17" s="117" t="s">
+      <c r="I22" s="116" t="s">
         <v>45</v>
       </c>
-      <c r="J17" s="117" t="s">
+      <c r="J22" s="116" t="s">
         <v>46</v>
       </c>
-      <c r="K17" s="117" t="s">
+      <c r="K22" s="116" t="s">
         <v>47</v>
       </c>
-      <c r="L17" s="117" t="s">
+      <c r="L22" s="116" t="s">
         <v>48</v>
       </c>
-      <c r="M17" s="118"/>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B23" s="1">
         <v>0.36172623860250602</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C23" s="1">
         <v>0.62794505494505404</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D23" s="14">
         <v>0.42459515065609998</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E23" s="14">
         <v>0.16172623860250601</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F23" s="1">
         <v>1.8</v>
       </c>
-      <c r="G18" s="14">
+      <c r="G23" s="14">
         <v>1</v>
       </c>
-      <c r="H18" s="1">
+      <c r="H23" s="1">
         <v>8.8823978216517399E-2</v>
       </c>
-      <c r="I18" s="1">
+      <c r="I23" s="1">
         <v>0.256467059746816</v>
       </c>
-      <c r="J18" s="1">
+      <c r="J23" s="1">
         <v>4.9183548166781603E-2</v>
       </c>
-      <c r="K18" s="1">
+      <c r="K23" s="1">
         <v>0.120554564658457</v>
       </c>
-      <c r="L18" s="1">
+      <c r="L23" s="1">
         <v>0.4</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="1">
-        <v>8.0291970802919693E-2</v>
-      </c>
-      <c r="C19" s="1">
-        <v>0.11</v>
-      </c>
-      <c r="D19" s="14">
-        <v>9.2827004219409204E-2</v>
-      </c>
-      <c r="E19" s="14">
-        <v>-0.11970802919708</v>
-      </c>
-      <c r="F19" s="1">
-        <v>1</v>
-      </c>
-      <c r="G19" s="14">
+      <c r="B24" s="1">
+        <v>5.4545454545454501E-2</v>
+      </c>
+      <c r="C24" s="1">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="D24" s="14">
+        <v>1.0810810810810799E-2</v>
+      </c>
+      <c r="E24" s="159">
+        <v>-0.145454545454545</v>
+      </c>
+      <c r="F24" s="1">
+        <v>2</v>
+      </c>
+      <c r="G24" s="14">
         <v>0.2</v>
       </c>
-      <c r="H19" s="1">
-        <v>0.160583941605839</v>
-      </c>
-      <c r="I19" s="1">
-        <v>0.22</v>
-      </c>
-      <c r="J19" s="1">
-        <v>0.18565400843881799</v>
-      </c>
-      <c r="K19" s="1">
-        <v>0.194890443371216</v>
-      </c>
-      <c r="L19" s="1">
+      <c r="H24" s="1">
+        <v>0.109090909090909</v>
+      </c>
+      <c r="I24" s="1">
+        <v>1.2E-2</v>
+      </c>
+      <c r="J24" s="1">
+        <v>2.1621621621621599E-2</v>
+      </c>
+      <c r="K24" s="1">
+        <v>0.184151482169439</v>
+      </c>
+      <c r="L24" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3597,23 +3877,21 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.6640625" customWidth="1"/>
-    <col min="5" max="5" width="9" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="11.83203125" customWidth="1"/>
-    <col min="8" max="8" width="12.6640625" customWidth="1"/>
-    <col min="9" max="9" width="9.6640625" customWidth="1"/>
-    <col min="10" max="10" width="8.1640625" customWidth="1"/>
-    <col min="11" max="11" width="10" customWidth="1"/>
-    <col min="12" max="12" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.6640625" customWidth="1"/>
-    <col min="14" max="14" width="3.83203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.6640625" customWidth="1"/>
-    <col min="16" max="16" width="7.6640625" customWidth="1"/>
-    <col min="17" max="17" width="8.1640625" customWidth="1"/>
-    <col min="18" max="18" width="7.6640625" customWidth="1"/>
-    <col min="19" max="19" width="8" customWidth="1"/>
+    <col min="2" max="2" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.1640625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="10.5" customWidth="1"/>
     <col min="21" max="21" width="4.6640625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="5.5" bestFit="1" customWidth="1"/>
@@ -3703,21 +3981,25 @@
       <c r="J2" s="35"/>
       <c r="K2" s="35"/>
       <c r="L2" s="35"/>
-      <c r="M2" s="124">
+      <c r="M2" s="122">
         <v>1.0869565217391301E-2</v>
       </c>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="119">
+      <c r="N2" s="35">
+        <v>0</v>
+      </c>
+      <c r="O2" s="35">
+        <v>0</v>
+      </c>
+      <c r="P2" s="117">
         <v>0.26086956521739102</v>
       </c>
-      <c r="Q2" s="119">
+      <c r="Q2" s="117">
         <v>0.70652173913043403</v>
       </c>
-      <c r="R2" s="124">
+      <c r="R2" s="122">
         <v>1.0869565217391301E-2</v>
       </c>
-      <c r="S2" s="125">
+      <c r="S2" s="123">
         <v>1.0869565217391301E-2</v>
       </c>
       <c r="T2" s="1">
@@ -3747,17 +4029,17 @@
       <c r="J3" s="53"/>
       <c r="K3" s="53"/>
       <c r="L3" s="53"/>
-      <c r="M3" s="120"/>
+      <c r="M3" s="118"/>
       <c r="N3" s="52"/>
       <c r="O3" s="52"/>
-      <c r="P3" s="126">
+      <c r="P3" s="124">
         <v>0.79310344827586199</v>
       </c>
-      <c r="Q3" s="89">
+      <c r="Q3" s="88">
         <v>0.20689655172413701</v>
       </c>
       <c r="R3" s="52"/>
-      <c r="S3" s="121"/>
+      <c r="S3" s="119"/>
       <c r="T3" s="1">
         <f>SUM(D3:S3)</f>
         <v>0.999999999999999</v>
@@ -3785,17 +4067,17 @@
       <c r="J4" s="36"/>
       <c r="K4" s="36"/>
       <c r="L4" s="36"/>
-      <c r="M4" s="100">
+      <c r="M4" s="99">
         <v>2.8571428571428501E-2</v>
       </c>
       <c r="N4" s="24"/>
       <c r="O4" s="24"/>
-      <c r="P4" s="100"/>
-      <c r="Q4" s="126">
+      <c r="P4" s="99"/>
+      <c r="Q4" s="124">
         <v>0.97142857142857097</v>
       </c>
       <c r="R4" s="24"/>
-      <c r="S4" s="112"/>
+      <c r="S4" s="110"/>
       <c r="T4" s="1">
         <f>SUM(D4:S4)</f>
         <v>0.99999999999999944</v>
@@ -3820,17 +4102,17 @@
       <c r="J5" s="53"/>
       <c r="K5" s="53"/>
       <c r="L5" s="53"/>
-      <c r="M5" s="120"/>
+      <c r="M5" s="118"/>
       <c r="N5" s="52"/>
       <c r="O5" s="52"/>
-      <c r="P5" s="127">
-        <v>0.25</v>
-      </c>
-      <c r="Q5" s="89">
-        <v>0.75</v>
+      <c r="P5" s="124">
+        <v>0.88</v>
+      </c>
+      <c r="Q5" s="88">
+        <v>0.12</v>
       </c>
       <c r="R5" s="52"/>
-      <c r="S5" s="121"/>
+      <c r="S5" s="119"/>
       <c r="T5" s="1">
         <f>SUM(D5:S5)</f>
         <v>1</v>
@@ -3855,59 +4137,55 @@
       <c r="J6" s="57"/>
       <c r="K6" s="57"/>
       <c r="L6" s="57"/>
-      <c r="M6" s="122">
-        <v>2.2222222222222199E-2</v>
+      <c r="M6" s="120">
+        <v>2.8571428571428501E-2</v>
       </c>
       <c r="N6" s="56"/>
       <c r="O6" s="56"/>
-      <c r="P6" s="100">
-        <v>4.4444444444444398E-2</v>
-      </c>
-      <c r="Q6" s="126">
-        <v>0.91111111111111098</v>
+      <c r="P6" s="99"/>
+      <c r="Q6" s="124">
+        <v>0.97142857142857097</v>
       </c>
       <c r="R6" s="56"/>
-      <c r="S6" s="123">
-        <v>2.2222222222222199E-2</v>
-      </c>
+      <c r="S6" s="121"/>
       <c r="T6" s="1">
         <f>SUM(D6:S6)</f>
-        <v>0.99999999999999978</v>
+        <v>0.99999999999999944</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A8" s="117"/>
-      <c r="B8" s="118" t="s">
+      <c r="A8" s="115"/>
+      <c r="B8" s="116" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="118" t="s">
+      <c r="C8" s="116" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="118" t="s">
+      <c r="D8" s="116" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="118" t="s">
+      <c r="E8" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="F8" s="118" t="s">
+      <c r="F8" s="116" t="s">
         <v>42</v>
       </c>
-      <c r="G8" s="118" t="s">
+      <c r="G8" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="H8" s="118" t="s">
+      <c r="H8" s="116" t="s">
         <v>44</v>
       </c>
-      <c r="I8" s="118" t="s">
+      <c r="I8" s="116" t="s">
         <v>45</v>
       </c>
-      <c r="J8" s="118" t="s">
+      <c r="J8" s="116" t="s">
         <v>46</v>
       </c>
-      <c r="K8" s="118" t="s">
+      <c r="K8" s="116" t="s">
         <v>47</v>
       </c>
-      <c r="L8" s="118" t="s">
+      <c r="L8" s="116" t="s">
         <v>48</v>
       </c>
     </row>
@@ -3954,37 +4232,37 @@
         <v>8</v>
       </c>
       <c r="B10" s="1">
-        <v>0.232222222222222</v>
+        <v>0.370285714285714</v>
       </c>
       <c r="C10" s="1">
-        <v>0.134487179487179</v>
+        <v>0.28794871794871701</v>
       </c>
       <c r="D10" s="14">
-        <v>0.16337662337662301</v>
+        <v>0.31559183673469299</v>
       </c>
       <c r="E10" s="14">
-        <v>3.2222222222222201E-2</v>
+        <v>0.17028571428571401</v>
       </c>
       <c r="F10" s="1">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G10" s="14">
         <v>0.4</v>
       </c>
       <c r="H10" s="1">
-        <v>0.35298375439132801</v>
+        <v>0.45442621367331898</v>
       </c>
       <c r="I10" s="1">
-        <v>0.248665207202066</v>
+        <v>0.37398259969999798</v>
       </c>
       <c r="J10" s="1">
-        <v>0.29235078752260402</v>
+        <v>0.39261677459722299</v>
       </c>
       <c r="K10" s="1">
-        <v>8.6183574879226996E-2</v>
+        <v>0.24854232837382001</v>
       </c>
       <c r="L10" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3995,27 +4273,26 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26299AB8-0881-F840-8E86-BEA796FBE472}">
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.1640625" customWidth="1"/>
-    <col min="6" max="6" width="7.6640625" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" customWidth="1"/>
+    <col min="6" max="6" width="10.1640625" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" customWidth="1"/>
+    <col min="8" max="8" width="15.1640625" customWidth="1"/>
+    <col min="9" max="9" width="11" customWidth="1"/>
+    <col min="10" max="12" width="9" customWidth="1"/>
+    <col min="13" max="13" width="5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.83203125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="5" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="4.83203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.33203125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -4085,24 +4362,24 @@
         <v>11</v>
       </c>
       <c r="C2" s="27"/>
-      <c r="D2" s="115">
+      <c r="D2" s="102">
         <v>0.40625</v>
       </c>
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>
-      <c r="I2" s="115">
+      <c r="I2" s="102">
         <v>6.25E-2</v>
       </c>
       <c r="J2" s="22"/>
-      <c r="K2" s="115">
+      <c r="K2" s="113">
         <v>3.125E-2</v>
       </c>
-      <c r="L2" s="115">
+      <c r="L2" s="102">
         <v>0.1875</v>
       </c>
-      <c r="M2" s="115">
+      <c r="M2" s="113">
         <v>3.125E-2</v>
       </c>
       <c r="N2" s="22"/>
@@ -4112,7 +4389,7 @@
       <c r="P2" s="22"/>
       <c r="Q2" s="22"/>
       <c r="R2" s="22"/>
-      <c r="S2" s="130">
+      <c r="S2" s="127">
         <v>0.21875</v>
       </c>
       <c r="T2" s="1">
@@ -4133,30 +4410,30 @@
       <c r="C3" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="126">
+      <c r="D3" s="124">
         <v>1</v>
       </c>
       <c r="E3" s="52"/>
       <c r="F3" s="52"/>
       <c r="G3" s="52"/>
       <c r="H3" s="52"/>
-      <c r="I3" s="89"/>
+      <c r="I3" s="88"/>
       <c r="J3" s="52"/>
-      <c r="K3" s="120"/>
-      <c r="L3" s="120"/>
-      <c r="M3" s="120"/>
+      <c r="K3" s="118"/>
+      <c r="L3" s="118"/>
+      <c r="M3" s="118"/>
       <c r="N3" s="52"/>
-      <c r="O3" s="120"/>
+      <c r="O3" s="118"/>
       <c r="P3" s="52"/>
       <c r="Q3" s="52"/>
       <c r="R3" s="52"/>
-      <c r="S3" s="121"/>
+      <c r="S3" s="119"/>
       <c r="T3" s="1">
-        <f t="shared" ref="T3:T10" si="0">SUM(D3:S3)</f>
+        <f t="shared" ref="T3:T9" si="0">SUM(D3:S3)</f>
         <v>1</v>
       </c>
       <c r="V3" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -4169,28 +4446,28 @@
       <c r="C4" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="94"/>
+      <c r="D4" s="93"/>
       <c r="E4" s="50"/>
       <c r="F4" s="50"/>
       <c r="G4" s="50"/>
       <c r="H4" s="50"/>
-      <c r="I4" s="126">
+      <c r="I4" s="124">
         <v>0.22222222222222199</v>
       </c>
       <c r="J4" s="50"/>
-      <c r="K4" s="97"/>
-      <c r="L4" s="128">
+      <c r="K4" s="96"/>
+      <c r="L4" s="125">
         <v>0.66666666666666596</v>
       </c>
-      <c r="M4" s="128">
+      <c r="M4" s="125">
         <v>0.11111111111111099</v>
       </c>
       <c r="N4" s="50"/>
-      <c r="O4" s="128"/>
+      <c r="O4" s="125"/>
       <c r="P4" s="50"/>
       <c r="Q4" s="50"/>
       <c r="R4" s="50"/>
-      <c r="S4" s="129"/>
+      <c r="S4" s="126"/>
       <c r="T4" s="1">
         <f t="shared" si="0"/>
         <v>0.99999999999999889</v>
@@ -4206,26 +4483,26 @@
       <c r="C5" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="128"/>
+      <c r="D5" s="125"/>
       <c r="E5" s="50"/>
       <c r="F5" s="50"/>
       <c r="G5" s="50"/>
       <c r="H5" s="50"/>
-      <c r="I5" s="94"/>
+      <c r="I5" s="93"/>
       <c r="J5" s="50"/>
-      <c r="K5" s="126">
+      <c r="K5" s="124">
         <v>0.1</v>
       </c>
-      <c r="L5" s="97"/>
-      <c r="M5" s="128"/>
+      <c r="L5" s="96"/>
+      <c r="M5" s="125"/>
       <c r="N5" s="50"/>
-      <c r="O5" s="128">
+      <c r="O5" s="125">
         <v>0.2</v>
       </c>
       <c r="P5" s="50"/>
       <c r="Q5" s="50"/>
       <c r="R5" s="50"/>
-      <c r="S5" s="129">
+      <c r="S5" s="126">
         <v>0.7</v>
       </c>
       <c r="T5" s="1">
@@ -4243,28 +4520,28 @@
       <c r="C6" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="128"/>
+      <c r="D6" s="125"/>
       <c r="E6" s="50"/>
       <c r="F6" s="50"/>
       <c r="G6" s="50"/>
       <c r="H6" s="50"/>
-      <c r="I6" s="128">
+      <c r="I6" s="125">
         <v>0.125</v>
       </c>
       <c r="J6" s="50"/>
-      <c r="K6" s="94"/>
-      <c r="L6" s="126">
+      <c r="K6" s="93"/>
+      <c r="L6" s="124">
         <v>0.75</v>
       </c>
-      <c r="M6" s="128">
+      <c r="M6" s="125">
         <v>0.125</v>
       </c>
       <c r="N6" s="50"/>
-      <c r="O6" s="97"/>
+      <c r="O6" s="96"/>
       <c r="P6" s="50"/>
       <c r="Q6" s="50"/>
       <c r="R6" s="50"/>
-      <c r="S6" s="129"/>
+      <c r="S6" s="126"/>
       <c r="T6" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -4280,24 +4557,24 @@
       <c r="C7" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="128"/>
+      <c r="D7" s="125"/>
       <c r="E7" s="50"/>
       <c r="F7" s="50"/>
       <c r="G7" s="50"/>
       <c r="H7" s="50"/>
-      <c r="I7" s="128"/>
+      <c r="I7" s="125"/>
       <c r="J7" s="50"/>
-      <c r="K7" s="128"/>
-      <c r="L7" s="94"/>
+      <c r="K7" s="125"/>
+      <c r="L7" s="93"/>
       <c r="M7" s="50"/>
       <c r="N7" s="50"/>
-      <c r="O7" s="126">
+      <c r="O7" s="124">
         <v>0.22222222222222199</v>
       </c>
       <c r="P7" s="50"/>
       <c r="Q7" s="50"/>
       <c r="R7" s="50"/>
-      <c r="S7" s="98">
+      <c r="S7" s="97">
         <v>0.77777777777777701</v>
       </c>
       <c r="T7" s="1">
@@ -4315,22 +4592,22 @@
       <c r="C8" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="100"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="24"/>
-      <c r="I8" s="100"/>
-      <c r="J8" s="24"/>
-      <c r="K8" s="100"/>
-      <c r="L8" s="100"/>
-      <c r="M8" s="24"/>
-      <c r="N8" s="24"/>
-      <c r="O8" s="100"/>
-      <c r="P8" s="24"/>
-      <c r="Q8" s="24"/>
-      <c r="R8" s="24"/>
-      <c r="S8" s="126">
+      <c r="D8" s="136"/>
+      <c r="E8" s="140"/>
+      <c r="F8" s="140"/>
+      <c r="G8" s="140"/>
+      <c r="H8" s="140"/>
+      <c r="I8" s="136"/>
+      <c r="J8" s="140"/>
+      <c r="K8" s="136"/>
+      <c r="L8" s="136"/>
+      <c r="M8" s="140"/>
+      <c r="N8" s="140"/>
+      <c r="O8" s="136"/>
+      <c r="P8" s="140"/>
+      <c r="Q8" s="140"/>
+      <c r="R8" s="140"/>
+      <c r="S8" s="111">
         <v>1</v>
       </c>
       <c r="T8" s="1">
@@ -4345,175 +4622,307 @@
       <c r="B9" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="64" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="120"/>
+      <c r="C9" s="162" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="124">
+        <v>1</v>
+      </c>
       <c r="E9" s="52"/>
       <c r="F9" s="52"/>
       <c r="G9" s="52"/>
       <c r="H9" s="52"/>
-      <c r="I9" s="120"/>
+      <c r="I9" s="88"/>
       <c r="J9" s="52"/>
-      <c r="K9" s="120"/>
-      <c r="L9" s="120"/>
+      <c r="K9" s="118"/>
+      <c r="L9" s="118"/>
       <c r="M9" s="52"/>
       <c r="N9" s="52"/>
-      <c r="O9" s="126">
-        <v>1</v>
-      </c>
+      <c r="O9" s="100"/>
       <c r="P9" s="52"/>
       <c r="Q9" s="52"/>
       <c r="R9" s="52"/>
-      <c r="S9" s="90"/>
+      <c r="S9" s="89"/>
       <c r="T9" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="88" t="s">
+      <c r="C10" s="163" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="164"/>
+      <c r="E10" s="140"/>
+      <c r="F10" s="140"/>
+      <c r="G10" s="140"/>
+      <c r="H10" s="140"/>
+      <c r="I10" s="124">
+        <v>1</v>
+      </c>
+      <c r="J10" s="140"/>
+      <c r="K10" s="136"/>
+      <c r="L10" s="136"/>
+      <c r="M10" s="140"/>
+      <c r="N10" s="140"/>
+      <c r="O10" s="136"/>
+      <c r="P10" s="140"/>
+      <c r="Q10" s="140"/>
+      <c r="R10" s="140"/>
+      <c r="S10" s="91"/>
+      <c r="T10" s="1">
+        <f>SUM(D13:S13)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="160" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="165"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="50"/>
+      <c r="H11" s="50"/>
+      <c r="I11" s="93"/>
+      <c r="J11" s="50"/>
+      <c r="K11" s="96"/>
+      <c r="L11" s="124">
+        <v>1</v>
+      </c>
+      <c r="M11" s="125"/>
+      <c r="N11" s="50"/>
+      <c r="O11" s="96"/>
+      <c r="P11" s="50"/>
+      <c r="Q11" s="50"/>
+      <c r="R11" s="50"/>
+      <c r="S11" s="95"/>
+    </row>
+    <row r="12" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="161" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="165"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="50"/>
+      <c r="H12" s="50"/>
+      <c r="I12" s="93"/>
+      <c r="J12" s="50"/>
+      <c r="K12" s="96"/>
+      <c r="L12" s="136"/>
+      <c r="M12" s="125"/>
+      <c r="N12" s="50"/>
+      <c r="O12" s="124">
+        <v>1</v>
+      </c>
+      <c r="P12" s="50"/>
+      <c r="Q12" s="50"/>
+      <c r="R12" s="50"/>
+      <c r="S12" s="97"/>
+    </row>
+    <row r="13" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="142" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="100"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="100"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="100"/>
-      <c r="L10" s="100"/>
-      <c r="M10" s="24"/>
-      <c r="N10" s="24"/>
-      <c r="O10" s="100"/>
-      <c r="P10" s="24"/>
-      <c r="Q10" s="24"/>
-      <c r="R10" s="24"/>
-      <c r="S10" s="126">
+      <c r="D13" s="166"/>
+      <c r="E13" s="56"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="56"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="99"/>
+      <c r="J13" s="56"/>
+      <c r="K13" s="120"/>
+      <c r="L13" s="120"/>
+      <c r="M13" s="120"/>
+      <c r="N13" s="56"/>
+      <c r="O13" s="99"/>
+      <c r="P13" s="56"/>
+      <c r="Q13" s="56"/>
+      <c r="R13" s="56"/>
+      <c r="S13" s="124">
         <v>1</v>
       </c>
-      <c r="T10" s="1">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A12" s="118"/>
-      <c r="B12" s="118" t="s">
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A15" s="158"/>
+      <c r="B15" s="158"/>
+      <c r="C15" s="158"/>
+      <c r="D15" s="158"/>
+      <c r="E15" s="158"/>
+      <c r="F15" s="158"/>
+      <c r="G15" s="158"/>
+      <c r="H15" s="158"/>
+      <c r="I15" s="158"/>
+      <c r="J15" s="158"/>
+      <c r="K15" s="158"/>
+      <c r="L15" s="158"/>
+      <c r="M15" s="137"/>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A16" s="137"/>
+      <c r="B16" s="136"/>
+      <c r="C16" s="136"/>
+      <c r="D16" s="136"/>
+      <c r="E16" s="136"/>
+      <c r="F16" s="136"/>
+      <c r="G16" s="136"/>
+      <c r="H16" s="136"/>
+      <c r="I16" s="136"/>
+      <c r="J16" s="136"/>
+      <c r="K16" s="136"/>
+      <c r="L16" s="136"/>
+      <c r="M16" s="137"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A17" s="137"/>
+      <c r="B17" s="136"/>
+      <c r="C17" s="136"/>
+      <c r="D17" s="136"/>
+      <c r="E17" s="136"/>
+      <c r="F17" s="136"/>
+      <c r="G17" s="136"/>
+      <c r="H17" s="136"/>
+      <c r="I17" s="136"/>
+      <c r="J17" s="136"/>
+      <c r="K17" s="136"/>
+      <c r="L17" s="136"/>
+      <c r="M17" s="137"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A19" s="116"/>
+      <c r="B19" s="116" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="118" t="s">
+      <c r="C19" s="116" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="118" t="s">
+      <c r="D19" s="116" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="118" t="s">
+      <c r="E19" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="118" t="s">
+      <c r="F19" s="116" t="s">
         <v>42</v>
       </c>
-      <c r="G12" s="118" t="s">
+      <c r="G19" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="H12" s="118" t="s">
+      <c r="H19" s="116" t="s">
         <v>44</v>
       </c>
-      <c r="I12" s="118" t="s">
+      <c r="I19" s="116" t="s">
         <v>45</v>
       </c>
-      <c r="J12" s="118" t="s">
+      <c r="J19" s="116" t="s">
         <v>46</v>
       </c>
-      <c r="K12" s="118" t="s">
+      <c r="K19" s="116" t="s">
         <v>47</v>
       </c>
-      <c r="L12" s="118" t="s">
+      <c r="L19" s="116" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B20" s="1">
         <v>0.47063492063492002</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C20" s="1">
         <v>0.85714285714285698</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D20" s="14">
         <v>0.53803339517625204</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E20" s="14">
         <v>0.327777777777777</v>
       </c>
-      <c r="F13" s="1">
-        <v>1.8332999999999999</v>
-      </c>
-      <c r="G13" s="14">
+      <c r="F20" s="1">
+        <v>1.83</v>
+      </c>
+      <c r="G20" s="14">
         <v>0.85714285714285698</v>
       </c>
-      <c r="H13" s="1">
+      <c r="H20" s="1">
         <v>0.40014012410859601</v>
       </c>
-      <c r="I13" s="1">
+      <c r="I20" s="1">
         <v>0.34992710611188199</v>
       </c>
-      <c r="J13" s="1">
+      <c r="J20" s="1">
         <v>0.37906934880683102</v>
       </c>
-      <c r="K13" s="1">
+      <c r="K20" s="1">
         <v>0.28882878648298599</v>
       </c>
-      <c r="L13" s="1">
+      <c r="L20" s="1">
         <v>0.37267799624996401</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="1">
-        <v>0.28571428571428498</v>
-      </c>
-      <c r="C14" s="1">
-        <v>0.132653061224489</v>
-      </c>
-      <c r="D14" s="14">
-        <v>0.18095238095238</v>
-      </c>
-      <c r="E14" s="14">
-        <v>0.14285714285714199</v>
-      </c>
-      <c r="F14" s="1">
-        <v>2</v>
-      </c>
-      <c r="G14" s="14">
-        <v>0.28571428571428498</v>
-      </c>
-      <c r="H14" s="1">
+      <c r="B21" s="1">
+        <v>0.71428571428571397</v>
+      </c>
+      <c r="C21" s="1">
+        <v>0.476190476190476</v>
+      </c>
+      <c r="D21" s="14">
+        <v>0.54761904761904701</v>
+      </c>
+      <c r="E21" s="14">
+        <v>0.57142857142857095</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="G21" s="14">
+        <v>0.71428571428571397</v>
+      </c>
+      <c r="H21" s="1">
         <v>0.45175395145262498</v>
       </c>
-      <c r="I14" s="1">
-        <v>0.210609871842349</v>
-      </c>
-      <c r="J14" s="1">
-        <v>0.28666508463414098</v>
-      </c>
-      <c r="K14" s="1">
-        <v>0.47093453550859199</v>
-      </c>
-      <c r="L14" s="1">
-        <v>0</v>
+      <c r="I21" s="1">
+        <v>0.38243758105259501</v>
+      </c>
+      <c r="J21" s="1">
+        <v>0.38539081086282401</v>
+      </c>
+      <c r="K21" s="1">
+        <v>0.39588927281063102</v>
+      </c>
+      <c r="L21" s="1">
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
@@ -4527,22 +4936,22 @@
   <dimension ref="A1:V29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.6640625" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" customWidth="1"/>
-    <col min="4" max="4" width="6.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.1640625" customWidth="1"/>
-    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.33203125" customWidth="1"/>
-    <col min="11" max="11" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.83203125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.83203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -4625,7 +5034,7 @@
       </c>
       <c r="K2" s="22"/>
       <c r="L2" s="22"/>
-      <c r="M2" s="89">
+      <c r="M2" s="88">
         <v>0</v>
       </c>
       <c r="N2" s="102">
@@ -4633,11 +5042,11 @@
       </c>
       <c r="O2" s="22"/>
       <c r="P2" s="22"/>
-      <c r="Q2" s="89">
+      <c r="Q2" s="88">
         <v>0</v>
       </c>
       <c r="R2" s="22"/>
-      <c r="S2" s="131"/>
+      <c r="S2" s="128"/>
       <c r="T2" s="1">
         <f>SUM(D2:S2)</f>
         <v>0.999999999999998</v>
@@ -4653,7 +5062,7 @@
       <c r="C3" s="29"/>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
-      <c r="F3" s="91">
+      <c r="F3" s="90">
         <v>0</v>
       </c>
       <c r="G3" s="23"/>
@@ -4664,7 +5073,7 @@
       </c>
       <c r="K3" s="23"/>
       <c r="L3" s="23"/>
-      <c r="M3" s="91">
+      <c r="M3" s="90">
         <v>0</v>
       </c>
       <c r="N3" s="101">
@@ -4676,7 +5085,7 @@
         <v>0.72</v>
       </c>
       <c r="R3" s="23"/>
-      <c r="S3" s="132"/>
+      <c r="S3" s="129"/>
       <c r="T3" s="1">
         <f t="shared" ref="T3:T25" si="0">SUM(D3:S3)</f>
         <v>1</v>
@@ -4706,10 +5115,10 @@
       </c>
       <c r="K4" s="23"/>
       <c r="L4" s="23"/>
-      <c r="M4" s="137">
+      <c r="M4" s="134">
         <v>5.2631578947368397E-2</v>
       </c>
-      <c r="N4" s="137">
+      <c r="N4" s="134">
         <v>0.105263157894736</v>
       </c>
       <c r="O4" s="23"/>
@@ -4718,7 +5127,7 @@
         <v>0.73684210526315697</v>
       </c>
       <c r="R4" s="23"/>
-      <c r="S4" s="132"/>
+      <c r="S4" s="129"/>
       <c r="T4" s="1">
         <f t="shared" si="0"/>
         <v>0.99999999999999822</v>
@@ -4739,24 +5148,24 @@
       </c>
       <c r="D5" s="22"/>
       <c r="E5" s="22"/>
-      <c r="F5" s="113">
+      <c r="F5" s="111">
         <v>0.83333333333333304</v>
       </c>
       <c r="G5" s="22"/>
       <c r="H5" s="22"/>
       <c r="I5" s="22"/>
-      <c r="J5" s="89">
+      <c r="J5" s="88">
         <v>0.16666666666666599</v>
       </c>
       <c r="K5" s="22"/>
       <c r="L5" s="22"/>
-      <c r="M5" s="89"/>
-      <c r="N5" s="89"/>
+      <c r="M5" s="88"/>
+      <c r="N5" s="88"/>
       <c r="O5" s="22"/>
       <c r="P5" s="22"/>
-      <c r="Q5" s="89"/>
+      <c r="Q5" s="88"/>
       <c r="R5" s="22"/>
-      <c r="S5" s="131"/>
+      <c r="S5" s="128"/>
       <c r="T5" s="1">
         <f t="shared" si="0"/>
         <v>0.999999999999999</v>
@@ -4774,22 +5183,22 @@
       </c>
       <c r="D6" s="23"/>
       <c r="E6" s="23"/>
-      <c r="F6" s="99">
+      <c r="F6" s="98">
         <v>0</v>
       </c>
       <c r="G6" s="23"/>
       <c r="H6" s="23"/>
       <c r="I6" s="23"/>
-      <c r="J6" s="91"/>
+      <c r="J6" s="90"/>
       <c r="K6" s="23"/>
       <c r="L6" s="23"/>
-      <c r="M6" s="91"/>
-      <c r="N6" s="91"/>
+      <c r="M6" s="90"/>
+      <c r="N6" s="90"/>
       <c r="O6" s="23"/>
       <c r="P6" s="23"/>
-      <c r="Q6" s="91"/>
+      <c r="Q6" s="90"/>
       <c r="R6" s="23"/>
-      <c r="S6" s="132"/>
+      <c r="S6" s="129"/>
       <c r="T6" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4813,16 +5222,16 @@
       <c r="G7" s="25"/>
       <c r="H7" s="25"/>
       <c r="I7" s="25"/>
-      <c r="J7" s="91"/>
+      <c r="J7" s="90"/>
       <c r="K7" s="25"/>
       <c r="L7" s="25"/>
-      <c r="M7" s="94"/>
-      <c r="N7" s="94"/>
+      <c r="M7" s="93"/>
+      <c r="N7" s="93"/>
       <c r="O7" s="25"/>
       <c r="P7" s="25"/>
-      <c r="Q7" s="94"/>
+      <c r="Q7" s="93"/>
       <c r="R7" s="25"/>
-      <c r="S7" s="133"/>
+      <c r="S7" s="130"/>
       <c r="T7" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4840,24 +5249,24 @@
       </c>
       <c r="D8" s="26"/>
       <c r="E8" s="26"/>
-      <c r="F8" s="91">
+      <c r="F8" s="90">
         <v>0.33333333333333298</v>
       </c>
       <c r="G8" s="26"/>
       <c r="H8" s="26"/>
       <c r="I8" s="26"/>
-      <c r="J8" s="113">
+      <c r="J8" s="111">
         <v>0.66666666666666596</v>
       </c>
       <c r="K8" s="26"/>
       <c r="L8" s="26"/>
-      <c r="M8" s="97"/>
-      <c r="N8" s="97"/>
+      <c r="M8" s="96"/>
+      <c r="N8" s="96"/>
       <c r="O8" s="26"/>
       <c r="P8" s="26"/>
-      <c r="Q8" s="97"/>
+      <c r="Q8" s="96"/>
       <c r="R8" s="26"/>
-      <c r="S8" s="134"/>
+      <c r="S8" s="131"/>
       <c r="T8" s="1">
         <f t="shared" si="0"/>
         <v>0.99999999999999889</v>
@@ -4875,22 +5284,22 @@
       </c>
       <c r="D9" s="23"/>
       <c r="E9" s="23"/>
-      <c r="F9" s="91"/>
+      <c r="F9" s="90"/>
       <c r="G9" s="23"/>
       <c r="H9" s="23"/>
       <c r="I9" s="23"/>
-      <c r="J9" s="136">
+      <c r="J9" s="133">
         <v>0</v>
       </c>
       <c r="K9" s="23"/>
       <c r="L9" s="23"/>
-      <c r="M9" s="91"/>
-      <c r="N9" s="91"/>
+      <c r="M9" s="90"/>
+      <c r="N9" s="90"/>
       <c r="O9" s="23"/>
       <c r="P9" s="23"/>
-      <c r="Q9" s="91"/>
+      <c r="Q9" s="90"/>
       <c r="R9" s="23"/>
-      <c r="S9" s="132"/>
+      <c r="S9" s="129"/>
       <c r="T9" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4908,7 +5317,7 @@
       </c>
       <c r="D10" s="25"/>
       <c r="E10" s="25"/>
-      <c r="F10" s="94"/>
+      <c r="F10" s="93"/>
       <c r="G10" s="25"/>
       <c r="H10" s="25"/>
       <c r="I10" s="25"/>
@@ -4917,13 +5326,13 @@
       </c>
       <c r="K10" s="25"/>
       <c r="L10" s="25"/>
-      <c r="M10" s="94"/>
-      <c r="N10" s="91"/>
+      <c r="M10" s="93"/>
+      <c r="N10" s="90"/>
       <c r="O10" s="25"/>
       <c r="P10" s="25"/>
-      <c r="Q10" s="94"/>
+      <c r="Q10" s="93"/>
       <c r="R10" s="25"/>
-      <c r="S10" s="133"/>
+      <c r="S10" s="130"/>
       <c r="T10" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4941,26 +5350,26 @@
       </c>
       <c r="D11" s="26"/>
       <c r="E11" s="26"/>
-      <c r="F11" s="97">
+      <c r="F11" s="96">
         <v>0.33333333333333298</v>
       </c>
       <c r="G11" s="26"/>
       <c r="H11" s="26"/>
       <c r="I11" s="26"/>
-      <c r="J11" s="91">
+      <c r="J11" s="90">
         <v>0.38888888888888801</v>
       </c>
       <c r="K11" s="26"/>
       <c r="L11" s="26"/>
-      <c r="M11" s="97"/>
+      <c r="M11" s="96"/>
       <c r="N11" s="105">
         <v>0.27777777777777701</v>
       </c>
       <c r="O11" s="26"/>
       <c r="P11" s="26"/>
-      <c r="Q11" s="97"/>
+      <c r="Q11" s="96"/>
       <c r="R11" s="26"/>
-      <c r="S11" s="134"/>
+      <c r="S11" s="131"/>
       <c r="T11" s="1">
         <f t="shared" si="0"/>
         <v>0.999999999999998</v>
@@ -4978,22 +5387,22 @@
       </c>
       <c r="D12" s="23"/>
       <c r="E12" s="23"/>
-      <c r="F12" s="91"/>
+      <c r="F12" s="90"/>
       <c r="G12" s="23"/>
       <c r="H12" s="23"/>
       <c r="I12" s="23"/>
-      <c r="J12" s="91"/>
+      <c r="J12" s="90"/>
       <c r="K12" s="23"/>
       <c r="L12" s="23"/>
-      <c r="M12" s="91"/>
-      <c r="N12" s="136">
+      <c r="M12" s="90"/>
+      <c r="N12" s="133">
         <v>0</v>
       </c>
       <c r="O12" s="23"/>
       <c r="P12" s="23"/>
-      <c r="Q12" s="91"/>
+      <c r="Q12" s="90"/>
       <c r="R12" s="23"/>
-      <c r="S12" s="132"/>
+      <c r="S12" s="129"/>
       <c r="T12" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5011,22 +5420,22 @@
       </c>
       <c r="D13" s="25"/>
       <c r="E13" s="25"/>
-      <c r="F13" s="94"/>
+      <c r="F13" s="93"/>
       <c r="G13" s="25"/>
       <c r="H13" s="25"/>
       <c r="I13" s="25"/>
-      <c r="J13" s="94"/>
+      <c r="J13" s="93"/>
       <c r="K13" s="25"/>
       <c r="L13" s="25"/>
-      <c r="M13" s="94"/>
+      <c r="M13" s="93"/>
       <c r="N13" s="106">
         <v>0</v>
       </c>
       <c r="O13" s="25"/>
       <c r="P13" s="25"/>
-      <c r="Q13" s="91"/>
+      <c r="Q13" s="90"/>
       <c r="R13" s="25"/>
-      <c r="S13" s="133"/>
+      <c r="S13" s="130"/>
       <c r="T13" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5044,28 +5453,28 @@
       </c>
       <c r="D14" s="26"/>
       <c r="E14" s="26"/>
-      <c r="F14" s="97">
+      <c r="F14" s="96">
         <v>0.15384615384615299</v>
       </c>
       <c r="G14" s="26"/>
       <c r="H14" s="26"/>
       <c r="I14" s="26"/>
-      <c r="J14" s="97">
+      <c r="J14" s="96">
         <v>0.46153846153846101</v>
       </c>
       <c r="K14" s="26"/>
       <c r="L14" s="26"/>
-      <c r="M14" s="97"/>
-      <c r="N14" s="91">
+      <c r="M14" s="96"/>
+      <c r="N14" s="90">
         <v>0.38461538461538403</v>
       </c>
       <c r="O14" s="26"/>
       <c r="P14" s="26"/>
-      <c r="Q14" s="93">
+      <c r="Q14" s="92">
         <v>0</v>
       </c>
       <c r="R14" s="26"/>
-      <c r="S14" s="134"/>
+      <c r="S14" s="131"/>
       <c r="T14" s="1">
         <f t="shared" si="0"/>
         <v>0.999999999999998</v>
@@ -5083,15 +5492,15 @@
       </c>
       <c r="D15" s="23"/>
       <c r="E15" s="23"/>
-      <c r="F15" s="91"/>
+      <c r="F15" s="90"/>
       <c r="G15" s="23"/>
       <c r="H15" s="23"/>
       <c r="I15" s="23"/>
-      <c r="J15" s="91"/>
+      <c r="J15" s="90"/>
       <c r="K15" s="23"/>
       <c r="L15" s="23"/>
-      <c r="M15" s="91"/>
-      <c r="N15" s="91">
+      <c r="M15" s="90"/>
+      <c r="N15" s="90">
         <v>0.14285714285714199</v>
       </c>
       <c r="O15" s="23"/>
@@ -5100,7 +5509,7 @@
         <v>0.85714285714285698</v>
       </c>
       <c r="R15" s="23"/>
-      <c r="S15" s="132"/>
+      <c r="S15" s="129"/>
       <c r="T15" s="1">
         <f t="shared" si="0"/>
         <v>0.999999999999999</v>
@@ -5118,17 +5527,17 @@
       </c>
       <c r="D16" s="24"/>
       <c r="E16" s="24"/>
-      <c r="F16" s="100"/>
+      <c r="F16" s="99"/>
       <c r="G16" s="24"/>
       <c r="H16" s="24"/>
       <c r="I16" s="24"/>
-      <c r="J16" s="100"/>
+      <c r="J16" s="99"/>
       <c r="K16" s="24"/>
       <c r="L16" s="24"/>
-      <c r="M16" s="100">
+      <c r="M16" s="99">
         <v>7.1428571428571397E-2</v>
       </c>
-      <c r="N16" s="100">
+      <c r="N16" s="99">
         <v>7.1428571428571397E-2</v>
       </c>
       <c r="O16" s="24"/>
@@ -5137,7 +5546,7 @@
         <v>0.85714285714285698</v>
       </c>
       <c r="R16" s="24"/>
-      <c r="S16" s="135"/>
+      <c r="S16" s="132"/>
       <c r="T16" s="1">
         <f t="shared" si="0"/>
         <v>0.99999999999999978</v>
@@ -5155,29 +5564,27 @@
       </c>
       <c r="D17" s="22"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="105">
-        <v>0.33333333333333298</v>
+      <c r="F17" s="111">
+        <v>0.75</v>
       </c>
       <c r="G17" s="22"/>
       <c r="H17" s="22"/>
       <c r="I17" s="22"/>
-      <c r="J17" s="89">
-        <v>0.38888888888888801</v>
+      <c r="J17" s="88">
+        <v>0.25</v>
       </c>
       <c r="K17" s="22"/>
       <c r="L17" s="22"/>
       <c r="M17" s="22"/>
-      <c r="N17" s="89">
-        <v>0.27777777777777701</v>
-      </c>
+      <c r="N17" s="88"/>
       <c r="O17" s="22"/>
       <c r="P17" s="22"/>
-      <c r="Q17" s="89"/>
+      <c r="Q17" s="88"/>
       <c r="R17" s="22"/>
-      <c r="S17" s="131"/>
+      <c r="S17" s="128"/>
       <c r="T17" s="1">
         <f t="shared" si="0"/>
-        <v>0.999999999999998</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.2">
@@ -5192,22 +5599,22 @@
       </c>
       <c r="D18" s="23"/>
       <c r="E18" s="23"/>
-      <c r="F18" s="99">
+      <c r="F18" s="98">
         <v>0</v>
       </c>
       <c r="G18" s="23"/>
       <c r="H18" s="23"/>
       <c r="I18" s="23"/>
-      <c r="J18" s="91"/>
+      <c r="J18" s="90"/>
       <c r="K18" s="23"/>
       <c r="L18" s="23"/>
       <c r="M18" s="23"/>
-      <c r="N18" s="91"/>
+      <c r="N18" s="90"/>
       <c r="O18" s="23"/>
       <c r="P18" s="23"/>
-      <c r="Q18" s="91"/>
+      <c r="Q18" s="90"/>
       <c r="R18" s="23"/>
-      <c r="S18" s="132"/>
+      <c r="S18" s="129"/>
       <c r="T18" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5231,16 +5638,16 @@
       <c r="G19" s="25"/>
       <c r="H19" s="25"/>
       <c r="I19" s="25"/>
-      <c r="J19" s="91"/>
+      <c r="J19" s="90"/>
       <c r="K19" s="25"/>
       <c r="L19" s="25"/>
       <c r="M19" s="25"/>
-      <c r="N19" s="94"/>
+      <c r="N19" s="93"/>
       <c r="O19" s="25"/>
       <c r="P19" s="25"/>
-      <c r="Q19" s="94"/>
+      <c r="Q19" s="93"/>
       <c r="R19" s="25"/>
-      <c r="S19" s="133"/>
+      <c r="S19" s="130"/>
       <c r="T19" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5258,29 +5665,27 @@
       </c>
       <c r="D20" s="26"/>
       <c r="E20" s="26"/>
-      <c r="F20" s="91">
-        <v>0.33333333333333298</v>
+      <c r="F20" s="90">
+        <v>0.5</v>
       </c>
       <c r="G20" s="26"/>
       <c r="H20" s="26"/>
       <c r="I20" s="26"/>
-      <c r="J20" s="105">
-        <v>0.38888888888888801</v>
+      <c r="J20" s="111">
+        <v>0.5</v>
       </c>
       <c r="K20" s="26"/>
       <c r="L20" s="26"/>
       <c r="M20" s="26"/>
-      <c r="N20" s="97">
-        <v>0.27777777777777701</v>
-      </c>
+      <c r="N20" s="96"/>
       <c r="O20" s="26"/>
       <c r="P20" s="26"/>
-      <c r="Q20" s="97"/>
+      <c r="Q20" s="96"/>
       <c r="R20" s="26"/>
-      <c r="S20" s="134"/>
+      <c r="S20" s="131"/>
       <c r="T20" s="1">
         <f t="shared" si="0"/>
-        <v>0.999999999999998</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.2">
@@ -5295,22 +5700,22 @@
       </c>
       <c r="D21" s="23"/>
       <c r="E21" s="23"/>
-      <c r="F21" s="91"/>
+      <c r="F21" s="90"/>
       <c r="G21" s="23"/>
       <c r="H21" s="23"/>
       <c r="I21" s="23"/>
-      <c r="J21" s="136">
+      <c r="J21" s="133">
         <v>0</v>
       </c>
       <c r="K21" s="23"/>
       <c r="L21" s="23"/>
       <c r="M21" s="23"/>
-      <c r="N21" s="91"/>
+      <c r="N21" s="90"/>
       <c r="O21" s="23"/>
       <c r="P21" s="23"/>
-      <c r="Q21" s="91"/>
+      <c r="Q21" s="90"/>
       <c r="R21" s="23"/>
-      <c r="S21" s="132"/>
+      <c r="S21" s="129"/>
       <c r="T21" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5328,7 +5733,7 @@
       </c>
       <c r="D22" s="25"/>
       <c r="E22" s="25"/>
-      <c r="F22" s="94"/>
+      <c r="F22" s="93"/>
       <c r="G22" s="25"/>
       <c r="H22" s="25"/>
       <c r="I22" s="25"/>
@@ -5338,12 +5743,12 @@
       <c r="K22" s="25"/>
       <c r="L22" s="25"/>
       <c r="M22" s="25"/>
-      <c r="N22" s="94"/>
+      <c r="N22" s="93"/>
       <c r="O22" s="25"/>
       <c r="P22" s="25"/>
-      <c r="Q22" s="91"/>
+      <c r="Q22" s="90"/>
       <c r="R22" s="25"/>
-      <c r="S22" s="133"/>
+      <c r="S22" s="130"/>
       <c r="T22" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5361,29 +5766,25 @@
       </c>
       <c r="D23" s="23"/>
       <c r="E23" s="23"/>
-      <c r="F23" s="91"/>
+      <c r="F23" s="90"/>
       <c r="G23" s="23"/>
       <c r="H23" s="23"/>
       <c r="I23" s="23"/>
-      <c r="J23" s="91">
-        <v>0.28571428571428498</v>
-      </c>
+      <c r="J23" s="90"/>
       <c r="K23" s="23"/>
       <c r="L23" s="23"/>
       <c r="M23" s="23"/>
-      <c r="N23" s="91">
-        <v>0.71428571428571397</v>
-      </c>
+      <c r="N23" s="90"/>
       <c r="O23" s="23"/>
       <c r="P23" s="23"/>
-      <c r="Q23" s="93">
+      <c r="Q23" s="92">
         <v>0</v>
       </c>
       <c r="R23" s="23"/>
-      <c r="S23" s="132"/>
+      <c r="S23" s="129"/>
       <c r="T23" s="1">
         <f t="shared" si="0"/>
-        <v>0.99999999999999889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.2">
@@ -5398,27 +5799,25 @@
       </c>
       <c r="D24" s="23"/>
       <c r="E24" s="23"/>
-      <c r="F24" s="91"/>
+      <c r="F24" s="90"/>
       <c r="G24" s="23"/>
       <c r="H24" s="23"/>
       <c r="I24" s="23"/>
-      <c r="J24" s="91"/>
+      <c r="J24" s="90"/>
       <c r="K24" s="23"/>
       <c r="L24" s="23"/>
       <c r="M24" s="23"/>
-      <c r="N24" s="91">
-        <v>0.2</v>
-      </c>
+      <c r="N24" s="90"/>
       <c r="O24" s="23"/>
       <c r="P24" s="23"/>
-      <c r="Q24" s="108">
-        <v>0.8</v>
+      <c r="Q24" s="133">
+        <v>0</v>
       </c>
       <c r="R24" s="23"/>
-      <c r="S24" s="132"/>
+      <c r="S24" s="129"/>
       <c r="T24" s="1">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -5433,62 +5832,62 @@
       </c>
       <c r="D25" s="24"/>
       <c r="E25" s="24"/>
-      <c r="F25" s="100"/>
+      <c r="F25" s="99"/>
       <c r="G25" s="24"/>
       <c r="H25" s="24"/>
       <c r="I25" s="24"/>
-      <c r="J25" s="100"/>
+      <c r="J25" s="99"/>
       <c r="K25" s="24"/>
       <c r="L25" s="24"/>
       <c r="M25" s="24"/>
-      <c r="N25" s="100">
+      <c r="N25" s="99">
         <v>0.25</v>
       </c>
       <c r="O25" s="24"/>
       <c r="P25" s="24"/>
-      <c r="Q25" s="114">
+      <c r="Q25" s="112">
         <v>0.75</v>
       </c>
       <c r="R25" s="24"/>
-      <c r="S25" s="135"/>
+      <c r="S25" s="132"/>
       <c r="T25" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A27" s="118"/>
-      <c r="B27" s="118" t="s">
+      <c r="A27" s="116"/>
+      <c r="B27" s="116" t="s">
         <v>38</v>
       </c>
-      <c r="C27" s="118" t="s">
+      <c r="C27" s="116" t="s">
         <v>39</v>
       </c>
-      <c r="D27" s="118" t="s">
+      <c r="D27" s="116" t="s">
         <v>40</v>
       </c>
-      <c r="E27" s="118" t="s">
+      <c r="E27" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="F27" s="118" t="s">
+      <c r="F27" s="116" t="s">
         <v>42</v>
       </c>
-      <c r="G27" s="118" t="s">
+      <c r="G27" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="H27" s="118" t="s">
+      <c r="H27" s="116" t="s">
         <v>44</v>
       </c>
-      <c r="I27" s="118" t="s">
+      <c r="I27" s="116" t="s">
         <v>45</v>
       </c>
-      <c r="J27" s="118" t="s">
+      <c r="J27" s="116" t="s">
         <v>46</v>
       </c>
-      <c r="K27" s="118" t="s">
+      <c r="K27" s="116" t="s">
         <v>47</v>
       </c>
-      <c r="L27" s="118" t="s">
+      <c r="L27" s="116" t="s">
         <v>48</v>
       </c>
     </row>
@@ -5535,34 +5934,34 @@
         <v>8</v>
       </c>
       <c r="B29" s="1">
-        <v>0.23194444444444401</v>
+        <v>0.4</v>
       </c>
       <c r="C29" s="1">
-        <v>0.370734126984127</v>
+        <v>0.12668650793650699</v>
       </c>
       <c r="D29" s="14">
-        <v>0.25803703703703701</v>
+        <v>0.178787878787878</v>
       </c>
       <c r="E29" s="14">
-        <v>3.19444444444444E-2</v>
+        <v>0.2</v>
       </c>
       <c r="F29" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="14">
         <v>0.6</v>
       </c>
       <c r="H29" s="1">
-        <v>0.19222944751995499</v>
+        <v>0.33911649915626302</v>
       </c>
       <c r="I29" s="1">
-        <v>0.37423648862785802</v>
+        <v>0.15783589860001199</v>
       </c>
       <c r="J29" s="1">
-        <v>0.224238861965011</v>
+        <v>0.19926402694271</v>
       </c>
       <c r="K29" s="1">
-        <v>0.17509861651972999</v>
+        <v>0.29350407322379601</v>
       </c>
       <c r="L29" s="1">
         <v>0</v>

--- a/patterns/results/exp1/4bins-results.xlsx
+++ b/patterns/results/exp1/4bins-results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59FFEA09-34E1-3F49-9EE6-410F73ED2096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D564F903-D713-EB44-BE35-3C217371404E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2060" yWindow="1020" windowWidth="31680" windowHeight="19340" activeTab="4" xr2:uid="{9429E1C1-1F54-8A42-9286-E37255B8DAF7}"/>
+    <workbookView xWindow="2440" yWindow="960" windowWidth="31680" windowHeight="19340" activeTab="2" xr2:uid="{9429E1C1-1F54-8A42-9286-E37255B8DAF7}"/>
   </bookViews>
   <sheets>
     <sheet name="GO" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
   <connection id="1" xr16:uid="{A8FB4FA6-6B9B-E14E-938E-0C0FCD3EE22E}" name="metrics-acl" type="6" refreshedVersion="8" background="1" saveData="1">
-    <textPr codePage="10000" sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/metrics-acl.csv" thousands="." comma="1">
+    <textPr sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/metrics-acl.csv" thousands="." comma="1">
       <textFields count="12">
         <textField/>
         <textField/>
@@ -72,7 +72,7 @@
     </textPr>
   </connection>
   <connection id="2" xr16:uid="{8F71BCCB-9DA0-144F-9D06-AF730388E029}" name="metrics-cqrs1" type="6" refreshedVersion="8" background="1" saveData="1">
-    <textPr codePage="10000" sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/metrics-cqrs.csv" thousands="." comma="1">
+    <textPr sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/metrics-cqrs.csv" thousands="." comma="1">
       <textFields count="12">
         <textField/>
         <textField/>
@@ -90,7 +90,7 @@
     </textPr>
   </connection>
   <connection id="3" xr16:uid="{0A4337A6-686E-6040-92B7-22F1899AA00C}" name="metrics-ga1" type="6" refreshedVersion="8" background="1" saveData="1">
-    <textPr codePage="10000" sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/metrics-ga.csv" thousands="." comma="1">
+    <textPr sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/metrics-ga.csv" thousands="." comma="1">
       <textFields count="12">
         <textField/>
         <textField/>
@@ -108,7 +108,7 @@
     </textPr>
   </connection>
   <connection id="4" xr16:uid="{134B4E51-F17D-E24F-8C43-5587947006CC}" name="metrics-go1" type="6" refreshedVersion="8" background="1" saveData="1">
-    <textPr codePage="10000" sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/metrics-go.csv" thousands="." comma="1">
+    <textPr sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/metrics-go.csv" thousands="." comma="1">
       <textFields count="12">
         <textField/>
         <textField/>
@@ -126,7 +126,7 @@
     </textPr>
   </connection>
   <connection id="5" xr16:uid="{A1D10C97-C0EC-584A-8D7D-53F84B328C43}" name="metrics-paf" type="6" refreshedVersion="8" background="1" saveData="1">
-    <textPr codePage="10000" sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/metrics-paf.csv" thousands="." comma="1">
+    <textPr sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/metrics-paf.csv" thousands="." comma="1">
       <textFields count="12">
         <textField/>
         <textField/>
@@ -1066,7 +1066,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="167">
+  <cellXfs count="156">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1169,64 +1169,54 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="12" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="13" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="14" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="14" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="14" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="12" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="13" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="36" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1242,20 +1232,19 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1549,7 +1538,7 @@
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="metrics_go_1" connectionId="4" xr16:uid="{63DCC8F5-17EE-1340-9B93-10B151E3B558}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="results_go_1" connectionId="9" xr16:uid="{F5596237-E230-FF47-BEBA-D881481B07E8}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable10.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1557,7 +1546,7 @@
 </file>
 
 <file path=xl/queryTables/queryTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="results_go_1" connectionId="9" xr16:uid="{F5596237-E230-FF47-BEBA-D881481B07E8}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="metrics_go_1" connectionId="4" xr16:uid="{63DCC8F5-17EE-1340-9B93-10B151E3B558}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1577,11 +1566,11 @@
 </file>
 
 <file path=xl/queryTables/queryTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="metrics_ga_1" connectionId="3" xr16:uid="{D3FD6001-8A85-AD43-91C6-1F875D4FBFD9}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="results_ga_1" connectionId="8" xr16:uid="{6942D71A-6248-0E43-BD5A-53429B6671E4}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="results_ga_1" connectionId="8" xr16:uid="{6942D71A-6248-0E43-BD5A-53429B6671E4}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="metrics_ga_1" connectionId="3" xr16:uid="{D3FD6001-8A85-AD43-91C6-1F875D4FBFD9}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable9.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2001,25 +1990,25 @@
       <c r="H2" s="22"/>
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
-      <c r="K2" s="88">
+      <c r="K2" s="10">
         <v>0</v>
       </c>
       <c r="L2" s="22"/>
       <c r="M2" s="22"/>
-      <c r="N2" s="88">
-        <v>0</v>
-      </c>
-      <c r="O2" s="88">
-        <v>0</v>
-      </c>
-      <c r="P2" s="102">
+      <c r="N2" s="10">
+        <v>0</v>
+      </c>
+      <c r="O2" s="10">
+        <v>0</v>
+      </c>
+      <c r="P2" s="99">
         <v>1</v>
       </c>
-      <c r="Q2" s="88">
+      <c r="Q2" s="10">
         <v>0</v>
       </c>
       <c r="R2" s="22"/>
-      <c r="S2" s="89">
+      <c r="S2" s="88">
         <v>0</v>
       </c>
       <c r="T2" s="1">
@@ -2045,25 +2034,25 @@
       <c r="H3" s="23"/>
       <c r="I3" s="23"/>
       <c r="J3" s="23"/>
-      <c r="K3" s="109">
+      <c r="K3" s="106">
         <v>0.11111111111111099</v>
       </c>
       <c r="L3" s="23"/>
       <c r="M3" s="23"/>
-      <c r="N3" s="90">
-        <v>0</v>
-      </c>
-      <c r="O3" s="101">
+      <c r="N3" s="12">
+        <v>0</v>
+      </c>
+      <c r="O3" s="98">
         <v>0.33333333333333298</v>
       </c>
-      <c r="P3" s="90">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="90">
+      <c r="P3" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="12">
         <v>0</v>
       </c>
       <c r="R3" s="23"/>
-      <c r="S3" s="103">
+      <c r="S3" s="100">
         <v>0.55555555555555503</v>
       </c>
       <c r="T3" s="1">
@@ -2089,25 +2078,25 @@
       <c r="H4" s="23"/>
       <c r="I4" s="23"/>
       <c r="J4" s="23"/>
-      <c r="K4" s="90">
+      <c r="K4" s="12">
         <v>0</v>
       </c>
       <c r="L4" s="23"/>
       <c r="M4" s="23"/>
-      <c r="N4" s="109">
+      <c r="N4" s="106">
         <v>0.28571428571428498</v>
       </c>
-      <c r="O4" s="90">
-        <v>0</v>
-      </c>
-      <c r="P4" s="90">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="101">
+      <c r="O4" s="12">
+        <v>0</v>
+      </c>
+      <c r="P4" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="98">
         <v>0.71428571428571397</v>
       </c>
       <c r="R4" s="23"/>
-      <c r="S4" s="91">
+      <c r="S4" s="89">
         <v>0</v>
       </c>
       <c r="T4" s="1">
@@ -2132,17 +2121,17 @@
       <c r="H5" s="22"/>
       <c r="I5" s="22"/>
       <c r="J5" s="22"/>
-      <c r="K5" s="88"/>
+      <c r="K5" s="10"/>
       <c r="L5" s="22"/>
       <c r="M5" s="22"/>
-      <c r="N5" s="88"/>
-      <c r="O5" s="92">
-        <v>0</v>
-      </c>
-      <c r="P5" s="88"/>
-      <c r="Q5" s="88"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="90">
+        <v>0</v>
+      </c>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
       <c r="R5" s="22"/>
-      <c r="S5" s="89"/>
+      <c r="S5" s="88"/>
       <c r="T5" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2165,19 +2154,19 @@
       <c r="H6" s="23"/>
       <c r="I6" s="23"/>
       <c r="J6" s="23"/>
-      <c r="K6" s="90">
+      <c r="K6" s="12">
         <v>0.11111111111111099</v>
       </c>
       <c r="L6" s="23"/>
       <c r="M6" s="23"/>
-      <c r="N6" s="90"/>
-      <c r="O6" s="104">
+      <c r="N6" s="12"/>
+      <c r="O6" s="101">
         <v>0.33333333333333298</v>
       </c>
-      <c r="P6" s="90"/>
-      <c r="Q6" s="90"/>
+      <c r="P6" s="12"/>
+      <c r="Q6" s="12"/>
       <c r="R6" s="23"/>
-      <c r="S6" s="91">
+      <c r="S6" s="89">
         <v>0.55555555555555503</v>
       </c>
       <c r="T6" s="1">
@@ -2202,17 +2191,17 @@
       <c r="H7" s="25"/>
       <c r="I7" s="25"/>
       <c r="J7" s="25"/>
-      <c r="K7" s="93"/>
+      <c r="K7" s="91"/>
       <c r="L7" s="25"/>
       <c r="M7" s="25"/>
-      <c r="N7" s="93"/>
-      <c r="O7" s="94">
-        <v>0</v>
-      </c>
-      <c r="P7" s="90"/>
-      <c r="Q7" s="93"/>
+      <c r="N7" s="91"/>
+      <c r="O7" s="92">
+        <v>0</v>
+      </c>
+      <c r="P7" s="12"/>
+      <c r="Q7" s="91"/>
       <c r="R7" s="25"/>
-      <c r="S7" s="95"/>
+      <c r="S7" s="93"/>
       <c r="T7" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2235,17 +2224,17 @@
       <c r="H8" s="26"/>
       <c r="I8" s="26"/>
       <c r="J8" s="26"/>
-      <c r="K8" s="96"/>
+      <c r="K8" s="94"/>
       <c r="L8" s="26"/>
       <c r="M8" s="26"/>
-      <c r="N8" s="96"/>
-      <c r="O8" s="90"/>
-      <c r="P8" s="105">
+      <c r="N8" s="94"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="102">
         <v>1</v>
       </c>
-      <c r="Q8" s="96"/>
+      <c r="Q8" s="94"/>
       <c r="R8" s="26"/>
-      <c r="S8" s="97"/>
+      <c r="S8" s="95"/>
       <c r="T8" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2268,17 +2257,17 @@
       <c r="H9" s="23"/>
       <c r="I9" s="23"/>
       <c r="J9" s="23"/>
-      <c r="K9" s="90"/>
+      <c r="K9" s="12"/>
       <c r="L9" s="23"/>
       <c r="M9" s="23"/>
-      <c r="N9" s="90"/>
-      <c r="O9" s="90"/>
-      <c r="P9" s="98">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="90"/>
+      <c r="N9" s="12"/>
+      <c r="O9" s="12"/>
+      <c r="P9" s="96">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="12"/>
       <c r="R9" s="23"/>
-      <c r="S9" s="91"/>
+      <c r="S9" s="89"/>
       <c r="T9" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2301,17 +2290,17 @@
       <c r="H10" s="25"/>
       <c r="I10" s="25"/>
       <c r="J10" s="25"/>
-      <c r="K10" s="93"/>
+      <c r="K10" s="91"/>
       <c r="L10" s="25"/>
       <c r="M10" s="25"/>
-      <c r="N10" s="93"/>
-      <c r="O10" s="93"/>
-      <c r="P10" s="94">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="90"/>
+      <c r="N10" s="91"/>
+      <c r="O10" s="91"/>
+      <c r="P10" s="92">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="12"/>
       <c r="R10" s="25"/>
-      <c r="S10" s="95"/>
+      <c r="S10" s="93"/>
       <c r="T10" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2334,17 +2323,17 @@
       <c r="H11" s="26"/>
       <c r="I11" s="26"/>
       <c r="J11" s="26"/>
-      <c r="K11" s="96"/>
+      <c r="K11" s="94"/>
       <c r="L11" s="26"/>
       <c r="M11" s="26"/>
-      <c r="N11" s="96"/>
-      <c r="O11" s="96"/>
-      <c r="P11" s="90"/>
-      <c r="Q11" s="92">
+      <c r="N11" s="94"/>
+      <c r="O11" s="94"/>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="90">
         <v>0</v>
       </c>
       <c r="R11" s="26"/>
-      <c r="S11" s="97"/>
+      <c r="S11" s="95"/>
       <c r="T11" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2367,17 +2356,17 @@
       <c r="H12" s="23"/>
       <c r="I12" s="23"/>
       <c r="J12" s="23"/>
-      <c r="K12" s="90"/>
+      <c r="K12" s="12"/>
       <c r="L12" s="23"/>
       <c r="M12" s="23"/>
-      <c r="N12" s="90"/>
-      <c r="O12" s="90"/>
-      <c r="P12" s="90"/>
-      <c r="Q12" s="98">
+      <c r="N12" s="12"/>
+      <c r="O12" s="12"/>
+      <c r="P12" s="12"/>
+      <c r="Q12" s="96">
         <v>0</v>
       </c>
       <c r="R12" s="23"/>
-      <c r="S12" s="91"/>
+      <c r="S12" s="89"/>
       <c r="T12" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2400,19 +2389,19 @@
       <c r="H13" s="25"/>
       <c r="I13" s="25"/>
       <c r="J13" s="25"/>
-      <c r="K13" s="93"/>
+      <c r="K13" s="91"/>
       <c r="L13" s="25"/>
       <c r="M13" s="25"/>
-      <c r="N13" s="93">
+      <c r="N13" s="91">
         <v>0.18181818181818099</v>
       </c>
-      <c r="O13" s="93"/>
-      <c r="P13" s="93"/>
-      <c r="Q13" s="107">
+      <c r="O13" s="91"/>
+      <c r="P13" s="91"/>
+      <c r="Q13" s="104">
         <v>0.81818181818181801</v>
       </c>
       <c r="R13" s="25"/>
-      <c r="S13" s="91"/>
+      <c r="S13" s="89"/>
       <c r="T13" s="1">
         <f t="shared" si="0"/>
         <v>0.999999999999999</v>
@@ -2435,15 +2424,15 @@
       <c r="H14" s="26"/>
       <c r="I14" s="26"/>
       <c r="J14" s="26"/>
-      <c r="K14" s="96"/>
+      <c r="K14" s="94"/>
       <c r="L14" s="26"/>
       <c r="M14" s="26"/>
-      <c r="N14" s="96"/>
-      <c r="O14" s="96"/>
-      <c r="P14" s="96"/>
-      <c r="Q14" s="90"/>
+      <c r="N14" s="94"/>
+      <c r="O14" s="94"/>
+      <c r="P14" s="94"/>
+      <c r="Q14" s="12"/>
       <c r="R14" s="26"/>
-      <c r="S14" s="92">
+      <c r="S14" s="90">
         <v>0</v>
       </c>
       <c r="T14" s="1">
@@ -2468,17 +2457,17 @@
       <c r="H15" s="23"/>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
-      <c r="K15" s="90"/>
+      <c r="K15" s="12"/>
       <c r="L15" s="23"/>
       <c r="M15" s="23"/>
-      <c r="N15" s="90"/>
-      <c r="O15" s="90">
+      <c r="N15" s="12"/>
+      <c r="O15" s="12">
         <v>0.28571428571428498</v>
       </c>
-      <c r="P15" s="90"/>
-      <c r="Q15" s="90"/>
+      <c r="P15" s="12"/>
+      <c r="Q15" s="12"/>
       <c r="R15" s="23"/>
-      <c r="S15" s="108">
+      <c r="S15" s="105">
         <v>0.71428571428571397</v>
       </c>
       <c r="T15" s="1">
@@ -2493,25 +2482,25 @@
       <c r="B16" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="139" t="s">
+      <c r="C16" s="131" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="140"/>
-      <c r="E16" s="140"/>
-      <c r="F16" s="140"/>
-      <c r="G16" s="140"/>
-      <c r="H16" s="140"/>
-      <c r="I16" s="140"/>
-      <c r="J16" s="140"/>
-      <c r="K16" s="136"/>
-      <c r="L16" s="140"/>
-      <c r="M16" s="140"/>
-      <c r="N16" s="136"/>
-      <c r="O16" s="136"/>
-      <c r="P16" s="136"/>
-      <c r="Q16" s="136"/>
-      <c r="R16" s="140"/>
-      <c r="S16" s="98">
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="12"/>
+      <c r="O16" s="12"/>
+      <c r="P16" s="12"/>
+      <c r="Q16" s="12"/>
+      <c r="R16" s="23"/>
+      <c r="S16" s="96">
         <v>0</v>
       </c>
       <c r="T16" s="1">
@@ -2526,7 +2515,7 @@
       <c r="B17" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="C17" s="143" t="s">
+      <c r="C17" s="133" t="s">
         <v>26</v>
       </c>
       <c r="D17" s="22"/>
@@ -2536,17 +2525,17 @@
       <c r="H17" s="22"/>
       <c r="I17" s="22"/>
       <c r="J17" s="22"/>
-      <c r="K17" s="88"/>
+      <c r="K17" s="10"/>
       <c r="L17" s="22"/>
       <c r="M17" s="22"/>
-      <c r="N17" s="88"/>
-      <c r="O17" s="92">
-        <v>0</v>
-      </c>
-      <c r="P17" s="88"/>
-      <c r="Q17" s="88"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="90">
+        <v>0</v>
+      </c>
+      <c r="P17" s="10"/>
+      <c r="Q17" s="10"/>
       <c r="R17" s="22"/>
-      <c r="S17" s="89"/>
+      <c r="S17" s="88"/>
       <c r="T17" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2556,43 +2545,43 @@
       <c r="A18" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="141" t="s">
+      <c r="B18" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="144" t="s">
+      <c r="C18" s="134" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="140"/>
-      <c r="E18" s="140"/>
-      <c r="F18" s="140"/>
-      <c r="G18" s="140"/>
-      <c r="H18" s="140"/>
-      <c r="I18" s="140"/>
-      <c r="J18" s="140"/>
-      <c r="K18" s="136"/>
-      <c r="L18" s="140"/>
-      <c r="M18" s="140"/>
-      <c r="N18" s="136"/>
-      <c r="O18" s="108">
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="23"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="23"/>
+      <c r="M18" s="23"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="105">
         <v>1</v>
       </c>
-      <c r="P18" s="136"/>
-      <c r="Q18" s="136"/>
-      <c r="R18" s="140"/>
-      <c r="S18" s="91"/>
+      <c r="P18" s="12"/>
+      <c r="Q18" s="12"/>
+      <c r="R18" s="23"/>
+      <c r="S18" s="89"/>
       <c r="T18" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="155" t="s">
+      <c r="A19" s="145" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="150" t="s">
+      <c r="B19" s="140" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="151" t="s">
+      <c r="C19" s="141" t="s">
         <v>26</v>
       </c>
       <c r="D19" s="25"/>
@@ -2602,30 +2591,30 @@
       <c r="H19" s="25"/>
       <c r="I19" s="25"/>
       <c r="J19" s="25"/>
-      <c r="K19" s="93"/>
+      <c r="K19" s="91"/>
       <c r="L19" s="25"/>
       <c r="M19" s="25"/>
-      <c r="N19" s="93"/>
-      <c r="O19" s="94">
-        <v>0</v>
-      </c>
-      <c r="P19" s="136"/>
-      <c r="Q19" s="93"/>
+      <c r="N19" s="91"/>
+      <c r="O19" s="92">
+        <v>0</v>
+      </c>
+      <c r="P19" s="12"/>
+      <c r="Q19" s="91"/>
       <c r="R19" s="25"/>
-      <c r="S19" s="95"/>
+      <c r="S19" s="93"/>
       <c r="T19" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A20" s="156" t="s">
+      <c r="A20" s="146" t="s">
         <v>8</v>
       </c>
-      <c r="B20" s="149" t="s">
+      <c r="B20" s="139" t="s">
         <v>4</v>
       </c>
-      <c r="C20" s="152" t="s">
+      <c r="C20" s="142" t="s">
         <v>27</v>
       </c>
       <c r="D20" s="26"/>
@@ -2635,17 +2624,17 @@
       <c r="H20" s="26"/>
       <c r="I20" s="26"/>
       <c r="J20" s="26"/>
-      <c r="K20" s="96"/>
+      <c r="K20" s="94"/>
       <c r="L20" s="26"/>
       <c r="M20" s="26"/>
-      <c r="N20" s="96"/>
-      <c r="O20" s="136"/>
-      <c r="P20" s="111">
+      <c r="N20" s="94"/>
+      <c r="O20" s="12"/>
+      <c r="P20" s="108">
         <v>1</v>
       </c>
-      <c r="Q20" s="96"/>
+      <c r="Q20" s="94"/>
       <c r="R20" s="26"/>
-      <c r="S20" s="97"/>
+      <c r="S20" s="95"/>
       <c r="T20" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2655,43 +2644,43 @@
       <c r="A21" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B21" s="141" t="s">
+      <c r="B21" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="145" t="s">
+      <c r="C21" s="135" t="s">
         <v>27</v>
       </c>
-      <c r="D21" s="140"/>
-      <c r="E21" s="140"/>
-      <c r="F21" s="140"/>
-      <c r="G21" s="140"/>
-      <c r="H21" s="140"/>
-      <c r="I21" s="140"/>
-      <c r="J21" s="140"/>
-      <c r="K21" s="136"/>
-      <c r="L21" s="140"/>
-      <c r="M21" s="140"/>
-      <c r="N21" s="136"/>
-      <c r="O21" s="136"/>
-      <c r="P21" s="98">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="136"/>
-      <c r="R21" s="140"/>
-      <c r="S21" s="91"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="23"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="23"/>
+      <c r="M21" s="23"/>
+      <c r="N21" s="12"/>
+      <c r="O21" s="12"/>
+      <c r="P21" s="96">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="12"/>
+      <c r="R21" s="23"/>
+      <c r="S21" s="89"/>
       <c r="T21" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="155" t="s">
+      <c r="A22" s="145" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="150" t="s">
+      <c r="B22" s="140" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="153" t="s">
+      <c r="C22" s="143" t="s">
         <v>27</v>
       </c>
       <c r="D22" s="25"/>
@@ -2701,30 +2690,30 @@
       <c r="H22" s="25"/>
       <c r="I22" s="25"/>
       <c r="J22" s="25"/>
-      <c r="K22" s="93"/>
+      <c r="K22" s="91"/>
       <c r="L22" s="25"/>
       <c r="M22" s="25"/>
-      <c r="N22" s="93"/>
-      <c r="O22" s="93"/>
-      <c r="P22" s="94">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="136"/>
+      <c r="N22" s="91"/>
+      <c r="O22" s="91"/>
+      <c r="P22" s="92">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="12"/>
       <c r="R22" s="25"/>
-      <c r="S22" s="95"/>
+      <c r="S22" s="93"/>
       <c r="T22" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A23" s="156" t="s">
+      <c r="A23" s="146" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="149" t="s">
+      <c r="B23" s="139" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="138" t="s">
+      <c r="C23" s="130" t="s">
         <v>28</v>
       </c>
       <c r="D23" s="26"/>
@@ -2734,17 +2723,17 @@
       <c r="H23" s="26"/>
       <c r="I23" s="26"/>
       <c r="J23" s="26"/>
-      <c r="K23" s="96"/>
+      <c r="K23" s="94"/>
       <c r="L23" s="26"/>
       <c r="M23" s="26"/>
-      <c r="N23" s="96"/>
-      <c r="O23" s="96"/>
-      <c r="P23" s="136"/>
-      <c r="Q23" s="92">
+      <c r="N23" s="94"/>
+      <c r="O23" s="94"/>
+      <c r="P23" s="12"/>
+      <c r="Q23" s="90">
         <v>0</v>
       </c>
       <c r="R23" s="26"/>
-      <c r="S23" s="97"/>
+      <c r="S23" s="95"/>
       <c r="T23" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2754,43 +2743,43 @@
       <c r="A24" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B24" s="141" t="s">
+      <c r="B24" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="146" t="s">
+      <c r="C24" s="136" t="s">
         <v>28</v>
       </c>
-      <c r="D24" s="140"/>
-      <c r="E24" s="140"/>
-      <c r="F24" s="140"/>
-      <c r="G24" s="140"/>
-      <c r="H24" s="140"/>
-      <c r="I24" s="140"/>
-      <c r="J24" s="140"/>
-      <c r="K24" s="136"/>
-      <c r="L24" s="140"/>
-      <c r="M24" s="140"/>
-      <c r="N24" s="136"/>
-      <c r="O24" s="136"/>
-      <c r="P24" s="136"/>
-      <c r="Q24" s="98">
-        <v>0</v>
-      </c>
-      <c r="R24" s="140"/>
-      <c r="S24" s="91"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="23"/>
+      <c r="I24" s="23"/>
+      <c r="J24" s="23"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="23"/>
+      <c r="M24" s="23"/>
+      <c r="N24" s="12"/>
+      <c r="O24" s="12"/>
+      <c r="P24" s="12"/>
+      <c r="Q24" s="96">
+        <v>0</v>
+      </c>
+      <c r="R24" s="23"/>
+      <c r="S24" s="89"/>
       <c r="T24" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="155" t="s">
+      <c r="A25" s="145" t="s">
         <v>8</v>
       </c>
-      <c r="B25" s="150" t="s">
+      <c r="B25" s="140" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="154" t="s">
+      <c r="C25" s="144" t="s">
         <v>28</v>
       </c>
       <c r="D25" s="25"/>
@@ -2800,17 +2789,17 @@
       <c r="H25" s="25"/>
       <c r="I25" s="25"/>
       <c r="J25" s="25"/>
-      <c r="K25" s="93"/>
+      <c r="K25" s="91"/>
       <c r="L25" s="25"/>
       <c r="M25" s="25"/>
-      <c r="N25" s="93"/>
-      <c r="O25" s="93"/>
-      <c r="P25" s="93"/>
-      <c r="Q25" s="107">
+      <c r="N25" s="91"/>
+      <c r="O25" s="91"/>
+      <c r="P25" s="91"/>
+      <c r="Q25" s="104">
         <v>1</v>
       </c>
       <c r="R25" s="25"/>
-      <c r="S25" s="91"/>
+      <c r="S25" s="89"/>
       <c r="T25" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2820,28 +2809,28 @@
       <c r="A26" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B26" s="141" t="s">
+      <c r="B26" t="s">
         <v>4</v>
       </c>
-      <c r="C26" s="147" t="s">
+      <c r="C26" s="137" t="s">
         <v>30</v>
       </c>
-      <c r="D26" s="140"/>
-      <c r="E26" s="140"/>
-      <c r="F26" s="140"/>
-      <c r="G26" s="140"/>
-      <c r="H26" s="140"/>
-      <c r="I26" s="140"/>
-      <c r="J26" s="140"/>
-      <c r="K26" s="136"/>
-      <c r="L26" s="140"/>
-      <c r="M26" s="140"/>
-      <c r="N26" s="136"/>
-      <c r="O26" s="136"/>
-      <c r="P26" s="136"/>
-      <c r="Q26" s="136"/>
-      <c r="R26" s="140"/>
-      <c r="S26" s="92">
+      <c r="D26" s="23"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="23"/>
+      <c r="I26" s="23"/>
+      <c r="J26" s="23"/>
+      <c r="K26" s="12"/>
+      <c r="L26" s="23"/>
+      <c r="M26" s="23"/>
+      <c r="N26" s="12"/>
+      <c r="O26" s="12"/>
+      <c r="P26" s="12"/>
+      <c r="Q26" s="12"/>
+      <c r="R26" s="23"/>
+      <c r="S26" s="90">
         <v>0</v>
       </c>
       <c r="T26" s="1">
@@ -2853,30 +2842,30 @@
       <c r="A27" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B27" s="141" t="s">
+      <c r="B27" t="s">
         <v>5</v>
       </c>
-      <c r="C27" s="147" t="s">
+      <c r="C27" s="137" t="s">
         <v>30</v>
       </c>
-      <c r="D27" s="140"/>
-      <c r="E27" s="140"/>
-      <c r="F27" s="140"/>
-      <c r="G27" s="140"/>
-      <c r="H27" s="140"/>
-      <c r="I27" s="140"/>
-      <c r="J27" s="140"/>
-      <c r="K27" s="136"/>
-      <c r="L27" s="140"/>
-      <c r="M27" s="140"/>
-      <c r="N27" s="136"/>
-      <c r="O27" s="136">
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
+      <c r="I27" s="23"/>
+      <c r="J27" s="23"/>
+      <c r="K27" s="12"/>
+      <c r="L27" s="23"/>
+      <c r="M27" s="23"/>
+      <c r="N27" s="12"/>
+      <c r="O27" s="12">
         <v>0.16666666666666599</v>
       </c>
-      <c r="P27" s="136"/>
-      <c r="Q27" s="136"/>
-      <c r="R27" s="140"/>
-      <c r="S27" s="108">
+      <c r="P27" s="12"/>
+      <c r="Q27" s="12"/>
+      <c r="R27" s="23"/>
+      <c r="S27" s="105">
         <v>0.83333333333333304</v>
       </c>
       <c r="T27" s="1">
@@ -2891,7 +2880,7 @@
       <c r="B28" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="148" t="s">
+      <c r="C28" s="138" t="s">
         <v>30</v>
       </c>
       <c r="D28" s="24"/>
@@ -2901,15 +2890,15 @@
       <c r="H28" s="24"/>
       <c r="I28" s="24"/>
       <c r="J28" s="24"/>
-      <c r="K28" s="99"/>
+      <c r="K28" s="9"/>
       <c r="L28" s="24"/>
       <c r="M28" s="24"/>
-      <c r="N28" s="99"/>
-      <c r="O28" s="99"/>
-      <c r="P28" s="99"/>
-      <c r="Q28" s="99"/>
+      <c r="N28" s="9"/>
+      <c r="O28" s="9"/>
+      <c r="P28" s="9"/>
+      <c r="Q28" s="9"/>
       <c r="R28" s="24"/>
-      <c r="S28" s="94">
+      <c r="S28" s="92">
         <v>0</v>
       </c>
       <c r="T28" s="1">
@@ -2930,82 +2919,82 @@
       <c r="M29" s="1"/>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A30" s="137"/>
-      <c r="B30" s="137"/>
-      <c r="C30" s="137"/>
-      <c r="D30" s="136"/>
-      <c r="E30" s="136"/>
-      <c r="F30" s="136"/>
-      <c r="G30" s="136"/>
-      <c r="H30" s="136"/>
-      <c r="I30" s="136"/>
-      <c r="J30" s="136"/>
-      <c r="K30" s="136"/>
-      <c r="L30" s="136"/>
+      <c r="A30" s="13"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="12"/>
+      <c r="L30" s="12"/>
       <c r="M30" s="1"/>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A31" s="137"/>
-      <c r="B31" s="136"/>
-      <c r="C31" s="136"/>
-      <c r="D31" s="136"/>
-      <c r="E31" s="136"/>
-      <c r="F31" s="136"/>
-      <c r="G31" s="136"/>
-      <c r="H31" s="136"/>
-      <c r="I31" s="136"/>
-      <c r="J31" s="136"/>
-      <c r="K31" s="136"/>
-      <c r="L31" s="136"/>
+      <c r="A31" s="13"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="12"/>
+      <c r="L31" s="12"/>
       <c r="M31" s="1"/>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A32" s="137"/>
-      <c r="B32" s="136"/>
-      <c r="C32" s="136"/>
-      <c r="D32" s="136"/>
-      <c r="E32" s="136"/>
-      <c r="F32" s="136"/>
-      <c r="G32" s="136"/>
-      <c r="H32" s="136"/>
-      <c r="I32" s="136"/>
-      <c r="J32" s="136"/>
-      <c r="K32" s="136"/>
-      <c r="L32" s="136"/>
+      <c r="A32" s="13"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="12"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A34" s="116"/>
-      <c r="B34" s="116" t="s">
+      <c r="A34" s="113"/>
+      <c r="B34" s="113" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="116" t="s">
+      <c r="C34" s="113" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="116" t="s">
+      <c r="D34" s="113" t="s">
         <v>40</v>
       </c>
-      <c r="E34" s="116" t="s">
+      <c r="E34" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="F34" s="116" t="s">
+      <c r="F34" s="113" t="s">
         <v>42</v>
       </c>
-      <c r="G34" s="116" t="s">
+      <c r="G34" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="H34" s="116" t="s">
+      <c r="H34" s="113" t="s">
         <v>44</v>
       </c>
-      <c r="I34" s="116" t="s">
+      <c r="I34" s="113" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="116" t="s">
+      <c r="J34" s="113" t="s">
         <v>46</v>
       </c>
-      <c r="K34" s="116" t="s">
+      <c r="K34" s="113" t="s">
         <v>47</v>
       </c>
-      <c r="L34" s="116" t="s">
+      <c r="L34" s="113" t="s">
         <v>48</v>
       </c>
     </row>
@@ -3195,22 +3184,22 @@
       <c r="K2" s="22"/>
       <c r="L2" s="22"/>
       <c r="M2" s="22"/>
-      <c r="N2" s="113">
+      <c r="N2" s="110">
         <v>5.5555555555555497E-2</v>
       </c>
       <c r="O2" s="22">
         <v>0</v>
       </c>
-      <c r="P2" s="113">
+      <c r="P2" s="110">
         <v>8.7301587301587297E-2</v>
       </c>
-      <c r="Q2" s="102">
+      <c r="Q2" s="99">
         <v>0.79365079365079305</v>
       </c>
-      <c r="R2" s="113">
+      <c r="R2" s="110">
         <v>6.3492063492063405E-2</v>
       </c>
-      <c r="S2" s="89">
+      <c r="S2" s="88">
         <v>0</v>
       </c>
       <c r="T2" s="1">
@@ -3239,22 +3228,22 @@
       <c r="K3" s="23"/>
       <c r="L3" s="23"/>
       <c r="M3" s="23"/>
-      <c r="N3" s="90">
+      <c r="N3" s="12">
         <v>0</v>
       </c>
       <c r="O3" s="23">
         <v>0</v>
       </c>
-      <c r="P3" s="90">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="90">
-        <v>0</v>
-      </c>
-      <c r="R3" s="90">
-        <v>0</v>
-      </c>
-      <c r="S3" s="114">
+      <c r="P3" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="12">
+        <v>0</v>
+      </c>
+      <c r="R3" s="12">
+        <v>0</v>
+      </c>
+      <c r="S3" s="111">
         <v>1</v>
       </c>
       <c r="T3" s="1">
@@ -3285,16 +3274,16 @@
       <c r="K4" s="22"/>
       <c r="L4" s="22"/>
       <c r="M4" s="22"/>
-      <c r="N4" s="111">
+      <c r="N4" s="108">
         <v>0.5</v>
       </c>
       <c r="O4" s="22"/>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88">
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10">
         <v>0.5</v>
       </c>
-      <c r="R4" s="88"/>
-      <c r="S4" s="89"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="88"/>
       <c r="T4" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -3320,14 +3309,14 @@
       <c r="K5" s="25"/>
       <c r="L5" s="25"/>
       <c r="M5" s="25"/>
-      <c r="N5" s="94">
+      <c r="N5" s="92">
         <v>0</v>
       </c>
       <c r="O5" s="25"/>
-      <c r="P5" s="90"/>
-      <c r="Q5" s="93"/>
-      <c r="R5" s="93"/>
-      <c r="S5" s="95">
+      <c r="P5" s="12"/>
+      <c r="Q5" s="91"/>
+      <c r="R5" s="91"/>
+      <c r="S5" s="93">
         <v>1</v>
       </c>
       <c r="T5" s="1">
@@ -3355,16 +3344,16 @@
       <c r="K6" s="26"/>
       <c r="L6" s="26"/>
       <c r="M6" s="26"/>
-      <c r="N6" s="90"/>
+      <c r="N6" s="12"/>
       <c r="O6" s="26"/>
-      <c r="P6" s="111">
+      <c r="P6" s="108">
         <v>0.64705882352941102</v>
       </c>
-      <c r="Q6" s="96">
+      <c r="Q6" s="94">
         <v>0.35294117647058798</v>
       </c>
-      <c r="R6" s="96"/>
-      <c r="S6" s="97"/>
+      <c r="R6" s="94"/>
+      <c r="S6" s="95"/>
       <c r="T6" s="1">
         <f t="shared" si="0"/>
         <v>0.999999999999999</v>
@@ -3390,14 +3379,14 @@
       <c r="K7" s="25"/>
       <c r="L7" s="25"/>
       <c r="M7" s="25"/>
-      <c r="N7" s="93"/>
+      <c r="N7" s="91"/>
       <c r="O7" s="25"/>
-      <c r="P7" s="94">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="90"/>
-      <c r="R7" s="93"/>
-      <c r="S7" s="95">
+      <c r="P7" s="92">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="12"/>
+      <c r="R7" s="91"/>
+      <c r="S7" s="93">
         <v>1</v>
       </c>
       <c r="T7" s="1">
@@ -3425,14 +3414,14 @@
       <c r="K8" s="26"/>
       <c r="L8" s="26"/>
       <c r="M8" s="26"/>
-      <c r="N8" s="96"/>
+      <c r="N8" s="94"/>
       <c r="O8" s="26"/>
-      <c r="P8" s="90"/>
-      <c r="Q8" s="111">
+      <c r="P8" s="12"/>
+      <c r="Q8" s="108">
         <v>1</v>
       </c>
-      <c r="R8" s="96"/>
-      <c r="S8" s="97"/>
+      <c r="R8" s="94"/>
+      <c r="S8" s="95"/>
       <c r="T8" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -3458,14 +3447,14 @@
       <c r="K9" s="25"/>
       <c r="L9" s="25"/>
       <c r="M9" s="25"/>
-      <c r="N9" s="93"/>
+      <c r="N9" s="91"/>
       <c r="O9" s="25"/>
-      <c r="P9" s="93"/>
-      <c r="Q9" s="94">
-        <v>0</v>
-      </c>
-      <c r="R9" s="90"/>
-      <c r="S9" s="95">
+      <c r="P9" s="91"/>
+      <c r="Q9" s="92">
+        <v>0</v>
+      </c>
+      <c r="R9" s="12"/>
+      <c r="S9" s="93">
         <v>1</v>
       </c>
       <c r="T9" s="1">
@@ -3493,18 +3482,18 @@
       <c r="K10" s="26"/>
       <c r="L10" s="26"/>
       <c r="M10" s="26"/>
-      <c r="N10" s="96">
+      <c r="N10" s="94">
         <v>8.3333333333333301E-2</v>
       </c>
       <c r="O10" s="26"/>
-      <c r="P10" s="96"/>
-      <c r="Q10" s="90">
+      <c r="P10" s="94"/>
+      <c r="Q10" s="12">
         <v>0.33333333333333298</v>
       </c>
-      <c r="R10" s="111">
+      <c r="R10" s="108">
         <v>0.58333333333333304</v>
       </c>
-      <c r="S10" s="97"/>
+      <c r="S10" s="95"/>
       <c r="T10" s="1">
         <f t="shared" si="0"/>
         <v>0.99999999999999933</v>
@@ -3530,14 +3519,14 @@
       <c r="K11" s="25"/>
       <c r="L11" s="25"/>
       <c r="M11" s="25"/>
-      <c r="N11" s="93"/>
+      <c r="N11" s="91"/>
       <c r="O11" s="25"/>
-      <c r="P11" s="93"/>
-      <c r="Q11" s="93"/>
-      <c r="R11" s="94">
-        <v>0</v>
-      </c>
-      <c r="S11" s="91">
+      <c r="P11" s="91"/>
+      <c r="Q11" s="91"/>
+      <c r="R11" s="92">
+        <v>0</v>
+      </c>
+      <c r="S11" s="89">
         <v>1</v>
       </c>
       <c r="T11" s="1">
@@ -3565,18 +3554,18 @@
       <c r="K12" s="26"/>
       <c r="L12" s="26"/>
       <c r="M12" s="26"/>
-      <c r="N12" s="96">
+      <c r="N12" s="94">
         <v>8.1967213114753995E-2</v>
       </c>
       <c r="O12" s="26"/>
-      <c r="P12" s="96">
+      <c r="P12" s="94">
         <v>0.18032786885245899</v>
       </c>
-      <c r="Q12" s="96">
+      <c r="Q12" s="94">
         <v>0.73770491803278604</v>
       </c>
-      <c r="R12" s="90"/>
-      <c r="S12" s="92"/>
+      <c r="R12" s="12"/>
+      <c r="S12" s="90"/>
       <c r="T12" s="1">
         <f t="shared" si="0"/>
         <v>0.999999999999999</v>
@@ -3602,12 +3591,12 @@
       <c r="K13" s="24"/>
       <c r="L13" s="24"/>
       <c r="M13" s="24"/>
-      <c r="N13" s="99"/>
+      <c r="N13" s="9"/>
       <c r="O13" s="24"/>
-      <c r="P13" s="99"/>
-      <c r="Q13" s="99"/>
-      <c r="R13" s="99"/>
-      <c r="S13" s="112">
+      <c r="P13" s="9"/>
+      <c r="Q13" s="9"/>
+      <c r="R13" s="9"/>
+      <c r="S13" s="109">
         <v>1</v>
       </c>
       <c r="T13" s="1">
@@ -3635,14 +3624,14 @@
       <c r="K14" s="22"/>
       <c r="L14" s="22"/>
       <c r="M14" s="22"/>
-      <c r="N14" s="88"/>
+      <c r="N14" s="10"/>
       <c r="O14" s="22"/>
-      <c r="P14" s="88"/>
-      <c r="Q14" s="111">
+      <c r="P14" s="10"/>
+      <c r="Q14" s="108">
         <v>1</v>
       </c>
-      <c r="R14" s="88"/>
-      <c r="S14" s="89"/>
+      <c r="R14" s="10"/>
+      <c r="S14" s="88"/>
       <c r="T14" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -3668,14 +3657,14 @@
       <c r="K15" s="24"/>
       <c r="L15" s="24"/>
       <c r="M15" s="24"/>
-      <c r="N15" s="99"/>
+      <c r="N15" s="9"/>
       <c r="O15" s="24"/>
-      <c r="P15" s="99"/>
-      <c r="Q15" s="94">
-        <v>0</v>
-      </c>
-      <c r="R15" s="99"/>
-      <c r="S15" s="110">
+      <c r="P15" s="9"/>
+      <c r="Q15" s="92">
+        <v>0</v>
+      </c>
+      <c r="R15" s="9"/>
+      <c r="S15" s="107">
         <v>1</v>
       </c>
       <c r="T15" s="1">
@@ -3684,105 +3673,102 @@
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A16" s="135"/>
-      <c r="B16" s="135"/>
-      <c r="C16" s="135"/>
-      <c r="D16" s="136"/>
-      <c r="E16" s="136"/>
-      <c r="F16" s="136"/>
-      <c r="G16" s="136"/>
-      <c r="H16" s="136"/>
-      <c r="I16" s="136"/>
-      <c r="J16" s="136"/>
-      <c r="K16" s="136"/>
-      <c r="L16" s="136"/>
-      <c r="M16" s="136"/>
-      <c r="N16" s="136"/>
-      <c r="O16" s="136"/>
-      <c r="P16" s="136"/>
-      <c r="Q16" s="136"/>
-      <c r="R16" s="136"/>
-      <c r="S16" s="136"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="12"/>
+      <c r="O16" s="12"/>
+      <c r="P16" s="12"/>
+      <c r="Q16" s="12"/>
+      <c r="R16" s="12"/>
+      <c r="S16" s="12"/>
       <c r="T16" s="1"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A18" s="157"/>
-      <c r="B18" s="157"/>
-      <c r="C18" s="157"/>
-      <c r="D18" s="157"/>
-      <c r="E18" s="157"/>
-      <c r="F18" s="157"/>
-      <c r="G18" s="157"/>
-      <c r="H18" s="157"/>
-      <c r="I18" s="157"/>
-      <c r="J18" s="157"/>
-      <c r="K18" s="157"/>
-      <c r="L18" s="157"/>
-      <c r="M18" s="158"/>
+      <c r="A18" s="147"/>
+      <c r="B18" s="147"/>
+      <c r="C18" s="147"/>
+      <c r="D18" s="147"/>
+      <c r="E18" s="147"/>
+      <c r="F18" s="147"/>
+      <c r="G18" s="147"/>
+      <c r="H18" s="147"/>
+      <c r="I18" s="147"/>
+      <c r="J18" s="147"/>
+      <c r="K18" s="147"/>
+      <c r="L18" s="147"/>
+      <c r="M18" s="148"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="136"/>
-      <c r="B19" s="136"/>
-      <c r="C19" s="136"/>
-      <c r="D19" s="136"/>
-      <c r="E19" s="136"/>
-      <c r="F19" s="136"/>
-      <c r="G19" s="136"/>
-      <c r="H19" s="136"/>
-      <c r="I19" s="136"/>
-      <c r="J19" s="136"/>
-      <c r="K19" s="136"/>
-      <c r="L19" s="136"/>
-      <c r="M19" s="137"/>
+      <c r="A19" s="12"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="13"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A20" s="136"/>
-      <c r="B20" s="136"/>
-      <c r="C20" s="136"/>
-      <c r="D20" s="136"/>
-      <c r="E20" s="136"/>
-      <c r="F20" s="136"/>
-      <c r="G20" s="136"/>
-      <c r="H20" s="136"/>
-      <c r="I20" s="136"/>
-      <c r="J20" s="136"/>
-      <c r="K20" s="136"/>
-      <c r="L20" s="136"/>
-      <c r="M20" s="137"/>
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="13"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="116"/>
-      <c r="B22" s="116" t="s">
+      <c r="A22" s="113"/>
+      <c r="B22" s="113" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="116" t="s">
+      <c r="C22" s="113" t="s">
         <v>39</v>
       </c>
-      <c r="D22" s="116" t="s">
+      <c r="D22" s="113" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="116" t="s">
+      <c r="E22" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="F22" s="116" t="s">
+      <c r="F22" s="113" t="s">
         <v>42</v>
       </c>
-      <c r="G22" s="116" t="s">
+      <c r="G22" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="H22" s="116" t="s">
+      <c r="H22" s="113" t="s">
         <v>44</v>
       </c>
-      <c r="I22" s="116" t="s">
+      <c r="I22" s="113" t="s">
         <v>45</v>
       </c>
-      <c r="J22" s="116" t="s">
+      <c r="J22" s="113" t="s">
         <v>46</v>
       </c>
-      <c r="K22" s="116" t="s">
+      <c r="K22" s="113" t="s">
         <v>47</v>
       </c>
-      <c r="L22" s="116" t="s">
+      <c r="L22" s="113" t="s">
         <v>48</v>
       </c>
     </row>
@@ -3837,7 +3823,7 @@
       <c r="D24" s="14">
         <v>1.0810810810810799E-2</v>
       </c>
-      <c r="E24" s="159">
+      <c r="E24" s="129">
         <v>-0.145454545454545</v>
       </c>
       <c r="F24" s="1">
@@ -3981,7 +3967,7 @@
       <c r="J2" s="35"/>
       <c r="K2" s="35"/>
       <c r="L2" s="35"/>
-      <c r="M2" s="122">
+      <c r="M2" s="110">
         <v>1.0869565217391301E-2</v>
       </c>
       <c r="N2" s="35">
@@ -3990,16 +3976,16 @@
       <c r="O2" s="35">
         <v>0</v>
       </c>
-      <c r="P2" s="117">
+      <c r="P2" s="99">
         <v>0.26086956521739102</v>
       </c>
-      <c r="Q2" s="117">
+      <c r="Q2" s="99">
         <v>0.70652173913043403</v>
       </c>
-      <c r="R2" s="122">
+      <c r="R2" s="110">
         <v>1.0869565217391301E-2</v>
       </c>
-      <c r="S2" s="123">
+      <c r="S2" s="118">
         <v>1.0869565217391301E-2</v>
       </c>
       <c r="T2" s="1">
@@ -4029,17 +4015,17 @@
       <c r="J3" s="53"/>
       <c r="K3" s="53"/>
       <c r="L3" s="53"/>
-      <c r="M3" s="118"/>
+      <c r="M3" s="114"/>
       <c r="N3" s="52"/>
       <c r="O3" s="52"/>
-      <c r="P3" s="124">
+      <c r="P3" s="119">
         <v>0.79310344827586199</v>
       </c>
-      <c r="Q3" s="88">
+      <c r="Q3" s="10">
         <v>0.20689655172413701</v>
       </c>
       <c r="R3" s="52"/>
-      <c r="S3" s="119"/>
+      <c r="S3" s="115"/>
       <c r="T3" s="1">
         <f>SUM(D3:S3)</f>
         <v>0.999999999999999</v>
@@ -4067,17 +4053,17 @@
       <c r="J4" s="36"/>
       <c r="K4" s="36"/>
       <c r="L4" s="36"/>
-      <c r="M4" s="99">
+      <c r="M4" s="9">
         <v>2.8571428571428501E-2</v>
       </c>
       <c r="N4" s="24"/>
       <c r="O4" s="24"/>
-      <c r="P4" s="99"/>
-      <c r="Q4" s="124">
+      <c r="P4" s="9"/>
+      <c r="Q4" s="119">
         <v>0.97142857142857097</v>
       </c>
       <c r="R4" s="24"/>
-      <c r="S4" s="110"/>
+      <c r="S4" s="107"/>
       <c r="T4" s="1">
         <f>SUM(D4:S4)</f>
         <v>0.99999999999999944</v>
@@ -4102,17 +4088,17 @@
       <c r="J5" s="53"/>
       <c r="K5" s="53"/>
       <c r="L5" s="53"/>
-      <c r="M5" s="118"/>
+      <c r="M5" s="114"/>
       <c r="N5" s="52"/>
       <c r="O5" s="52"/>
-      <c r="P5" s="124">
+      <c r="P5" s="119">
         <v>0.88</v>
       </c>
-      <c r="Q5" s="88">
+      <c r="Q5" s="10">
         <v>0.12</v>
       </c>
       <c r="R5" s="52"/>
-      <c r="S5" s="119"/>
+      <c r="S5" s="115"/>
       <c r="T5" s="1">
         <f>SUM(D5:S5)</f>
         <v>1</v>
@@ -4137,55 +4123,55 @@
       <c r="J6" s="57"/>
       <c r="K6" s="57"/>
       <c r="L6" s="57"/>
-      <c r="M6" s="120">
+      <c r="M6" s="116">
         <v>2.8571428571428501E-2</v>
       </c>
       <c r="N6" s="56"/>
       <c r="O6" s="56"/>
-      <c r="P6" s="99"/>
-      <c r="Q6" s="124">
+      <c r="P6" s="9"/>
+      <c r="Q6" s="119">
         <v>0.97142857142857097</v>
       </c>
       <c r="R6" s="56"/>
-      <c r="S6" s="121"/>
+      <c r="S6" s="117"/>
       <c r="T6" s="1">
         <f>SUM(D6:S6)</f>
         <v>0.99999999999999944</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A8" s="115"/>
-      <c r="B8" s="116" t="s">
+      <c r="A8" s="112"/>
+      <c r="B8" s="113" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="116" t="s">
+      <c r="C8" s="113" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="116" t="s">
+      <c r="D8" s="113" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="116" t="s">
+      <c r="E8" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="F8" s="116" t="s">
+      <c r="F8" s="113" t="s">
         <v>42</v>
       </c>
-      <c r="G8" s="116" t="s">
+      <c r="G8" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="H8" s="116" t="s">
+      <c r="H8" s="113" t="s">
         <v>44</v>
       </c>
-      <c r="I8" s="116" t="s">
+      <c r="I8" s="113" t="s">
         <v>45</v>
       </c>
-      <c r="J8" s="116" t="s">
+      <c r="J8" s="113" t="s">
         <v>46</v>
       </c>
-      <c r="K8" s="116" t="s">
+      <c r="K8" s="113" t="s">
         <v>47</v>
       </c>
-      <c r="L8" s="116" t="s">
+      <c r="L8" s="113" t="s">
         <v>48</v>
       </c>
     </row>
@@ -4362,34 +4348,34 @@
         <v>11</v>
       </c>
       <c r="C2" s="27"/>
-      <c r="D2" s="102">
+      <c r="D2" s="99">
         <v>0.40625</v>
       </c>
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>
-      <c r="I2" s="102">
+      <c r="I2" s="99">
         <v>6.25E-2</v>
       </c>
       <c r="J2" s="22"/>
-      <c r="K2" s="113">
+      <c r="K2" s="110">
         <v>3.125E-2</v>
       </c>
-      <c r="L2" s="102">
+      <c r="L2" s="99">
         <v>0.1875</v>
       </c>
-      <c r="M2" s="113">
+      <c r="M2" s="110">
         <v>3.125E-2</v>
       </c>
       <c r="N2" s="22"/>
-      <c r="O2" s="102">
+      <c r="O2" s="99">
         <v>6.25E-2</v>
       </c>
       <c r="P2" s="22"/>
       <c r="Q2" s="22"/>
       <c r="R2" s="22"/>
-      <c r="S2" s="127">
+      <c r="S2" s="122">
         <v>0.21875</v>
       </c>
       <c r="T2" s="1">
@@ -4410,24 +4396,24 @@
       <c r="C3" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="124">
+      <c r="D3" s="119">
         <v>1</v>
       </c>
       <c r="E3" s="52"/>
       <c r="F3" s="52"/>
       <c r="G3" s="52"/>
       <c r="H3" s="52"/>
-      <c r="I3" s="88"/>
+      <c r="I3" s="10"/>
       <c r="J3" s="52"/>
-      <c r="K3" s="118"/>
-      <c r="L3" s="118"/>
-      <c r="M3" s="118"/>
+      <c r="K3" s="114"/>
+      <c r="L3" s="114"/>
+      <c r="M3" s="114"/>
       <c r="N3" s="52"/>
-      <c r="O3" s="118"/>
+      <c r="O3" s="114"/>
       <c r="P3" s="52"/>
       <c r="Q3" s="52"/>
       <c r="R3" s="52"/>
-      <c r="S3" s="119"/>
+      <c r="S3" s="115"/>
       <c r="T3" s="1">
         <f t="shared" ref="T3:T9" si="0">SUM(D3:S3)</f>
         <v>1</v>
@@ -4446,28 +4432,28 @@
       <c r="C4" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="93"/>
+      <c r="D4" s="91"/>
       <c r="E4" s="50"/>
       <c r="F4" s="50"/>
       <c r="G4" s="50"/>
       <c r="H4" s="50"/>
-      <c r="I4" s="124">
+      <c r="I4" s="119">
         <v>0.22222222222222199</v>
       </c>
       <c r="J4" s="50"/>
-      <c r="K4" s="96"/>
-      <c r="L4" s="125">
+      <c r="K4" s="94"/>
+      <c r="L4" s="120">
         <v>0.66666666666666596</v>
       </c>
-      <c r="M4" s="125">
+      <c r="M4" s="120">
         <v>0.11111111111111099</v>
       </c>
       <c r="N4" s="50"/>
-      <c r="O4" s="125"/>
+      <c r="O4" s="120"/>
       <c r="P4" s="50"/>
       <c r="Q4" s="50"/>
       <c r="R4" s="50"/>
-      <c r="S4" s="126"/>
+      <c r="S4" s="121"/>
       <c r="T4" s="1">
         <f t="shared" si="0"/>
         <v>0.99999999999999889</v>
@@ -4483,26 +4469,26 @@
       <c r="C5" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="125"/>
+      <c r="D5" s="120"/>
       <c r="E5" s="50"/>
       <c r="F5" s="50"/>
       <c r="G5" s="50"/>
       <c r="H5" s="50"/>
-      <c r="I5" s="93"/>
+      <c r="I5" s="91"/>
       <c r="J5" s="50"/>
-      <c r="K5" s="124">
+      <c r="K5" s="119">
         <v>0.1</v>
       </c>
-      <c r="L5" s="96"/>
-      <c r="M5" s="125"/>
+      <c r="L5" s="94"/>
+      <c r="M5" s="120"/>
       <c r="N5" s="50"/>
-      <c r="O5" s="125">
+      <c r="O5" s="120">
         <v>0.2</v>
       </c>
       <c r="P5" s="50"/>
       <c r="Q5" s="50"/>
       <c r="R5" s="50"/>
-      <c r="S5" s="126">
+      <c r="S5" s="121">
         <v>0.7</v>
       </c>
       <c r="T5" s="1">
@@ -4520,28 +4506,28 @@
       <c r="C6" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="125"/>
+      <c r="D6" s="120"/>
       <c r="E6" s="50"/>
       <c r="F6" s="50"/>
       <c r="G6" s="50"/>
       <c r="H6" s="50"/>
-      <c r="I6" s="125">
+      <c r="I6" s="120">
         <v>0.125</v>
       </c>
       <c r="J6" s="50"/>
-      <c r="K6" s="93"/>
-      <c r="L6" s="124">
+      <c r="K6" s="91"/>
+      <c r="L6" s="119">
         <v>0.75</v>
       </c>
-      <c r="M6" s="125">
+      <c r="M6" s="120">
         <v>0.125</v>
       </c>
       <c r="N6" s="50"/>
-      <c r="O6" s="96"/>
+      <c r="O6" s="94"/>
       <c r="P6" s="50"/>
       <c r="Q6" s="50"/>
       <c r="R6" s="50"/>
-      <c r="S6" s="126"/>
+      <c r="S6" s="121"/>
       <c r="T6" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -4557,24 +4543,24 @@
       <c r="C7" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="125"/>
+      <c r="D7" s="120"/>
       <c r="E7" s="50"/>
       <c r="F7" s="50"/>
       <c r="G7" s="50"/>
       <c r="H7" s="50"/>
-      <c r="I7" s="125"/>
+      <c r="I7" s="120"/>
       <c r="J7" s="50"/>
-      <c r="K7" s="125"/>
-      <c r="L7" s="93"/>
+      <c r="K7" s="120"/>
+      <c r="L7" s="91"/>
       <c r="M7" s="50"/>
       <c r="N7" s="50"/>
-      <c r="O7" s="124">
+      <c r="O7" s="119">
         <v>0.22222222222222199</v>
       </c>
       <c r="P7" s="50"/>
       <c r="Q7" s="50"/>
       <c r="R7" s="50"/>
-      <c r="S7" s="97">
+      <c r="S7" s="95">
         <v>0.77777777777777701</v>
       </c>
       <c r="T7" s="1">
@@ -4592,22 +4578,22 @@
       <c r="C8" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="136"/>
-      <c r="E8" s="140"/>
-      <c r="F8" s="140"/>
-      <c r="G8" s="140"/>
-      <c r="H8" s="140"/>
-      <c r="I8" s="136"/>
-      <c r="J8" s="140"/>
-      <c r="K8" s="136"/>
-      <c r="L8" s="136"/>
-      <c r="M8" s="140"/>
-      <c r="N8" s="140"/>
-      <c r="O8" s="136"/>
-      <c r="P8" s="140"/>
-      <c r="Q8" s="140"/>
-      <c r="R8" s="140"/>
-      <c r="S8" s="111">
+      <c r="D8" s="12"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="23"/>
+      <c r="R8" s="23"/>
+      <c r="S8" s="108">
         <v>1</v>
       </c>
       <c r="T8" s="1">
@@ -4622,27 +4608,27 @@
       <c r="B9" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="162" t="s">
+      <c r="C9" s="151" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="124">
+      <c r="D9" s="119">
         <v>1</v>
       </c>
       <c r="E9" s="52"/>
       <c r="F9" s="52"/>
       <c r="G9" s="52"/>
       <c r="H9" s="52"/>
-      <c r="I9" s="88"/>
+      <c r="I9" s="10"/>
       <c r="J9" s="52"/>
-      <c r="K9" s="118"/>
-      <c r="L9" s="118"/>
+      <c r="K9" s="114"/>
+      <c r="L9" s="114"/>
       <c r="M9" s="52"/>
       <c r="N9" s="52"/>
-      <c r="O9" s="100"/>
+      <c r="O9" s="97"/>
       <c r="P9" s="52"/>
       <c r="Q9" s="52"/>
       <c r="R9" s="52"/>
-      <c r="S9" s="89"/>
+      <c r="S9" s="88"/>
       <c r="T9" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -4655,27 +4641,27 @@
       <c r="B10" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="163" t="s">
+      <c r="C10" s="152" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="164"/>
-      <c r="E10" s="140"/>
-      <c r="F10" s="140"/>
-      <c r="G10" s="140"/>
-      <c r="H10" s="140"/>
-      <c r="I10" s="124">
+      <c r="D10" s="153"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="23"/>
+      <c r="I10" s="119">
         <v>1</v>
       </c>
-      <c r="J10" s="140"/>
-      <c r="K10" s="136"/>
-      <c r="L10" s="136"/>
-      <c r="M10" s="140"/>
-      <c r="N10" s="140"/>
-      <c r="O10" s="136"/>
-      <c r="P10" s="140"/>
-      <c r="Q10" s="140"/>
-      <c r="R10" s="140"/>
-      <c r="S10" s="91"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="23"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="23"/>
+      <c r="Q10" s="23"/>
+      <c r="R10" s="23"/>
+      <c r="S10" s="89"/>
       <c r="T10" s="1">
         <f>SUM(D13:S13)</f>
         <v>1</v>
@@ -4688,27 +4674,27 @@
       <c r="B11" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="160" t="s">
+      <c r="C11" s="149" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="165"/>
+      <c r="D11" s="154"/>
       <c r="E11" s="50"/>
       <c r="F11" s="50"/>
       <c r="G11" s="50"/>
       <c r="H11" s="50"/>
-      <c r="I11" s="93"/>
+      <c r="I11" s="91"/>
       <c r="J11" s="50"/>
-      <c r="K11" s="96"/>
-      <c r="L11" s="124">
+      <c r="K11" s="94"/>
+      <c r="L11" s="119">
         <v>1</v>
       </c>
-      <c r="M11" s="125"/>
+      <c r="M11" s="120"/>
       <c r="N11" s="50"/>
-      <c r="O11" s="96"/>
+      <c r="O11" s="94"/>
       <c r="P11" s="50"/>
       <c r="Q11" s="50"/>
       <c r="R11" s="50"/>
-      <c r="S11" s="95"/>
+      <c r="S11" s="93"/>
     </row>
     <row r="12" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
@@ -4717,27 +4703,27 @@
       <c r="B12" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="161" t="s">
+      <c r="C12" s="150" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="165"/>
+      <c r="D12" s="154"/>
       <c r="E12" s="50"/>
       <c r="F12" s="50"/>
       <c r="G12" s="50"/>
       <c r="H12" s="50"/>
-      <c r="I12" s="93"/>
+      <c r="I12" s="91"/>
       <c r="J12" s="50"/>
-      <c r="K12" s="96"/>
-      <c r="L12" s="136"/>
-      <c r="M12" s="125"/>
+      <c r="K12" s="94"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="120"/>
       <c r="N12" s="50"/>
-      <c r="O12" s="124">
+      <c r="O12" s="119">
         <v>1</v>
       </c>
       <c r="P12" s="50"/>
       <c r="Q12" s="50"/>
       <c r="R12" s="50"/>
-      <c r="S12" s="97"/>
+      <c r="S12" s="95"/>
     </row>
     <row r="13" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
@@ -4746,106 +4732,106 @@
       <c r="B13" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="142" t="s">
+      <c r="C13" s="132" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="166"/>
+      <c r="D13" s="155"/>
       <c r="E13" s="56"/>
       <c r="F13" s="56"/>
       <c r="G13" s="56"/>
       <c r="H13" s="56"/>
-      <c r="I13" s="99"/>
+      <c r="I13" s="9"/>
       <c r="J13" s="56"/>
-      <c r="K13" s="120"/>
-      <c r="L13" s="120"/>
-      <c r="M13" s="120"/>
+      <c r="K13" s="116"/>
+      <c r="L13" s="116"/>
+      <c r="M13" s="116"/>
       <c r="N13" s="56"/>
-      <c r="O13" s="99"/>
+      <c r="O13" s="9"/>
       <c r="P13" s="56"/>
       <c r="Q13" s="56"/>
       <c r="R13" s="56"/>
-      <c r="S13" s="124">
+      <c r="S13" s="119">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A15" s="158"/>
-      <c r="B15" s="158"/>
-      <c r="C15" s="158"/>
-      <c r="D15" s="158"/>
-      <c r="E15" s="158"/>
-      <c r="F15" s="158"/>
-      <c r="G15" s="158"/>
-      <c r="H15" s="158"/>
-      <c r="I15" s="158"/>
-      <c r="J15" s="158"/>
-      <c r="K15" s="158"/>
-      <c r="L15" s="158"/>
-      <c r="M15" s="137"/>
+      <c r="A15" s="148"/>
+      <c r="B15" s="148"/>
+      <c r="C15" s="148"/>
+      <c r="D15" s="148"/>
+      <c r="E15" s="148"/>
+      <c r="F15" s="148"/>
+      <c r="G15" s="148"/>
+      <c r="H15" s="148"/>
+      <c r="I15" s="148"/>
+      <c r="J15" s="148"/>
+      <c r="K15" s="148"/>
+      <c r="L15" s="148"/>
+      <c r="M15" s="13"/>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A16" s="137"/>
-      <c r="B16" s="136"/>
-      <c r="C16" s="136"/>
-      <c r="D16" s="136"/>
-      <c r="E16" s="136"/>
-      <c r="F16" s="136"/>
-      <c r="G16" s="136"/>
-      <c r="H16" s="136"/>
-      <c r="I16" s="136"/>
-      <c r="J16" s="136"/>
-      <c r="K16" s="136"/>
-      <c r="L16" s="136"/>
-      <c r="M16" s="137"/>
+      <c r="A16" s="13"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="13"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A17" s="137"/>
-      <c r="B17" s="136"/>
-      <c r="C17" s="136"/>
-      <c r="D17" s="136"/>
-      <c r="E17" s="136"/>
-      <c r="F17" s="136"/>
-      <c r="G17" s="136"/>
-      <c r="H17" s="136"/>
-      <c r="I17" s="136"/>
-      <c r="J17" s="136"/>
-      <c r="K17" s="136"/>
-      <c r="L17" s="136"/>
-      <c r="M17" s="137"/>
+      <c r="A17" s="13"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="13"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="116"/>
-      <c r="B19" s="116" t="s">
+      <c r="A19" s="113"/>
+      <c r="B19" s="113" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="116" t="s">
+      <c r="C19" s="113" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="116" t="s">
+      <c r="D19" s="113" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="116" t="s">
+      <c r="E19" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="F19" s="116" t="s">
+      <c r="F19" s="113" t="s">
         <v>42</v>
       </c>
-      <c r="G19" s="116" t="s">
+      <c r="G19" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="H19" s="116" t="s">
+      <c r="H19" s="113" t="s">
         <v>44</v>
       </c>
-      <c r="I19" s="116" t="s">
+      <c r="I19" s="113" t="s">
         <v>45</v>
       </c>
-      <c r="J19" s="116" t="s">
+      <c r="J19" s="113" t="s">
         <v>46</v>
       </c>
-      <c r="K19" s="116" t="s">
+      <c r="K19" s="113" t="s">
         <v>47</v>
       </c>
-      <c r="L19" s="116" t="s">
+      <c r="L19" s="113" t="s">
         <v>48</v>
       </c>
     </row>
@@ -5023,30 +5009,30 @@
       <c r="C2" s="66"/>
       <c r="D2" s="22"/>
       <c r="E2" s="22"/>
-      <c r="F2" s="102">
+      <c r="F2" s="99">
         <v>0.33333333333333298</v>
       </c>
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>
       <c r="I2" s="22"/>
-      <c r="J2" s="102">
+      <c r="J2" s="99">
         <v>0.38888888888888801</v>
       </c>
       <c r="K2" s="22"/>
       <c r="L2" s="22"/>
-      <c r="M2" s="88">
-        <v>0</v>
-      </c>
-      <c r="N2" s="102">
+      <c r="M2" s="10">
+        <v>0</v>
+      </c>
+      <c r="N2" s="99">
         <v>0.27777777777777701</v>
       </c>
       <c r="O2" s="22"/>
       <c r="P2" s="22"/>
-      <c r="Q2" s="88">
+      <c r="Q2" s="10">
         <v>0</v>
       </c>
       <c r="R2" s="22"/>
-      <c r="S2" s="128"/>
+      <c r="S2" s="123"/>
       <c r="T2" s="1">
         <f>SUM(D2:S2)</f>
         <v>0.999999999999998</v>
@@ -5062,30 +5048,30 @@
       <c r="C3" s="29"/>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
-      <c r="F3" s="90">
+      <c r="F3" s="12">
         <v>0</v>
       </c>
       <c r="G3" s="23"/>
       <c r="H3" s="23"/>
       <c r="I3" s="23"/>
-      <c r="J3" s="101">
+      <c r="J3" s="98">
         <v>0.04</v>
       </c>
       <c r="K3" s="23"/>
       <c r="L3" s="23"/>
-      <c r="M3" s="90">
-        <v>0</v>
-      </c>
-      <c r="N3" s="101">
+      <c r="M3" s="12">
+        <v>0</v>
+      </c>
+      <c r="N3" s="98">
         <v>0.24</v>
       </c>
       <c r="O3" s="23"/>
       <c r="P3" s="23"/>
-      <c r="Q3" s="101">
+      <c r="Q3" s="98">
         <v>0.72</v>
       </c>
       <c r="R3" s="23"/>
-      <c r="S3" s="129"/>
+      <c r="S3" s="124"/>
       <c r="T3" s="1">
         <f t="shared" ref="T3:T25" si="0">SUM(D3:S3)</f>
         <v>1</v>
@@ -5104,30 +5090,30 @@
       <c r="C4" s="29"/>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
-      <c r="F4" s="101">
+      <c r="F4" s="98">
         <v>5.2631578947368397E-2</v>
       </c>
       <c r="G4" s="23"/>
       <c r="H4" s="23"/>
       <c r="I4" s="23"/>
-      <c r="J4" s="101">
+      <c r="J4" s="98">
         <v>5.2631578947368397E-2</v>
       </c>
       <c r="K4" s="23"/>
       <c r="L4" s="23"/>
-      <c r="M4" s="134">
+      <c r="M4" s="129">
         <v>5.2631578947368397E-2</v>
       </c>
-      <c r="N4" s="134">
+      <c r="N4" s="129">
         <v>0.105263157894736</v>
       </c>
       <c r="O4" s="23"/>
       <c r="P4" s="23"/>
-      <c r="Q4" s="101">
+      <c r="Q4" s="98">
         <v>0.73684210526315697</v>
       </c>
       <c r="R4" s="23"/>
-      <c r="S4" s="129"/>
+      <c r="S4" s="124"/>
       <c r="T4" s="1">
         <f t="shared" si="0"/>
         <v>0.99999999999999822</v>
@@ -5148,24 +5134,24 @@
       </c>
       <c r="D5" s="22"/>
       <c r="E5" s="22"/>
-      <c r="F5" s="111">
+      <c r="F5" s="108">
         <v>0.83333333333333304</v>
       </c>
       <c r="G5" s="22"/>
       <c r="H5" s="22"/>
       <c r="I5" s="22"/>
-      <c r="J5" s="88">
+      <c r="J5" s="10">
         <v>0.16666666666666599</v>
       </c>
       <c r="K5" s="22"/>
       <c r="L5" s="22"/>
-      <c r="M5" s="88"/>
-      <c r="N5" s="88"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
       <c r="O5" s="22"/>
       <c r="P5" s="22"/>
-      <c r="Q5" s="88"/>
+      <c r="Q5" s="10"/>
       <c r="R5" s="22"/>
-      <c r="S5" s="128"/>
+      <c r="S5" s="123"/>
       <c r="T5" s="1">
         <f t="shared" si="0"/>
         <v>0.999999999999999</v>
@@ -5183,22 +5169,22 @@
       </c>
       <c r="D6" s="23"/>
       <c r="E6" s="23"/>
-      <c r="F6" s="98">
+      <c r="F6" s="96">
         <v>0</v>
       </c>
       <c r="G6" s="23"/>
       <c r="H6" s="23"/>
       <c r="I6" s="23"/>
-      <c r="J6" s="90"/>
+      <c r="J6" s="12"/>
       <c r="K6" s="23"/>
       <c r="L6" s="23"/>
-      <c r="M6" s="90"/>
-      <c r="N6" s="90"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="12"/>
       <c r="O6" s="23"/>
       <c r="P6" s="23"/>
-      <c r="Q6" s="90"/>
+      <c r="Q6" s="12"/>
       <c r="R6" s="23"/>
-      <c r="S6" s="129"/>
+      <c r="S6" s="124"/>
       <c r="T6" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5216,22 +5202,22 @@
       </c>
       <c r="D7" s="25"/>
       <c r="E7" s="25"/>
-      <c r="F7" s="106">
+      <c r="F7" s="103">
         <v>0</v>
       </c>
       <c r="G7" s="25"/>
       <c r="H7" s="25"/>
       <c r="I7" s="25"/>
-      <c r="J7" s="90"/>
+      <c r="J7" s="12"/>
       <c r="K7" s="25"/>
       <c r="L7" s="25"/>
-      <c r="M7" s="93"/>
-      <c r="N7" s="93"/>
+      <c r="M7" s="91"/>
+      <c r="N7" s="91"/>
       <c r="O7" s="25"/>
       <c r="P7" s="25"/>
-      <c r="Q7" s="93"/>
+      <c r="Q7" s="91"/>
       <c r="R7" s="25"/>
-      <c r="S7" s="130"/>
+      <c r="S7" s="125"/>
       <c r="T7" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5249,24 +5235,24 @@
       </c>
       <c r="D8" s="26"/>
       <c r="E8" s="26"/>
-      <c r="F8" s="90">
+      <c r="F8" s="12">
         <v>0.33333333333333298</v>
       </c>
       <c r="G8" s="26"/>
       <c r="H8" s="26"/>
       <c r="I8" s="26"/>
-      <c r="J8" s="111">
+      <c r="J8" s="108">
         <v>0.66666666666666596</v>
       </c>
       <c r="K8" s="26"/>
       <c r="L8" s="26"/>
-      <c r="M8" s="96"/>
-      <c r="N8" s="96"/>
+      <c r="M8" s="94"/>
+      <c r="N8" s="94"/>
       <c r="O8" s="26"/>
       <c r="P8" s="26"/>
-      <c r="Q8" s="96"/>
+      <c r="Q8" s="94"/>
       <c r="R8" s="26"/>
-      <c r="S8" s="131"/>
+      <c r="S8" s="126"/>
       <c r="T8" s="1">
         <f t="shared" si="0"/>
         <v>0.99999999999999889</v>
@@ -5284,22 +5270,22 @@
       </c>
       <c r="D9" s="23"/>
       <c r="E9" s="23"/>
-      <c r="F9" s="90"/>
+      <c r="F9" s="12"/>
       <c r="G9" s="23"/>
       <c r="H9" s="23"/>
       <c r="I9" s="23"/>
-      <c r="J9" s="133">
+      <c r="J9" s="128">
         <v>0</v>
       </c>
       <c r="K9" s="23"/>
       <c r="L9" s="23"/>
-      <c r="M9" s="90"/>
-      <c r="N9" s="90"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
       <c r="O9" s="23"/>
       <c r="P9" s="23"/>
-      <c r="Q9" s="90"/>
+      <c r="Q9" s="12"/>
       <c r="R9" s="23"/>
-      <c r="S9" s="129"/>
+      <c r="S9" s="124"/>
       <c r="T9" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5317,22 +5303,22 @@
       </c>
       <c r="D10" s="25"/>
       <c r="E10" s="25"/>
-      <c r="F10" s="93"/>
+      <c r="F10" s="91"/>
       <c r="G10" s="25"/>
       <c r="H10" s="25"/>
       <c r="I10" s="25"/>
-      <c r="J10" s="106">
+      <c r="J10" s="103">
         <v>0</v>
       </c>
       <c r="K10" s="25"/>
       <c r="L10" s="25"/>
-      <c r="M10" s="93"/>
-      <c r="N10" s="90"/>
+      <c r="M10" s="91"/>
+      <c r="N10" s="12"/>
       <c r="O10" s="25"/>
       <c r="P10" s="25"/>
-      <c r="Q10" s="93"/>
+      <c r="Q10" s="91"/>
       <c r="R10" s="25"/>
-      <c r="S10" s="130"/>
+      <c r="S10" s="125"/>
       <c r="T10" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5350,26 +5336,26 @@
       </c>
       <c r="D11" s="26"/>
       <c r="E11" s="26"/>
-      <c r="F11" s="96">
+      <c r="F11" s="94">
         <v>0.33333333333333298</v>
       </c>
       <c r="G11" s="26"/>
       <c r="H11" s="26"/>
       <c r="I11" s="26"/>
-      <c r="J11" s="90">
+      <c r="J11" s="12">
         <v>0.38888888888888801</v>
       </c>
       <c r="K11" s="26"/>
       <c r="L11" s="26"/>
-      <c r="M11" s="96"/>
-      <c r="N11" s="105">
+      <c r="M11" s="94"/>
+      <c r="N11" s="102">
         <v>0.27777777777777701</v>
       </c>
       <c r="O11" s="26"/>
       <c r="P11" s="26"/>
-      <c r="Q11" s="96"/>
+      <c r="Q11" s="94"/>
       <c r="R11" s="26"/>
-      <c r="S11" s="131"/>
+      <c r="S11" s="126"/>
       <c r="T11" s="1">
         <f t="shared" si="0"/>
         <v>0.999999999999998</v>
@@ -5387,22 +5373,22 @@
       </c>
       <c r="D12" s="23"/>
       <c r="E12" s="23"/>
-      <c r="F12" s="90"/>
+      <c r="F12" s="12"/>
       <c r="G12" s="23"/>
       <c r="H12" s="23"/>
       <c r="I12" s="23"/>
-      <c r="J12" s="90"/>
+      <c r="J12" s="12"/>
       <c r="K12" s="23"/>
       <c r="L12" s="23"/>
-      <c r="M12" s="90"/>
-      <c r="N12" s="133">
+      <c r="M12" s="12"/>
+      <c r="N12" s="128">
         <v>0</v>
       </c>
       <c r="O12" s="23"/>
       <c r="P12" s="23"/>
-      <c r="Q12" s="90"/>
+      <c r="Q12" s="12"/>
       <c r="R12" s="23"/>
-      <c r="S12" s="129"/>
+      <c r="S12" s="124"/>
       <c r="T12" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5420,22 +5406,22 @@
       </c>
       <c r="D13" s="25"/>
       <c r="E13" s="25"/>
-      <c r="F13" s="93"/>
+      <c r="F13" s="91"/>
       <c r="G13" s="25"/>
       <c r="H13" s="25"/>
       <c r="I13" s="25"/>
-      <c r="J13" s="93"/>
+      <c r="J13" s="91"/>
       <c r="K13" s="25"/>
       <c r="L13" s="25"/>
-      <c r="M13" s="93"/>
-      <c r="N13" s="106">
+      <c r="M13" s="91"/>
+      <c r="N13" s="103">
         <v>0</v>
       </c>
       <c r="O13" s="25"/>
       <c r="P13" s="25"/>
-      <c r="Q13" s="90"/>
+      <c r="Q13" s="12"/>
       <c r="R13" s="25"/>
-      <c r="S13" s="130"/>
+      <c r="S13" s="125"/>
       <c r="T13" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5453,28 +5439,28 @@
       </c>
       <c r="D14" s="26"/>
       <c r="E14" s="26"/>
-      <c r="F14" s="96">
+      <c r="F14" s="94">
         <v>0.15384615384615299</v>
       </c>
       <c r="G14" s="26"/>
       <c r="H14" s="26"/>
       <c r="I14" s="26"/>
-      <c r="J14" s="96">
+      <c r="J14" s="94">
         <v>0.46153846153846101</v>
       </c>
       <c r="K14" s="26"/>
       <c r="L14" s="26"/>
-      <c r="M14" s="96"/>
-      <c r="N14" s="90">
+      <c r="M14" s="94"/>
+      <c r="N14" s="12">
         <v>0.38461538461538403</v>
       </c>
       <c r="O14" s="26"/>
       <c r="P14" s="26"/>
-      <c r="Q14" s="92">
+      <c r="Q14" s="90">
         <v>0</v>
       </c>
       <c r="R14" s="26"/>
-      <c r="S14" s="131"/>
+      <c r="S14" s="126"/>
       <c r="T14" s="1">
         <f t="shared" si="0"/>
         <v>0.999999999999998</v>
@@ -5492,24 +5478,24 @@
       </c>
       <c r="D15" s="23"/>
       <c r="E15" s="23"/>
-      <c r="F15" s="90"/>
+      <c r="F15" s="12"/>
       <c r="G15" s="23"/>
       <c r="H15" s="23"/>
       <c r="I15" s="23"/>
-      <c r="J15" s="90"/>
+      <c r="J15" s="12"/>
       <c r="K15" s="23"/>
       <c r="L15" s="23"/>
-      <c r="M15" s="90"/>
-      <c r="N15" s="90">
+      <c r="M15" s="12"/>
+      <c r="N15" s="12">
         <v>0.14285714285714199</v>
       </c>
       <c r="O15" s="23"/>
       <c r="P15" s="23"/>
-      <c r="Q15" s="108">
+      <c r="Q15" s="105">
         <v>0.85714285714285698</v>
       </c>
       <c r="R15" s="23"/>
-      <c r="S15" s="129"/>
+      <c r="S15" s="124"/>
       <c r="T15" s="1">
         <f t="shared" si="0"/>
         <v>0.999999999999999</v>
@@ -5527,26 +5513,26 @@
       </c>
       <c r="D16" s="24"/>
       <c r="E16" s="24"/>
-      <c r="F16" s="99"/>
+      <c r="F16" s="9"/>
       <c r="G16" s="24"/>
       <c r="H16" s="24"/>
       <c r="I16" s="24"/>
-      <c r="J16" s="99"/>
+      <c r="J16" s="9"/>
       <c r="K16" s="24"/>
       <c r="L16" s="24"/>
-      <c r="M16" s="99">
+      <c r="M16" s="9">
         <v>7.1428571428571397E-2</v>
       </c>
-      <c r="N16" s="99">
+      <c r="N16" s="9">
         <v>7.1428571428571397E-2</v>
       </c>
       <c r="O16" s="24"/>
       <c r="P16" s="24"/>
-      <c r="Q16" s="107">
+      <c r="Q16" s="104">
         <v>0.85714285714285698</v>
       </c>
       <c r="R16" s="24"/>
-      <c r="S16" s="132"/>
+      <c r="S16" s="127"/>
       <c r="T16" s="1">
         <f t="shared" si="0"/>
         <v>0.99999999999999978</v>
@@ -5564,24 +5550,24 @@
       </c>
       <c r="D17" s="22"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="111">
+      <c r="F17" s="108">
         <v>0.75</v>
       </c>
       <c r="G17" s="22"/>
       <c r="H17" s="22"/>
       <c r="I17" s="22"/>
-      <c r="J17" s="88">
+      <c r="J17" s="10">
         <v>0.25</v>
       </c>
       <c r="K17" s="22"/>
       <c r="L17" s="22"/>
       <c r="M17" s="22"/>
-      <c r="N17" s="88"/>
+      <c r="N17" s="10"/>
       <c r="O17" s="22"/>
       <c r="P17" s="22"/>
-      <c r="Q17" s="88"/>
+      <c r="Q17" s="10"/>
       <c r="R17" s="22"/>
-      <c r="S17" s="128"/>
+      <c r="S17" s="123"/>
       <c r="T17" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -5599,22 +5585,22 @@
       </c>
       <c r="D18" s="23"/>
       <c r="E18" s="23"/>
-      <c r="F18" s="98">
+      <c r="F18" s="96">
         <v>0</v>
       </c>
       <c r="G18" s="23"/>
       <c r="H18" s="23"/>
       <c r="I18" s="23"/>
-      <c r="J18" s="90"/>
+      <c r="J18" s="12"/>
       <c r="K18" s="23"/>
       <c r="L18" s="23"/>
       <c r="M18" s="23"/>
-      <c r="N18" s="90"/>
+      <c r="N18" s="12"/>
       <c r="O18" s="23"/>
       <c r="P18" s="23"/>
-      <c r="Q18" s="90"/>
+      <c r="Q18" s="12"/>
       <c r="R18" s="23"/>
-      <c r="S18" s="129"/>
+      <c r="S18" s="124"/>
       <c r="T18" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5632,22 +5618,22 @@
       </c>
       <c r="D19" s="25"/>
       <c r="E19" s="25"/>
-      <c r="F19" s="106">
+      <c r="F19" s="103">
         <v>0</v>
       </c>
       <c r="G19" s="25"/>
       <c r="H19" s="25"/>
       <c r="I19" s="25"/>
-      <c r="J19" s="90"/>
+      <c r="J19" s="12"/>
       <c r="K19" s="25"/>
       <c r="L19" s="25"/>
       <c r="M19" s="25"/>
-      <c r="N19" s="93"/>
+      <c r="N19" s="91"/>
       <c r="O19" s="25"/>
       <c r="P19" s="25"/>
-      <c r="Q19" s="93"/>
+      <c r="Q19" s="91"/>
       <c r="R19" s="25"/>
-      <c r="S19" s="130"/>
+      <c r="S19" s="125"/>
       <c r="T19" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5665,24 +5651,24 @@
       </c>
       <c r="D20" s="26"/>
       <c r="E20" s="26"/>
-      <c r="F20" s="90">
+      <c r="F20" s="12">
         <v>0.5</v>
       </c>
       <c r="G20" s="26"/>
       <c r="H20" s="26"/>
       <c r="I20" s="26"/>
-      <c r="J20" s="111">
+      <c r="J20" s="108">
         <v>0.5</v>
       </c>
       <c r="K20" s="26"/>
       <c r="L20" s="26"/>
       <c r="M20" s="26"/>
-      <c r="N20" s="96"/>
+      <c r="N20" s="94"/>
       <c r="O20" s="26"/>
       <c r="P20" s="26"/>
-      <c r="Q20" s="96"/>
+      <c r="Q20" s="94"/>
       <c r="R20" s="26"/>
-      <c r="S20" s="131"/>
+      <c r="S20" s="126"/>
       <c r="T20" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -5700,22 +5686,22 @@
       </c>
       <c r="D21" s="23"/>
       <c r="E21" s="23"/>
-      <c r="F21" s="90"/>
+      <c r="F21" s="12"/>
       <c r="G21" s="23"/>
       <c r="H21" s="23"/>
       <c r="I21" s="23"/>
-      <c r="J21" s="133">
+      <c r="J21" s="128">
         <v>0</v>
       </c>
       <c r="K21" s="23"/>
       <c r="L21" s="23"/>
       <c r="M21" s="23"/>
-      <c r="N21" s="90"/>
+      <c r="N21" s="12"/>
       <c r="O21" s="23"/>
       <c r="P21" s="23"/>
-      <c r="Q21" s="90"/>
+      <c r="Q21" s="12"/>
       <c r="R21" s="23"/>
-      <c r="S21" s="129"/>
+      <c r="S21" s="124"/>
       <c r="T21" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5733,22 +5719,22 @@
       </c>
       <c r="D22" s="25"/>
       <c r="E22" s="25"/>
-      <c r="F22" s="93"/>
+      <c r="F22" s="91"/>
       <c r="G22" s="25"/>
       <c r="H22" s="25"/>
       <c r="I22" s="25"/>
-      <c r="J22" s="106">
+      <c r="J22" s="103">
         <v>0</v>
       </c>
       <c r="K22" s="25"/>
       <c r="L22" s="25"/>
       <c r="M22" s="25"/>
-      <c r="N22" s="93"/>
+      <c r="N22" s="91"/>
       <c r="O22" s="25"/>
       <c r="P22" s="25"/>
-      <c r="Q22" s="90"/>
+      <c r="Q22" s="12"/>
       <c r="R22" s="25"/>
-      <c r="S22" s="130"/>
+      <c r="S22" s="125"/>
       <c r="T22" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5766,22 +5752,22 @@
       </c>
       <c r="D23" s="23"/>
       <c r="E23" s="23"/>
-      <c r="F23" s="90"/>
+      <c r="F23" s="12"/>
       <c r="G23" s="23"/>
       <c r="H23" s="23"/>
       <c r="I23" s="23"/>
-      <c r="J23" s="90"/>
+      <c r="J23" s="12"/>
       <c r="K23" s="23"/>
       <c r="L23" s="23"/>
       <c r="M23" s="23"/>
-      <c r="N23" s="90"/>
+      <c r="N23" s="12"/>
       <c r="O23" s="23"/>
       <c r="P23" s="23"/>
-      <c r="Q23" s="92">
+      <c r="Q23" s="90">
         <v>0</v>
       </c>
       <c r="R23" s="23"/>
-      <c r="S23" s="129"/>
+      <c r="S23" s="124"/>
       <c r="T23" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5799,22 +5785,22 @@
       </c>
       <c r="D24" s="23"/>
       <c r="E24" s="23"/>
-      <c r="F24" s="90"/>
+      <c r="F24" s="12"/>
       <c r="G24" s="23"/>
       <c r="H24" s="23"/>
       <c r="I24" s="23"/>
-      <c r="J24" s="90"/>
+      <c r="J24" s="12"/>
       <c r="K24" s="23"/>
       <c r="L24" s="23"/>
       <c r="M24" s="23"/>
-      <c r="N24" s="90"/>
+      <c r="N24" s="12"/>
       <c r="O24" s="23"/>
       <c r="P24" s="23"/>
-      <c r="Q24" s="133">
+      <c r="Q24" s="128">
         <v>0</v>
       </c>
       <c r="R24" s="23"/>
-      <c r="S24" s="129"/>
+      <c r="S24" s="124"/>
       <c r="T24" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5832,62 +5818,62 @@
       </c>
       <c r="D25" s="24"/>
       <c r="E25" s="24"/>
-      <c r="F25" s="99"/>
+      <c r="F25" s="9"/>
       <c r="G25" s="24"/>
       <c r="H25" s="24"/>
       <c r="I25" s="24"/>
-      <c r="J25" s="99"/>
+      <c r="J25" s="9"/>
       <c r="K25" s="24"/>
       <c r="L25" s="24"/>
       <c r="M25" s="24"/>
-      <c r="N25" s="99">
+      <c r="N25" s="9">
         <v>0.25</v>
       </c>
       <c r="O25" s="24"/>
       <c r="P25" s="24"/>
-      <c r="Q25" s="112">
+      <c r="Q25" s="109">
         <v>0.75</v>
       </c>
       <c r="R25" s="24"/>
-      <c r="S25" s="132"/>
+      <c r="S25" s="127"/>
       <c r="T25" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A27" s="116"/>
-      <c r="B27" s="116" t="s">
+      <c r="A27" s="113"/>
+      <c r="B27" s="113" t="s">
         <v>38</v>
       </c>
-      <c r="C27" s="116" t="s">
+      <c r="C27" s="113" t="s">
         <v>39</v>
       </c>
-      <c r="D27" s="116" t="s">
+      <c r="D27" s="113" t="s">
         <v>40</v>
       </c>
-      <c r="E27" s="116" t="s">
+      <c r="E27" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="F27" s="116" t="s">
+      <c r="F27" s="113" t="s">
         <v>42</v>
       </c>
-      <c r="G27" s="116" t="s">
+      <c r="G27" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="H27" s="116" t="s">
+      <c r="H27" s="113" t="s">
         <v>44</v>
       </c>
-      <c r="I27" s="116" t="s">
+      <c r="I27" s="113" t="s">
         <v>45</v>
       </c>
-      <c r="J27" s="116" t="s">
+      <c r="J27" s="113" t="s">
         <v>46</v>
       </c>
-      <c r="K27" s="116" t="s">
+      <c r="K27" s="113" t="s">
         <v>47</v>
       </c>
-      <c r="L27" s="116" t="s">
+      <c r="L27" s="113" t="s">
         <v>48</v>
       </c>
     </row>

--- a/patterns/results/exp1/4bins-results.xlsx
+++ b/patterns/results/exp1/4bins-results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D564F903-D713-EB44-BE35-3C217371404E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2C585ED-3623-1847-BA9C-076AAB260423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2440" yWindow="960" windowWidth="31680" windowHeight="19340" activeTab="2" xr2:uid="{9429E1C1-1F54-8A42-9286-E37255B8DAF7}"/>
+    <workbookView xWindow="-24780" yWindow="2120" windowWidth="22260" windowHeight="13960" activeTab="6" xr2:uid="{9429E1C1-1F54-8A42-9286-E37255B8DAF7}"/>
   </bookViews>
   <sheets>
     <sheet name="GO" sheetId="1" r:id="rId1"/>
@@ -18,11 +18,15 @@
     <sheet name="ACL" sheetId="3" r:id="rId3"/>
     <sheet name="GA" sheetId="4" r:id="rId4"/>
     <sheet name="PAF" sheetId="5" r:id="rId5"/>
+    <sheet name="4bins-all-metrics" sheetId="6" r:id="rId6"/>
+    <sheet name="tradeoff-definition-all-metrics" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
+    <definedName name="_2bins_metrics_go" localSheetId="6">'tradeoff-definition-all-metrics'!$C$2:$L$4</definedName>
     <definedName name="metrics_acl" localSheetId="2">ACL!$A$8:$L$10</definedName>
     <definedName name="metrics_cqrs_2" localSheetId="1">CQRS!$A$22:$L$24</definedName>
     <definedName name="metrics_ga_1" localSheetId="3">GA!$A$19:$L$21</definedName>
+    <definedName name="metrics_go_1" localSheetId="5">'4bins-all-metrics'!$B$1:$J$3</definedName>
     <definedName name="metrics_go_1" localSheetId="0">GO!$A$34:$L$36</definedName>
     <definedName name="metrics_paf" localSheetId="4">PAF!$A$27:$L$29</definedName>
     <definedName name="results_acl_1" localSheetId="2">ACL!$A$1:$S$6</definedName>
@@ -53,8 +57,8 @@
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
-  <connection id="1" xr16:uid="{A8FB4FA6-6B9B-E14E-938E-0C0FCD3EE22E}" name="metrics-acl" type="6" refreshedVersion="8" background="1" saveData="1">
-    <textPr sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/metrics-acl.csv" thousands="." comma="1">
+  <connection id="1" xr16:uid="{B290AE95-8982-A54A-A530-46E142315A67}" name="2bins-metrics-go" type="6" refreshedVersion="8" background="1" saveData="1">
+    <textPr codePage="10000" sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp2/go/2bins-metrics-go.csv" thousands="." comma="1">
       <textFields count="12">
         <textField/>
         <textField/>
@@ -71,8 +75,8 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="2" xr16:uid="{8F71BCCB-9DA0-144F-9D06-AF730388E029}" name="metrics-cqrs1" type="6" refreshedVersion="8" background="1" saveData="1">
-    <textPr sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/metrics-cqrs.csv" thousands="." comma="1">
+  <connection id="2" xr16:uid="{A8FB4FA6-6B9B-E14E-938E-0C0FCD3EE22E}" name="metrics-acl" type="6" refreshedVersion="8" background="1" saveData="1">
+    <textPr sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/metrics-acl.csv" thousands="." comma="1">
       <textFields count="12">
         <textField/>
         <textField/>
@@ -89,8 +93,8 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="3" xr16:uid="{0A4337A6-686E-6040-92B7-22F1899AA00C}" name="metrics-ga1" type="6" refreshedVersion="8" background="1" saveData="1">
-    <textPr sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/metrics-ga.csv" thousands="." comma="1">
+  <connection id="3" xr16:uid="{8F71BCCB-9DA0-144F-9D06-AF730388E029}" name="metrics-cqrs1" type="6" refreshedVersion="8" background="1" saveData="1">
+    <textPr sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/metrics-cqrs.csv" thousands="." comma="1">
       <textFields count="12">
         <textField/>
         <textField/>
@@ -107,8 +111,8 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="4" xr16:uid="{134B4E51-F17D-E24F-8C43-5587947006CC}" name="metrics-go1" type="6" refreshedVersion="8" background="1" saveData="1">
-    <textPr sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/metrics-go.csv" thousands="." comma="1">
+  <connection id="4" xr16:uid="{0A4337A6-686E-6040-92B7-22F1899AA00C}" name="metrics-ga1" type="6" refreshedVersion="8" background="1" saveData="1">
+    <textPr sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/metrics-ga.csv" thousands="." comma="1">
       <textFields count="12">
         <textField/>
         <textField/>
@@ -125,8 +129,8 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="5" xr16:uid="{A1D10C97-C0EC-584A-8D7D-53F84B328C43}" name="metrics-paf" type="6" refreshedVersion="8" background="1" saveData="1">
-    <textPr sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/metrics-paf.csv" thousands="." comma="1">
+  <connection id="5" xr16:uid="{134B4E51-F17D-E24F-8C43-5587947006CC}" name="metrics-go1" type="6" refreshedVersion="8" background="1" saveData="1">
+    <textPr sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/metrics-go.csv" thousands="." comma="1">
       <textFields count="12">
         <textField/>
         <textField/>
@@ -143,16 +147,9 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="6" xr16:uid="{A1430DA1-26ED-C243-830D-75657F385EB6}" name="results-acl" type="6" refreshedVersion="8" background="1" saveData="1">
-    <textPr sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/4bins-results-acl.csv" decimal="," thousands="." comma="1">
-      <textFields count="19">
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
+  <connection id="6" xr16:uid="{BF145D20-8141-B843-9179-C2D595934D51}" name="metrics-go11" type="6" refreshedVersion="8" background="1" saveData="1">
+    <textPr sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/metrics-go.csv" thousands="." comma="1">
+      <textFields count="12">
         <textField/>
         <textField/>
         <textField/>
@@ -168,16 +165,9 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="7" xr16:uid="{ADEA1934-A907-904C-BF9E-085F0CDA397C}" name="results-cqrs" type="6" refreshedVersion="8" background="1" saveData="1">
-    <textPr sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/4bins-results-cqrs.csv" decimal="," thousands="." comma="1">
-      <textFields count="19">
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
+  <connection id="7" xr16:uid="{A1D10C97-C0EC-584A-8D7D-53F84B328C43}" name="metrics-paf" type="6" refreshedVersion="8" background="1" saveData="1">
+    <textPr sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/metrics-paf.csv" thousands="." comma="1">
+      <textFields count="12">
         <textField/>
         <textField/>
         <textField/>
@@ -193,8 +183,8 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="8" xr16:uid="{036B15E2-FDA2-654B-9E05-694F72A14804}" name="results-ga" type="6" refreshedVersion="8" background="1" saveData="1">
-    <textPr sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/4bins-results-ga.csv" decimal="," thousands="." comma="1">
+  <connection id="8" xr16:uid="{A1430DA1-26ED-C243-830D-75657F385EB6}" name="results-acl" type="6" refreshedVersion="8" background="1" saveData="1">
+    <textPr sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/4bins-results-acl.csv" decimal="," thousands="." comma="1">
       <textFields count="19">
         <textField/>
         <textField/>
@@ -218,8 +208,8 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="9" xr16:uid="{7B95F622-C983-F145-A4DD-4DFC5DCB8877}" name="results-go" type="6" refreshedVersion="8" background="1" saveData="1">
-    <textPr sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/4bins-results-go.csv" decimal="," thousands="." comma="1">
+  <connection id="9" xr16:uid="{ADEA1934-A907-904C-BF9E-085F0CDA397C}" name="results-cqrs" type="6" refreshedVersion="8" background="1" saveData="1">
+    <textPr sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/4bins-results-cqrs.csv" decimal="," thousands="." comma="1">
       <textFields count="19">
         <textField/>
         <textField/>
@@ -243,7 +233,57 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="10" xr16:uid="{12E4085D-00EC-674E-8746-2BBD798472BA}" name="results-paf" type="6" refreshedVersion="8" background="1" saveData="1">
+  <connection id="10" xr16:uid="{036B15E2-FDA2-654B-9E05-694F72A14804}" name="results-ga" type="6" refreshedVersion="8" background="1" saveData="1">
+    <textPr sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/4bins-results-ga.csv" decimal="," thousands="." comma="1">
+      <textFields count="19">
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+      </textFields>
+    </textPr>
+  </connection>
+  <connection id="11" xr16:uid="{7B95F622-C983-F145-A4DD-4DFC5DCB8877}" name="results-go" type="6" refreshedVersion="8" background="1" saveData="1">
+    <textPr sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/4bins-results-go.csv" decimal="," thousands="." comma="1">
+      <textFields count="19">
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+      </textFields>
+    </textPr>
+  </connection>
+  <connection id="12" xr16:uid="{12E4085D-00EC-674E-8746-2BBD798472BA}" name="results-paf" type="6" refreshedVersion="8" background="1" saveData="1">
     <textPr sourceFile="/Users/adiazpace/Documents/GitHub/patterns-sa/patterns/results/exp1/4bins-results-paf.csv" decimal="," thousands="." comma="1">
       <textFields count="19">
         <textField/>
@@ -272,7 +312,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="78">
   <si>
     <t>method</t>
   </si>
@@ -425,6 +465,87 @@
   </si>
   <si>
     <t>cart: 5 boxes</t>
+  </si>
+  <si>
+    <t>GO</t>
+  </si>
+  <si>
+    <t>CQRS</t>
+  </si>
+  <si>
+    <t>ACL</t>
+  </si>
+  <si>
+    <t>GA</t>
+  </si>
+  <si>
+    <t>PRIM</t>
+  </si>
+  <si>
+    <t>CART</t>
+  </si>
+  <si>
+    <t>PAF</t>
+  </si>
+  <si>
+    <t>Pattern</t>
+  </si>
+  <si>
+    <t>Algorithm</t>
+  </si>
+  <si>
+    <t>Recall (sd)</t>
+  </si>
+  <si>
+    <t>F1-measure (sd)</t>
+  </si>
+  <si>
+    <t>Lift (sd)</t>
+  </si>
+  <si>
+    <t>Lift (avg)</t>
+  </si>
+  <si>
+    <t>F1-measure (avg)</t>
+  </si>
+  <si>
+    <t>Recall (avg)</t>
+  </si>
+  <si>
+    <t>Precision (avg)</t>
+  </si>
+  <si>
+    <t>Precision (sd)</t>
+  </si>
+  <si>
+    <t>2 bins</t>
+  </si>
+  <si>
+    <t>Strategy</t>
+  </si>
+  <si>
+    <t>4 bins</t>
+  </si>
+  <si>
+    <t>Pareto (2 bins)</t>
+  </si>
+  <si>
+    <t>clustering (3 x 3 bins)</t>
+  </si>
+  <si>
+    <t>2 x 2 bins</t>
+  </si>
+  <si>
+    <t>4 x 4 bins</t>
+  </si>
+  <si>
+    <t>Pareto (2 x 2 bins)</t>
+  </si>
+  <si>
+    <t>clustering (2 x 4 bins)</t>
+  </si>
+  <si>
+    <t>clustering (4 x 2 bins)</t>
   </si>
 </sst>
 </file>
@@ -572,7 +693,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="41">
+  <borders count="56">
     <border>
       <left/>
       <right/>
@@ -1062,11 +1183,216 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="156">
+  <cellXfs count="188">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1245,6 +1571,54 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1538,43 +1912,51 @@
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="results_go_1" connectionId="9" xr16:uid="{F5596237-E230-FF47-BEBA-D881481B07E8}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="results_go_1" connectionId="11" xr16:uid="{F5596237-E230-FF47-BEBA-D881481B07E8}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="results_paf_1" connectionId="10" xr16:uid="{C391B844-9B8B-8A4F-A15C-7E2019CF319D}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="results_paf_1" connectionId="12" xr16:uid="{C391B844-9B8B-8A4F-A15C-7E2019CF319D}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+</file>
+
+<file path=xl/queryTables/queryTable11.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="metrics_go_1" connectionId="6" xr16:uid="{A7703EE3-B2CD-A04A-ABF4-6ACC4566956C}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+</file>
+
+<file path=xl/queryTables/queryTable12.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="2bins-metrics-go" connectionId="1" xr16:uid="{21A55DFC-CC46-FD40-B5EB-D05259714724}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="metrics_go_1" connectionId="4" xr16:uid="{63DCC8F5-17EE-1340-9B93-10B151E3B558}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="metrics_go_1" connectionId="5" xr16:uid="{63DCC8F5-17EE-1340-9B93-10B151E3B558}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="metrics_cqrs_2" connectionId="2" xr16:uid="{77D8AEF2-F397-354F-B98D-BFCA42AA18FB}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="metrics_cqrs_2" connectionId="3" xr16:uid="{77D8AEF2-F397-354F-B98D-BFCA42AA18FB}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="results_cqrs_1" connectionId="7" xr16:uid="{6CCBBBBE-F26D-314E-B996-641B36214936}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="results_cqrs_1" connectionId="9" xr16:uid="{6CCBBBBE-F26D-314E-B996-641B36214936}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="metrics-acl" connectionId="1" xr16:uid="{E638D66A-320D-5341-84C6-11CFD9D60604}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="metrics-acl" connectionId="2" xr16:uid="{E638D66A-320D-5341-84C6-11CFD9D60604}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="results_acl_1" connectionId="6" xr16:uid="{E40068BA-D949-8547-8AA3-07795D0F4991}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="results_acl_1" connectionId="8" xr16:uid="{E40068BA-D949-8547-8AA3-07795D0F4991}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="results_ga_1" connectionId="8" xr16:uid="{6942D71A-6248-0E43-BD5A-53429B6671E4}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="results_ga_1" connectionId="10" xr16:uid="{6942D71A-6248-0E43-BD5A-53429B6671E4}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="metrics_ga_1" connectionId="3" xr16:uid="{D3FD6001-8A85-AD43-91C6-1F875D4FBFD9}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="metrics_ga_1" connectionId="4" xr16:uid="{D3FD6001-8A85-AD43-91C6-1F875D4FBFD9}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="metrics-paf" connectionId="5" xr16:uid="{3C4AE3B1-BE7E-C341-9541-F9DC7A8CC91F}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="metrics-paf" connectionId="7" xr16:uid="{3C4AE3B1-BE7E-C341-9541-F9DC7A8CC91F}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5960,4 +6342,1283 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0851A52-764B-534D-842D-B10F819047DC}">
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="15.1640625" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="15" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5" customWidth="1"/>
+    <col min="7" max="7" width="18.1640625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="13.33203125" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="15.83203125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" hidden="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="G1" s="113" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1" s="113" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="113" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1" s="113" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" s="170" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="171" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="172">
+        <v>0.47763347763347702</v>
+      </c>
+      <c r="D2" s="173">
+        <v>0.65</v>
+      </c>
+      <c r="E2" s="172">
+        <v>0.53174603174603097</v>
+      </c>
+      <c r="F2" s="174">
+        <v>0.31096681096681</v>
+      </c>
+      <c r="G2" s="12">
+        <v>0.39198942303110901</v>
+      </c>
+      <c r="H2" s="12">
+        <v>0.46097722286464399</v>
+      </c>
+      <c r="I2" s="12">
+        <v>0.404684088380379</v>
+      </c>
+      <c r="J2" s="12">
+        <v>0.314997533323503</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" s="165"/>
+      <c r="B3" s="168" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="157">
+        <v>0.63888888888888895</v>
+      </c>
+      <c r="D3" s="156">
+        <v>0.48888888888888798</v>
+      </c>
+      <c r="E3" s="156">
+        <v>0.52651515151515105</v>
+      </c>
+      <c r="F3" s="161">
+        <v>0.47222222222222199</v>
+      </c>
+      <c r="G3" s="12">
+        <v>0.455589429634909</v>
+      </c>
+      <c r="H3" s="12">
+        <v>0.41573970964154899</v>
+      </c>
+      <c r="I3" s="12">
+        <v>0.40324456027362099</v>
+      </c>
+      <c r="J3" s="12">
+        <v>0.39928078125199801</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" s="164" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="168" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="157">
+        <v>0.36</v>
+      </c>
+      <c r="D4" s="157">
+        <v>0.63</v>
+      </c>
+      <c r="E4" s="156">
+        <v>0.53174603174603097</v>
+      </c>
+      <c r="F4" s="161">
+        <v>0.31096681096681</v>
+      </c>
+      <c r="G4" s="12">
+        <v>0.39198942303110901</v>
+      </c>
+      <c r="H4" s="12">
+        <v>0.46097722286464399</v>
+      </c>
+      <c r="I4" s="12">
+        <v>0.404684088380379</v>
+      </c>
+      <c r="J4" s="12">
+        <v>0.314997533323503</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" s="165"/>
+      <c r="B5" s="168" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="156">
+        <v>0.05</v>
+      </c>
+      <c r="D5" s="156">
+        <v>0.01</v>
+      </c>
+      <c r="E5" s="156">
+        <v>0.52651515151515105</v>
+      </c>
+      <c r="F5" s="160">
+        <v>-0.15</v>
+      </c>
+      <c r="G5" s="12">
+        <v>0.455589429634909</v>
+      </c>
+      <c r="H5" s="12">
+        <v>0.41573970964154899</v>
+      </c>
+      <c r="I5" s="12">
+        <v>0.40324456027362099</v>
+      </c>
+      <c r="J5" s="12">
+        <v>0.39928078125199801</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" s="164" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="168" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="156">
+        <v>0.35290640394088602</v>
+      </c>
+      <c r="D6" s="156">
+        <v>0.29628205128205098</v>
+      </c>
+      <c r="E6" s="156">
+        <v>0.309584905660377</v>
+      </c>
+      <c r="F6" s="160">
+        <v>0.152906403940886</v>
+      </c>
+      <c r="G6" s="12">
+        <v>0.43588344757340203</v>
+      </c>
+      <c r="H6" s="12">
+        <v>0.38809714651718202</v>
+      </c>
+      <c r="I6" s="12">
+        <v>0.38379132813661299</v>
+      </c>
+      <c r="J6" s="12">
+        <v>0.21766999636473</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" s="165"/>
+      <c r="B7" s="168" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="156">
+        <v>0.370285714285714</v>
+      </c>
+      <c r="D7" s="156">
+        <v>0.28794871794871701</v>
+      </c>
+      <c r="E7" s="156">
+        <v>0.31559183673469299</v>
+      </c>
+      <c r="F7" s="160">
+        <v>0.17028571428571401</v>
+      </c>
+      <c r="G7" s="12">
+        <v>0.45442621367331898</v>
+      </c>
+      <c r="H7" s="12">
+        <v>0.37398259969999798</v>
+      </c>
+      <c r="I7" s="12">
+        <v>0.39261677459722299</v>
+      </c>
+      <c r="J7" s="12">
+        <v>0.24854232837382001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" s="164" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="168" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="156">
+        <v>0.47063492063492002</v>
+      </c>
+      <c r="D8" s="157">
+        <v>0.85714285714285698</v>
+      </c>
+      <c r="E8" s="156">
+        <v>0.53803339517625204</v>
+      </c>
+      <c r="F8" s="160">
+        <v>0.327777777777777</v>
+      </c>
+      <c r="G8" s="12">
+        <v>0.40014012410859601</v>
+      </c>
+      <c r="H8" s="12">
+        <v>0.34992710611188199</v>
+      </c>
+      <c r="I8" s="12">
+        <v>0.37906934880683102</v>
+      </c>
+      <c r="J8" s="12">
+        <v>0.28882878648298599</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" s="165"/>
+      <c r="B9" s="168" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="157">
+        <v>0.71428571428571397</v>
+      </c>
+      <c r="D9" s="156">
+        <v>0.476190476190476</v>
+      </c>
+      <c r="E9" s="156">
+        <v>0.54761904761904701</v>
+      </c>
+      <c r="F9" s="161">
+        <v>0.57142857142857095</v>
+      </c>
+      <c r="G9" s="12">
+        <v>0.45175395145262498</v>
+      </c>
+      <c r="H9" s="12">
+        <v>0.38243758105259501</v>
+      </c>
+      <c r="I9" s="12">
+        <v>0.38539081086282401</v>
+      </c>
+      <c r="J9" s="12">
+        <v>0.39588927281063102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" s="164" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" s="168" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="157">
+        <v>0.47262872628726199</v>
+      </c>
+      <c r="D10" s="157">
+        <v>0.45866910866910798</v>
+      </c>
+      <c r="E10" s="156">
+        <v>0.456535798860147</v>
+      </c>
+      <c r="F10" s="161">
+        <v>0.27262872628726198</v>
+      </c>
+      <c r="G10" s="12">
+        <v>0.29725847365073799</v>
+      </c>
+      <c r="H10" s="12">
+        <v>0.27065741581432801</v>
+      </c>
+      <c r="I10" s="12">
+        <v>0.27219305671655902</v>
+      </c>
+      <c r="J10" s="12">
+        <v>0.29293235647106602</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="166"/>
+      <c r="B11" s="169" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="162">
+        <v>0.4</v>
+      </c>
+      <c r="D11" s="162">
+        <v>0.12668650793650699</v>
+      </c>
+      <c r="E11" s="162">
+        <v>0.178787878787878</v>
+      </c>
+      <c r="F11" s="163">
+        <v>0.2</v>
+      </c>
+      <c r="G11" s="12">
+        <v>0.33911649915626302</v>
+      </c>
+      <c r="H11" s="12">
+        <v>0.15783589860001199</v>
+      </c>
+      <c r="I11" s="12">
+        <v>0.19926402694271</v>
+      </c>
+      <c r="J11" s="12">
+        <v>0.29350407322379601</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4732A64E-9DD5-C840-A68A-062C141067E3}">
+  <dimension ref="A1:L26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="19.33203125" customWidth="1"/>
+    <col min="4" max="4" width="15.1640625" customWidth="1"/>
+    <col min="5" max="5" width="13.33203125" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" customWidth="1"/>
+    <col min="8" max="11" width="0" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="12" hidden="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="167" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="167" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="167" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="167" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2" s="177" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" s="178" t="s">
+        <v>63</v>
+      </c>
+      <c r="H2" s="176" t="s">
+        <v>43</v>
+      </c>
+      <c r="I2" s="175" t="s">
+        <v>44</v>
+      </c>
+      <c r="J2" s="175" t="s">
+        <v>45</v>
+      </c>
+      <c r="K2" s="175" t="s">
+        <v>46</v>
+      </c>
+      <c r="L2" s="175" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" s="183" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="184" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="44">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="E3" s="10">
+        <v>0.64385964912280702</v>
+      </c>
+      <c r="F3" s="10">
+        <v>0.59937233112105703</v>
+      </c>
+      <c r="G3" s="88">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="H3" s="159">
+        <v>1</v>
+      </c>
+      <c r="I3" s="159">
+        <v>0.395447342667826</v>
+      </c>
+      <c r="J3" s="159">
+        <v>0.122781952329282</v>
+      </c>
+      <c r="K3" s="159">
+        <v>0.29655421196448301</v>
+      </c>
+      <c r="L3" s="159">
+        <v>0.215550998239769</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="170"/>
+      <c r="B4" s="171"/>
+      <c r="C4" s="140" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="180">
+        <v>0.64814814814814803</v>
+      </c>
+      <c r="E4" s="91">
+        <v>0.49824561403508699</v>
+      </c>
+      <c r="F4" s="91">
+        <v>0.55630630630630595</v>
+      </c>
+      <c r="G4" s="93">
+        <v>0.31481481481481399</v>
+      </c>
+      <c r="H4" s="159">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="I4" s="159">
+        <v>0.45887080345792097</v>
+      </c>
+      <c r="J4" s="159">
+        <v>0.37229376434248501</v>
+      </c>
+      <c r="K4" s="159">
+        <v>0.39936694081116902</v>
+      </c>
+      <c r="L4" s="159">
+        <v>0.30312472130060403</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" s="170"/>
+      <c r="B5" s="185" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="139" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="179">
+        <v>0.47763347763347702</v>
+      </c>
+      <c r="E5" s="94">
+        <v>0.65</v>
+      </c>
+      <c r="F5" s="94">
+        <v>0.53174603174603097</v>
+      </c>
+      <c r="G5" s="95">
+        <v>0.31096681096681</v>
+      </c>
+      <c r="H5" s="159">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="I5" s="159">
+        <v>0.39198942303110901</v>
+      </c>
+      <c r="J5" s="159">
+        <v>0.46097722286464399</v>
+      </c>
+      <c r="K5" s="159">
+        <v>0.404684088380379</v>
+      </c>
+      <c r="L5" s="159">
+        <v>0.314997533323503</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" s="170"/>
+      <c r="B6" s="171"/>
+      <c r="C6" s="140" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="180">
+        <v>0.63888888888888895</v>
+      </c>
+      <c r="E6" s="91">
+        <v>0.48888888888888798</v>
+      </c>
+      <c r="F6" s="91">
+        <v>0.52651515151515105</v>
+      </c>
+      <c r="G6" s="93">
+        <v>0.47222222222222199</v>
+      </c>
+      <c r="H6" s="159">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="I6" s="159">
+        <v>0.455589429634909</v>
+      </c>
+      <c r="J6" s="159">
+        <v>0.41573970964154899</v>
+      </c>
+      <c r="K6" s="159">
+        <v>0.40324456027362099</v>
+      </c>
+      <c r="L6" s="159">
+        <v>0.39928078125199801</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="170"/>
+      <c r="B7" s="185" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="139" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="179">
+        <v>0.60317460317460303</v>
+      </c>
+      <c r="E7" s="94">
+        <v>0.50427350427350404</v>
+      </c>
+      <c r="F7" s="94">
+        <v>0.53888888888888797</v>
+      </c>
+      <c r="G7" s="95">
+        <v>0.35317460317460297</v>
+      </c>
+      <c r="H7" s="159">
+        <v>0.75</v>
+      </c>
+      <c r="I7" s="159">
+        <v>0.38342451838670299</v>
+      </c>
+      <c r="J7" s="159">
+        <v>0.355138233065243</v>
+      </c>
+      <c r="K7" s="159">
+        <v>0.356032666000269</v>
+      </c>
+      <c r="L7" s="159">
+        <v>0.28044006655009501</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" s="170"/>
+      <c r="B8" s="171"/>
+      <c r="C8" s="140" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="180">
+        <v>0.66428571428571404</v>
+      </c>
+      <c r="E8" s="91">
+        <v>0.47649572649572602</v>
+      </c>
+      <c r="F8" s="91">
+        <v>0.54285714285714204</v>
+      </c>
+      <c r="G8" s="93">
+        <v>0.41428571428571398</v>
+      </c>
+      <c r="H8" s="159">
+        <v>0.75</v>
+      </c>
+      <c r="I8" s="159">
+        <v>0.39038181205542</v>
+      </c>
+      <c r="J8" s="159">
+        <v>0.35438535036103702</v>
+      </c>
+      <c r="K8" s="159">
+        <v>0.356284683238283</v>
+      </c>
+      <c r="L8" s="159">
+        <v>0.28125062381803401</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" s="170"/>
+      <c r="B9" s="186" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9" s="158" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="153">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="E9" s="159">
+        <v>0.88888888888888795</v>
+      </c>
+      <c r="F9" s="159">
+        <v>0.78977272727272696</v>
+      </c>
+      <c r="G9" s="89">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="H9" s="159">
+        <v>1</v>
+      </c>
+      <c r="I9" s="159">
+        <v>0.28508896885815999</v>
+      </c>
+      <c r="J9" s="159">
+        <v>0.24845199749997601</v>
+      </c>
+      <c r="K9" s="159">
+        <v>0.25993930076586003</v>
+      </c>
+      <c r="L9" s="159">
+        <v>0.267963598927143</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="166"/>
+      <c r="B10" s="187"/>
+      <c r="C10" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="11">
+        <v>0.96296296296296202</v>
+      </c>
+      <c r="E10" s="9">
+        <v>0.80555555555555503</v>
+      </c>
+      <c r="F10" s="9">
+        <v>0.84027777777777701</v>
+      </c>
+      <c r="G10" s="107">
+        <v>0.79629629629629595</v>
+      </c>
+      <c r="H10" s="9">
+        <v>1</v>
+      </c>
+      <c r="I10" s="9">
+        <v>8.2817332499992194E-2</v>
+      </c>
+      <c r="J10" s="9">
+        <v>0.27916321169780201</v>
+      </c>
+      <c r="K10" s="9">
+        <v>0.193075538534136</v>
+      </c>
+      <c r="L10" s="9">
+        <v>0.15450227657812601</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" s="183" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="184" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="44">
+        <v>0.50164141414141405</v>
+      </c>
+      <c r="E11" s="10">
+        <v>0.35688101894998397</v>
+      </c>
+      <c r="F11" s="10">
+        <v>0.41645773063323599</v>
+      </c>
+      <c r="G11" s="88">
+        <v>1.64141414141416E-3</v>
+      </c>
+      <c r="H11" s="10">
+        <v>1</v>
+      </c>
+      <c r="I11" s="10">
+        <v>7.1085858585858502E-2</v>
+      </c>
+      <c r="J11" s="10">
+        <v>7.7601739670705105E-2</v>
+      </c>
+      <c r="K11" s="10">
+        <v>7.7659916425586603E-2</v>
+      </c>
+      <c r="L11" s="10">
+        <v>4.6796085858585804E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" s="170"/>
+      <c r="B12" s="186"/>
+      <c r="C12" s="158" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" s="153">
+        <v>0.5</v>
+      </c>
+      <c r="E12" s="159">
+        <v>4.4827586206896503E-2</v>
+      </c>
+      <c r="F12" s="159">
+        <v>8.2278481012658194E-2</v>
+      </c>
+      <c r="G12" s="89">
+        <v>0</v>
+      </c>
+      <c r="H12" s="159">
+        <v>0.5</v>
+      </c>
+      <c r="I12" s="159">
+        <v>0.5</v>
+      </c>
+      <c r="J12" s="159">
+        <v>4.4827586206896503E-2</v>
+      </c>
+      <c r="K12" s="159">
+        <v>8.2278481012658194E-2</v>
+      </c>
+      <c r="L12" s="159">
+        <v>0.43359375</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" s="170"/>
+      <c r="B13" s="185" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" s="139" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="179">
+        <v>0.36172623860250602</v>
+      </c>
+      <c r="E13" s="94">
+        <v>0.62794505494505404</v>
+      </c>
+      <c r="F13" s="94">
+        <v>0.42459515065609998</v>
+      </c>
+      <c r="G13" s="95">
+        <v>0.16172623860250601</v>
+      </c>
+      <c r="H13" s="159">
+        <v>1</v>
+      </c>
+      <c r="I13" s="159">
+        <v>8.8823978216517399E-2</v>
+      </c>
+      <c r="J13" s="159">
+        <v>0.256467059746816</v>
+      </c>
+      <c r="K13" s="159">
+        <v>4.9183548166781603E-2</v>
+      </c>
+      <c r="L13" s="159">
+        <v>0.120554564658457</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14" s="170"/>
+      <c r="B14" s="171"/>
+      <c r="C14" s="140" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="180">
+        <v>5.4545454545454501E-2</v>
+      </c>
+      <c r="E14" s="91">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="F14" s="91">
+        <v>1.0810810810810799E-2</v>
+      </c>
+      <c r="G14" s="93">
+        <v>-0.145454545454545</v>
+      </c>
+      <c r="H14" s="159">
+        <v>0.2</v>
+      </c>
+      <c r="I14" s="159">
+        <v>0.109090909090909</v>
+      </c>
+      <c r="J14" s="159">
+        <v>1.2E-2</v>
+      </c>
+      <c r="K14" s="159">
+        <v>2.1621621621621599E-2</v>
+      </c>
+      <c r="L14" s="159">
+        <v>0.184151482169439</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15" s="170"/>
+      <c r="B15" s="185" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" s="139" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="179">
+        <v>0.63658026755852803</v>
+      </c>
+      <c r="E15" s="94">
+        <v>0.43323482510146499</v>
+      </c>
+      <c r="F15" s="94">
+        <v>0.459334481428191</v>
+      </c>
+      <c r="G15" s="95">
+        <v>0.38658026755852798</v>
+      </c>
+      <c r="H15" s="159">
+        <v>1</v>
+      </c>
+      <c r="I15" s="159">
+        <v>0.20658529547014701</v>
+      </c>
+      <c r="J15" s="159">
+        <v>0.18525729405212099</v>
+      </c>
+      <c r="K15" s="159">
+        <v>0.103079113926654</v>
+      </c>
+      <c r="L15" s="159">
+        <v>0.11918481905985399</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" s="170"/>
+      <c r="B16" s="171"/>
+      <c r="C16" s="140" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="180">
+        <v>0.44642857142857101</v>
+      </c>
+      <c r="E16" s="91">
+        <v>7.3581660275208599E-2</v>
+      </c>
+      <c r="F16" s="91">
+        <v>0.12611714406330499</v>
+      </c>
+      <c r="G16" s="93">
+        <v>0.19642857142857101</v>
+      </c>
+      <c r="H16" s="159">
+        <v>0.75</v>
+      </c>
+      <c r="I16" s="159">
+        <v>0.36552659804390503</v>
+      </c>
+      <c r="J16" s="159">
+        <v>6.0202593211829497E-2</v>
+      </c>
+      <c r="K16" s="159">
+        <v>0.103230862063993</v>
+      </c>
+      <c r="L16" s="159">
+        <v>0.25314193980306898</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A17" s="170"/>
+      <c r="B17" s="186" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" s="158" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="153">
+        <v>0.31201551973249397</v>
+      </c>
+      <c r="E17" s="159">
+        <v>0.50613093966913103</v>
+      </c>
+      <c r="F17" s="159">
+        <v>0.372798116322552</v>
+      </c>
+      <c r="G17" s="89">
+        <v>0.14534885306582701</v>
+      </c>
+      <c r="H17" s="159">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="I17" s="159">
+        <v>0.19793055234314999</v>
+      </c>
+      <c r="J17" s="159">
+        <v>0.33505019870431901</v>
+      </c>
+      <c r="K17" s="159">
+        <v>0.23730272762931201</v>
+      </c>
+      <c r="L17" s="159">
+        <v>0.110430996554312</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="166"/>
+      <c r="B18" s="187"/>
+      <c r="C18" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="11">
+        <v>0.13888888888888801</v>
+      </c>
+      <c r="E18" s="9">
+        <v>4.7398144413069703E-3</v>
+      </c>
+      <c r="F18" s="9">
+        <v>9.1599222034004606E-3</v>
+      </c>
+      <c r="G18" s="107">
+        <v>-2.77777777777777E-2</v>
+      </c>
+      <c r="H18" s="9">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="I18" s="9">
+        <v>0.202225274702236</v>
+      </c>
+      <c r="J18" s="9">
+        <v>6.7154891240413898E-3</v>
+      </c>
+      <c r="K18" s="9">
+        <v>1.29832238356211E-2</v>
+      </c>
+      <c r="L18" s="9">
+        <v>0.17458386335053899</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A19" s="183" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19" s="184" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="44">
+        <v>0.54417907513882702</v>
+      </c>
+      <c r="E19" s="10">
+        <v>0.68555749805749799</v>
+      </c>
+      <c r="F19" s="10">
+        <v>0.59682539682539604</v>
+      </c>
+      <c r="G19" s="88">
+        <v>0.21084574180549401</v>
+      </c>
+      <c r="H19" s="159">
+        <v>1</v>
+      </c>
+      <c r="I19" s="159">
+        <v>9.2186776408215904E-2</v>
+      </c>
+      <c r="J19" s="159">
+        <v>0.13832975255767299</v>
+      </c>
+      <c r="K19" s="159">
+        <v>7.7793973046621195E-2</v>
+      </c>
+      <c r="L19" s="159">
+        <v>0.14224368490535899</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A20" s="170"/>
+      <c r="B20" s="171"/>
+      <c r="C20" s="140" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" s="180">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="E20" s="91">
+        <v>0.217317404817404</v>
+      </c>
+      <c r="F20" s="91">
+        <v>0.286036036036036</v>
+      </c>
+      <c r="G20" s="93">
+        <v>0.25</v>
+      </c>
+      <c r="H20" s="159">
+        <v>1</v>
+      </c>
+      <c r="I20" s="159">
+        <v>6.80413817439771E-2</v>
+      </c>
+      <c r="J20" s="159">
+        <v>0.16027832076913801</v>
+      </c>
+      <c r="K20" s="159">
+        <v>0.16200568025544501</v>
+      </c>
+      <c r="L20" s="159">
+        <v>0.20670394152865301</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A21" s="170"/>
+      <c r="B21" s="185" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" s="181" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" s="179">
+        <v>0.47262872628726199</v>
+      </c>
+      <c r="E21" s="94">
+        <v>0.45866910866910798</v>
+      </c>
+      <c r="F21" s="94">
+        <v>0.456535798860147</v>
+      </c>
+      <c r="G21" s="95">
+        <v>0.27262872628726198</v>
+      </c>
+      <c r="H21" s="159">
+        <v>0.8</v>
+      </c>
+      <c r="I21" s="159">
+        <v>0.29725847365073799</v>
+      </c>
+      <c r="J21" s="159">
+        <v>0.27065741581432801</v>
+      </c>
+      <c r="K21" s="159">
+        <v>0.27219305671655902</v>
+      </c>
+      <c r="L21" s="159">
+        <v>0.29293235647106602</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A22" s="170"/>
+      <c r="B22" s="171"/>
+      <c r="C22" s="182" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="180">
+        <v>0.4</v>
+      </c>
+      <c r="E22" s="91">
+        <v>0.12668650793650699</v>
+      </c>
+      <c r="F22" s="91">
+        <v>0.178787878787878</v>
+      </c>
+      <c r="G22" s="93">
+        <v>0.2</v>
+      </c>
+      <c r="H22" s="159">
+        <v>0.6</v>
+      </c>
+      <c r="I22" s="159">
+        <v>0.33911649915626302</v>
+      </c>
+      <c r="J22" s="159">
+        <v>0.15783589860001199</v>
+      </c>
+      <c r="K22" s="159">
+        <v>0.19926402694271</v>
+      </c>
+      <c r="L22" s="159">
+        <v>0.29350407322379601</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A23" s="170"/>
+      <c r="B23" s="185" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" s="139" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="179">
+        <v>1</v>
+      </c>
+      <c r="E23" s="94">
+        <v>0.69354838709677402</v>
+      </c>
+      <c r="F23" s="94">
+        <v>0.81904761904761902</v>
+      </c>
+      <c r="G23" s="95">
+        <v>0</v>
+      </c>
+      <c r="H23" s="159">
+        <v>0</v>
+      </c>
+      <c r="I23" s="159">
+        <v>0</v>
+      </c>
+      <c r="J23" s="159">
+        <v>0</v>
+      </c>
+      <c r="K23" s="159">
+        <v>0</v>
+      </c>
+      <c r="L23" s="159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A24" s="170"/>
+      <c r="B24" s="171"/>
+      <c r="C24" s="140" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="180">
+        <v>1</v>
+      </c>
+      <c r="E24" s="91">
+        <v>0.54838709677419295</v>
+      </c>
+      <c r="F24" s="91">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="G24" s="93">
+        <v>0</v>
+      </c>
+      <c r="H24" s="159">
+        <v>0</v>
+      </c>
+      <c r="I24" s="159">
+        <v>0</v>
+      </c>
+      <c r="J24" s="159">
+        <v>0</v>
+      </c>
+      <c r="K24" s="159">
+        <v>0</v>
+      </c>
+      <c r="L24" s="159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A25" s="170"/>
+      <c r="B25" s="186" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25" s="158" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="153">
+        <v>0.76930846930846897</v>
+      </c>
+      <c r="E25" s="159">
+        <v>0.85555555555555496</v>
+      </c>
+      <c r="F25" s="159">
+        <v>0.78491355361636705</v>
+      </c>
+      <c r="G25" s="89">
+        <v>0.43597513597513599</v>
+      </c>
+      <c r="H25" s="159">
+        <v>1</v>
+      </c>
+      <c r="I25" s="159">
+        <v>0.14955159843384699</v>
+      </c>
+      <c r="J25" s="159">
+        <v>0.13966450099973901</v>
+      </c>
+      <c r="K25" s="159">
+        <v>5.51222416605541E-2</v>
+      </c>
+      <c r="L25" s="159">
+        <v>0.29551970039758502</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="166"/>
+      <c r="B26" s="187"/>
+      <c r="C26" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="11">
+        <v>0.88888888888888795</v>
+      </c>
+      <c r="E26" s="9">
+        <v>0.32440087145969498</v>
+      </c>
+      <c r="F26" s="9">
+        <v>0.45860805860805798</v>
+      </c>
+      <c r="G26" s="107">
+        <v>0.55555555555555503</v>
+      </c>
+      <c r="H26" s="9">
+        <v>1</v>
+      </c>
+      <c r="I26" s="9">
+        <v>0.15713484026367699</v>
+      </c>
+      <c r="J26" s="9">
+        <v>0.17960607779901699</v>
+      </c>
+      <c r="K26" s="9">
+        <v>0.209966488477872</v>
+      </c>
+      <c r="L26" s="9">
+        <v>0.313655911930597</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A3:A10"/>
+    <mergeCell ref="A11:A18"/>
+    <mergeCell ref="A19:A26"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>